--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21902E8-6307-4931-86F7-5A8DFEDC91B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5562D23F-CBD7-4446-875F-2592E2435837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="12" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>

--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F18947-897E-47E5-A387-17856BC142D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE5A790-219A-4857-B7C4-AE3F880B5597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10897,13 +10897,13 @@
     <t>PriceListDescription.Root1</t>
   </si>
   <si>
-    <t>Fullname=price_data/price.xlsx;PriceListMap=35, 5 , 6,7 ,   8 , 9  ,  10   |35, 11 , 12,13 ,   14 , 15  ,  16   ;</t>
-  </si>
-  <si>
-    <t>Fullname=Катанка ГОСТ 30136-95;Limit1=5;UnitLimit=тн;</t>
-  </si>
-  <si>
-    <t>Fullname=Арматура ГОСТ 5781-82, 52544-2006;Limit1=5;UnitLimit=тн;</t>
+    <t>Fullname=price.xlsx;PriceListMap=35, 5 , 6,7 ,   8 , 9  ,  10   |35, 11 , 12,13 ,   14 , 15  ,  16   ;</t>
+  </si>
+  <si>
+    <t>Fullname=Арматура ГОСТ 5781-82, 52544-2006;UnitLimit=тн,5;</t>
+  </si>
+  <si>
+    <t>Fullname=Катанка ГОСТ 30136-95;UnitLimit=тн;</t>
   </si>
 </sst>
 </file>
@@ -18254,7 +18254,7 @@
         <v>2871</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="118" t="s">
         <v>3612</v>
       </c>
@@ -18306,10 +18306,10 @@
         <v>3608</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>3615</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="118" t="s">
         <v>3610</v>
       </c>
@@ -18325,7 +18325,7 @@
         <v>3611</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>3614</v>
+        <v>3615</v>
       </c>
     </row>
   </sheetData>

--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4FF498-3576-45B0-8050-AA4A7DBE36C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4276DA6F-3339-4676-BB79-26B70E1FFA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11224" uniqueCount="3054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11242" uniqueCount="3070">
   <si>
     <t>WB_Specification</t>
   </si>
@@ -8662,9 +8662,6 @@
     <t>AbcBasic=Workbook.Basic;AbcUpdate=Workbook.Update;AbcWorkDay=WorkDay;</t>
   </si>
   <si>
-    <t>19;20;18;22;17;22;22;20;22;21;21;22;</t>
-  </si>
-  <si>
     <t>21;21;17;22;20;20;22;21;21;22;21;21;</t>
   </si>
   <si>
@@ -9013,18 +9010,6 @@
     <t>Face.Test.2.Turn.Amount</t>
   </si>
   <si>
-    <t>PriceListDescription.Root</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Partition1</t>
-  </si>
-  <si>
-    <t>PriceListDescription.ProductGroup1</t>
-  </si>
-  <si>
-    <t>Описание прайс листа. Корень</t>
-  </si>
-  <si>
     <t>Описание прайс листа. Раздел 1</t>
   </si>
   <si>
@@ -9034,18 +9019,12 @@
     <t>Fullname=Металлопрокат;</t>
   </si>
   <si>
-    <t>PriceListDescription.ProductGroup2</t>
-  </si>
-  <si>
     <t>Описание прайс листа. Товарная группа2</t>
   </si>
   <si>
     <t>PriceListDescription.Root1</t>
   </si>
   <si>
-    <t>Fullname=price.xlsx;PriceListMap=35, 5 , 6,7 ,   8 , 9  ,  10   |35, 11 , 12,13 ,   14 , 15  ,  16   ;</t>
-  </si>
-  <si>
     <t>Fullname=Арматура ГОСТ 5781-82, 52544-2006;UnitLimit=тн,5;</t>
   </si>
   <si>
@@ -9218,6 +9197,75 @@
   </si>
   <si>
     <t>NormCode=1250;</t>
+  </si>
+  <si>
+    <t>-03-15</t>
+  </si>
+  <si>
+    <t>Описание прайс листа. Корень 1</t>
+  </si>
+  <si>
+    <t>19;20;18;22;17;22;22;21;22;21;21;22;</t>
+  </si>
+  <si>
+    <t>PublicHoliday.ConstitutionDay.2027</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root2</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root1.Partition1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root2.Partition1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root2.Partition1.ProductGroup1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root2.Partition1.ProductGroup2</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root1.Partition1.ProductGroup1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root1.Partition1.ProductGroup2</t>
+  </si>
+  <si>
+    <t>Описание прайс листа. Корень 2</t>
+  </si>
+  <si>
+    <t>Fullname=ТНП;</t>
+  </si>
+  <si>
+    <t>Fullname=Валенки рабочие;UnitLimit=шт,5;</t>
+  </si>
+  <si>
+    <t>Fullname=Спецовка;UnitLimit=шт;</t>
+  </si>
+  <si>
+    <t>Fullname=price.xlsx;PriceListMap=(35, 5 , 1,2 ,   3 , 4   )(5,6);</t>
+  </si>
+  <si>
+    <t>Fullname=price.xlsx;PriceListMap=(35, 5 , 1,2 ,   3 , 4   )(5,6)|(35, 5 , 7,8 ,   9 , 10   )(11,12);</t>
+  </si>
+  <si>
+    <t>ProductVar1</t>
+  </si>
+  <si>
+    <t>ProductVar2</t>
+  </si>
+  <si>
+    <t>Переменная товара 1</t>
+  </si>
+  <si>
+    <t>Переменная товара 2</t>
+  </si>
+  <si>
+    <t>Fullname=Цена1;</t>
+  </si>
+  <si>
+    <t>Fullname=Цена2;</t>
   </si>
 </sst>
 </file>
@@ -12445,7 +12493,7 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>604</v>
@@ -12453,13 +12501,13 @@
       <c r="C33" s="22"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>2914</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="G33" s="33" t="s">
         <v>2915</v>
-      </c>
-      <c r="G33" s="33" t="s">
-        <v>2916</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -13315,7 +13363,7 @@
     </row>
     <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="33" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="B79" s="33" t="s">
         <v>652</v>
@@ -13323,7 +13371,7 @@
       <c r="C79" s="32"/>
       <c r="D79" s="33"/>
       <c r="E79" s="33" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="F79" s="33" t="s">
         <v>2371</v>
@@ -13615,7 +13663,7 @@
     </row>
     <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B95" s="33" t="s">
         <v>681</v>
@@ -13623,10 +13671,10 @@
       <c r="C95" s="22"/>
       <c r="D95" s="33"/>
       <c r="E95" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="F95" s="33" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="G95" s="45" t="s">
         <v>592</v>
@@ -13634,7 +13682,7 @@
     </row>
     <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="B96" s="33" t="s">
         <v>681</v>
@@ -13642,10 +13690,10 @@
       <c r="C96" s="22"/>
       <c r="D96" s="33"/>
       <c r="E96" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="F96" s="33" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="G96" s="45" t="s">
         <v>592</v>
@@ -13653,7 +13701,7 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B97" s="33" t="s">
         <v>681</v>
@@ -13661,10 +13709,10 @@
       <c r="C97" s="22"/>
       <c r="D97" s="33"/>
       <c r="E97" s="33" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="F97" s="33" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="G97" s="45" t="s">
         <v>592</v>
@@ -13729,7 +13777,7 @@
     </row>
     <row r="101" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="33" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="B101" s="33" t="s">
         <v>681</v>
@@ -13737,10 +13785,10 @@
       <c r="C101" s="22"/>
       <c r="D101" s="33"/>
       <c r="E101" s="33" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F101" s="33" t="s">
         <v>2918</v>
-      </c>
-      <c r="F101" s="33" t="s">
-        <v>2919</v>
       </c>
       <c r="G101" s="45" t="s">
         <v>592</v>
@@ -15929,26 +15977,26 @@
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="96" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="B63" s="96" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="96" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B64" s="96" t="s">
         <v>2905</v>
-      </c>
-      <c r="B64" s="96" t="s">
-        <v>2906</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="96" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B65" s="96" t="s">
         <v>2920</v>
-      </c>
-      <c r="B65" s="96" t="s">
-        <v>2921</v>
       </c>
     </row>
   </sheetData>
@@ -16503,16 +16551,16 @@
   <sheetPr codeName="Лист13">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="65.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" style="86" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" style="86" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" style="86" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" style="86" customWidth="1"/>
-    <col min="5" max="5" width="36.140625" style="86" customWidth="1"/>
+    <col min="1" max="1" width="52" style="86" customWidth="1"/>
+    <col min="2" max="2" width="35.42578125" style="86" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" style="86" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" style="86" customWidth="1"/>
+    <col min="5" max="5" width="51.28515625" style="86" customWidth="1"/>
     <col min="6" max="6" width="42.28515625" style="86" customWidth="1"/>
-    <col min="7" max="7" width="51.28515625" style="86" customWidth="1"/>
+    <col min="7" max="7" width="58" style="86" customWidth="1"/>
     <col min="8" max="16384" width="65.5703125" style="86"/>
   </cols>
   <sheetData>
@@ -16577,79 +16625,192 @@
     </row>
     <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
-        <v>2994</v>
+        <v>2988</v>
       </c>
       <c r="B4" s="109"/>
       <c r="C4" s="110"/>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>2994</v>
+        <v>2988</v>
       </c>
       <c r="F4" s="109" t="s">
-        <v>2988</v>
+        <v>3048</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>2995</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="109" t="s">
-        <v>2986</v>
+        <v>3052</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>2985</v>
+        <v>2988</v>
       </c>
       <c r="C5" s="110"/>
       <c r="D5" s="110"/>
       <c r="E5" s="109" t="s">
-        <v>2986</v>
+        <v>3052</v>
       </c>
       <c r="F5" s="109" t="s">
-        <v>2989</v>
+        <v>2984</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>2991</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
-        <v>2987</v>
+        <v>3064</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>2986</v>
+        <v>3052</v>
       </c>
       <c r="C6" s="110"/>
       <c r="D6" s="110"/>
       <c r="E6" s="109" t="s">
-        <v>2987</v>
+        <v>3064</v>
       </c>
       <c r="F6" s="109" t="s">
-        <v>2990</v>
+        <v>3066</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>2996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
-        <v>2992</v>
+        <v>3065</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>2986</v>
+        <v>3052</v>
       </c>
       <c r="C7" s="110"/>
       <c r="D7" s="110"/>
       <c r="E7" s="109" t="s">
-        <v>2992</v>
+        <v>3065</v>
       </c>
       <c r="F7" s="109" t="s">
-        <v>2993</v>
+        <v>3067</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>2997</v>
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="109" t="s">
+        <v>3056</v>
+      </c>
+      <c r="B8" s="109" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="109" t="s">
+        <v>3056</v>
+      </c>
+      <c r="F8" s="109" t="s">
+        <v>2985</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>3060</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="109" t="s">
+        <v>3057</v>
+      </c>
+      <c r="B9" s="109" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="109" t="s">
+        <v>3057</v>
+      </c>
+      <c r="F9" s="109" t="s">
+        <v>2987</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="109" t="s">
+        <v>3051</v>
+      </c>
+      <c r="B10" s="109"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="109" t="s">
+        <v>3051</v>
+      </c>
+      <c r="F10" s="109" t="s">
+        <v>3058</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>3063</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="109" t="s">
+        <v>3053</v>
+      </c>
+      <c r="B11" s="109" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="109" t="s">
+        <v>3053</v>
+      </c>
+      <c r="F11" s="109" t="s">
+        <v>2984</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="109" t="s">
+        <v>3054</v>
+      </c>
+      <c r="B12" s="109" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="109" t="s">
+        <v>3054</v>
+      </c>
+      <c r="F12" s="109" t="s">
+        <v>2985</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="109" t="s">
+        <v>3055</v>
+      </c>
+      <c r="B13" s="109" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="109" t="s">
+        <v>3055</v>
+      </c>
+      <c r="F13" s="109" t="s">
+        <v>2987</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>2990</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.118055555555556" right="0.118055555555556" top="0.15763888888888899" bottom="0.15763888888888899" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="38" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -16719,10 +16880,10 @@
       <c r="P1" s="56"/>
       <c r="Q1" s="56"/>
       <c r="R1" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="S1" s="33" t="s">
         <v>2917</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>2918</v>
       </c>
       <c r="T1" s="51" t="s">
         <v>886</v>
@@ -16731,7 +16892,7 @@
         <v>896</v>
       </c>
       <c r="V1" s="52" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="W1" s="60" t="s">
         <v>897</v>
@@ -16742,7 +16903,7 @@
     </row>
     <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="56" t="s">
@@ -16756,10 +16917,10 @@
       <c r="G2" s="53"/>
       <c r="H2" s="53"/>
       <c r="I2" s="56" t="s">
+        <v>2921</v>
+      </c>
+      <c r="J2" s="56" t="s">
         <v>2922</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>2923</v>
       </c>
       <c r="K2" s="63"/>
       <c r="L2" s="64"/>
@@ -16769,10 +16930,10 @@
       <c r="P2" s="56"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="S2" s="33" t="s">
         <v>2917</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>2918</v>
       </c>
       <c r="T2" s="51" t="s">
         <v>884</v>
@@ -16781,7 +16942,7 @@
         <v>896</v>
       </c>
       <c r="V2" s="52" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="W2" s="60" t="s">
         <v>897</v>
@@ -16819,10 +16980,10 @@
       <c r="P3" s="56"/>
       <c r="Q3" s="56"/>
       <c r="R3" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="S3" s="33" t="s">
         <v>2917</v>
-      </c>
-      <c r="S3" s="33" t="s">
-        <v>2918</v>
       </c>
       <c r="T3" s="51" t="s">
         <v>886</v>
@@ -16831,7 +16992,7 @@
         <v>900</v>
       </c>
       <c r="V3" s="52" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="W3" s="60" t="s">
         <v>893</v>
@@ -16842,7 +17003,7 @@
     </row>
     <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="B4" s="56"/>
       <c r="C4" s="56" t="s">
@@ -16856,10 +17017,10 @@
       <c r="G4" s="53"/>
       <c r="H4" s="53"/>
       <c r="I4" s="56" t="s">
+        <v>2923</v>
+      </c>
+      <c r="J4" s="56" t="s">
         <v>2924</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>2925</v>
       </c>
       <c r="K4" s="63"/>
       <c r="L4" s="64"/>
@@ -16869,10 +17030,10 @@
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
       <c r="R4" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="S4" s="33" t="s">
         <v>2917</v>
-      </c>
-      <c r="S4" s="33" t="s">
-        <v>2918</v>
       </c>
       <c r="T4" s="51" t="s">
         <v>884</v>
@@ -16881,7 +17042,7 @@
         <v>900</v>
       </c>
       <c r="V4" s="52" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="W4" s="60" t="s">
         <v>893</v>
@@ -16892,7 +17053,7 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="56" t="s">
@@ -16906,10 +17067,10 @@
       <c r="G5" s="53"/>
       <c r="H5" s="53"/>
       <c r="I5" s="56" t="s">
+        <v>2937</v>
+      </c>
+      <c r="J5" s="56" t="s">
         <v>2938</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>2939</v>
       </c>
       <c r="K5" s="63"/>
       <c r="L5" s="64"/>
@@ -16919,22 +17080,22 @@
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
       <c r="R5" s="24" t="s">
+        <v>2916</v>
+      </c>
+      <c r="S5" s="33" t="s">
         <v>2917</v>
-      </c>
-      <c r="S5" s="33" t="s">
-        <v>2918</v>
       </c>
       <c r="T5" s="51" t="s">
         <v>884</v>
       </c>
       <c r="U5" s="56" t="s">
+        <v>2939</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>2934</v>
+      </c>
+      <c r="W5" s="60" t="s">
         <v>2940</v>
-      </c>
-      <c r="V5" s="52" t="s">
-        <v>2935</v>
-      </c>
-      <c r="W5" s="60" t="s">
-        <v>2941</v>
       </c>
       <c r="X5" s="50" t="s">
         <v>830</v>
@@ -16949,7 +17110,7 @@
         <v>232</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>518</v>
@@ -16958,7 +17119,7 @@
         <v>74</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H6" s="53"/>
       <c r="I6" s="56" t="s">
@@ -16980,7 +17141,7 @@
         <v>259</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="T6" s="68" t="s">
         <v>841</v>
@@ -17009,7 +17170,7 @@
         <v>232</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>518</v>
@@ -17018,7 +17179,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H7" s="53"/>
       <c r="I7" s="56" t="s">
@@ -17037,26 +17198,26 @@
         <v>108</v>
       </c>
       <c r="N7" s="26" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="P7" s="56"/>
       <c r="Q7" s="35" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="T7" s="56" t="s">
         <v>842</v>
       </c>
       <c r="U7" s="56" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="V7" s="69" t="s">
         <v>213</v>
@@ -17079,7 +17240,7 @@
         <v>232</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>518</v>
@@ -17088,7 +17249,7 @@
         <v>74</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H8" s="53"/>
       <c r="I8" s="56" t="s">
@@ -17107,26 +17268,26 @@
         <v>108</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="O8" s="28" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="P8" s="56"/>
       <c r="Q8" s="35" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="S8" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="T8" s="56" t="s">
         <v>834</v>
       </c>
       <c r="U8" s="56" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="V8" s="56" t="s">
         <v>579</v>
@@ -17154,7 +17315,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H9" s="53" t="s">
         <v>902</v>
@@ -17178,7 +17339,7 @@
         <v>259</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="T9" s="68" t="s">
         <v>841</v>
@@ -17214,7 +17375,7 @@
         <v>74</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H10" s="53"/>
       <c r="I10" s="56" t="s">
@@ -17233,7 +17394,7 @@
         <v>143</v>
       </c>
       <c r="N10" s="56" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
@@ -17241,16 +17402,16 @@
         <v>306</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="S10" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="T10" s="56" t="s">
         <v>834</v>
       </c>
       <c r="U10" s="56" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="V10" s="56" t="s">
         <v>579</v>
@@ -17280,7 +17441,7 @@
         <v>74</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H11" s="53"/>
       <c r="I11" s="56" t="s">
@@ -17305,16 +17466,16 @@
       </c>
       <c r="Q11" s="56"/>
       <c r="R11" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="S11" s="33" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="T11" s="56" t="s">
         <v>834</v>
       </c>
       <c r="U11" s="56" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="V11" s="56" t="s">
         <v>579</v>
@@ -17344,7 +17505,7 @@
         <v>74</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="H12" s="53"/>
       <c r="I12" s="56" t="s">
@@ -17363,7 +17524,7 @@
         <v>143</v>
       </c>
       <c r="N12" s="56" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="O12" s="56"/>
       <c r="P12" s="56"/>
@@ -17371,16 +17532,16 @@
         <v>306</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="S12" s="33" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="T12" s="56" t="s">
         <v>834</v>
       </c>
       <c r="U12" s="56" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="V12" s="56" t="s">
         <v>579</v>
@@ -31728,7 +31889,7 @@
         <v>1426</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="27"/>
@@ -31747,7 +31908,7 @@
         <v>1428</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="27"/>
@@ -31766,7 +31927,7 @@
         <v>1430</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="27"/>
@@ -31785,7 +31946,7 @@
         <v>1432</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="27"/>
@@ -31801,7 +31962,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>1423</v>
@@ -31809,10 +31970,10 @@
       <c r="C21" s="22"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F21" s="27" t="s">
         <v>2947</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>2948</v>
       </c>
       <c r="G21" s="45" t="s">
         <v>628</v>
@@ -31861,7 +32022,7 @@
         <v>1437</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="27"/>
@@ -31880,7 +32041,7 @@
         <v>1439</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="27"/>
@@ -31937,7 +32098,7 @@
         <v>1444</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="27"/>
@@ -31956,7 +32117,7 @@
         <v>1446</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="27"/>
@@ -32181,7 +32342,7 @@
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="27" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="B41" s="27" t="s">
         <v>1423</v>
@@ -32189,10 +32350,10 @@
       <c r="C41" s="22"/>
       <c r="D41" s="27"/>
       <c r="E41" s="27" t="s">
+        <v>2925</v>
+      </c>
+      <c r="F41" s="33" t="s">
         <v>2926</v>
-      </c>
-      <c r="F41" s="33" t="s">
-        <v>2927</v>
       </c>
       <c r="G41" s="45" t="s">
         <v>628</v>
@@ -33765,7 +33926,7 @@
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B125" s="27" t="s">
         <v>2634</v>
@@ -33773,10 +33934,10 @@
       <c r="C125" s="22"/>
       <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
+        <v>2956</v>
+      </c>
+      <c r="F125" s="27" t="s">
         <v>2957</v>
-      </c>
-      <c r="F125" s="27" t="s">
-        <v>2958</v>
       </c>
       <c r="G125" s="45" t="s">
         <v>628</v>
@@ -33784,7 +33945,7 @@
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A126" s="24" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="B126" s="27" t="s">
         <v>2634</v>
@@ -33792,7 +33953,7 @@
       <c r="C126" s="22"/>
       <c r="D126" s="27"/>
       <c r="E126" s="24" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="F126" s="27" t="s">
         <v>1533</v>
@@ -34517,7 +34678,7 @@
     </row>
     <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="27" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="B165" s="27" t="s">
         <v>1601</v>
@@ -34525,10 +34686,10 @@
       <c r="C165" s="22"/>
       <c r="D165" s="27"/>
       <c r="E165" s="27" t="s">
+        <v>2907</v>
+      </c>
+      <c r="F165" s="27" t="s">
         <v>2908</v>
-      </c>
-      <c r="F165" s="27" t="s">
-        <v>2909</v>
       </c>
       <c r="G165" s="45" t="s">
         <v>628</v>
@@ -36309,7 +36470,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A26" s="52" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>881</v>
@@ -36317,16 +36478,16 @@
       <c r="C26" s="36"/>
       <c r="D26" s="52"/>
       <c r="E26" s="52" t="s">
+        <v>2909</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>2910</v>
-      </c>
-      <c r="F26" s="52" t="s">
-        <v>2911</v>
       </c>
       <c r="G26" s="24" t="s">
         <v>292</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -36865,7 +37026,7 @@
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="52" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="B52" s="52" t="s">
         <v>213</v>
@@ -36873,21 +37034,21 @@
       <c r="C52" s="36"/>
       <c r="D52" s="52"/>
       <c r="E52" s="52" t="s">
+        <v>2931</v>
+      </c>
+      <c r="F52" s="52" t="s">
         <v>2932</v>
-      </c>
-      <c r="F52" s="52" t="s">
-        <v>2933</v>
       </c>
       <c r="G52" s="24" t="s">
         <v>296</v>
       </c>
       <c r="H52" s="52" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="52" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="B53" s="52" t="s">
         <v>213</v>
@@ -36895,21 +37056,21 @@
       <c r="C53" s="36"/>
       <c r="D53" s="52"/>
       <c r="E53" s="52" t="s">
+        <v>2934</v>
+      </c>
+      <c r="F53" s="52" t="s">
         <v>2935</v>
-      </c>
-      <c r="F53" s="52" t="s">
-        <v>2936</v>
       </c>
       <c r="G53" s="24" t="s">
         <v>296</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A54" s="52" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="B54" s="52" t="s">
         <v>213</v>
@@ -36917,16 +37078,16 @@
       <c r="C54" s="36"/>
       <c r="D54" s="52"/>
       <c r="E54" s="52" t="s">
+        <v>2941</v>
+      </c>
+      <c r="F54" s="52" t="s">
         <v>2942</v>
-      </c>
-      <c r="F54" s="52" t="s">
-        <v>2943</v>
       </c>
       <c r="G54" s="24" t="s">
         <v>296</v>
       </c>
       <c r="H54" s="52" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -37623,7 +37784,7 @@
         <v>78</v>
       </c>
       <c r="I1" s="111" t="s">
-        <v>2998</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37648,7 +37809,7 @@
         <v>78</v>
       </c>
       <c r="I2" s="111" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37673,7 +37834,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="111" t="s">
-        <v>3001</v>
+        <v>2994</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37698,7 +37859,7 @@
         <v>78</v>
       </c>
       <c r="I4" s="111" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37723,7 +37884,7 @@
         <v>78</v>
       </c>
       <c r="I5" s="111" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37748,7 +37909,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="111" t="s">
-        <v>3000</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37773,7 +37934,7 @@
         <v>78</v>
       </c>
       <c r="I7" s="111" t="s">
-        <v>3002</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37796,7 +37957,7 @@
         <v>78</v>
       </c>
       <c r="I8" s="111" t="s">
-        <v>3003</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37821,7 +37982,7 @@
         <v>84</v>
       </c>
       <c r="I9" s="111" t="s">
-        <v>3004</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37844,7 +38005,7 @@
         <v>84</v>
       </c>
       <c r="I10" s="111" t="s">
-        <v>3005</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37867,7 +38028,7 @@
         <v>78</v>
       </c>
       <c r="I11" s="111" t="s">
-        <v>3006</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37892,7 +38053,7 @@
         <v>78</v>
       </c>
       <c r="I12" s="111" t="s">
-        <v>3007</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37917,7 +38078,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="111" t="s">
-        <v>3008</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37942,7 +38103,7 @@
         <v>78</v>
       </c>
       <c r="I14" s="111" t="s">
-        <v>3009</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37967,7 +38128,7 @@
         <v>78</v>
       </c>
       <c r="I15" s="111" t="s">
-        <v>3010</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37992,7 +38153,7 @@
         <v>78</v>
       </c>
       <c r="I16" s="111" t="s">
-        <v>3011</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38015,7 +38176,7 @@
         <v>78</v>
       </c>
       <c r="I17" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38040,7 +38201,7 @@
         <v>78</v>
       </c>
       <c r="I18" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38065,7 +38226,7 @@
         <v>78</v>
       </c>
       <c r="I19" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38090,7 +38251,7 @@
         <v>84</v>
       </c>
       <c r="I20" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38115,7 +38276,7 @@
         <v>78</v>
       </c>
       <c r="I21" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38140,7 +38301,7 @@
         <v>78</v>
       </c>
       <c r="I22" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38165,7 +38326,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38190,7 +38351,7 @@
         <v>78</v>
       </c>
       <c r="I24" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38215,7 +38376,7 @@
         <v>78</v>
       </c>
       <c r="I25" s="111" t="s">
-        <v>2999</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38238,7 +38399,7 @@
         <v>78</v>
       </c>
       <c r="I26" s="111" t="s">
-        <v>3012</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38261,7 +38422,7 @@
         <v>78</v>
       </c>
       <c r="I27" s="111" t="s">
-        <v>3013</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38284,7 +38445,7 @@
         <v>84</v>
       </c>
       <c r="I28" s="111" t="s">
-        <v>3014</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38309,7 +38470,7 @@
         <v>84</v>
       </c>
       <c r="I29" s="111" t="s">
-        <v>3015</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38334,7 +38495,7 @@
         <v>84</v>
       </c>
       <c r="I30" s="111" t="s">
-        <v>3016</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38359,7 +38520,7 @@
         <v>84</v>
       </c>
       <c r="I31" s="111" t="s">
-        <v>3017</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38384,7 +38545,7 @@
         <v>84</v>
       </c>
       <c r="I32" s="111" t="s">
-        <v>3018</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38407,7 +38568,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="111" t="s">
-        <v>3019</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38432,7 +38593,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="111" t="s">
-        <v>3020</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38457,7 +38618,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="111" t="s">
-        <v>3021</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38482,7 +38643,7 @@
         <v>78</v>
       </c>
       <c r="I36" s="111" t="s">
-        <v>3022</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38505,7 +38666,7 @@
         <v>84</v>
       </c>
       <c r="I37" s="111" t="s">
-        <v>3023</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38530,7 +38691,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="111" t="s">
-        <v>3024</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38553,7 +38714,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="111" t="s">
-        <v>3025</v>
+        <v>3018</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38578,7 +38739,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="111" t="s">
-        <v>3026</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38601,7 +38762,7 @@
         <v>84</v>
       </c>
       <c r="I41" s="111" t="s">
-        <v>3027</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38626,7 +38787,7 @@
         <v>84</v>
       </c>
       <c r="I42" s="111" t="s">
-        <v>3024</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38651,7 +38812,7 @@
         <v>84</v>
       </c>
       <c r="I43" s="111" t="s">
-        <v>3028</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38676,7 +38837,7 @@
         <v>84</v>
       </c>
       <c r="I44" s="111" t="s">
-        <v>3029</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38701,7 +38862,7 @@
         <v>84</v>
       </c>
       <c r="I45" s="111" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38726,7 +38887,7 @@
         <v>84</v>
       </c>
       <c r="I46" s="111" t="s">
-        <v>3031</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38751,7 +38912,7 @@
         <v>84</v>
       </c>
       <c r="I47" s="111" t="s">
-        <v>3032</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38776,7 +38937,7 @@
         <v>84</v>
       </c>
       <c r="I48" s="111" t="s">
-        <v>3033</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38801,7 +38962,7 @@
         <v>84</v>
       </c>
       <c r="I49" s="111" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38826,7 +38987,7 @@
         <v>84</v>
       </c>
       <c r="I50" s="111" t="s">
-        <v>3030</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38851,7 +39012,7 @@
         <v>84</v>
       </c>
       <c r="I51" s="111" t="s">
-        <v>3034</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38876,7 +39037,7 @@
         <v>84</v>
       </c>
       <c r="I52" s="111" t="s">
-        <v>3035</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38901,7 +39062,7 @@
         <v>84</v>
       </c>
       <c r="I53" s="111" t="s">
-        <v>3036</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38926,7 +39087,7 @@
         <v>84</v>
       </c>
       <c r="I54" s="111" t="s">
-        <v>3037</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38951,7 +39112,7 @@
         <v>78</v>
       </c>
       <c r="I55" s="111" t="s">
-        <v>3038</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38976,7 +39137,7 @@
         <v>84</v>
       </c>
       <c r="I56" s="111" t="s">
-        <v>3039</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -38990,7 +39151,7 @@
         <v>1251</v>
       </c>
       <c r="F57" s="111" t="s">
-        <v>3052</v>
+        <v>3045</v>
       </c>
       <c r="G57" s="111" t="s">
         <v>86</v>
@@ -38999,7 +39160,7 @@
         <v>78</v>
       </c>
       <c r="I57" s="111" t="s">
-        <v>3053</v>
+        <v>3046</v>
       </c>
     </row>
   </sheetData>
@@ -39011,7 +39172,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr codeName="Лист19"/>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" style="16" bestFit="1" customWidth="1"/>
@@ -39038,80 +39199,62 @@
     <col min="23" max="16384" width="8.7109375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="76" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>1818</v>
-      </c>
-      <c r="B1" s="76" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>1821</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>1822</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>1823</v>
-      </c>
-      <c r="G1" s="76" t="s">
-        <v>1824</v>
-      </c>
-      <c r="H1" s="76" t="s">
-        <v>1825</v>
-      </c>
-      <c r="I1" s="76" t="s">
-        <v>1826</v>
-      </c>
-      <c r="J1" s="76" t="s">
-        <v>1827</v>
-      </c>
-      <c r="K1" s="76" t="s">
-        <v>1828</v>
-      </c>
-      <c r="L1" s="76" t="s">
-        <v>1829</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>1830</v>
-      </c>
-      <c r="N1" s="76" t="s">
-        <v>1831</v>
-      </c>
-      <c r="O1" s="76" t="s">
-        <v>1832</v>
-      </c>
-      <c r="P1" s="76" t="s">
-        <v>1833</v>
-      </c>
-      <c r="Q1" s="76" t="s">
-        <v>1834</v>
-      </c>
-      <c r="R1" s="76" t="s">
-        <v>1835</v>
-      </c>
-      <c r="S1" s="76" t="s">
-        <v>1836</v>
-      </c>
-      <c r="T1" s="76" t="s">
-        <v>1837</v>
-      </c>
-      <c r="U1" s="76" t="s">
-        <v>1838</v>
-      </c>
-      <c r="V1" s="76" t="s">
-        <v>1839</v>
-      </c>
-      <c r="W1" s="76" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" s="108" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="108" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="106" t="s">
+        <v>2977</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>518</v>
+      </c>
+      <c r="F1" s="106" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="107" t="s">
+        <v>2980</v>
+      </c>
+      <c r="I1" s="106" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J1" s="106" t="s">
+        <v>2977</v>
+      </c>
+      <c r="K1" s="56" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" s="56" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q1" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>2953</v>
+      </c>
+      <c r="S1" s="68" t="s">
+        <v>841</v>
+      </c>
+      <c r="T1" s="56">
+        <v>1</v>
+      </c>
+      <c r="U1" s="69" t="s">
+        <v>844</v>
+      </c>
+      <c r="V1" s="37" t="s">
+        <v>2961</v>
+      </c>
+      <c r="W1" s="84" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="106" t="s">
-        <v>2978</v>
+        <v>2962</v>
+      </c>
+      <c r="B2" s="106" t="s">
+        <v>2977</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>232</v>
@@ -39123,37 +39266,46 @@
         <v>76</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="I2" s="106" t="s">
-        <v>2978</v>
+        <v>2962</v>
       </c>
       <c r="J2" s="106" t="s">
-        <v>2978</v>
+        <v>2962</v>
       </c>
       <c r="K2" s="56" t="s">
         <v>215</v>
       </c>
+      <c r="L2" s="58" t="s">
+        <v>917</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>151</v>
+      </c>
       <c r="N2" s="56" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q2" s="56" t="s">
-        <v>259</v>
+        <v>1093</v>
+      </c>
+      <c r="O2" s="106" t="s">
+        <v>2958</v>
+      </c>
+      <c r="Q2" s="27" t="s">
+        <v>2956</v>
       </c>
       <c r="R2" s="33" t="s">
-        <v>2954</v>
+        <v>690</v>
       </c>
       <c r="S2" s="68" t="s">
-        <v>841</v>
-      </c>
-      <c r="T2" s="56">
-        <v>1</v>
+        <v>842</v>
+      </c>
+      <c r="T2" s="16">
+        <v>2</v>
       </c>
       <c r="U2" s="69" t="s">
-        <v>844</v>
+        <v>213</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="W2" s="84" t="s">
         <v>2245</v>
@@ -39164,7 +39316,7 @@
         <v>2963</v>
       </c>
       <c r="B3" s="106" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>232</v>
@@ -39176,7 +39328,7 @@
         <v>76</v>
       </c>
       <c r="G3" s="107" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="I3" s="106" t="s">
         <v>2963</v>
@@ -39194,28 +39346,28 @@
         <v>151</v>
       </c>
       <c r="N3" s="56" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="O3" s="106" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="R3" s="33" t="s">
-        <v>690</v>
-      </c>
-      <c r="S3" s="68" t="s">
-        <v>842</v>
+        <v>682</v>
+      </c>
+      <c r="S3" s="56" t="s">
+        <v>834</v>
       </c>
       <c r="T3" s="16">
-        <v>2</v>
-      </c>
-      <c r="U3" s="69" t="s">
-        <v>213</v>
+        <v>2000</v>
+      </c>
+      <c r="U3" s="56" t="s">
+        <v>579</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="W3" s="84" t="s">
         <v>2245</v>
@@ -39226,7 +39378,7 @@
         <v>2964</v>
       </c>
       <c r="B4" s="106" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="C4" s="41" t="s">
         <v>232</v>
@@ -39238,7 +39390,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="107" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="I4" s="106" t="s">
         <v>2964</v>
@@ -39256,28 +39408,28 @@
         <v>151</v>
       </c>
       <c r="N4" s="56" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="O4" s="106" t="s">
-        <v>2959</v>
+        <v>2960</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="R4" s="33" t="s">
-        <v>682</v>
-      </c>
-      <c r="S4" s="56" t="s">
-        <v>834</v>
+        <v>690</v>
+      </c>
+      <c r="S4" s="68" t="s">
+        <v>842</v>
       </c>
       <c r="T4" s="16">
-        <v>2000</v>
-      </c>
-      <c r="U4" s="56" t="s">
-        <v>579</v>
+        <v>3</v>
+      </c>
+      <c r="U4" s="69" t="s">
+        <v>213</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="W4" s="84" t="s">
         <v>2245</v>
@@ -39288,7 +39440,7 @@
         <v>2965</v>
       </c>
       <c r="B5" s="106" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>232</v>
@@ -39300,7 +39452,7 @@
         <v>76</v>
       </c>
       <c r="G5" s="107" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="I5" s="106" t="s">
         <v>2965</v>
@@ -39318,39 +39470,36 @@
         <v>151</v>
       </c>
       <c r="N5" s="56" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="O5" s="106" t="s">
+        <v>2960</v>
+      </c>
+      <c r="Q5" s="27" t="s">
+        <v>2956</v>
+      </c>
+      <c r="R5" s="33" t="s">
+        <v>682</v>
+      </c>
+      <c r="S5" s="56" t="s">
+        <v>834</v>
+      </c>
+      <c r="T5" s="16">
+        <v>3000</v>
+      </c>
+      <c r="U5" s="56" t="s">
+        <v>579</v>
+      </c>
+      <c r="V5" s="37" t="s">
         <v>2961</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>2957</v>
-      </c>
-      <c r="R5" s="33" t="s">
-        <v>690</v>
-      </c>
-      <c r="S5" s="68" t="s">
-        <v>842</v>
-      </c>
-      <c r="T5" s="16">
-        <v>3</v>
-      </c>
-      <c r="U5" s="69" t="s">
-        <v>213</v>
-      </c>
-      <c r="V5" s="37" t="s">
-        <v>2962</v>
       </c>
       <c r="W5" s="84" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" s="108" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="106" t="s">
-        <v>2966</v>
-      </c>
-      <c r="B6" s="106" t="s">
-        <v>2978</v>
+        <v>2981</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>232</v>
@@ -39365,55 +39514,52 @@
         <v>2980</v>
       </c>
       <c r="I6" s="106" t="s">
-        <v>2966</v>
+        <v>2981</v>
       </c>
       <c r="J6" s="106" t="s">
-        <v>2966</v>
+        <v>2981</v>
       </c>
       <c r="K6" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="L6" s="58" t="s">
-        <v>917</v>
-      </c>
-      <c r="M6" s="21" t="s">
-        <v>151</v>
-      </c>
       <c r="N6" s="56" t="s">
-        <v>1096</v>
-      </c>
-      <c r="O6" s="106" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q6" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="R6" s="33" t="s">
+        <v>2953</v>
+      </c>
+      <c r="S6" s="68" t="s">
+        <v>841</v>
+      </c>
+      <c r="T6" s="56">
+        <v>1</v>
+      </c>
+      <c r="U6" s="69" t="s">
+        <v>844</v>
+      </c>
+      <c r="V6" s="37" t="s">
         <v>2961</v>
-      </c>
-      <c r="Q6" s="27" t="s">
-        <v>2957</v>
-      </c>
-      <c r="R6" s="33" t="s">
-        <v>682</v>
-      </c>
-      <c r="S6" s="56" t="s">
-        <v>834</v>
-      </c>
-      <c r="T6" s="16">
-        <v>3000</v>
-      </c>
-      <c r="U6" s="56" t="s">
-        <v>579</v>
-      </c>
-      <c r="V6" s="37" t="s">
-        <v>2962</v>
       </c>
       <c r="W6" s="84" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="108" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="106" t="s">
         <v>2982</v>
       </c>
+      <c r="B7" s="106" t="s">
+        <v>2981</v>
+      </c>
       <c r="C7" s="41" t="s">
         <v>232</v>
       </c>
+      <c r="D7" s="41" t="s">
+        <v>236</v>
+      </c>
       <c r="E7" s="57" t="s">
         <v>518</v>
       </c>
@@ -39421,7 +39567,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="107" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="I7" s="106" t="s">
         <v>2982</v>
@@ -39432,43 +39578,50 @@
       <c r="K7" s="56" t="s">
         <v>215</v>
       </c>
+      <c r="L7" s="58" t="s">
+        <v>917</v>
+      </c>
+      <c r="M7" s="21" t="s">
+        <v>122</v>
+      </c>
       <c r="N7" s="56" t="s">
-        <v>1091</v>
-      </c>
-      <c r="Q7" s="56" t="s">
-        <v>259</v>
+        <v>1096</v>
+      </c>
+      <c r="O7" s="106"/>
+      <c r="Q7" s="27" t="s">
+        <v>2956</v>
       </c>
       <c r="R7" s="33" t="s">
-        <v>2954</v>
-      </c>
-      <c r="S7" s="68" t="s">
-        <v>841</v>
-      </c>
-      <c r="T7" s="56">
-        <v>1</v>
-      </c>
-      <c r="U7" s="69" t="s">
-        <v>844</v>
+        <v>682</v>
+      </c>
+      <c r="S7" s="56" t="s">
+        <v>834</v>
+      </c>
+      <c r="T7" s="16">
+        <v>4000</v>
+      </c>
+      <c r="U7" s="56" t="s">
+        <v>579</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="W7" s="84" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="106" t="s">
         <v>2983</v>
       </c>
       <c r="B8" s="106" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="D8" s="41" t="s">
-        <v>236</v>
+      <c r="D8" s="106" t="s">
+        <v>240</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>518</v>
@@ -39477,7 +39630,7 @@
         <v>76</v>
       </c>
       <c r="G8" s="107" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="I8" s="106" t="s">
         <v>2983</v>
@@ -39492,14 +39645,14 @@
         <v>917</v>
       </c>
       <c r="M8" s="21" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="N8" s="56" t="s">
         <v>1096</v>
       </c>
       <c r="O8" s="106"/>
       <c r="Q8" s="27" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="R8" s="33" t="s">
         <v>682</v>
@@ -39508,78 +39661,15 @@
         <v>834</v>
       </c>
       <c r="T8" s="16">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="U8" s="56" t="s">
         <v>579</v>
       </c>
       <c r="V8" s="37" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="W8" s="84" t="s">
-        <v>2245</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A9" s="106" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B9" s="106" t="s">
-        <v>2982</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="D9" s="106" t="s">
-        <v>240</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>518</v>
-      </c>
-      <c r="F9" s="106" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="107" t="s">
-        <v>2980</v>
-      </c>
-      <c r="I9" s="106" t="s">
-        <v>2984</v>
-      </c>
-      <c r="J9" s="106" t="s">
-        <v>2984</v>
-      </c>
-      <c r="K9" s="56" t="s">
-        <v>215</v>
-      </c>
-      <c r="L9" s="58" t="s">
-        <v>917</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="N9" s="56" t="s">
-        <v>1096</v>
-      </c>
-      <c r="O9" s="106"/>
-      <c r="Q9" s="27" t="s">
-        <v>2957</v>
-      </c>
-      <c r="R9" s="33" t="s">
-        <v>682</v>
-      </c>
-      <c r="S9" s="56" t="s">
-        <v>834</v>
-      </c>
-      <c r="T9" s="16">
-        <v>5000</v>
-      </c>
-      <c r="U9" s="56" t="s">
-        <v>579</v>
-      </c>
-      <c r="V9" s="37" t="s">
-        <v>2962</v>
-      </c>
-      <c r="W9" s="84" t="s">
         <v>2245</v>
       </c>
     </row>
@@ -39595,7 +39685,7 @@
   <sheetPr codeName="Лист20">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W202"/>
+  <dimension ref="A1:W203"/>
   <sheetFormatPr defaultColWidth="26" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.42578125" style="75" customWidth="1"/>
@@ -40312,6 +40402,9 @@
       <c r="G28" s="77" t="s">
         <v>1851</v>
       </c>
+      <c r="H28" s="77" t="s">
+        <v>1935</v>
+      </c>
       <c r="I28" s="77" t="s">
         <v>2202</v>
       </c>
@@ -40337,18 +40430,41 @@
         <v>830</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="78"/>
-      <c r="W29" s="77"/>
+    <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>3050</v>
+      </c>
+      <c r="F29" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="77" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77" t="s">
+        <v>3050</v>
+      </c>
+      <c r="J29" s="77" t="s">
+        <v>1862</v>
+      </c>
+      <c r="K29" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S29" s="77" t="s">
+        <v>866</v>
+      </c>
+      <c r="T29" s="77" t="s">
+        <v>3047</v>
+      </c>
+      <c r="U29" s="77" t="s">
+        <v>1754</v>
+      </c>
+      <c r="V29" s="78" t="s">
+        <v>1910</v>
+      </c>
+      <c r="W29" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="30" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="77"/>
@@ -40364,46 +40480,21 @@
       <c r="W30" s="77"/>
     </row>
     <row r="31" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="77" t="s">
-        <v>2203</v>
-      </c>
-      <c r="F31" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="77" t="s">
-        <v>1851</v>
-      </c>
-      <c r="H31" s="77" t="s">
-        <v>1864</v>
-      </c>
-      <c r="I31" s="77" t="s">
-        <v>2203</v>
-      </c>
-      <c r="J31" s="77" t="s">
-        <v>1865</v>
-      </c>
-      <c r="K31" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S31" s="77" t="s">
-        <v>866</v>
-      </c>
-      <c r="T31" s="77" t="s">
-        <v>1866</v>
-      </c>
-      <c r="U31" s="77" t="s">
-        <v>1754</v>
-      </c>
-      <c r="V31" s="78" t="s">
-        <v>1910</v>
-      </c>
-      <c r="W31" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="S31" s="77"/>
+      <c r="T31" s="77"/>
+      <c r="U31" s="77"/>
+      <c r="V31" s="78"/>
+      <c r="W31" s="77"/>
     </row>
     <row r="32" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="77" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="F32" s="77" t="s">
         <v>76</v>
@@ -40415,7 +40506,7 @@
         <v>1864</v>
       </c>
       <c r="I32" s="77" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="J32" s="77" t="s">
         <v>1865</v>
@@ -40427,7 +40518,7 @@
         <v>866</v>
       </c>
       <c r="T32" s="77" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="U32" s="77" t="s">
         <v>1754</v>
@@ -40441,16 +40532,19 @@
     </row>
     <row r="33" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="77" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="F33" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G33" s="77" t="s">
-        <v>1868</v>
+        <v>1851</v>
+      </c>
+      <c r="H33" s="77" t="s">
+        <v>1864</v>
       </c>
       <c r="I33" s="77" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="J33" s="77" t="s">
         <v>1865</v>
@@ -40462,7 +40556,7 @@
         <v>866</v>
       </c>
       <c r="T33" s="77" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="U33" s="77" t="s">
         <v>1754</v>
@@ -40475,17 +40569,39 @@
       </c>
     </row>
     <row r="34" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
-      <c r="S34" s="77"/>
-      <c r="T34" s="77"/>
-      <c r="U34" s="77"/>
-      <c r="V34" s="78"/>
-      <c r="W34" s="77"/>
+      <c r="A34" s="77" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F34" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G34" s="77" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I34" s="77" t="s">
+        <v>2205</v>
+      </c>
+      <c r="J34" s="77" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K34" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S34" s="77" t="s">
+        <v>866</v>
+      </c>
+      <c r="T34" s="77" t="s">
+        <v>1866</v>
+      </c>
+      <c r="U34" s="77" t="s">
+        <v>1754</v>
+      </c>
+      <c r="V34" s="78" t="s">
+        <v>1910</v>
+      </c>
+      <c r="W34" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="35" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="77"/>
@@ -40500,57 +40616,56 @@
       <c r="V35" s="78"/>
       <c r="W35" s="77"/>
     </row>
-    <row r="36" spans="1:23" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="77" t="s">
+    <row r="36" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
+      <c r="S36" s="77"/>
+      <c r="T36" s="77"/>
+      <c r="U36" s="77"/>
+      <c r="V36" s="78"/>
+      <c r="W36" s="77"/>
+    </row>
+    <row r="37" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="77" t="s">
         <v>2206</v>
       </c>
-      <c r="F36" s="77" t="s">
+      <c r="F37" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="77" t="s">
+      <c r="G37" s="77" t="s">
         <v>1851</v>
       </c>
-      <c r="H36" s="77" t="s">
+      <c r="H37" s="77" t="s">
         <v>1864</v>
       </c>
-      <c r="I36" s="77" t="s">
+      <c r="I37" s="77" t="s">
         <v>2206</v>
       </c>
-      <c r="J36" s="77" t="s">
+      <c r="J37" s="77" t="s">
         <v>1869</v>
       </c>
-      <c r="K36" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S36" s="77" t="s">
+      <c r="K37" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S37" s="77" t="s">
         <v>866</v>
       </c>
-      <c r="T36" s="77" t="s">
+      <c r="T37" s="77" t="s">
         <v>1870</v>
       </c>
-      <c r="U36" s="77" t="s">
+      <c r="U37" s="77" t="s">
         <v>1754</v>
       </c>
-      <c r="V36" s="78" t="s">
+      <c r="V37" s="78" t="s">
         <v>1910</v>
       </c>
-      <c r="W36" s="77" t="s">
+      <c r="W37" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="37" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="78"/>
-      <c r="W37" s="77"/>
     </row>
     <row r="38" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="77"/>
@@ -40567,52 +40682,53 @@
       <c r="W38" s="77"/>
     </row>
     <row r="39" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="77" t="s">
+      <c r="A39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="77"/>
+      <c r="U39" s="77"/>
+      <c r="V39" s="78"/>
+      <c r="W39" s="77"/>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="77" t="s">
         <v>2207</v>
       </c>
-      <c r="F39" s="77" t="s">
+      <c r="F40" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="77" t="s">
+      <c r="G40" s="77" t="s">
         <v>1868</v>
       </c>
-      <c r="I39" s="77" t="s">
+      <c r="I40" s="77" t="s">
         <v>2207</v>
       </c>
-      <c r="J39" s="77" t="s">
+      <c r="J40" s="77" t="s">
         <v>1871</v>
       </c>
-      <c r="K39" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S39" s="77" t="s">
+      <c r="K40" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S40" s="77" t="s">
         <v>866</v>
       </c>
-      <c r="T39" s="77" t="s">
+      <c r="T40" s="77" t="s">
         <v>1872</v>
       </c>
-      <c r="U39" s="77" t="s">
+      <c r="U40" s="77" t="s">
         <v>1754</v>
       </c>
-      <c r="V39" s="78" t="s">
+      <c r="V40" s="78" t="s">
         <v>1910</v>
       </c>
-      <c r="W39" s="77" t="s">
+      <c r="W40" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="40" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="77"/>
-      <c r="V40" s="78"/>
-      <c r="W40" s="77"/>
     </row>
     <row r="41" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="77"/>
@@ -40628,52 +40744,52 @@
       <c r="W41" s="77"/>
     </row>
     <row r="42" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="77" t="s">
+      <c r="A42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
+      <c r="K42" s="77"/>
+      <c r="S42" s="77"/>
+      <c r="T42" s="77"/>
+      <c r="U42" s="77"/>
+      <c r="V42" s="78"/>
+      <c r="W42" s="77"/>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="77" t="s">
         <v>2181</v>
       </c>
-      <c r="F42" s="77" t="s">
+      <c r="F43" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G42" s="77" t="s">
+      <c r="G43" s="77" t="s">
         <v>1851</v>
       </c>
-      <c r="I42" s="77" t="s">
+      <c r="I43" s="77" t="s">
         <v>2181</v>
       </c>
-      <c r="J42" s="77" t="s">
+      <c r="J43" s="77" t="s">
         <v>2182</v>
       </c>
-      <c r="K42" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S42" s="77" t="s">
+      <c r="K43" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S43" s="77" t="s">
         <v>850</v>
       </c>
-      <c r="T42" s="77" t="s">
+      <c r="T43" s="77" t="s">
         <v>1873</v>
       </c>
-      <c r="U42" s="77" t="s">
+      <c r="U43" s="77" t="s">
         <v>1754</v>
       </c>
-      <c r="V42" s="78" t="s">
+      <c r="V43" s="78" t="s">
         <v>1910</v>
       </c>
-      <c r="W42" s="77" t="s">
+      <c r="W43" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="43" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="77"/>
-      <c r="K43" s="77"/>
-      <c r="S43" s="77"/>
-      <c r="T43" s="77"/>
-      <c r="U43" s="77"/>
-      <c r="V43" s="78"/>
-      <c r="W43" s="77"/>
     </row>
     <row r="44" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="77"/>
@@ -40689,61 +40805,36 @@
       <c r="W44" s="77"/>
     </row>
     <row r="45" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="77" t="s">
-        <v>1874</v>
-      </c>
-      <c r="F45" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45" s="77" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H45" s="77" t="s">
-        <v>1876</v>
-      </c>
-      <c r="I45" s="77" t="s">
-        <v>1874</v>
-      </c>
-      <c r="J45" s="77" t="s">
-        <v>1877</v>
-      </c>
-      <c r="K45" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S45" s="77" t="s">
-        <v>850</v>
-      </c>
-      <c r="T45" s="77" t="s">
-        <v>1878</v>
-      </c>
-      <c r="U45" s="77" t="s">
-        <v>1748</v>
-      </c>
-      <c r="V45" s="78" t="s">
-        <v>1910</v>
-      </c>
-      <c r="W45" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="77"/>
+      <c r="I45" s="77"/>
+      <c r="J45" s="77"/>
+      <c r="K45" s="77"/>
+      <c r="S45" s="77"/>
+      <c r="T45" s="77"/>
+      <c r="U45" s="77"/>
+      <c r="V45" s="78"/>
+      <c r="W45" s="77"/>
     </row>
     <row r="46" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="77" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="F46" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G46" s="77" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="H46" s="77" t="s">
-        <v>1864</v>
+        <v>1876</v>
       </c>
       <c r="I46" s="77" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="J46" s="77" t="s">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="K46" s="77" t="s">
         <v>215</v>
@@ -40752,7 +40843,7 @@
         <v>850</v>
       </c>
       <c r="T46" s="77" t="s">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="U46" s="77" t="s">
         <v>1748</v>
@@ -40766,22 +40857,22 @@
     </row>
     <row r="47" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="77" t="s">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="F47" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="77" t="s">
-        <v>1868</v>
+        <v>1880</v>
       </c>
       <c r="H47" s="77" t="s">
-        <v>1884</v>
+        <v>1864</v>
       </c>
       <c r="I47" s="77" t="s">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="J47" s="77" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="K47" s="77" t="s">
         <v>215</v>
@@ -40790,7 +40881,7 @@
         <v>850</v>
       </c>
       <c r="T47" s="77" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="U47" s="77" t="s">
         <v>1748</v>
@@ -40804,22 +40895,22 @@
     </row>
     <row r="48" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="77" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="F48" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G48" s="77" t="s">
-        <v>1888</v>
+        <v>1868</v>
       </c>
       <c r="H48" s="77" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I48" s="77" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="J48" s="77" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="K48" s="77" t="s">
         <v>215</v>
@@ -40828,7 +40919,7 @@
         <v>850</v>
       </c>
       <c r="T48" s="77" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="U48" s="77" t="s">
         <v>1748</v>
@@ -40842,22 +40933,22 @@
     </row>
     <row r="49" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="77" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="F49" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G49" s="77" t="s">
-        <v>419</v>
+        <v>1888</v>
       </c>
       <c r="H49" s="77" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="I49" s="77" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="J49" s="77" t="s">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="K49" s="77" t="s">
         <v>215</v>
@@ -40866,7 +40957,7 @@
         <v>850</v>
       </c>
       <c r="T49" s="77" t="s">
-        <v>2877</v>
+        <v>1891</v>
       </c>
       <c r="U49" s="77" t="s">
         <v>1748</v>
@@ -40880,22 +40971,22 @@
     </row>
     <row r="50" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="77" t="s">
-        <v>2159</v>
+        <v>1892</v>
       </c>
       <c r="F50" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G50" s="77" t="s">
-        <v>1934</v>
+        <v>419</v>
       </c>
       <c r="H50" s="77" t="s">
-        <v>1935</v>
+        <v>1893</v>
       </c>
       <c r="I50" s="77" t="s">
-        <v>2159</v>
+        <v>1892</v>
       </c>
       <c r="J50" s="77" t="s">
-        <v>2160</v>
+        <v>1894</v>
       </c>
       <c r="K50" s="77" t="s">
         <v>215</v>
@@ -40904,7 +40995,7 @@
         <v>850</v>
       </c>
       <c r="T50" s="77" t="s">
-        <v>2161</v>
+        <v>2876</v>
       </c>
       <c r="U50" s="77" t="s">
         <v>1748</v>
@@ -40918,22 +41009,22 @@
     </row>
     <row r="51" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="77" t="s">
-        <v>2779</v>
+        <v>2159</v>
       </c>
       <c r="F51" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G51" s="77" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="H51" s="77" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="I51" s="77" t="s">
-        <v>2779</v>
+        <v>2159</v>
       </c>
       <c r="J51" s="77" t="s">
-        <v>2878</v>
+        <v>2160</v>
       </c>
       <c r="K51" s="77" t="s">
         <v>215</v>
@@ -40942,7 +41033,7 @@
         <v>850</v>
       </c>
       <c r="T51" s="77" t="s">
-        <v>2879</v>
+        <v>2161</v>
       </c>
       <c r="U51" s="77" t="s">
         <v>1748</v>
@@ -40956,22 +41047,22 @@
     </row>
     <row r="52" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="77" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="F52" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G52" s="77" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="H52" s="77" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="I52" s="77" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="J52" s="77" t="s">
-        <v>2880</v>
+        <v>2877</v>
       </c>
       <c r="K52" s="77" t="s">
         <v>215</v>
@@ -40980,7 +41071,7 @@
         <v>850</v>
       </c>
       <c r="T52" s="77" t="s">
-        <v>2881</v>
+        <v>2878</v>
       </c>
       <c r="U52" s="77" t="s">
         <v>1748</v>
@@ -40994,22 +41085,22 @@
     </row>
     <row r="53" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="77" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="F53" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G53" s="77" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="H53" s="77" t="s">
-        <v>2804</v>
+        <v>1943</v>
       </c>
       <c r="I53" s="77" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="J53" s="77" t="s">
-        <v>2882</v>
+        <v>2879</v>
       </c>
       <c r="K53" s="77" t="s">
         <v>215</v>
@@ -41018,7 +41109,7 @@
         <v>850</v>
       </c>
       <c r="T53" s="77" t="s">
-        <v>2883</v>
+        <v>2880</v>
       </c>
       <c r="U53" s="77" t="s">
         <v>1748</v>
@@ -41032,22 +41123,22 @@
     </row>
     <row r="54" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="77" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="F54" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G54" s="77" t="s">
-        <v>2793</v>
+        <v>1946</v>
       </c>
       <c r="H54" s="77" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="I54" s="77" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="J54" s="77" t="s">
-        <v>2884</v>
+        <v>2881</v>
       </c>
       <c r="K54" s="77" t="s">
         <v>215</v>
@@ -41056,7 +41147,7 @@
         <v>850</v>
       </c>
       <c r="T54" s="77" t="s">
-        <v>2885</v>
+        <v>2882</v>
       </c>
       <c r="U54" s="77" t="s">
         <v>1748</v>
@@ -41070,22 +41161,22 @@
     </row>
     <row r="55" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="77" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="F55" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G55" s="77" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="H55" s="77" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="I55" s="77" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="J55" s="77" t="s">
-        <v>2886</v>
+        <v>2883</v>
       </c>
       <c r="K55" s="77" t="s">
         <v>215</v>
@@ -41094,7 +41185,7 @@
         <v>850</v>
       </c>
       <c r="T55" s="77" t="s">
-        <v>2887</v>
+        <v>2884</v>
       </c>
       <c r="U55" s="77" t="s">
         <v>1748</v>
@@ -41108,22 +41199,22 @@
     </row>
     <row r="56" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="77" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="F56" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G56" s="77" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="H56" s="77" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="I56" s="77" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="J56" s="77" t="s">
-        <v>2888</v>
+        <v>2885</v>
       </c>
       <c r="K56" s="77" t="s">
         <v>215</v>
@@ -41132,7 +41223,7 @@
         <v>850</v>
       </c>
       <c r="T56" s="77" t="s">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="U56" s="77" t="s">
         <v>1748</v>
@@ -41146,22 +41237,22 @@
     </row>
     <row r="57" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="77" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="F57" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G57" s="77" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="H57" s="77" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="I57" s="77" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="J57" s="77" t="s">
-        <v>2890</v>
+        <v>2887</v>
       </c>
       <c r="K57" s="77" t="s">
         <v>215</v>
@@ -41170,7 +41261,7 @@
         <v>850</v>
       </c>
       <c r="T57" s="77" t="s">
-        <v>2891</v>
+        <v>2888</v>
       </c>
       <c r="U57" s="77" t="s">
         <v>1748</v>
@@ -41184,22 +41275,22 @@
     </row>
     <row r="58" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="77" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="F58" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G58" s="77" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="H58" s="77" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="I58" s="77" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="J58" s="77" t="s">
-        <v>2892</v>
+        <v>2889</v>
       </c>
       <c r="K58" s="77" t="s">
         <v>215</v>
@@ -41208,7 +41299,7 @@
         <v>850</v>
       </c>
       <c r="T58" s="77" t="s">
-        <v>2893</v>
+        <v>2890</v>
       </c>
       <c r="U58" s="77" t="s">
         <v>1748</v>
@@ -41222,22 +41313,22 @@
     </row>
     <row r="59" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="77" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="F59" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G59" s="77" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="H59" s="77" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="I59" s="77" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="J59" s="77" t="s">
-        <v>2894</v>
+        <v>2891</v>
       </c>
       <c r="K59" s="77" t="s">
         <v>215</v>
@@ -41246,7 +41337,7 @@
         <v>850</v>
       </c>
       <c r="T59" s="77" t="s">
-        <v>2895</v>
+        <v>2892</v>
       </c>
       <c r="U59" s="77" t="s">
         <v>1748</v>
@@ -41260,22 +41351,22 @@
     </row>
     <row r="60" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="77" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="F60" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G60" s="77" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="H60" s="77" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="I60" s="77" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="J60" s="77" t="s">
-        <v>2896</v>
+        <v>2893</v>
       </c>
       <c r="K60" s="77" t="s">
         <v>215</v>
@@ -41284,7 +41375,7 @@
         <v>850</v>
       </c>
       <c r="T60" s="77" t="s">
-        <v>2897</v>
+        <v>2894</v>
       </c>
       <c r="U60" s="77" t="s">
         <v>1748</v>
@@ -41298,22 +41389,22 @@
     </row>
     <row r="61" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="77" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="F61" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="77" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="H61" s="77" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="I61" s="77" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="J61" s="77" t="s">
-        <v>2898</v>
+        <v>2895</v>
       </c>
       <c r="K61" s="77" t="s">
         <v>215</v>
@@ -41322,7 +41413,7 @@
         <v>850</v>
       </c>
       <c r="T61" s="77" t="s">
-        <v>2899</v>
+        <v>2896</v>
       </c>
       <c r="U61" s="77" t="s">
         <v>1748</v>
@@ -41336,22 +41427,22 @@
     </row>
     <row r="62" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="77" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="F62" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G62" s="77" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="H62" s="77" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="I62" s="77" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="J62" s="77" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="K62" s="77" t="s">
         <v>215</v>
@@ -41360,7 +41451,7 @@
         <v>850</v>
       </c>
       <c r="T62" s="77" t="s">
-        <v>2901</v>
+        <v>2898</v>
       </c>
       <c r="U62" s="77" t="s">
         <v>1748</v>
@@ -41374,22 +41465,22 @@
     </row>
     <row r="63" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="77" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="F63" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G63" s="77" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="H63" s="77" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="I63" s="77" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="J63" s="77" t="s">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="K63" s="77" t="s">
         <v>215</v>
@@ -41398,7 +41489,7 @@
         <v>850</v>
       </c>
       <c r="T63" s="77" t="s">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="U63" s="77" t="s">
         <v>1748</v>
@@ -41412,22 +41503,22 @@
     </row>
     <row r="64" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="77" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="F64" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G64" s="77" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="H64" s="77" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="I64" s="77" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="J64" s="77" t="s">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="K64" s="77" t="s">
         <v>215</v>
@@ -41436,7 +41527,7 @@
         <v>850</v>
       </c>
       <c r="T64" s="77" t="s">
-        <v>2816</v>
+        <v>2902</v>
       </c>
       <c r="U64" s="77" t="s">
         <v>1748</v>
@@ -41449,18 +41540,42 @@
       </c>
     </row>
     <row r="65" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="77"/>
-      <c r="F65" s="77"/>
-      <c r="G65" s="77"/>
-      <c r="H65" s="77"/>
-      <c r="I65" s="77"/>
-      <c r="J65" s="77"/>
-      <c r="K65" s="77"/>
-      <c r="S65" s="77"/>
-      <c r="T65" s="77"/>
-      <c r="U65" s="77"/>
-      <c r="V65" s="78"/>
-      <c r="W65" s="77"/>
+      <c r="A65" s="77" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F65" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G65" s="77" t="s">
+        <v>2803</v>
+      </c>
+      <c r="H65" s="77" t="s">
+        <v>2815</v>
+      </c>
+      <c r="I65" s="77" t="s">
+        <v>2792</v>
+      </c>
+      <c r="J65" s="77" t="s">
+        <v>2903</v>
+      </c>
+      <c r="K65" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S65" s="77" t="s">
+        <v>850</v>
+      </c>
+      <c r="T65" s="77" t="s">
+        <v>2816</v>
+      </c>
+      <c r="U65" s="77" t="s">
+        <v>1748</v>
+      </c>
+      <c r="V65" s="78" t="s">
+        <v>1910</v>
+      </c>
+      <c r="W65" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="66" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="77"/>
@@ -41477,61 +41592,37 @@
       <c r="W66" s="77"/>
     </row>
     <row r="67" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="77" t="s">
-        <v>1895</v>
-      </c>
-      <c r="F67" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G67" s="77" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H67" s="77" t="s">
-        <v>1896</v>
-      </c>
-      <c r="I67" s="77" t="s">
-        <v>1895</v>
-      </c>
-      <c r="J67" s="77" t="s">
-        <v>1897</v>
-      </c>
-      <c r="K67" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S67" s="77" t="s">
-        <v>834</v>
-      </c>
-      <c r="T67" s="75">
-        <v>2651</v>
-      </c>
-      <c r="U67" s="77" t="s">
-        <v>579</v>
-      </c>
-      <c r="V67" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W67" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A67" s="77"/>
+      <c r="F67" s="77"/>
+      <c r="G67" s="77"/>
+      <c r="H67" s="77"/>
+      <c r="I67" s="77"/>
+      <c r="J67" s="77"/>
+      <c r="K67" s="77"/>
+      <c r="S67" s="77"/>
+      <c r="T67" s="77"/>
+      <c r="U67" s="77"/>
+      <c r="V67" s="78"/>
+      <c r="W67" s="77"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="77" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="F68" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G68" s="77" t="s">
-        <v>1899</v>
+        <v>1875</v>
       </c>
       <c r="H68" s="77" t="s">
-        <v>1876</v>
+        <v>1896</v>
       </c>
       <c r="I68" s="77" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="J68" s="77" t="s">
-        <v>1900</v>
+        <v>1897</v>
       </c>
       <c r="K68" s="77" t="s">
         <v>215</v>
@@ -41540,7 +41631,7 @@
         <v>834</v>
       </c>
       <c r="T68" s="75">
-        <v>2778</v>
+        <v>2651</v>
       </c>
       <c r="U68" s="77" t="s">
         <v>579</v>
@@ -41554,22 +41645,22 @@
     </row>
     <row r="69" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="77" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="F69" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G69" s="77" t="s">
-        <v>1880</v>
+        <v>1899</v>
       </c>
       <c r="H69" s="77" t="s">
-        <v>1864</v>
+        <v>1876</v>
       </c>
       <c r="I69" s="77" t="s">
-        <v>1901</v>
+        <v>1898</v>
       </c>
       <c r="J69" s="77" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="K69" s="77" t="s">
         <v>215</v>
@@ -41578,7 +41669,7 @@
         <v>834</v>
       </c>
       <c r="T69" s="75">
-        <v>2917</v>
+        <v>2778</v>
       </c>
       <c r="U69" s="77" t="s">
         <v>579</v>
@@ -41592,22 +41683,22 @@
     </row>
     <row r="70" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="77" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="F70" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G70" s="77" t="s">
-        <v>1868</v>
+        <v>1880</v>
       </c>
       <c r="H70" s="77" t="s">
-        <v>1884</v>
+        <v>1864</v>
       </c>
       <c r="I70" s="77" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="J70" s="77" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="K70" s="77" t="s">
         <v>215</v>
@@ -41616,7 +41707,7 @@
         <v>834</v>
       </c>
       <c r="T70" s="75">
-        <v>3063</v>
+        <v>2917</v>
       </c>
       <c r="U70" s="77" t="s">
         <v>579</v>
@@ -41630,22 +41721,22 @@
     </row>
     <row r="71" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="77" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="F71" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G71" s="77" t="s">
-        <v>1888</v>
+        <v>1868</v>
       </c>
       <c r="H71" s="77" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I71" s="77" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="J71" s="77" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="K71" s="77" t="s">
         <v>215</v>
@@ -41654,7 +41745,7 @@
         <v>834</v>
       </c>
       <c r="T71" s="75">
-        <v>3450</v>
+        <v>3063</v>
       </c>
       <c r="U71" s="77" t="s">
         <v>579</v>
@@ -41668,22 +41759,22 @@
     </row>
     <row r="72" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="77" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="F72" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G72" s="77" t="s">
-        <v>419</v>
+        <v>1888</v>
       </c>
       <c r="H72" s="77" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="I72" s="77" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="J72" s="77" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="K72" s="77" t="s">
         <v>215</v>
@@ -41691,8 +41782,8 @@
       <c r="S72" s="77" t="s">
         <v>834</v>
       </c>
-      <c r="T72" s="77" t="s">
-        <v>1909</v>
+      <c r="T72" s="75">
+        <v>3450</v>
       </c>
       <c r="U72" s="77" t="s">
         <v>579</v>
@@ -41706,22 +41797,22 @@
     </row>
     <row r="73" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="77" t="s">
-        <v>2148</v>
+        <v>1907</v>
       </c>
       <c r="F73" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G73" s="77" t="s">
-        <v>1934</v>
+        <v>419</v>
       </c>
       <c r="H73" s="77" t="s">
-        <v>1935</v>
+        <v>1893</v>
       </c>
       <c r="I73" s="77" t="s">
-        <v>2148</v>
+        <v>1907</v>
       </c>
       <c r="J73" s="77" t="s">
-        <v>2149</v>
+        <v>1908</v>
       </c>
       <c r="K73" s="77" t="s">
         <v>215</v>
@@ -41730,7 +41821,7 @@
         <v>834</v>
       </c>
       <c r="T73" s="77" t="s">
-        <v>2150</v>
+        <v>1909</v>
       </c>
       <c r="U73" s="77" t="s">
         <v>579</v>
@@ -41744,22 +41835,22 @@
     </row>
     <row r="74" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="77" t="s">
-        <v>2817</v>
+        <v>2148</v>
       </c>
       <c r="F74" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G74" s="77" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="H74" s="77" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="I74" s="77" t="s">
-        <v>2817</v>
+        <v>2148</v>
       </c>
       <c r="J74" s="77" t="s">
-        <v>2818</v>
+        <v>2149</v>
       </c>
       <c r="K74" s="77" t="s">
         <v>215</v>
@@ -41768,7 +41859,7 @@
         <v>834</v>
       </c>
       <c r="T74" s="77" t="s">
-        <v>2819</v>
+        <v>2150</v>
       </c>
       <c r="U74" s="77" t="s">
         <v>579</v>
@@ -41781,18 +41872,42 @@
       </c>
     </row>
     <row r="75" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="77"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="77"/>
-      <c r="H75" s="77"/>
-      <c r="I75" s="77"/>
-      <c r="J75" s="77"/>
-      <c r="K75" s="77"/>
-      <c r="S75" s="77"/>
-      <c r="T75" s="77"/>
-      <c r="U75" s="77"/>
-      <c r="V75" s="78"/>
-      <c r="W75" s="77"/>
+      <c r="A75" s="77" t="s">
+        <v>2817</v>
+      </c>
+      <c r="F75" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G75" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H75" s="77" t="s">
+        <v>1939</v>
+      </c>
+      <c r="I75" s="77" t="s">
+        <v>2817</v>
+      </c>
+      <c r="J75" s="77" t="s">
+        <v>2818</v>
+      </c>
+      <c r="K75" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S75" s="77" t="s">
+        <v>834</v>
+      </c>
+      <c r="T75" s="77" t="s">
+        <v>2819</v>
+      </c>
+      <c r="U75" s="77" t="s">
+        <v>579</v>
+      </c>
+      <c r="V75" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W75" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="76" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="77"/>
@@ -41809,61 +41924,37 @@
       <c r="W76" s="77"/>
     </row>
     <row r="77" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="77" t="s">
-        <v>1911</v>
-      </c>
-      <c r="F77" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G77" s="77" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H77" s="77" t="s">
-        <v>1896</v>
-      </c>
-      <c r="I77" s="77" t="s">
-        <v>1911</v>
-      </c>
-      <c r="J77" s="77" t="s">
-        <v>1912</v>
-      </c>
-      <c r="K77" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S77" s="77" t="s">
-        <v>834</v>
-      </c>
-      <c r="T77" s="75">
-        <v>42500</v>
-      </c>
-      <c r="U77" s="77" t="s">
-        <v>579</v>
-      </c>
-      <c r="V77" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W77" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A77" s="77"/>
+      <c r="F77" s="77"/>
+      <c r="G77" s="77"/>
+      <c r="H77" s="77"/>
+      <c r="I77" s="77"/>
+      <c r="J77" s="77"/>
+      <c r="K77" s="77"/>
+      <c r="S77" s="77"/>
+      <c r="T77" s="77"/>
+      <c r="U77" s="77"/>
+      <c r="V77" s="78"/>
+      <c r="W77" s="77"/>
     </row>
     <row r="78" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="77" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="F78" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G78" s="77" t="s">
-        <v>1899</v>
+        <v>1875</v>
       </c>
       <c r="H78" s="77" t="s">
-        <v>1876</v>
+        <v>1896</v>
       </c>
       <c r="I78" s="77" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="J78" s="77" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="K78" s="77" t="s">
         <v>215</v>
@@ -41886,22 +41977,22 @@
     </row>
     <row r="79" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="77" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="F79" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G79" s="77" t="s">
-        <v>1880</v>
+        <v>1899</v>
       </c>
       <c r="H79" s="77" t="s">
-        <v>1864</v>
+        <v>1876</v>
       </c>
       <c r="I79" s="77" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="J79" s="77" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="K79" s="77" t="s">
         <v>215</v>
@@ -41924,22 +42015,22 @@
     </row>
     <row r="80" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="77" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="F80" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G80" s="77" t="s">
-        <v>1868</v>
+        <v>1880</v>
       </c>
       <c r="H80" s="77" t="s">
-        <v>1884</v>
+        <v>1864</v>
       </c>
       <c r="I80" s="77" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="J80" s="77" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="K80" s="77" t="s">
         <v>215</v>
@@ -41948,7 +42039,7 @@
         <v>834</v>
       </c>
       <c r="T80" s="75">
-        <v>60000</v>
+        <v>42500</v>
       </c>
       <c r="U80" s="77" t="s">
         <v>579</v>
@@ -41962,22 +42053,22 @@
     </row>
     <row r="81" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="77" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="F81" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G81" s="77" t="s">
-        <v>1888</v>
+        <v>1868</v>
       </c>
       <c r="H81" s="77" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I81" s="77" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="J81" s="77" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="K81" s="77" t="s">
         <v>215</v>
@@ -41986,7 +42077,7 @@
         <v>834</v>
       </c>
       <c r="T81" s="75">
-        <v>70000</v>
+        <v>60000</v>
       </c>
       <c r="U81" s="77" t="s">
         <v>579</v>
@@ -42000,22 +42091,22 @@
     </row>
     <row r="82" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="77" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="F82" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G82" s="77" t="s">
-        <v>419</v>
+        <v>1888</v>
       </c>
       <c r="H82" s="77" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="I82" s="77" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="J82" s="77" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="K82" s="77" t="s">
         <v>215</v>
@@ -42023,8 +42114,8 @@
       <c r="S82" s="77" t="s">
         <v>834</v>
       </c>
-      <c r="T82" s="77" t="s">
-        <v>1923</v>
+      <c r="T82" s="75">
+        <v>70000</v>
       </c>
       <c r="U82" s="77" t="s">
         <v>579</v>
@@ -42036,57 +42127,81 @@
         <v>830</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A83" s="75" t="s">
+    <row r="83" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="77" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F83" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83" s="77" t="s">
+        <v>419</v>
+      </c>
+      <c r="H83" s="77" t="s">
+        <v>1893</v>
+      </c>
+      <c r="I83" s="77" t="s">
+        <v>1921</v>
+      </c>
+      <c r="J83" s="77" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K83" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S83" s="77" t="s">
+        <v>834</v>
+      </c>
+      <c r="T83" s="77" t="s">
+        <v>1923</v>
+      </c>
+      <c r="U83" s="77" t="s">
+        <v>579</v>
+      </c>
+      <c r="V83" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W83" s="77" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A84" s="75" t="s">
         <v>2145</v>
       </c>
-      <c r="F83" s="75" t="s">
+      <c r="F84" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="G83" s="75" t="s">
+      <c r="G84" s="75" t="s">
         <v>1934</v>
       </c>
-      <c r="H83" s="75" t="s">
+      <c r="H84" s="75" t="s">
         <v>1935</v>
       </c>
-      <c r="I83" s="75" t="s">
+      <c r="I84" s="75" t="s">
         <v>2145</v>
       </c>
-      <c r="J83" s="75" t="s">
+      <c r="J84" s="75" t="s">
         <v>2146</v>
       </c>
-      <c r="K83" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="S83" s="75" t="s">
+      <c r="K84" s="75" t="s">
+        <v>215</v>
+      </c>
+      <c r="S84" s="75" t="s">
         <v>834</v>
       </c>
-      <c r="T83" s="75" t="s">
+      <c r="T84" s="75" t="s">
         <v>1923</v>
       </c>
-      <c r="U83" s="75" t="s">
+      <c r="U84" s="75" t="s">
         <v>579</v>
       </c>
-      <c r="V83" s="75" t="s">
+      <c r="V84" s="75" t="s">
         <v>2147</v>
       </c>
-      <c r="W83" s="75" t="s">
+      <c r="W84" s="75" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="84" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="77"/>
-      <c r="F84" s="77"/>
-      <c r="G84" s="77"/>
-      <c r="H84" s="77"/>
-      <c r="I84" s="77"/>
-      <c r="J84" s="77"/>
-      <c r="K84" s="77"/>
-      <c r="S84" s="77"/>
-      <c r="T84" s="77"/>
-      <c r="U84" s="77"/>
-      <c r="V84" s="78"/>
-      <c r="W84" s="77"/>
     </row>
     <row r="85" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="77"/>
@@ -42103,58 +42218,34 @@
       <c r="W85" s="77"/>
     </row>
     <row r="86" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="77" t="s">
-        <v>2151</v>
-      </c>
-      <c r="F86" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G86" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="H86" s="77" t="s">
-        <v>1893</v>
-      </c>
-      <c r="I86" s="77" t="s">
-        <v>2151</v>
-      </c>
-      <c r="J86" s="77" t="s">
-        <v>1924</v>
-      </c>
-      <c r="K86" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P86" s="77" t="s">
-        <v>1925</v>
-      </c>
-      <c r="S86" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T86" s="75" t="s">
-        <v>1940</v>
-      </c>
-      <c r="U86" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V86" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W86" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A86" s="77"/>
+      <c r="F86" s="77"/>
+      <c r="G86" s="77"/>
+      <c r="H86" s="77"/>
+      <c r="I86" s="77"/>
+      <c r="J86" s="77"/>
+      <c r="K86" s="77"/>
+      <c r="S86" s="77"/>
+      <c r="T86" s="77"/>
+      <c r="U86" s="77"/>
+      <c r="V86" s="78"/>
+      <c r="W86" s="77"/>
     </row>
     <row r="87" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="77" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="F87" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G87" s="77" t="s">
-        <v>1934</v>
+        <v>891</v>
+      </c>
+      <c r="H87" s="77" t="s">
+        <v>1893</v>
       </c>
       <c r="I87" s="77" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="J87" s="77" t="s">
         <v>1924</v>
@@ -42169,7 +42260,7 @@
         <v>869</v>
       </c>
       <c r="T87" s="75" t="s">
-        <v>1947</v>
+        <v>1940</v>
       </c>
       <c r="U87" s="77" t="s">
         <v>871</v>
@@ -42182,17 +42273,42 @@
       </c>
     </row>
     <row r="88" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="77"/>
-      <c r="F88" s="77"/>
-      <c r="G88" s="77"/>
-      <c r="I88" s="77"/>
-      <c r="J88" s="77"/>
-      <c r="K88" s="77"/>
-      <c r="P88" s="77"/>
-      <c r="S88" s="77"/>
-      <c r="U88" s="77"/>
-      <c r="V88" s="78"/>
-      <c r="W88" s="77"/>
+      <c r="A88" s="77" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F88" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G88" s="77" t="s">
+        <v>1934</v>
+      </c>
+      <c r="I88" s="77" t="s">
+        <v>2152</v>
+      </c>
+      <c r="J88" s="77" t="s">
+        <v>1924</v>
+      </c>
+      <c r="K88" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P88" s="77" t="s">
+        <v>1925</v>
+      </c>
+      <c r="S88" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T88" s="75" t="s">
+        <v>1947</v>
+      </c>
+      <c r="U88" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V88" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W88" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="89" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="77"/>
@@ -42207,53 +42323,53 @@
       <c r="V89" s="78"/>
       <c r="W89" s="77"/>
     </row>
-    <row r="90" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="77" t="s">
+    <row r="90" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="77"/>
+      <c r="F90" s="77"/>
+      <c r="G90" s="77"/>
+      <c r="I90" s="77"/>
+      <c r="J90" s="77"/>
+      <c r="K90" s="77"/>
+      <c r="P90" s="77"/>
+      <c r="S90" s="77"/>
+      <c r="U90" s="77"/>
+      <c r="V90" s="78"/>
+      <c r="W90" s="77"/>
+    </row>
+    <row r="91" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="77" t="s">
         <v>2168</v>
       </c>
-      <c r="F90" s="77" t="s">
+      <c r="F91" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G90" s="77" t="s">
+      <c r="G91" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I90" s="77" t="s">
+      <c r="I91" s="77" t="s">
         <v>344</v>
       </c>
-      <c r="J90" s="77" t="s">
+      <c r="J91" s="77" t="s">
         <v>345</v>
       </c>
-      <c r="K90" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S90" s="77" t="s">
+      <c r="K91" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S91" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T90" s="75">
+      <c r="T91" s="75">
         <v>7</v>
       </c>
-      <c r="U90" s="77" t="s">
+      <c r="U91" s="77" t="s">
         <v>1774</v>
       </c>
-      <c r="V90" s="78" t="s">
+      <c r="V91" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W90" s="77" t="s">
+      <c r="W91" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="91" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="77"/>
-      <c r="F91" s="77"/>
-      <c r="G91" s="77"/>
-      <c r="I91" s="77"/>
-      <c r="J91" s="77"/>
-      <c r="K91" s="77"/>
-      <c r="P91" s="77"/>
-      <c r="S91" s="77"/>
-      <c r="U91" s="77"/>
-      <c r="V91" s="78"/>
-      <c r="W91" s="77"/>
     </row>
     <row r="92" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="77"/>
@@ -42269,55 +42385,55 @@
       <c r="W92" s="77"/>
     </row>
     <row r="93" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="77" t="s">
+      <c r="A93" s="77"/>
+      <c r="F93" s="77"/>
+      <c r="G93" s="77"/>
+      <c r="I93" s="77"/>
+      <c r="J93" s="77"/>
+      <c r="K93" s="77"/>
+      <c r="P93" s="77"/>
+      <c r="S93" s="77"/>
+      <c r="U93" s="77"/>
+      <c r="V93" s="78"/>
+      <c r="W93" s="77"/>
+    </row>
+    <row r="94" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="77" t="s">
         <v>2165</v>
       </c>
-      <c r="F93" s="77" t="s">
+      <c r="F94" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G93" s="77" t="s">
+      <c r="G94" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I93" s="77" t="s">
+      <c r="I94" s="77" t="s">
         <v>2165</v>
       </c>
-      <c r="J93" s="77" t="s">
+      <c r="J94" s="77" t="s">
         <v>1926</v>
       </c>
-      <c r="K93" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P93" s="77" t="s">
+      <c r="K94" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P94" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S93" s="77" t="s">
+      <c r="S94" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T93" s="75">
+      <c r="T94" s="75">
         <v>10</v>
       </c>
-      <c r="U93" s="77" t="s">
+      <c r="U94" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V93" s="78" t="s">
+      <c r="V94" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W93" s="77" t="s">
+      <c r="W94" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="94" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="77"/>
-      <c r="F94" s="77"/>
-      <c r="G94" s="77"/>
-      <c r="I94" s="77"/>
-      <c r="J94" s="77"/>
-      <c r="K94" s="77"/>
-      <c r="P94" s="77"/>
-      <c r="S94" s="77"/>
-      <c r="U94" s="77"/>
-      <c r="V94" s="78"/>
-      <c r="W94" s="77"/>
     </row>
     <row r="95" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="77"/>
@@ -42333,55 +42449,55 @@
       <c r="W95" s="77"/>
     </row>
     <row r="96" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="77" t="s">
+      <c r="A96" s="77"/>
+      <c r="F96" s="77"/>
+      <c r="G96" s="77"/>
+      <c r="I96" s="77"/>
+      <c r="J96" s="77"/>
+      <c r="K96" s="77"/>
+      <c r="P96" s="77"/>
+      <c r="S96" s="77"/>
+      <c r="U96" s="77"/>
+      <c r="V96" s="78"/>
+      <c r="W96" s="77"/>
+    </row>
+    <row r="97" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="77" t="s">
         <v>2850</v>
       </c>
-      <c r="F96" s="77" t="s">
+      <c r="F97" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G96" s="77" t="s">
+      <c r="G97" s="77" t="s">
         <v>1938</v>
       </c>
-      <c r="I96" s="77" t="s">
+      <c r="I97" s="77" t="s">
         <v>2850</v>
       </c>
-      <c r="J96" s="77" t="s">
+      <c r="J97" s="77" t="s">
         <v>2848</v>
       </c>
-      <c r="K96" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P96" s="77" t="s">
+      <c r="K97" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P97" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S96" s="77" t="s">
+      <c r="S97" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T96" s="75" t="s">
+      <c r="T97" s="75" t="s">
         <v>2849</v>
       </c>
-      <c r="U96" s="82" t="s">
+      <c r="U97" s="82" t="s">
         <v>1772</v>
       </c>
-      <c r="V96" s="78" t="s">
+      <c r="V97" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W96" s="77" t="s">
+      <c r="W97" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="97" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="77"/>
-      <c r="F97" s="77"/>
-      <c r="G97" s="77"/>
-      <c r="I97" s="77"/>
-      <c r="J97" s="77"/>
-      <c r="K97" s="77"/>
-      <c r="P97" s="77"/>
-      <c r="S97" s="77"/>
-      <c r="U97" s="77"/>
-      <c r="V97" s="78"/>
-      <c r="W97" s="77"/>
     </row>
     <row r="98" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="77"/>
@@ -42397,55 +42513,55 @@
       <c r="W98" s="77"/>
     </row>
     <row r="99" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="77" t="s">
+      <c r="A99" s="77"/>
+      <c r="F99" s="77"/>
+      <c r="G99" s="77"/>
+      <c r="I99" s="77"/>
+      <c r="J99" s="77"/>
+      <c r="K99" s="77"/>
+      <c r="P99" s="77"/>
+      <c r="S99" s="77"/>
+      <c r="U99" s="77"/>
+      <c r="V99" s="78"/>
+      <c r="W99" s="77"/>
+    </row>
+    <row r="100" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="77" t="s">
         <v>2847</v>
       </c>
-      <c r="F99" s="77" t="s">
+      <c r="F100" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G99" s="77" t="s">
+      <c r="G100" s="77" t="s">
         <v>1938</v>
       </c>
-      <c r="I99" s="77" t="s">
+      <c r="I100" s="77" t="s">
         <v>2847</v>
       </c>
-      <c r="J99" s="77" t="s">
+      <c r="J100" s="77" t="s">
         <v>2845</v>
       </c>
-      <c r="K99" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P99" s="77" t="s">
+      <c r="K100" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P100" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S99" s="77" t="s">
+      <c r="S100" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T99" s="75" t="s">
+      <c r="T100" s="75" t="s">
         <v>2846</v>
       </c>
-      <c r="U99" s="77" t="s">
+      <c r="U100" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V99" s="78" t="s">
+      <c r="V100" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W99" s="77" t="s">
+      <c r="W100" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="100" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="77"/>
-      <c r="F100" s="77"/>
-      <c r="G100" s="77"/>
-      <c r="I100" s="77"/>
-      <c r="J100" s="77"/>
-      <c r="K100" s="77"/>
-      <c r="P100" s="77"/>
-      <c r="S100" s="77"/>
-      <c r="U100" s="77"/>
-      <c r="V100" s="78"/>
-      <c r="W100" s="77"/>
     </row>
     <row r="101" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="77"/>
@@ -42461,55 +42577,55 @@
       <c r="W101" s="77"/>
     </row>
     <row r="102" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="77" t="s">
+      <c r="A102" s="77"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="77"/>
+      <c r="I102" s="77"/>
+      <c r="J102" s="77"/>
+      <c r="K102" s="77"/>
+      <c r="P102" s="77"/>
+      <c r="S102" s="77"/>
+      <c r="U102" s="77"/>
+      <c r="V102" s="78"/>
+      <c r="W102" s="77"/>
+    </row>
+    <row r="103" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="77" t="s">
         <v>2166</v>
       </c>
-      <c r="F102" s="77" t="s">
+      <c r="F103" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G102" s="77" t="s">
+      <c r="G103" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I102" s="77" t="s">
+      <c r="I103" s="77" t="s">
         <v>2166</v>
       </c>
-      <c r="J102" s="77" t="s">
+      <c r="J103" s="77" t="s">
         <v>379</v>
       </c>
-      <c r="K102" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P102" s="77" t="s">
+      <c r="K103" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P103" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S102" s="77" t="s">
+      <c r="S103" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T102" s="75">
+      <c r="T103" s="75">
         <v>20</v>
       </c>
-      <c r="U102" s="77" t="s">
+      <c r="U103" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V102" s="78" t="s">
+      <c r="V103" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W102" s="77" t="s">
+      <c r="W103" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="103" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="77"/>
-      <c r="F103" s="77"/>
-      <c r="G103" s="77"/>
-      <c r="I103" s="77"/>
-      <c r="J103" s="77"/>
-      <c r="K103" s="77"/>
-      <c r="P103" s="77"/>
-      <c r="S103" s="77"/>
-      <c r="U103" s="77"/>
-      <c r="V103" s="78"/>
-      <c r="W103" s="77"/>
     </row>
     <row r="104" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="77"/>
@@ -42525,62 +42641,33 @@
       <c r="W104" s="77"/>
     </row>
     <row r="105" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="79" t="s">
-        <v>2162</v>
-      </c>
-      <c r="F105" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G105" s="77" t="s">
-        <v>1868</v>
-      </c>
-      <c r="H105" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I105" s="79" t="s">
-        <v>2162</v>
-      </c>
-      <c r="J105" s="79" t="s">
-        <v>368</v>
-      </c>
-      <c r="K105" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q105" s="79" t="s">
-        <v>292</v>
-      </c>
-      <c r="R105" s="79" t="s">
-        <v>369</v>
-      </c>
-      <c r="S105" s="77" t="s">
-        <v>842</v>
-      </c>
-      <c r="T105" s="75">
-        <v>14</v>
-      </c>
-      <c r="U105" s="82" t="s">
-        <v>1772</v>
-      </c>
-      <c r="V105" s="78" t="s">
-        <v>1910</v>
-      </c>
-      <c r="W105" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A105" s="77"/>
+      <c r="F105" s="77"/>
+      <c r="G105" s="77"/>
+      <c r="I105" s="77"/>
+      <c r="J105" s="77"/>
+      <c r="K105" s="77"/>
+      <c r="P105" s="77"/>
+      <c r="S105" s="77"/>
+      <c r="U105" s="77"/>
+      <c r="V105" s="78"/>
+      <c r="W105" s="77"/>
     </row>
     <row r="106" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="79" t="s">
-        <v>2820</v>
+        <v>2162</v>
       </c>
       <c r="F106" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G106" s="77" t="s">
-        <v>1938</v>
-      </c>
-      <c r="H106" s="77"/>
+        <v>1868</v>
+      </c>
+      <c r="H106" s="77" t="s">
+        <v>1935</v>
+      </c>
       <c r="I106" s="79" t="s">
-        <v>2820</v>
+        <v>2162</v>
       </c>
       <c r="J106" s="79" t="s">
         <v>368</v>
@@ -42597,8 +42684,8 @@
       <c r="S106" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T106" s="75" t="s">
-        <v>2821</v>
+      <c r="T106" s="75">
+        <v>14</v>
       </c>
       <c r="U106" s="82" t="s">
         <v>1772</v>
@@ -42611,17 +42698,46 @@
       </c>
     </row>
     <row r="107" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="77"/>
-      <c r="F107" s="77"/>
-      <c r="G107" s="77"/>
-      <c r="I107" s="77"/>
-      <c r="J107" s="77"/>
-      <c r="K107" s="77"/>
-      <c r="P107" s="77"/>
-      <c r="S107" s="77"/>
-      <c r="U107" s="77"/>
-      <c r="V107" s="78"/>
-      <c r="W107" s="77"/>
+      <c r="A107" s="79" t="s">
+        <v>2820</v>
+      </c>
+      <c r="F107" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G107" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H107" s="77"/>
+      <c r="I107" s="79" t="s">
+        <v>2820</v>
+      </c>
+      <c r="J107" s="79" t="s">
+        <v>368</v>
+      </c>
+      <c r="K107" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q107" s="79" t="s">
+        <v>292</v>
+      </c>
+      <c r="R107" s="79" t="s">
+        <v>369</v>
+      </c>
+      <c r="S107" s="77" t="s">
+        <v>842</v>
+      </c>
+      <c r="T107" s="75" t="s">
+        <v>2821</v>
+      </c>
+      <c r="U107" s="82" t="s">
+        <v>1772</v>
+      </c>
+      <c r="V107" s="78" t="s">
+        <v>1910</v>
+      </c>
+      <c r="W107" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="108" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="77"/>
@@ -42637,55 +42753,55 @@
       <c r="W108" s="77"/>
     </row>
     <row r="109" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="77" t="s">
+      <c r="A109" s="77"/>
+      <c r="F109" s="77"/>
+      <c r="G109" s="77"/>
+      <c r="I109" s="77"/>
+      <c r="J109" s="77"/>
+      <c r="K109" s="77"/>
+      <c r="P109" s="77"/>
+      <c r="S109" s="77"/>
+      <c r="U109" s="77"/>
+      <c r="V109" s="78"/>
+      <c r="W109" s="77"/>
+    </row>
+    <row r="110" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="77" t="s">
         <v>2167</v>
       </c>
-      <c r="F109" s="77" t="s">
+      <c r="F110" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G109" s="77" t="s">
+      <c r="G110" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I109" s="77" t="s">
+      <c r="I110" s="77" t="s">
         <v>2167</v>
       </c>
-      <c r="J109" s="77" t="s">
+      <c r="J110" s="77" t="s">
         <v>414</v>
       </c>
-      <c r="K109" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P109" s="77" t="s">
+      <c r="K110" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P110" s="77" t="s">
         <v>242</v>
       </c>
-      <c r="S109" s="77" t="s">
+      <c r="S110" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T109" s="75">
+      <c r="T110" s="75">
         <v>10</v>
       </c>
-      <c r="U109" s="77" t="s">
+      <c r="U110" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V109" s="78" t="s">
+      <c r="V110" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W109" s="77" t="s">
+      <c r="W110" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="110" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="77"/>
-      <c r="F110" s="77"/>
-      <c r="G110" s="77"/>
-      <c r="I110" s="77"/>
-      <c r="J110" s="77"/>
-      <c r="K110" s="77"/>
-      <c r="P110" s="77"/>
-      <c r="S110" s="77"/>
-      <c r="U110" s="77"/>
-      <c r="V110" s="78"/>
-      <c r="W110" s="77"/>
     </row>
     <row r="111" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="77"/>
@@ -42701,52 +42817,52 @@
       <c r="W111" s="77"/>
     </row>
     <row r="112" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="77" t="s">
+      <c r="A112" s="77"/>
+      <c r="F112" s="77"/>
+      <c r="G112" s="77"/>
+      <c r="I112" s="77"/>
+      <c r="J112" s="77"/>
+      <c r="K112" s="77"/>
+      <c r="P112" s="77"/>
+      <c r="S112" s="77"/>
+      <c r="U112" s="77"/>
+      <c r="V112" s="78"/>
+      <c r="W112" s="77"/>
+    </row>
+    <row r="113" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="77" t="s">
         <v>2169</v>
       </c>
-      <c r="F112" s="77" t="s">
+      <c r="F113" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G112" s="77" t="s">
+      <c r="G113" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I112" s="77" t="s">
+      <c r="I113" s="77" t="s">
         <v>2169</v>
       </c>
-      <c r="J112" s="77" t="s">
+      <c r="J113" s="77" t="s">
         <v>406</v>
       </c>
-      <c r="K112" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S112" s="77" t="s">
+      <c r="K113" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S113" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T112" s="75">
+      <c r="T113" s="75">
         <v>50</v>
       </c>
-      <c r="U112" s="77" t="s">
+      <c r="U113" s="77" t="s">
         <v>1774</v>
       </c>
-      <c r="V112" s="78" t="s">
+      <c r="V113" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W112" s="77" t="s">
+      <c r="W113" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="113" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="77"/>
-      <c r="F113" s="77"/>
-      <c r="G113" s="77"/>
-      <c r="I113" s="77"/>
-      <c r="J113" s="77"/>
-      <c r="K113" s="77"/>
-      <c r="P113" s="77"/>
-      <c r="S113" s="77"/>
-      <c r="U113" s="77"/>
-      <c r="V113" s="78"/>
-      <c r="W113" s="77"/>
     </row>
     <row r="114" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="77"/>
@@ -42762,43 +42878,21 @@
       <c r="W114" s="77"/>
     </row>
     <row r="115" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="77" t="s">
-        <v>2163</v>
-      </c>
-      <c r="F115" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G115" s="77" t="s">
-        <v>419</v>
-      </c>
-      <c r="I115" s="77" t="s">
-        <v>2163</v>
-      </c>
-      <c r="J115" s="77" t="s">
-        <v>423</v>
-      </c>
-      <c r="K115" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S115" s="77" t="s">
-        <v>842</v>
-      </c>
-      <c r="T115" s="77" t="s">
-        <v>1347</v>
-      </c>
-      <c r="U115" s="77" t="s">
-        <v>1774</v>
-      </c>
-      <c r="V115" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W115" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A115" s="77"/>
+      <c r="F115" s="77"/>
+      <c r="G115" s="77"/>
+      <c r="I115" s="77"/>
+      <c r="J115" s="77"/>
+      <c r="K115" s="77"/>
+      <c r="P115" s="77"/>
+      <c r="S115" s="77"/>
+      <c r="U115" s="77"/>
+      <c r="V115" s="78"/>
+      <c r="W115" s="77"/>
     </row>
     <row r="116" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="77" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="F116" s="77" t="s">
         <v>76</v>
@@ -42807,10 +42901,10 @@
         <v>419</v>
       </c>
       <c r="I116" s="77" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="J116" s="77" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="K116" s="77" t="s">
         <v>215</v>
@@ -42818,8 +42912,8 @@
       <c r="S116" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T116" s="75">
-        <v>50</v>
+      <c r="T116" s="77" t="s">
+        <v>1347</v>
       </c>
       <c r="U116" s="77" t="s">
         <v>1774</v>
@@ -42832,16 +42926,39 @@
       </c>
     </row>
     <row r="117" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="77"/>
-      <c r="F117" s="77"/>
-      <c r="G117" s="77"/>
-      <c r="I117" s="77"/>
-      <c r="J117" s="77"/>
-      <c r="K117" s="77"/>
-      <c r="S117" s="77"/>
-      <c r="U117" s="77"/>
-      <c r="V117" s="78"/>
-      <c r="W117" s="77"/>
+      <c r="A117" s="77" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F117" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G117" s="77" t="s">
+        <v>419</v>
+      </c>
+      <c r="I117" s="77" t="s">
+        <v>2164</v>
+      </c>
+      <c r="J117" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="K117" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S117" s="77" t="s">
+        <v>842</v>
+      </c>
+      <c r="T117" s="75">
+        <v>50</v>
+      </c>
+      <c r="U117" s="77" t="s">
+        <v>1774</v>
+      </c>
+      <c r="V117" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W117" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="118" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="77"/>
@@ -42856,58 +42973,32 @@
       <c r="W118" s="77"/>
     </row>
     <row r="119" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="77" t="s">
-        <v>1931</v>
-      </c>
-      <c r="F119" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G119" s="77" t="s">
-        <v>419</v>
-      </c>
-      <c r="H119" s="77" t="s">
-        <v>1893</v>
-      </c>
-      <c r="I119" s="77" t="s">
-        <v>1931</v>
-      </c>
-      <c r="J119" s="77" t="s">
-        <v>427</v>
-      </c>
-      <c r="K119" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="S119" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T119" s="77" t="s">
-        <v>1932</v>
-      </c>
-      <c r="U119" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V119" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W119" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A119" s="77"/>
+      <c r="F119" s="77"/>
+      <c r="G119" s="77"/>
+      <c r="I119" s="77"/>
+      <c r="J119" s="77"/>
+      <c r="K119" s="77"/>
+      <c r="S119" s="77"/>
+      <c r="U119" s="77"/>
+      <c r="V119" s="78"/>
+      <c r="W119" s="77"/>
     </row>
     <row r="120" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="77" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="F120" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G120" s="77" t="s">
-        <v>1934</v>
+        <v>419</v>
       </c>
       <c r="H120" s="77" t="s">
-        <v>1935</v>
+        <v>1893</v>
       </c>
       <c r="I120" s="77" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="J120" s="77" t="s">
         <v>427</v>
@@ -42919,7 +43010,7 @@
         <v>869</v>
       </c>
       <c r="T120" s="77" t="s">
-        <v>1936</v>
+        <v>1932</v>
       </c>
       <c r="U120" s="77" t="s">
         <v>871</v>
@@ -42933,19 +43024,19 @@
     </row>
     <row r="121" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="77" t="s">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="F121" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G121" s="77" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="H121" s="77" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="I121" s="77" t="s">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="J121" s="77" t="s">
         <v>427</v>
@@ -42957,7 +43048,7 @@
         <v>869</v>
       </c>
       <c r="T121" s="77" t="s">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="U121" s="77" t="s">
         <v>871</v>
@@ -42971,19 +43062,19 @@
     </row>
     <row r="122" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="77" t="s">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="F122" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G122" s="77" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="H122" s="77" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="I122" s="77" t="s">
-        <v>1941</v>
+        <v>1937</v>
       </c>
       <c r="J122" s="77" t="s">
         <v>427</v>
@@ -42995,7 +43086,7 @@
         <v>869</v>
       </c>
       <c r="T122" s="77" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="U122" s="77" t="s">
         <v>871</v>
@@ -43009,16 +43100,19 @@
     </row>
     <row r="123" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="77" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="F123" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G123" s="77" t="s">
-        <v>1946</v>
+        <v>1942</v>
+      </c>
+      <c r="H123" s="77" t="s">
+        <v>1943</v>
       </c>
       <c r="I123" s="77" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="J123" s="77" t="s">
         <v>427</v>
@@ -43030,7 +43124,7 @@
         <v>869</v>
       </c>
       <c r="T123" s="77" t="s">
-        <v>1947</v>
+        <v>1944</v>
       </c>
       <c r="U123" s="77" t="s">
         <v>871</v>
@@ -43043,17 +43137,39 @@
       </c>
     </row>
     <row r="124" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="77"/>
-      <c r="F124" s="77"/>
-      <c r="G124" s="77"/>
-      <c r="I124" s="77"/>
-      <c r="J124" s="77"/>
-      <c r="K124" s="77"/>
-      <c r="P124" s="77"/>
-      <c r="S124" s="77"/>
-      <c r="U124" s="77"/>
-      <c r="V124" s="78"/>
-      <c r="W124" s="77"/>
+      <c r="A124" s="77" t="s">
+        <v>1945</v>
+      </c>
+      <c r="F124" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G124" s="77" t="s">
+        <v>1946</v>
+      </c>
+      <c r="I124" s="77" t="s">
+        <v>1945</v>
+      </c>
+      <c r="J124" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="K124" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="S124" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T124" s="77" t="s">
+        <v>1947</v>
+      </c>
+      <c r="U124" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V124" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W124" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="125" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="77"/>
@@ -43069,55 +43185,55 @@
       <c r="W125" s="77"/>
     </row>
     <row r="126" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="77" t="s">
+      <c r="A126" s="77"/>
+      <c r="F126" s="77"/>
+      <c r="G126" s="77"/>
+      <c r="I126" s="77"/>
+      <c r="J126" s="77"/>
+      <c r="K126" s="77"/>
+      <c r="P126" s="77"/>
+      <c r="S126" s="77"/>
+      <c r="U126" s="77"/>
+      <c r="V126" s="78"/>
+      <c r="W126" s="77"/>
+    </row>
+    <row r="127" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A127" s="77" t="s">
         <v>2158</v>
       </c>
-      <c r="F126" s="77" t="s">
+      <c r="F127" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G126" s="77" t="s">
+      <c r="G127" s="77" t="s">
         <v>1880</v>
       </c>
-      <c r="I126" s="77" t="s">
+      <c r="I127" s="77" t="s">
         <v>2158</v>
       </c>
-      <c r="J126" s="77" t="s">
+      <c r="J127" s="77" t="s">
         <v>395</v>
       </c>
-      <c r="K126" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P126" s="77" t="s">
+      <c r="K127" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P127" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="S126" s="77" t="s">
+      <c r="S127" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T126" s="75">
+      <c r="T127" s="75">
         <v>2</v>
       </c>
-      <c r="U126" s="77" t="s">
+      <c r="U127" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V126" s="78" t="s">
+      <c r="V127" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W126" s="77" t="s">
+      <c r="W127" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="127" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="77"/>
-      <c r="F127" s="77"/>
-      <c r="G127" s="77"/>
-      <c r="I127" s="77"/>
-      <c r="J127" s="77"/>
-      <c r="K127" s="77"/>
-      <c r="P127" s="77"/>
-      <c r="S127" s="77"/>
-      <c r="U127" s="77"/>
-      <c r="V127" s="78"/>
-      <c r="W127" s="77"/>
     </row>
     <row r="128" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="77"/>
@@ -43133,58 +43249,33 @@
       <c r="W128" s="77"/>
     </row>
     <row r="129" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="77" t="s">
-        <v>2174</v>
-      </c>
-      <c r="F129" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G129" s="77" t="s">
-        <v>1875</v>
-      </c>
-      <c r="H129" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I129" s="77" t="s">
-        <v>2174</v>
-      </c>
-      <c r="J129" s="77" t="s">
-        <v>2170</v>
-      </c>
-      <c r="K129" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P129" s="77" t="s">
-        <v>246</v>
-      </c>
-      <c r="S129" s="77" t="s">
-        <v>842</v>
-      </c>
-      <c r="T129" s="75">
-        <v>10</v>
-      </c>
-      <c r="U129" s="77" t="s">
-        <v>1774</v>
-      </c>
-      <c r="V129" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W129" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A129" s="77"/>
+      <c r="F129" s="77"/>
+      <c r="G129" s="77"/>
+      <c r="I129" s="77"/>
+      <c r="J129" s="77"/>
+      <c r="K129" s="77"/>
+      <c r="P129" s="77"/>
+      <c r="S129" s="77"/>
+      <c r="U129" s="77"/>
+      <c r="V129" s="78"/>
+      <c r="W129" s="77"/>
     </row>
     <row r="130" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="77" t="s">
-        <v>2824</v>
+        <v>2174</v>
       </c>
       <c r="F130" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G130" s="77" t="s">
-        <v>1938</v>
+        <v>1875</v>
+      </c>
+      <c r="H130" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I130" s="77" t="s">
-        <v>2824</v>
+        <v>2174</v>
       </c>
       <c r="J130" s="77" t="s">
         <v>2170</v>
@@ -43198,8 +43289,8 @@
       <c r="S130" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T130" s="75" t="s">
-        <v>2826</v>
+      <c r="T130" s="75">
+        <v>10</v>
       </c>
       <c r="U130" s="77" t="s">
         <v>1774</v>
@@ -43212,17 +43303,42 @@
       </c>
     </row>
     <row r="131" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="77"/>
-      <c r="F131" s="77"/>
-      <c r="G131" s="77"/>
-      <c r="I131" s="77"/>
-      <c r="J131" s="77"/>
-      <c r="K131" s="77"/>
-      <c r="P131" s="77"/>
-      <c r="S131" s="77"/>
-      <c r="U131" s="77"/>
-      <c r="V131" s="78"/>
-      <c r="W131" s="77"/>
+      <c r="A131" s="77" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F131" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G131" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I131" s="77" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J131" s="77" t="s">
+        <v>2170</v>
+      </c>
+      <c r="K131" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P131" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="S131" s="77" t="s">
+        <v>842</v>
+      </c>
+      <c r="T131" s="75" t="s">
+        <v>2826</v>
+      </c>
+      <c r="U131" s="77" t="s">
+        <v>1774</v>
+      </c>
+      <c r="V131" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W131" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="132" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="77"/>
@@ -43238,55 +43354,55 @@
       <c r="W132" s="77"/>
     </row>
     <row r="133" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="77" t="s">
+      <c r="A133" s="77"/>
+      <c r="F133" s="77"/>
+      <c r="G133" s="77"/>
+      <c r="I133" s="77"/>
+      <c r="J133" s="77"/>
+      <c r="K133" s="77"/>
+      <c r="P133" s="77"/>
+      <c r="S133" s="77"/>
+      <c r="U133" s="77"/>
+      <c r="V133" s="78"/>
+      <c r="W133" s="77"/>
+    </row>
+    <row r="134" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A134" s="77" t="s">
         <v>2173</v>
       </c>
-      <c r="F133" s="77" t="s">
+      <c r="F134" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G133" s="77" t="s">
+      <c r="G134" s="77" t="s">
         <v>891</v>
       </c>
-      <c r="I133" s="77" t="s">
+      <c r="I134" s="77" t="s">
         <v>2173</v>
       </c>
-      <c r="J133" s="77" t="s">
+      <c r="J134" s="77" t="s">
         <v>2171</v>
       </c>
-      <c r="K133" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P133" s="77" t="s">
+      <c r="K134" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P134" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="S133" s="77" t="s">
+      <c r="S134" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T133" s="75" t="s">
+      <c r="T134" s="75" t="s">
         <v>2172</v>
       </c>
-      <c r="U133" s="77" t="s">
+      <c r="U134" s="77" t="s">
         <v>1774</v>
       </c>
-      <c r="V133" s="78" t="s">
+      <c r="V134" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W133" s="77" t="s">
+      <c r="W134" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="134" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="77"/>
-      <c r="F134" s="77"/>
-      <c r="G134" s="77"/>
-      <c r="I134" s="77"/>
-      <c r="J134" s="77"/>
-      <c r="K134" s="77"/>
-      <c r="P134" s="77"/>
-      <c r="S134" s="77"/>
-      <c r="U134" s="77"/>
-      <c r="V134" s="78"/>
-      <c r="W134" s="77"/>
     </row>
     <row r="135" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="77"/>
@@ -43302,55 +43418,55 @@
       <c r="W135" s="77"/>
     </row>
     <row r="136" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="77" t="s">
+      <c r="A136" s="77"/>
+      <c r="F136" s="77"/>
+      <c r="G136" s="77"/>
+      <c r="I136" s="77"/>
+      <c r="J136" s="77"/>
+      <c r="K136" s="77"/>
+      <c r="P136" s="77"/>
+      <c r="S136" s="77"/>
+      <c r="U136" s="77"/>
+      <c r="V136" s="78"/>
+      <c r="W136" s="77"/>
+    </row>
+    <row r="137" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A137" s="77" t="s">
         <v>2208</v>
       </c>
-      <c r="F136" s="77" t="s">
+      <c r="F137" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G136" s="77" t="s">
+      <c r="G137" s="77" t="s">
         <v>1868</v>
       </c>
-      <c r="I136" s="77" t="s">
+      <c r="I137" s="77" t="s">
         <v>2208</v>
       </c>
-      <c r="J136" s="77" t="s">
+      <c r="J137" s="77" t="s">
         <v>1927</v>
       </c>
-      <c r="K136" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P136" s="77" t="s">
+      <c r="K137" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P137" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="S136" s="77" t="s">
+      <c r="S137" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T136" s="75">
+      <c r="T137" s="75">
         <v>3</v>
       </c>
-      <c r="U136" s="77" t="s">
+      <c r="U137" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V136" s="78" t="s">
+      <c r="V137" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W136" s="77" t="s">
+      <c r="W137" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="137" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="77"/>
-      <c r="F137" s="77"/>
-      <c r="G137" s="77"/>
-      <c r="I137" s="77"/>
-      <c r="J137" s="77"/>
-      <c r="K137" s="77"/>
-      <c r="P137" s="77"/>
-      <c r="S137" s="77"/>
-      <c r="U137" s="77"/>
-      <c r="V137" s="78"/>
-      <c r="W137" s="77"/>
     </row>
     <row r="138" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="77"/>
@@ -43366,58 +43482,33 @@
       <c r="W138" s="77"/>
     </row>
     <row r="139" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="77" t="s">
-        <v>2179</v>
-      </c>
-      <c r="F139" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G139" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="H139" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I139" s="77" t="s">
-        <v>2180</v>
-      </c>
-      <c r="J139" s="77" t="s">
-        <v>2175</v>
-      </c>
-      <c r="K139" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P139" s="77" t="s">
-        <v>246</v>
-      </c>
-      <c r="S139" s="77" t="s">
-        <v>842</v>
-      </c>
-      <c r="T139" s="75">
-        <v>10</v>
-      </c>
-      <c r="U139" s="77" t="s">
-        <v>1774</v>
-      </c>
-      <c r="V139" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W139" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A139" s="77"/>
+      <c r="F139" s="77"/>
+      <c r="G139" s="77"/>
+      <c r="I139" s="77"/>
+      <c r="J139" s="77"/>
+      <c r="K139" s="77"/>
+      <c r="P139" s="77"/>
+      <c r="S139" s="77"/>
+      <c r="U139" s="77"/>
+      <c r="V139" s="78"/>
+      <c r="W139" s="77"/>
     </row>
     <row r="140" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="77" t="s">
-        <v>2823</v>
+        <v>2179</v>
       </c>
       <c r="F140" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G140" s="77" t="s">
-        <v>1938</v>
+        <v>891</v>
+      </c>
+      <c r="H140" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I140" s="77" t="s">
-        <v>2824</v>
+        <v>2180</v>
       </c>
       <c r="J140" s="77" t="s">
         <v>2175</v>
@@ -43431,8 +43522,8 @@
       <c r="S140" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T140" s="75" t="s">
-        <v>2825</v>
+      <c r="T140" s="75">
+        <v>10</v>
       </c>
       <c r="U140" s="77" t="s">
         <v>1774</v>
@@ -43445,17 +43536,42 @@
       </c>
     </row>
     <row r="141" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="77"/>
-      <c r="F141" s="77"/>
-      <c r="G141" s="77"/>
-      <c r="I141" s="77"/>
-      <c r="J141" s="77"/>
-      <c r="K141" s="77"/>
-      <c r="P141" s="77"/>
-      <c r="S141" s="77"/>
-      <c r="U141" s="77"/>
-      <c r="V141" s="78"/>
-      <c r="W141" s="77"/>
+      <c r="A141" s="77" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F141" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G141" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I141" s="77" t="s">
+        <v>2824</v>
+      </c>
+      <c r="J141" s="77" t="s">
+        <v>2175</v>
+      </c>
+      <c r="K141" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P141" s="77" t="s">
+        <v>246</v>
+      </c>
+      <c r="S141" s="77" t="s">
+        <v>842</v>
+      </c>
+      <c r="T141" s="75" t="s">
+        <v>2825</v>
+      </c>
+      <c r="U141" s="77" t="s">
+        <v>1774</v>
+      </c>
+      <c r="V141" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W141" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="142" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="77"/>
@@ -43471,55 +43587,55 @@
       <c r="W142" s="77"/>
     </row>
     <row r="143" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="77" t="s">
+      <c r="A143" s="77"/>
+      <c r="F143" s="77"/>
+      <c r="G143" s="77"/>
+      <c r="I143" s="77"/>
+      <c r="J143" s="77"/>
+      <c r="K143" s="77"/>
+      <c r="P143" s="77"/>
+      <c r="S143" s="77"/>
+      <c r="U143" s="77"/>
+      <c r="V143" s="78"/>
+      <c r="W143" s="77"/>
+    </row>
+    <row r="144" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A144" s="77" t="s">
         <v>2177</v>
       </c>
-      <c r="F143" s="77" t="s">
+      <c r="F144" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G143" s="77" t="s">
+      <c r="G144" s="77" t="s">
         <v>2153</v>
       </c>
-      <c r="I143" s="77" t="s">
+      <c r="I144" s="77" t="s">
         <v>2178</v>
       </c>
-      <c r="J143" s="77" t="s">
+      <c r="J144" s="77" t="s">
         <v>2176</v>
       </c>
-      <c r="K143" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P143" s="77" t="s">
+      <c r="K144" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P144" s="77" t="s">
         <v>246</v>
       </c>
-      <c r="S143" s="77" t="s">
+      <c r="S144" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T143" s="75" t="s">
+      <c r="T144" s="75" t="s">
         <v>2172</v>
       </c>
-      <c r="U143" s="77" t="s">
+      <c r="U144" s="77" t="s">
         <v>1774</v>
       </c>
-      <c r="V143" s="78" t="s">
+      <c r="V144" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W143" s="77" t="s">
+      <c r="W144" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="144" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="77"/>
-      <c r="F144" s="77"/>
-      <c r="G144" s="77"/>
-      <c r="I144" s="77"/>
-      <c r="J144" s="77"/>
-      <c r="K144" s="77"/>
-      <c r="P144" s="77"/>
-      <c r="S144" s="77"/>
-      <c r="U144" s="77"/>
-      <c r="V144" s="78"/>
-      <c r="W144" s="77"/>
     </row>
     <row r="145" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="77"/>
@@ -43535,61 +43651,33 @@
       <c r="W145" s="77"/>
     </row>
     <row r="146" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="77" t="s">
-        <v>2154</v>
-      </c>
-      <c r="F146" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G146" s="77" t="s">
-        <v>2153</v>
-      </c>
-      <c r="H146" s="75" t="s">
-        <v>1893</v>
-      </c>
-      <c r="I146" s="77" t="s">
-        <v>2154</v>
-      </c>
-      <c r="J146" s="77" t="s">
-        <v>1928</v>
-      </c>
-      <c r="K146" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P146" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S146" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T146" s="75" t="s">
-        <v>2155</v>
-      </c>
-      <c r="U146" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V146" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W146" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A146" s="77"/>
+      <c r="F146" s="77"/>
+      <c r="G146" s="77"/>
+      <c r="I146" s="77"/>
+      <c r="J146" s="77"/>
+      <c r="K146" s="77"/>
+      <c r="P146" s="77"/>
+      <c r="S146" s="77"/>
+      <c r="U146" s="77"/>
+      <c r="V146" s="78"/>
+      <c r="W146" s="77"/>
     </row>
     <row r="147" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="77" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="F147" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G147" s="77" t="s">
-        <v>1934</v>
-      </c>
-      <c r="H147" s="77" t="s">
-        <v>1935</v>
+        <v>2153</v>
+      </c>
+      <c r="H147" s="75" t="s">
+        <v>1893</v>
       </c>
       <c r="I147" s="77" t="s">
-        <v>2156</v>
+        <v>2154</v>
       </c>
       <c r="J147" s="77" t="s">
         <v>1928</v>
@@ -43604,7 +43692,7 @@
         <v>869</v>
       </c>
       <c r="T147" s="75" t="s">
-        <v>2157</v>
+        <v>2155</v>
       </c>
       <c r="U147" s="77" t="s">
         <v>871</v>
@@ -43618,16 +43706,19 @@
     </row>
     <row r="148" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="77" t="s">
-        <v>2628</v>
+        <v>2156</v>
       </c>
       <c r="F148" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G148" s="77" t="s">
-        <v>1938</v>
+        <v>1934</v>
+      </c>
+      <c r="H148" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I148" s="77" t="s">
-        <v>2628</v>
+        <v>2156</v>
       </c>
       <c r="J148" s="77" t="s">
         <v>1928</v>
@@ -43642,7 +43733,7 @@
         <v>869</v>
       </c>
       <c r="T148" s="75" t="s">
-        <v>2629</v>
+        <v>2157</v>
       </c>
       <c r="U148" s="77" t="s">
         <v>871</v>
@@ -43655,17 +43746,42 @@
       </c>
     </row>
     <row r="149" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="77"/>
-      <c r="F149" s="77"/>
-      <c r="G149" s="77"/>
-      <c r="I149" s="77"/>
-      <c r="J149" s="77"/>
-      <c r="K149" s="77"/>
-      <c r="P149" s="77"/>
-      <c r="S149" s="77"/>
-      <c r="U149" s="77"/>
-      <c r="V149" s="78"/>
-      <c r="W149" s="77"/>
+      <c r="A149" s="77" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F149" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G149" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I149" s="77" t="s">
+        <v>2628</v>
+      </c>
+      <c r="J149" s="77" t="s">
+        <v>1928</v>
+      </c>
+      <c r="K149" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P149" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S149" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T149" s="75" t="s">
+        <v>2629</v>
+      </c>
+      <c r="U149" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V149" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W149" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="150" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="77"/>
@@ -43681,55 +43797,55 @@
       <c r="W150" s="77"/>
     </row>
     <row r="151" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="77" t="s">
+      <c r="A151" s="77"/>
+      <c r="F151" s="77"/>
+      <c r="G151" s="77"/>
+      <c r="I151" s="77"/>
+      <c r="J151" s="77"/>
+      <c r="K151" s="77"/>
+      <c r="P151" s="77"/>
+      <c r="S151" s="77"/>
+      <c r="U151" s="77"/>
+      <c r="V151" s="78"/>
+      <c r="W151" s="77"/>
+    </row>
+    <row r="152" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A152" s="77" t="s">
         <v>2827</v>
       </c>
-      <c r="F151" s="77" t="s">
+      <c r="F152" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G151" s="77" t="s">
+      <c r="G152" s="77" t="s">
         <v>1868</v>
       </c>
-      <c r="I151" s="77" t="s">
+      <c r="I152" s="77" t="s">
         <v>2827</v>
       </c>
-      <c r="J151" s="77" t="s">
+      <c r="J152" s="77" t="s">
         <v>2828</v>
       </c>
-      <c r="K151" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P151" s="77" t="s">
+      <c r="K152" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P152" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S151" s="77" t="s">
+      <c r="S152" s="77" t="s">
         <v>842</v>
       </c>
-      <c r="T151" s="75" t="s">
+      <c r="T152" s="75" t="s">
         <v>2829</v>
       </c>
-      <c r="U151" s="82" t="s">
+      <c r="U152" s="82" t="s">
         <v>1772</v>
       </c>
-      <c r="V151" s="78" t="s">
+      <c r="V152" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W151" s="77" t="s">
+      <c r="W152" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="152" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="77"/>
-      <c r="F152" s="77"/>
-      <c r="G152" s="77"/>
-      <c r="I152" s="77"/>
-      <c r="J152" s="77"/>
-      <c r="K152" s="77"/>
-      <c r="P152" s="77"/>
-      <c r="S152" s="77"/>
-      <c r="U152" s="77"/>
-      <c r="V152" s="78"/>
-      <c r="W152" s="77"/>
     </row>
     <row r="153" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="77"/>
@@ -43745,46 +43861,21 @@
       <c r="W153" s="77"/>
     </row>
     <row r="154" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="79" t="s">
-        <v>2183</v>
-      </c>
-      <c r="F154" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G154" s="77" t="s">
-        <v>1851</v>
-      </c>
-      <c r="I154" s="79" t="s">
-        <v>2183</v>
-      </c>
-      <c r="J154" s="79" t="s">
-        <v>318</v>
-      </c>
-      <c r="K154" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="P154" s="77" t="s">
-        <v>239</v>
-      </c>
-      <c r="S154" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T154" s="75">
-        <v>10</v>
-      </c>
-      <c r="U154" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V154" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W154" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A154" s="77"/>
+      <c r="F154" s="77"/>
+      <c r="G154" s="77"/>
+      <c r="I154" s="77"/>
+      <c r="J154" s="77"/>
+      <c r="K154" s="77"/>
+      <c r="P154" s="77"/>
+      <c r="S154" s="77"/>
+      <c r="U154" s="77"/>
+      <c r="V154" s="78"/>
+      <c r="W154" s="77"/>
     </row>
     <row r="155" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="79" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="F155" s="77" t="s">
         <v>76</v>
@@ -43793,10 +43884,10 @@
         <v>1851</v>
       </c>
       <c r="I155" s="79" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="J155" s="79" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K155" s="77" t="s">
         <v>215</v>
@@ -43808,7 +43899,7 @@
         <v>869</v>
       </c>
       <c r="T155" s="75">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="U155" s="77" t="s">
         <v>871</v>
@@ -43822,7 +43913,7 @@
     </row>
     <row r="156" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="79" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="F156" s="77" t="s">
         <v>76</v>
@@ -43831,10 +43922,10 @@
         <v>1851</v>
       </c>
       <c r="I156" s="79" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="J156" s="79" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K156" s="77" t="s">
         <v>215</v>
@@ -43846,7 +43937,7 @@
         <v>869</v>
       </c>
       <c r="T156" s="75">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="U156" s="77" t="s">
         <v>871</v>
@@ -43860,7 +43951,7 @@
     </row>
     <row r="157" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="79" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="F157" s="77" t="s">
         <v>76</v>
@@ -43869,10 +43960,10 @@
         <v>1851</v>
       </c>
       <c r="I157" s="79" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="J157" s="79" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="K157" s="77" t="s">
         <v>215</v>
@@ -43884,7 +43975,7 @@
         <v>869</v>
       </c>
       <c r="T157" s="75">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="U157" s="77" t="s">
         <v>871</v>
@@ -43897,17 +43988,42 @@
       </c>
     </row>
     <row r="158" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="79"/>
-      <c r="F158" s="77"/>
-      <c r="G158" s="77"/>
-      <c r="I158" s="79"/>
-      <c r="J158" s="79"/>
-      <c r="K158" s="77"/>
-      <c r="P158" s="77"/>
-      <c r="S158" s="77"/>
-      <c r="U158" s="77"/>
-      <c r="V158" s="78"/>
-      <c r="W158" s="77"/>
+      <c r="A158" s="79" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F158" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G158" s="77" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I158" s="79" t="s">
+        <v>2186</v>
+      </c>
+      <c r="J158" s="79" t="s">
+        <v>327</v>
+      </c>
+      <c r="K158" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="P158" s="77" t="s">
+        <v>239</v>
+      </c>
+      <c r="S158" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T158" s="75">
+        <v>15</v>
+      </c>
+      <c r="U158" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V158" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W158" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="159" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="79"/>
@@ -43923,61 +44039,33 @@
       <c r="W159" s="77"/>
     </row>
     <row r="160" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="77" t="s">
-        <v>2187</v>
-      </c>
-      <c r="F160" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G160" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="H160" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I160" s="77" t="s">
-        <v>2187</v>
-      </c>
-      <c r="J160" s="77" t="s">
-        <v>466</v>
-      </c>
-      <c r="K160" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O160" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="P160" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S160" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T160" s="75">
-        <v>12</v>
-      </c>
-      <c r="U160" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V160" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W160" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A160" s="79"/>
+      <c r="F160" s="77"/>
+      <c r="G160" s="77"/>
+      <c r="I160" s="79"/>
+      <c r="J160" s="79"/>
+      <c r="K160" s="77"/>
+      <c r="P160" s="77"/>
+      <c r="S160" s="77"/>
+      <c r="U160" s="77"/>
+      <c r="V160" s="78"/>
+      <c r="W160" s="77"/>
     </row>
     <row r="161" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="77" t="s">
-        <v>2630</v>
+        <v>2187</v>
       </c>
       <c r="F161" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G161" s="77" t="s">
-        <v>1938</v>
+        <v>891</v>
+      </c>
+      <c r="H161" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I161" s="77" t="s">
-        <v>2630</v>
+        <v>2187</v>
       </c>
       <c r="J161" s="77" t="s">
         <v>466</v>
@@ -43994,8 +44082,8 @@
       <c r="S161" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T161" s="75" t="s">
-        <v>2631</v>
+      <c r="T161" s="75">
+        <v>12</v>
       </c>
       <c r="U161" s="77" t="s">
         <v>871</v>
@@ -44008,18 +44096,45 @@
       </c>
     </row>
     <row r="162" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="77"/>
-      <c r="F162" s="77"/>
-      <c r="G162" s="77"/>
-      <c r="I162" s="77"/>
-      <c r="J162" s="77"/>
-      <c r="K162" s="77"/>
-      <c r="O162" s="77"/>
-      <c r="P162" s="77"/>
-      <c r="S162" s="77"/>
-      <c r="U162" s="77"/>
-      <c r="V162" s="78"/>
-      <c r="W162" s="77"/>
+      <c r="A162" s="77" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F162" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G162" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I162" s="77" t="s">
+        <v>2630</v>
+      </c>
+      <c r="J162" s="77" t="s">
+        <v>466</v>
+      </c>
+      <c r="K162" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O162" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="P162" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S162" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T162" s="75" t="s">
+        <v>2631</v>
+      </c>
+      <c r="U162" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V162" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W162" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="163" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="77"/>
@@ -44036,61 +44151,34 @@
       <c r="W163" s="77"/>
     </row>
     <row r="164" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="77" t="s">
-        <v>2188</v>
-      </c>
-      <c r="F164" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G164" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="H164" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I164" s="77" t="s">
-        <v>2188</v>
-      </c>
-      <c r="J164" s="77" t="s">
-        <v>470</v>
-      </c>
-      <c r="K164" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O164" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="P164" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S164" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T164" s="75">
-        <v>12</v>
-      </c>
-      <c r="U164" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V164" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W164" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A164" s="77"/>
+      <c r="F164" s="77"/>
+      <c r="G164" s="77"/>
+      <c r="I164" s="77"/>
+      <c r="J164" s="77"/>
+      <c r="K164" s="77"/>
+      <c r="O164" s="77"/>
+      <c r="P164" s="77"/>
+      <c r="S164" s="77"/>
+      <c r="U164" s="77"/>
+      <c r="V164" s="78"/>
+      <c r="W164" s="77"/>
     </row>
     <row r="165" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="77" t="s">
-        <v>2632</v>
+        <v>2188</v>
       </c>
       <c r="F165" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G165" s="77" t="s">
-        <v>1938</v>
+        <v>891</v>
+      </c>
+      <c r="H165" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I165" s="77" t="s">
-        <v>2632</v>
+        <v>2188</v>
       </c>
       <c r="J165" s="77" t="s">
         <v>470</v>
@@ -44107,8 +44195,8 @@
       <c r="S165" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T165" s="75" t="s">
-        <v>2631</v>
+      <c r="T165" s="75">
+        <v>12</v>
       </c>
       <c r="U165" s="77" t="s">
         <v>871</v>
@@ -44121,18 +44209,45 @@
       </c>
     </row>
     <row r="166" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="77"/>
-      <c r="F166" s="77"/>
-      <c r="G166" s="77"/>
-      <c r="I166" s="77"/>
-      <c r="J166" s="77"/>
-      <c r="K166" s="77"/>
-      <c r="O166" s="77"/>
-      <c r="P166" s="77"/>
-      <c r="S166" s="77"/>
-      <c r="U166" s="77"/>
-      <c r="V166" s="78"/>
-      <c r="W166" s="77"/>
+      <c r="A166" s="77" t="s">
+        <v>2632</v>
+      </c>
+      <c r="F166" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G166" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I166" s="77" t="s">
+        <v>2632</v>
+      </c>
+      <c r="J166" s="77" t="s">
+        <v>470</v>
+      </c>
+      <c r="K166" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O166" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="P166" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S166" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T166" s="75" t="s">
+        <v>2631</v>
+      </c>
+      <c r="U166" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V166" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W166" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="167" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" s="77"/>
@@ -44149,62 +44264,62 @@
       <c r="W167" s="77"/>
     </row>
     <row r="168" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="77" t="s">
+      <c r="A168" s="77"/>
+      <c r="F168" s="77"/>
+      <c r="G168" s="77"/>
+      <c r="I168" s="77"/>
+      <c r="J168" s="77"/>
+      <c r="K168" s="77"/>
+      <c r="O168" s="77"/>
+      <c r="P168" s="77"/>
+      <c r="S168" s="77"/>
+      <c r="U168" s="77"/>
+      <c r="V168" s="78"/>
+      <c r="W168" s="77"/>
+    </row>
+    <row r="169" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A169" s="77" t="s">
         <v>2838</v>
       </c>
-      <c r="F168" s="77" t="s">
+      <c r="F169" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G168" s="77" t="s">
+      <c r="G169" s="77" t="s">
         <v>2830</v>
       </c>
-      <c r="H168" s="77" t="s">
+      <c r="H169" s="77" t="s">
         <v>2832</v>
       </c>
-      <c r="I168" s="77" t="s">
+      <c r="I169" s="77" t="s">
         <v>2838</v>
       </c>
-      <c r="J168" s="77" t="s">
+      <c r="J169" s="77" t="s">
         <v>1929</v>
       </c>
-      <c r="K168" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O168" s="77" t="s">
+      <c r="K169" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O169" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="P168" s="77" t="s">
+      <c r="P169" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S168" s="77" t="s">
+      <c r="S169" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T168" s="75">
+      <c r="T169" s="75">
         <v>8</v>
       </c>
-      <c r="U168" s="77" t="s">
+      <c r="U169" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V168" s="78" t="s">
+      <c r="V169" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W168" s="77" t="s">
+      <c r="W169" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="169" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="77"/>
-      <c r="F169" s="77"/>
-      <c r="G169" s="77"/>
-      <c r="I169" s="77"/>
-      <c r="J169" s="77"/>
-      <c r="K169" s="77"/>
-      <c r="O169" s="77"/>
-      <c r="P169" s="77"/>
-      <c r="S169" s="77"/>
-      <c r="U169" s="77"/>
-      <c r="V169" s="78"/>
-      <c r="W169" s="77"/>
     </row>
     <row r="170" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" s="77"/>
@@ -44221,50 +44336,22 @@
       <c r="W170" s="77"/>
     </row>
     <row r="171" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="77" t="s">
-        <v>2839</v>
-      </c>
-      <c r="F171" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G171" s="77" t="s">
-        <v>1938</v>
-      </c>
-      <c r="H171" s="77"/>
-      <c r="I171" s="77" t="s">
-        <v>2839</v>
-      </c>
-      <c r="J171" s="77" t="s">
-        <v>2841</v>
-      </c>
-      <c r="K171" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O171" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="P171" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S171" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T171" s="75" t="s">
-        <v>1947</v>
-      </c>
-      <c r="U171" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V171" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W171" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A171" s="77"/>
+      <c r="F171" s="77"/>
+      <c r="G171" s="77"/>
+      <c r="I171" s="77"/>
+      <c r="J171" s="77"/>
+      <c r="K171" s="77"/>
+      <c r="O171" s="77"/>
+      <c r="P171" s="77"/>
+      <c r="S171" s="77"/>
+      <c r="U171" s="77"/>
+      <c r="V171" s="78"/>
+      <c r="W171" s="77"/>
     </row>
     <row r="172" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="77" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="F172" s="77" t="s">
         <v>76</v>
@@ -44274,10 +44361,10 @@
       </c>
       <c r="H172" s="77"/>
       <c r="I172" s="77" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="J172" s="77" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="K172" s="77" t="s">
         <v>215</v>
@@ -44292,7 +44379,7 @@
         <v>869</v>
       </c>
       <c r="T172" s="75" t="s">
-        <v>2837</v>
+        <v>1947</v>
       </c>
       <c r="U172" s="77" t="s">
         <v>871</v>
@@ -44305,18 +44392,46 @@
       </c>
     </row>
     <row r="173" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="77"/>
-      <c r="F173" s="77"/>
-      <c r="G173" s="77"/>
-      <c r="I173" s="77"/>
-      <c r="J173" s="77"/>
-      <c r="K173" s="77"/>
-      <c r="O173" s="77"/>
-      <c r="P173" s="77"/>
-      <c r="S173" s="77"/>
-      <c r="U173" s="77"/>
-      <c r="V173" s="78"/>
-      <c r="W173" s="77"/>
+      <c r="A173" s="77" t="s">
+        <v>2840</v>
+      </c>
+      <c r="F173" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G173" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H173" s="77"/>
+      <c r="I173" s="77" t="s">
+        <v>2840</v>
+      </c>
+      <c r="J173" s="77" t="s">
+        <v>2842</v>
+      </c>
+      <c r="K173" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O173" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="P173" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S173" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T173" s="75" t="s">
+        <v>2837</v>
+      </c>
+      <c r="U173" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V173" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W173" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="174" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" s="77"/>
@@ -44333,61 +44448,34 @@
       <c r="W174" s="77"/>
     </row>
     <row r="175" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="77" t="s">
-        <v>2189</v>
-      </c>
-      <c r="F175" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G175" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="H175" s="77" t="s">
-        <v>1935</v>
-      </c>
-      <c r="I175" s="77" t="s">
-        <v>2189</v>
-      </c>
-      <c r="J175" s="77" t="s">
-        <v>489</v>
-      </c>
-      <c r="K175" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O175" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="P175" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S175" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T175" s="75">
-        <v>12</v>
-      </c>
-      <c r="U175" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V175" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W175" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A175" s="77"/>
+      <c r="F175" s="77"/>
+      <c r="G175" s="77"/>
+      <c r="I175" s="77"/>
+      <c r="J175" s="77"/>
+      <c r="K175" s="77"/>
+      <c r="O175" s="77"/>
+      <c r="P175" s="77"/>
+      <c r="S175" s="77"/>
+      <c r="U175" s="77"/>
+      <c r="V175" s="78"/>
+      <c r="W175" s="77"/>
     </row>
     <row r="176" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" s="77" t="s">
-        <v>2633</v>
+        <v>2189</v>
       </c>
       <c r="F176" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G176" s="77" t="s">
-        <v>1938</v>
+        <v>891</v>
+      </c>
+      <c r="H176" s="77" t="s">
+        <v>1935</v>
       </c>
       <c r="I176" s="77" t="s">
-        <v>2633</v>
+        <v>2189</v>
       </c>
       <c r="J176" s="77" t="s">
         <v>489</v>
@@ -44404,8 +44492,8 @@
       <c r="S176" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T176" s="75" t="s">
-        <v>2631</v>
+      <c r="T176" s="75">
+        <v>12</v>
       </c>
       <c r="U176" s="77" t="s">
         <v>871</v>
@@ -44418,18 +44506,45 @@
       </c>
     </row>
     <row r="177" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="77"/>
-      <c r="F177" s="77"/>
-      <c r="G177" s="77"/>
-      <c r="I177" s="77"/>
-      <c r="J177" s="77"/>
-      <c r="K177" s="77"/>
-      <c r="O177" s="77"/>
-      <c r="P177" s="77"/>
-      <c r="S177" s="77"/>
-      <c r="U177" s="77"/>
-      <c r="V177" s="78"/>
-      <c r="W177" s="77"/>
+      <c r="A177" s="77" t="s">
+        <v>2633</v>
+      </c>
+      <c r="F177" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G177" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="I177" s="77" t="s">
+        <v>2633</v>
+      </c>
+      <c r="J177" s="77" t="s">
+        <v>489</v>
+      </c>
+      <c r="K177" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O177" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="P177" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S177" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T177" s="75" t="s">
+        <v>2631</v>
+      </c>
+      <c r="U177" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V177" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W177" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="178" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="77"/>
@@ -44446,63 +44561,62 @@
       <c r="W178" s="77"/>
     </row>
     <row r="179" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="77" t="s">
+      <c r="A179" s="77"/>
+      <c r="F179" s="77"/>
+      <c r="G179" s="77"/>
+      <c r="I179" s="77"/>
+      <c r="J179" s="77"/>
+      <c r="K179" s="77"/>
+      <c r="O179" s="77"/>
+      <c r="P179" s="77"/>
+      <c r="S179" s="77"/>
+      <c r="U179" s="77"/>
+      <c r="V179" s="78"/>
+      <c r="W179" s="77"/>
+    </row>
+    <row r="180" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A180" s="77" t="s">
         <v>2831</v>
       </c>
-      <c r="F179" s="77" t="s">
+      <c r="F180" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G179" s="77" t="s">
+      <c r="G180" s="77" t="s">
         <v>2830</v>
       </c>
-      <c r="H179" s="77" t="s">
+      <c r="H180" s="77" t="s">
         <v>2832</v>
       </c>
-      <c r="I179" s="77" t="s">
+      <c r="I180" s="77" t="s">
         <v>2831</v>
       </c>
-      <c r="J179" s="77" t="s">
+      <c r="J180" s="77" t="s">
         <v>1930</v>
       </c>
-      <c r="K179" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O179" s="77" t="s">
+      <c r="K180" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O180" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="P179" s="77" t="s">
+      <c r="P180" s="77" t="s">
         <v>911</v>
       </c>
-      <c r="S179" s="77" t="s">
+      <c r="S180" s="77" t="s">
         <v>869</v>
       </c>
-      <c r="T179" s="75">
+      <c r="T180" s="75">
         <v>8</v>
       </c>
-      <c r="U179" s="77" t="s">
+      <c r="U180" s="77" t="s">
         <v>871</v>
       </c>
-      <c r="V179" s="78" t="s">
+      <c r="V180" s="78" t="s">
         <v>2147</v>
       </c>
-      <c r="W179" s="77" t="s">
+      <c r="W180" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="180" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="77"/>
-      <c r="F180" s="77"/>
-      <c r="G180" s="77"/>
-      <c r="H180" s="77"/>
-      <c r="I180" s="77"/>
-      <c r="J180" s="77"/>
-      <c r="K180" s="77"/>
-      <c r="O180" s="77"/>
-      <c r="P180" s="77"/>
-      <c r="S180" s="77"/>
-      <c r="U180" s="77"/>
-      <c r="V180" s="78"/>
-      <c r="W180" s="77"/>
     </row>
     <row r="181" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="77"/>
@@ -44520,50 +44634,23 @@
       <c r="W181" s="77"/>
     </row>
     <row r="182" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="77" t="s">
-        <v>2833</v>
-      </c>
-      <c r="F182" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G182" s="77" t="s">
-        <v>1938</v>
-      </c>
+      <c r="A182" s="77"/>
+      <c r="F182" s="77"/>
+      <c r="G182" s="77"/>
       <c r="H182" s="77"/>
-      <c r="I182" s="77" t="s">
-        <v>2833</v>
-      </c>
-      <c r="J182" s="77" t="s">
-        <v>2834</v>
-      </c>
-      <c r="K182" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="O182" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="P182" s="77" t="s">
-        <v>911</v>
-      </c>
-      <c r="S182" s="77" t="s">
-        <v>869</v>
-      </c>
-      <c r="T182" s="75" t="s">
-        <v>1947</v>
-      </c>
-      <c r="U182" s="77" t="s">
-        <v>871</v>
-      </c>
-      <c r="V182" s="78" t="s">
-        <v>2147</v>
-      </c>
-      <c r="W182" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="I182" s="77"/>
+      <c r="J182" s="77"/>
+      <c r="K182" s="77"/>
+      <c r="O182" s="77"/>
+      <c r="P182" s="77"/>
+      <c r="S182" s="77"/>
+      <c r="U182" s="77"/>
+      <c r="V182" s="78"/>
+      <c r="W182" s="77"/>
     </row>
     <row r="183" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="77" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="F183" s="77" t="s">
         <v>76</v>
@@ -44573,10 +44660,10 @@
       </c>
       <c r="H183" s="77"/>
       <c r="I183" s="77" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="J183" s="77" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
       <c r="K183" s="77" t="s">
         <v>215</v>
@@ -44591,7 +44678,7 @@
         <v>869</v>
       </c>
       <c r="T183" s="75" t="s">
-        <v>2837</v>
+        <v>1947</v>
       </c>
       <c r="U183" s="77" t="s">
         <v>871</v>
@@ -44604,18 +44691,46 @@
       </c>
     </row>
     <row r="184" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="77"/>
-      <c r="F184" s="77"/>
-      <c r="G184" s="77"/>
-      <c r="I184" s="77"/>
-      <c r="J184" s="77"/>
-      <c r="K184" s="77"/>
-      <c r="O184" s="77"/>
-      <c r="P184" s="77"/>
-      <c r="S184" s="77"/>
-      <c r="U184" s="77"/>
-      <c r="V184" s="78"/>
-      <c r="W184" s="77"/>
+      <c r="A184" s="77" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F184" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G184" s="77" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H184" s="77"/>
+      <c r="I184" s="77" t="s">
+        <v>2835</v>
+      </c>
+      <c r="J184" s="77" t="s">
+        <v>2836</v>
+      </c>
+      <c r="K184" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="O184" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="P184" s="77" t="s">
+        <v>911</v>
+      </c>
+      <c r="S184" s="77" t="s">
+        <v>869</v>
+      </c>
+      <c r="T184" s="75" t="s">
+        <v>2837</v>
+      </c>
+      <c r="U184" s="77" t="s">
+        <v>871</v>
+      </c>
+      <c r="V184" s="78" t="s">
+        <v>2147</v>
+      </c>
+      <c r="W184" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="185" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="77"/>
@@ -44624,56 +44739,29 @@
       <c r="I185" s="77"/>
       <c r="J185" s="77"/>
       <c r="K185" s="77"/>
-      <c r="M185" s="77"/>
+      <c r="O185" s="77"/>
+      <c r="P185" s="77"/>
       <c r="S185" s="77"/>
-      <c r="T185" s="77"/>
       <c r="U185" s="77"/>
       <c r="V185" s="78"/>
+      <c r="W185" s="77"/>
     </row>
     <row r="186" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A186" s="77" t="s">
-        <v>3044</v>
-      </c>
-      <c r="F186" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="G186" s="77" t="s">
-        <v>891</v>
-      </c>
-      <c r="I186" s="77" t="s">
-        <v>3044</v>
-      </c>
-      <c r="J186" s="77" t="s">
-        <v>3046</v>
-      </c>
-      <c r="K186" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="L186" s="77"/>
-      <c r="M186" s="80"/>
-      <c r="N186" s="77"/>
-      <c r="Q186" s="81" t="s">
-        <v>292</v>
-      </c>
-      <c r="S186" s="77" t="s">
-        <v>861</v>
-      </c>
-      <c r="T186" s="75" t="s">
-        <v>3042</v>
-      </c>
-      <c r="U186" s="77" t="s">
-        <v>1727</v>
-      </c>
-      <c r="V186" s="78" t="s">
-        <v>2822</v>
-      </c>
-      <c r="W186" s="77" t="s">
-        <v>830</v>
-      </c>
+      <c r="A186" s="77"/>
+      <c r="F186" s="77"/>
+      <c r="G186" s="77"/>
+      <c r="I186" s="77"/>
+      <c r="J186" s="77"/>
+      <c r="K186" s="77"/>
+      <c r="M186" s="77"/>
+      <c r="S186" s="77"/>
+      <c r="T186" s="77"/>
+      <c r="U186" s="77"/>
+      <c r="V186" s="78"/>
     </row>
     <row r="187" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="77" t="s">
-        <v>3045</v>
+        <v>3037</v>
       </c>
       <c r="F187" s="77" t="s">
         <v>76</v>
@@ -44682,10 +44770,10 @@
         <v>891</v>
       </c>
       <c r="I187" s="77" t="s">
-        <v>3045</v>
+        <v>3037</v>
       </c>
       <c r="J187" s="77" t="s">
-        <v>3047</v>
+        <v>3039</v>
       </c>
       <c r="K187" s="77" t="s">
         <v>215</v>
@@ -44700,7 +44788,7 @@
         <v>861</v>
       </c>
       <c r="T187" s="75" t="s">
-        <v>3040</v>
+        <v>3035</v>
       </c>
       <c r="U187" s="77" t="s">
         <v>1727</v>
@@ -44714,7 +44802,7 @@
     </row>
     <row r="188" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="77" t="s">
-        <v>3050</v>
+        <v>3038</v>
       </c>
       <c r="F188" s="77" t="s">
         <v>76</v>
@@ -44723,10 +44811,10 @@
         <v>891</v>
       </c>
       <c r="I188" s="77" t="s">
-        <v>3050</v>
+        <v>3038</v>
       </c>
       <c r="J188" s="77" t="s">
-        <v>3049</v>
+        <v>3040</v>
       </c>
       <c r="K188" s="77" t="s">
         <v>215</v>
@@ -44741,7 +44829,7 @@
         <v>861</v>
       </c>
       <c r="T188" s="75" t="s">
-        <v>3041</v>
+        <v>3033</v>
       </c>
       <c r="U188" s="77" t="s">
         <v>1727</v>
@@ -44755,7 +44843,7 @@
     </row>
     <row r="189" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="77" t="s">
-        <v>3051</v>
+        <v>3043</v>
       </c>
       <c r="F189" s="77" t="s">
         <v>76</v>
@@ -44764,10 +44852,10 @@
         <v>891</v>
       </c>
       <c r="I189" s="77" t="s">
-        <v>3051</v>
+        <v>3043</v>
       </c>
       <c r="J189" s="77" t="s">
-        <v>3048</v>
+        <v>3042</v>
       </c>
       <c r="K189" s="77" t="s">
         <v>215</v>
@@ -44782,7 +44870,7 @@
         <v>861</v>
       </c>
       <c r="T189" s="75" t="s">
-        <v>3043</v>
+        <v>3034</v>
       </c>
       <c r="U189" s="77" t="s">
         <v>1727</v>
@@ -44795,21 +44883,45 @@
       </c>
     </row>
     <row r="190" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A190" s="77"/>
-      <c r="F190" s="77"/>
-      <c r="G190" s="77"/>
-      <c r="I190" s="77"/>
-      <c r="J190" s="77"/>
-      <c r="K190" s="77"/>
+      <c r="A190" s="77" t="s">
+        <v>3044</v>
+      </c>
+      <c r="F190" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="G190" s="77" t="s">
+        <v>891</v>
+      </c>
+      <c r="I190" s="77" t="s">
+        <v>3044</v>
+      </c>
+      <c r="J190" s="77" t="s">
+        <v>3041</v>
+      </c>
+      <c r="K190" s="77" t="s">
+        <v>215</v>
+      </c>
       <c r="L190" s="77"/>
       <c r="M190" s="80"/>
       <c r="N190" s="77"/>
-      <c r="Q190" s="81"/>
-      <c r="S190" s="77"/>
-      <c r="T190" s="77"/>
-      <c r="U190" s="77"/>
-      <c r="V190" s="78"/>
-      <c r="W190" s="77"/>
+      <c r="Q190" s="81" t="s">
+        <v>292</v>
+      </c>
+      <c r="S190" s="77" t="s">
+        <v>861</v>
+      </c>
+      <c r="T190" s="75" t="s">
+        <v>3036</v>
+      </c>
+      <c r="U190" s="77" t="s">
+        <v>1727</v>
+      </c>
+      <c r="V190" s="78" t="s">
+        <v>2822</v>
+      </c>
+      <c r="W190" s="77" t="s">
+        <v>830</v>
+      </c>
     </row>
     <row r="191" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" s="77"/>
@@ -44829,55 +44941,59 @@
       <c r="W191" s="77"/>
     </row>
     <row r="192" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A192" s="77" t="s">
+      <c r="A192" s="77"/>
+      <c r="F192" s="77"/>
+      <c r="G192" s="77"/>
+      <c r="I192" s="77"/>
+      <c r="J192" s="77"/>
+      <c r="K192" s="77"/>
+      <c r="L192" s="77"/>
+      <c r="M192" s="80"/>
+      <c r="N192" s="77"/>
+      <c r="Q192" s="81"/>
+      <c r="S192" s="77"/>
+      <c r="T192" s="77"/>
+      <c r="U192" s="77"/>
+      <c r="V192" s="78"/>
+      <c r="W192" s="77"/>
+    </row>
+    <row r="193" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A193" s="77" t="s">
         <v>1948</v>
       </c>
-      <c r="F192" s="77" t="s">
+      <c r="F193" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="G192" s="77" t="s">
+      <c r="G193" s="77" t="s">
         <v>1851</v>
       </c>
-      <c r="I192" s="77" t="s">
+      <c r="I193" s="77" t="s">
         <v>1948</v>
       </c>
-      <c r="J192" s="77" t="s">
+      <c r="J193" s="77" t="s">
         <v>1949</v>
       </c>
-      <c r="K192" s="77" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q192" s="77" t="s">
+      <c r="K193" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q193" s="77" t="s">
         <v>292</v>
       </c>
-      <c r="S192" s="77" t="s">
+      <c r="S193" s="77" t="s">
         <v>875</v>
       </c>
-      <c r="T192" s="75">
+      <c r="T193" s="75">
         <v>8</v>
       </c>
-      <c r="U192" s="77" t="s">
+      <c r="U193" s="77" t="s">
         <v>889</v>
       </c>
-      <c r="V192" s="78" t="s">
+      <c r="V193" s="78" t="s">
         <v>1910</v>
       </c>
-      <c r="W192" s="77" t="s">
+      <c r="W193" s="77" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="193" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="77"/>
-      <c r="F193" s="77"/>
-      <c r="G193" s="77"/>
-      <c r="I193" s="77"/>
-      <c r="J193" s="77"/>
-      <c r="K193" s="77"/>
-      <c r="Q193" s="77"/>
-      <c r="S193" s="77"/>
-      <c r="U193" s="77"/>
-      <c r="V193" s="78"/>
-      <c r="W193" s="77"/>
     </row>
     <row r="194" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="77"/>
@@ -44892,65 +45008,37 @@
       <c r="V194" s="78"/>
       <c r="W194" s="77"/>
     </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A195" s="75" t="s">
-        <v>2857</v>
-      </c>
-      <c r="F195" s="75" t="s">
-        <v>76</v>
-      </c>
-      <c r="G195" s="75" t="s">
-        <v>1868</v>
-      </c>
-      <c r="H195" s="75" t="s">
-        <v>1884</v>
-      </c>
-      <c r="I195" s="75" t="s">
-        <v>2857</v>
-      </c>
-      <c r="J195" s="75" t="s">
-        <v>2862</v>
-      </c>
-      <c r="K195" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q195" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="S195" s="75" t="s">
-        <v>875</v>
-      </c>
-      <c r="T195" s="75" t="s">
-        <v>2855</v>
-      </c>
-      <c r="U195" s="75" t="s">
-        <v>2852</v>
-      </c>
-      <c r="V195" s="75" t="s">
-        <v>2867</v>
-      </c>
-      <c r="W195" s="77" t="s">
-        <v>830</v>
-      </c>
+    <row r="195" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A195" s="77"/>
+      <c r="F195" s="77"/>
+      <c r="G195" s="77"/>
+      <c r="I195" s="77"/>
+      <c r="J195" s="77"/>
+      <c r="K195" s="77"/>
+      <c r="Q195" s="77"/>
+      <c r="S195" s="77"/>
+      <c r="U195" s="77"/>
+      <c r="V195" s="78"/>
+      <c r="W195" s="77"/>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="75" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="F196" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G196" s="75" t="s">
-        <v>1888</v>
+        <v>1868</v>
       </c>
       <c r="H196" s="75" t="s">
-        <v>1889</v>
+        <v>1884</v>
       </c>
       <c r="I196" s="75" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="J196" s="75" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="K196" s="75" t="s">
         <v>215</v>
@@ -44962,7 +45050,7 @@
         <v>875</v>
       </c>
       <c r="T196" s="75" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="U196" s="75" t="s">
         <v>2852</v>
@@ -44976,22 +45064,22 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="75" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="F197" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G197" s="75" t="s">
-        <v>419</v>
+        <v>1888</v>
       </c>
       <c r="H197" s="75" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="I197" s="75" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="J197" s="75" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="K197" s="75" t="s">
         <v>215</v>
@@ -45003,7 +45091,7 @@
         <v>875</v>
       </c>
       <c r="T197" s="75" t="s">
-        <v>2869</v>
+        <v>2856</v>
       </c>
       <c r="U197" s="75" t="s">
         <v>2852</v>
@@ -45017,22 +45105,22 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="75" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="F198" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G198" s="75" t="s">
-        <v>1934</v>
+        <v>419</v>
       </c>
       <c r="H198" s="75" t="s">
-        <v>1935</v>
+        <v>1893</v>
       </c>
       <c r="I198" s="75" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="J198" s="75" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="K198" s="75" t="s">
         <v>215</v>
@@ -45044,7 +45132,7 @@
         <v>875</v>
       </c>
       <c r="T198" s="75" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="U198" s="75" t="s">
         <v>2852</v>
@@ -45058,22 +45146,22 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="75" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="F199" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G199" s="75" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="H199" s="75" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="I199" s="75" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="J199" s="75" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="K199" s="75" t="s">
         <v>215</v>
@@ -45085,7 +45173,7 @@
         <v>875</v>
       </c>
       <c r="T199" s="75" t="s">
-        <v>2868</v>
+        <v>2869</v>
       </c>
       <c r="U199" s="75" t="s">
         <v>2852</v>
@@ -45099,22 +45187,22 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="75" t="s">
-        <v>2871</v>
+        <v>2861</v>
       </c>
       <c r="F200" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G200" s="75" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="H200" s="75" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="I200" s="75" t="s">
-        <v>2871</v>
+        <v>2861</v>
       </c>
       <c r="J200" s="75" t="s">
-        <v>2872</v>
+        <v>2866</v>
       </c>
       <c r="K200" s="75" t="s">
         <v>215</v>
@@ -45125,34 +45213,37 @@
       <c r="S200" s="75" t="s">
         <v>875</v>
       </c>
+      <c r="T200" s="75" t="s">
+        <v>3049</v>
+      </c>
       <c r="U200" s="75" t="s">
         <v>2852</v>
       </c>
       <c r="V200" s="75" t="s">
         <v>2867</v>
       </c>
-      <c r="W200" s="75" t="s">
+      <c r="W200" s="77" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="75" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
       <c r="F201" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G201" s="75" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
       <c r="H201" s="75" t="s">
-        <v>2804</v>
+        <v>1943</v>
       </c>
       <c r="I201" s="75" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
       <c r="J201" s="75" t="s">
-        <v>2874</v>
+        <v>2871</v>
       </c>
       <c r="K201" s="75" t="s">
         <v>215</v>
@@ -45175,22 +45266,22 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="75" t="s">
-        <v>2875</v>
+        <v>2872</v>
       </c>
       <c r="F202" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G202" s="75" t="s">
-        <v>2793</v>
+        <v>1946</v>
       </c>
       <c r="H202" s="75" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="I202" s="75" t="s">
-        <v>2875</v>
+        <v>2872</v>
       </c>
       <c r="J202" s="75" t="s">
-        <v>2876</v>
+        <v>2873</v>
       </c>
       <c r="K202" s="75" t="s">
         <v>215</v>
@@ -45208,6 +45299,44 @@
         <v>2867</v>
       </c>
       <c r="W202" s="75" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A203" s="75" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F203" s="75" t="s">
+        <v>76</v>
+      </c>
+      <c r="G203" s="75" t="s">
+        <v>2793</v>
+      </c>
+      <c r="H203" s="75" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I203" s="75" t="s">
+        <v>2874</v>
+      </c>
+      <c r="J203" s="75" t="s">
+        <v>2875</v>
+      </c>
+      <c r="K203" s="75" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q203" s="75" t="s">
+        <v>292</v>
+      </c>
+      <c r="S203" s="75" t="s">
+        <v>875</v>
+      </c>
+      <c r="U203" s="75" t="s">
+        <v>2852</v>
+      </c>
+      <c r="V203" s="75" t="s">
+        <v>2867</v>
+      </c>
+      <c r="W203" s="75" t="s">
         <v>830</v>
       </c>
     </row>
@@ -45273,13 +45402,13 @@
     </row>
     <row r="2" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="85"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="F2" s="87" t="s">
         <v>90</v>
@@ -45288,7 +45417,7 @@
         <v>215</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>593</v>
@@ -45297,7 +45426,7 @@
         <v>2258</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="L2" s="88" t="s">
         <v>830</v>
@@ -45305,24 +45434,24 @@
     </row>
     <row r="3" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="C3" s="85"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="I3" s="26" t="s">
         <v>593</v>
@@ -45331,7 +45460,7 @@
         <v>2258</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="L3" s="84" t="s">
         <v>2245</v>
@@ -45339,24 +45468,24 @@
     </row>
     <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="C4" s="85"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="I4" s="26" t="s">
         <v>593</v>
@@ -45365,7 +45494,7 @@
         <v>2258</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="L4" s="84" t="s">
         <v>2245</v>
@@ -45995,22 +46124,22 @@
     </row>
     <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="B23" s="26"/>
       <c r="C23" s="89"/>
       <c r="D23" s="26"/>
       <c r="E23" s="26" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="I23" s="26" t="s">
         <v>593</v>
@@ -46019,7 +46148,7 @@
         <v>844</v>
       </c>
       <c r="K23" s="26" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="L23" s="84" t="s">
         <v>2245</v>
@@ -46027,22 +46156,22 @@
     </row>
     <row r="24" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="89"/>
       <c r="D24" s="26"/>
       <c r="E24" s="26" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>593</v>
@@ -46051,7 +46180,7 @@
         <v>844</v>
       </c>
       <c r="K24" s="26" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="L24" s="84" t="s">
         <v>2245</v>
@@ -46059,16 +46188,16 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B25" s="26"/>
       <c r="C25" s="85"/>
       <c r="D25" s="26"/>
       <c r="E25" s="26" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F25" s="87" t="s">
         <v>2974</v>
-      </c>
-      <c r="F25" s="87" t="s">
-        <v>2975</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>215</v>
@@ -46083,7 +46212,7 @@
         <v>213</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="L25" s="88" t="s">
         <v>830</v>
@@ -47450,21 +47579,21 @@
     </row>
     <row r="37" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="28" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="F37" s="22"/>
       <c r="G37" s="28"/>
       <c r="H37" s="28" t="s">
+        <v>2975</v>
+      </c>
+      <c r="I37" s="28" t="s">
         <v>2976</v>
-      </c>
-      <c r="I37" s="28" t="s">
-        <v>2977</v>
       </c>
       <c r="J37" s="28" t="s">
         <v>215</v>
@@ -50322,16 +50451,16 @@
     </row>
     <row r="102" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A102" s="35" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B102" s="35"/>
       <c r="C102" s="36"/>
       <c r="D102" s="35"/>
       <c r="E102" s="35" t="s">
+        <v>2971</v>
+      </c>
+      <c r="F102" s="35" t="s">
         <v>2972</v>
-      </c>
-      <c r="F102" s="35" t="s">
-        <v>2973</v>
       </c>
       <c r="G102" s="35" t="s">
         <v>215</v>
@@ -52493,16 +52622,16 @@
     </row>
     <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="B57" s="41"/>
       <c r="C57" s="85"/>
       <c r="D57" s="41"/>
       <c r="E57" s="41" t="s">
+        <v>2966</v>
+      </c>
+      <c r="F57" s="41" t="s">
         <v>2967</v>
-      </c>
-      <c r="F57" s="41" t="s">
-        <v>2968</v>
       </c>
       <c r="G57" s="41" t="s">
         <v>215</v>

--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E80D69-486C-4990-9B5F-394F97343752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407ED8E5-CBB5-4F7C-8F95-F9C1D99FA09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="7" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>
@@ -6403,9 +6403,6 @@
     <t>Debt.OSMS.EmployeeFee.RateBasic</t>
   </si>
   <si>
-    <t>FullName=метр;MKEI=6;Lenght=100.00(Unit.Cm);Width=100.00(Unit.Cm);Height=100.00(Unit.Cm);AbcBasic=Unit.Basic;AbcExpectedValue=Unit.ExpectedDouble;</t>
-  </si>
-  <si>
     <t>FullName=сантиметр;Lenght=10.00(Unit.Mm);Width=10.00(Unit.Mm);Height=10.00(Unit.Mm);AbcBasic=Unit.Basic;AbcExpectedValue=Unit.ExpectedDouble;</t>
   </si>
   <si>
@@ -8717,6 +8714,9 @@
   </si>
   <si>
     <t>продукт лист курс валют</t>
+  </si>
+  <si>
+    <t>FullName=метр;MKEI=6;Lenght=100.00(Unit.Cm);Width=100.00(Unit.Cm);Height=100.00(Unit.Cm);Squared=Unit.SquareMeter;Cubed=Unit.Cbm;AbcBasic=Unit.Basic;AbcExpectedValue=Unit.ExpectedDouble;</t>
   </si>
 </sst>
 </file>
@@ -11116,7 +11116,7 @@
         <v>42</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -11447,7 +11447,7 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>589</v>
@@ -11455,7 +11455,7 @@
       <c r="C7" s="89"/>
       <c r="D7" s="33"/>
       <c r="E7" s="33" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="F7" s="33" t="s">
         <v>681</v>
@@ -11485,7 +11485,7 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>589</v>
@@ -11493,10 +11493,10 @@
       <c r="C9" s="89"/>
       <c r="D9" s="33"/>
       <c r="E9" s="33" t="s">
+        <v>2130</v>
+      </c>
+      <c r="F9" s="33" t="s">
         <v>2131</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>2132</v>
       </c>
       <c r="G9" s="45" t="s">
         <v>590</v>
@@ -11504,7 +11504,7 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>589</v>
@@ -11512,18 +11512,18 @@
       <c r="C10" s="22"/>
       <c r="D10" s="33"/>
       <c r="E10" s="33" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>2537</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="G10" s="33" t="s">
         <v>2538</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>2539</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>589</v>
@@ -11531,18 +11531,18 @@
       <c r="C11" s="22"/>
       <c r="D11" s="33"/>
       <c r="E11" s="33" t="s">
+        <v>2539</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>2540</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="G11" s="33" t="s">
         <v>2541</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>2542</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>589</v>
@@ -11550,18 +11550,18 @@
       <c r="C12" s="22"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33" t="s">
+        <v>2542</v>
+      </c>
+      <c r="F12" s="33" t="s">
         <v>2543</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="G12" s="33" t="s">
         <v>2544</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>589</v>
@@ -11569,18 +11569,18 @@
       <c r="C13" s="22"/>
       <c r="D13" s="33"/>
       <c r="E13" s="33" t="s">
+        <v>2545</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>2546</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="G13" s="33" t="s">
         <v>2547</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>2548</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="B14" s="33" t="s">
         <v>589</v>
@@ -11588,18 +11588,18 @@
       <c r="C14" s="22"/>
       <c r="D14" s="33"/>
       <c r="E14" s="33" t="s">
+        <v>2548</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>2549</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="G14" s="33" t="s">
         <v>2550</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>2551</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>589</v>
@@ -11607,18 +11607,18 @@
       <c r="C15" s="22"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33" t="s">
+        <v>2551</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>2552</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="G15" s="33" t="s">
         <v>2553</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>2554</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>589</v>
@@ -11626,18 +11626,18 @@
       <c r="C16" s="22"/>
       <c r="D16" s="33"/>
       <c r="E16" s="33" t="s">
+        <v>2554</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>2555</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="G16" s="33" t="s">
         <v>2556</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>2557</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="B17" s="33" t="s">
         <v>589</v>
@@ -11645,18 +11645,18 @@
       <c r="C17" s="22"/>
       <c r="D17" s="33"/>
       <c r="E17" s="33" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>2558</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="G17" s="33" t="s">
         <v>2559</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>2560</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>589</v>
@@ -11664,18 +11664,18 @@
       <c r="C18" s="22"/>
       <c r="D18" s="33"/>
       <c r="E18" s="33" t="s">
+        <v>2560</v>
+      </c>
+      <c r="F18" s="33" t="s">
         <v>2561</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="G18" s="33" t="s">
         <v>2562</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>2563</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="B19" s="33" t="s">
         <v>589</v>
@@ -11683,18 +11683,18 @@
       <c r="C19" s="22"/>
       <c r="D19" s="33"/>
       <c r="E19" s="33" t="s">
+        <v>2563</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>2564</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="G19" s="33" t="s">
         <v>2565</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>2566</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>589</v>
@@ -11702,18 +11702,18 @@
       <c r="C20" s="22"/>
       <c r="D20" s="33"/>
       <c r="E20" s="33" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>2567</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="G20" s="33" t="s">
         <v>2568</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>2569</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>589</v>
@@ -11721,18 +11721,18 @@
       <c r="C21" s="22"/>
       <c r="D21" s="33"/>
       <c r="E21" s="33" t="s">
+        <v>2569</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>2570</v>
       </c>
-      <c r="F21" s="33" t="s">
+      <c r="G21" s="33" t="s">
         <v>2571</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>2572</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>589</v>
@@ -11740,18 +11740,18 @@
       <c r="C22" s="22"/>
       <c r="D22" s="33"/>
       <c r="E22" s="33" t="s">
+        <v>2572</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>2573</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="G22" s="33" t="s">
         <v>2574</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>2575</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>589</v>
@@ -11759,13 +11759,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="33"/>
       <c r="E23" s="33" t="s">
+        <v>2575</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>2576</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="G23" s="33" t="s">
         <v>2577</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>2578</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11800,10 +11800,10 @@
         <v>606</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11838,15 +11838,15 @@
         <v>610</v>
       </c>
       <c r="F27" s="33" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G27" s="33" t="s">
         <v>2491</v>
-      </c>
-      <c r="G27" s="33" t="s">
-        <v>2492</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>602</v>
@@ -11854,18 +11854,18 @@
       <c r="C28" s="22"/>
       <c r="D28" s="33"/>
       <c r="E28" s="33" t="s">
+        <v>2495</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>2496</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="G28" s="31" t="s">
         <v>2497</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>2498</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>602</v>
@@ -11873,13 +11873,13 @@
       <c r="C29" s="22"/>
       <c r="D29" s="33"/>
       <c r="E29" s="33" t="s">
+        <v>2498</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>2499</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="G29" s="33" t="s">
         <v>2500</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>2501</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11941,7 +11941,7 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>602</v>
@@ -11949,13 +11949,13 @@
       <c r="C33" s="22"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>2714</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="G33" s="33" t="s">
         <v>2715</v>
-      </c>
-      <c r="G33" s="33" t="s">
-        <v>2716</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -12028,10 +12028,10 @@
         <v>625</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -12050,7 +12050,7 @@
         <v>629</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -12066,15 +12066,15 @@
         <v>1928</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>602</v>
@@ -12082,18 +12082,18 @@
       <c r="C40" s="32"/>
       <c r="D40" s="33"/>
       <c r="E40" s="33" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>2529</v>
       </c>
-      <c r="F40" s="33" t="s">
-        <v>2530</v>
-      </c>
       <c r="G40" s="45" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="33" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="B41" s="33" t="s">
         <v>602</v>
@@ -12101,18 +12101,18 @@
       <c r="C41" s="32"/>
       <c r="D41" s="33"/>
       <c r="E41" s="33" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F41" s="33" t="s">
         <v>2531</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="G41" s="45" t="s">
         <v>2532</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>2533</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="B42" s="33" t="s">
         <v>602</v>
@@ -12120,18 +12120,18 @@
       <c r="C42" s="32"/>
       <c r="D42" s="33"/>
       <c r="E42" s="33" t="s">
+        <v>2533</v>
+      </c>
+      <c r="F42" s="33" t="s">
         <v>2534</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="G42" s="45" t="s">
         <v>2535</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>2536</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B43" s="33" t="s">
         <v>602</v>
@@ -12139,10 +12139,10 @@
       <c r="C43" s="32"/>
       <c r="D43" s="33"/>
       <c r="E43" s="33" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F43" s="33" t="s">
         <v>2502</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>2503</v>
       </c>
       <c r="G43" s="45" t="s">
         <v>590</v>
@@ -12395,7 +12395,7 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="33" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B57" s="33" t="s">
         <v>630</v>
@@ -12403,18 +12403,18 @@
       <c r="C57" s="22"/>
       <c r="D57" s="33"/>
       <c r="E57" s="33" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F57" s="33" t="s">
         <v>2309</v>
       </c>
-      <c r="F57" s="33" t="s">
+      <c r="G57" s="45" t="s">
         <v>2310</v>
-      </c>
-      <c r="G57" s="45" t="s">
-        <v>2311</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="33" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="B58" s="33" t="s">
         <v>630</v>
@@ -12422,10 +12422,10 @@
       <c r="C58" s="22"/>
       <c r="D58" s="33"/>
       <c r="E58" s="33" t="s">
+        <v>2343</v>
+      </c>
+      <c r="F58" s="33" t="s">
         <v>2344</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>2345</v>
       </c>
       <c r="G58" s="45" t="s">
         <v>590</v>
@@ -12433,7 +12433,7 @@
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="33" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="B59" s="33" t="s">
         <v>630</v>
@@ -12441,7 +12441,7 @@
       <c r="C59" s="22"/>
       <c r="D59" s="33"/>
       <c r="E59" s="33" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="F59" s="27" t="s">
         <v>1450</v>
@@ -12507,7 +12507,7 @@
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="33" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B63" s="33" t="s">
         <v>644</v>
@@ -12515,7 +12515,7 @@
       <c r="C63" s="22"/>
       <c r="D63" s="33"/>
       <c r="E63" s="33" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="F63" s="33" t="s">
         <v>546</v>
@@ -12659,7 +12659,7 @@
     </row>
     <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="33" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B71" s="33" t="s">
         <v>644</v>
@@ -12667,10 +12667,10 @@
       <c r="C71" s="32"/>
       <c r="D71" s="33"/>
       <c r="E71" s="33" t="s">
+        <v>2255</v>
+      </c>
+      <c r="F71" s="33" t="s">
         <v>2256</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>2257</v>
       </c>
       <c r="G71" s="45" t="s">
         <v>590</v>
@@ -12678,7 +12678,7 @@
     </row>
     <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="27" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B72" s="33" t="s">
         <v>644</v>
@@ -12686,7 +12686,7 @@
       <c r="C72" s="32"/>
       <c r="D72" s="27"/>
       <c r="E72" s="27" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="F72" s="27" t="s">
         <v>620</v>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="27" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B73" s="33" t="s">
         <v>644</v>
@@ -12705,10 +12705,10 @@
       <c r="C73" s="32"/>
       <c r="D73" s="27"/>
       <c r="E73" s="27" t="s">
+        <v>2258</v>
+      </c>
+      <c r="F73" s="27" t="s">
         <v>2259</v>
-      </c>
-      <c r="F73" s="27" t="s">
-        <v>2260</v>
       </c>
       <c r="G73" s="45" t="s">
         <v>626</v>
@@ -12716,7 +12716,7 @@
     </row>
     <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="27" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="B74" s="33" t="s">
         <v>644</v>
@@ -12724,10 +12724,10 @@
       <c r="C74" s="32"/>
       <c r="D74" s="27"/>
       <c r="E74" s="27" t="s">
+        <v>2319</v>
+      </c>
+      <c r="F74" s="33" t="s">
         <v>2320</v>
-      </c>
-      <c r="F74" s="33" t="s">
-        <v>2321</v>
       </c>
       <c r="G74" s="45" t="s">
         <v>626</v>
@@ -12735,7 +12735,7 @@
     </row>
     <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="B75" s="33" t="s">
         <v>644</v>
@@ -12743,10 +12743,10 @@
       <c r="C75" s="32"/>
       <c r="D75" s="27"/>
       <c r="E75" s="27" t="s">
+        <v>2443</v>
+      </c>
+      <c r="F75" s="33" t="s">
         <v>2444</v>
-      </c>
-      <c r="F75" s="33" t="s">
-        <v>2445</v>
       </c>
       <c r="G75" s="45" t="s">
         <v>626</v>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="B76" s="33" t="s">
         <v>644</v>
@@ -12762,10 +12762,10 @@
       <c r="C76" s="32"/>
       <c r="D76" s="27"/>
       <c r="E76" s="27" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F76" s="33" t="s">
         <v>2488</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>2489</v>
       </c>
       <c r="G76" s="45" t="s">
         <v>626</v>
@@ -12959,7 +12959,7 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="B87" s="33" t="s">
         <v>673</v>
@@ -12967,10 +12967,10 @@
       <c r="C87" s="22"/>
       <c r="D87" s="33"/>
       <c r="E87" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="F87" s="33" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="G87" s="45" t="s">
         <v>590</v>
@@ -12978,7 +12978,7 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="B88" s="33" t="s">
         <v>673</v>
@@ -12986,10 +12986,10 @@
       <c r="C88" s="22"/>
       <c r="D88" s="33"/>
       <c r="E88" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="F88" s="33" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="G88" s="45" t="s">
         <v>590</v>
@@ -12997,7 +12997,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="B89" s="33" t="s">
         <v>673</v>
@@ -13005,10 +13005,10 @@
       <c r="C89" s="22"/>
       <c r="D89" s="33"/>
       <c r="E89" s="33" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="G89" s="45" t="s">
         <v>590</v>
@@ -13073,7 +13073,7 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="s">
-        <v>2718</v>
+        <v>2717</v>
       </c>
       <c r="B93" s="33" t="s">
         <v>673</v>
@@ -13081,10 +13081,10 @@
       <c r="C93" s="22"/>
       <c r="D93" s="33"/>
       <c r="E93" s="33" t="s">
+        <v>2717</v>
+      </c>
+      <c r="F93" s="33" t="s">
         <v>2718</v>
-      </c>
-      <c r="F93" s="33" t="s">
-        <v>2719</v>
       </c>
       <c r="G93" s="45" t="s">
         <v>590</v>
@@ -13147,7 +13147,7 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B97" s="33" t="s">
         <v>693</v>
@@ -13155,18 +13155,18 @@
       <c r="C97" s="32"/>
       <c r="D97" s="33"/>
       <c r="E97" s="33" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F97" s="33" t="s">
         <v>2232</v>
       </c>
-      <c r="F97" s="33" t="s">
-        <v>2233</v>
-      </c>
       <c r="G97" s="45" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B98" s="33" t="s">
         <v>693</v>
@@ -13174,13 +13174,13 @@
       <c r="C98" s="32"/>
       <c r="D98" s="33"/>
       <c r="E98" s="33" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="F98" s="33" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="G98" s="45" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -13601,7 +13601,7 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="B121" s="33" t="s">
         <v>697</v>
@@ -13609,10 +13609,10 @@
       <c r="C121" s="22"/>
       <c r="D121" s="33"/>
       <c r="E121" s="33" t="s">
+        <v>2644</v>
+      </c>
+      <c r="F121" s="33" t="s">
         <v>2645</v>
-      </c>
-      <c r="F121" s="33" t="s">
-        <v>2646</v>
       </c>
       <c r="G121" s="45" t="s">
         <v>590</v>
@@ -14455,16 +14455,16 @@
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B7" s="50"/>
       <c r="C7" s="36"/>
       <c r="D7" s="50"/>
       <c r="E7" s="50" t="s">
+        <v>2132</v>
+      </c>
+      <c r="F7" s="50" t="s">
         <v>2133</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>2134</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>808</v>
@@ -14487,10 +14487,10 @@
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A9" s="95" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B9" s="99" t="s">
         <v>2355</v>
-      </c>
-      <c r="B9" s="99" t="s">
-        <v>2356</v>
       </c>
       <c r="C9" s="97"/>
       <c r="D9" s="97"/>
@@ -14500,10 +14500,10 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A10" s="95" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B10" s="99" t="s">
         <v>2357</v>
-      </c>
-      <c r="B10" s="99" t="s">
-        <v>2358</v>
       </c>
       <c r="C10" s="97"/>
       <c r="D10" s="97"/>
@@ -14513,10 +14513,10 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A11" s="95" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="B11" s="99" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
       <c r="C11" s="97"/>
       <c r="D11" s="97"/>
@@ -14526,10 +14526,10 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A12" s="95" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="B12" s="99" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="C12" s="97"/>
       <c r="D12" s="97"/>
@@ -14539,10 +14539,10 @@
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A13" s="95" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B13" s="99" t="s">
         <v>2361</v>
-      </c>
-      <c r="B13" s="99" t="s">
-        <v>2362</v>
       </c>
       <c r="C13" s="97"/>
       <c r="D13" s="97"/>
@@ -14552,10 +14552,10 @@
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A14" s="95" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B14" s="99" t="s">
         <v>2365</v>
-      </c>
-      <c r="B14" s="99" t="s">
-        <v>2366</v>
       </c>
       <c r="C14" s="97"/>
       <c r="D14" s="97"/>
@@ -14565,10 +14565,10 @@
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A15" s="95" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B15" s="99" t="s">
         <v>2367</v>
-      </c>
-      <c r="B15" s="99" t="s">
-        <v>2368</v>
       </c>
       <c r="C15" s="97"/>
       <c r="D15" s="97"/>
@@ -14578,10 +14578,10 @@
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A16" s="95" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B16" s="99" t="s">
         <v>2369</v>
-      </c>
-      <c r="B16" s="99" t="s">
-        <v>2370</v>
       </c>
       <c r="C16" s="97"/>
       <c r="D16" s="97"/>
@@ -14591,10 +14591,10 @@
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A17" s="95" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="B17" s="99" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="C17" s="97"/>
       <c r="D17" s="97"/>
@@ -14604,10 +14604,10 @@
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A18" s="95" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B18" s="99" t="s">
         <v>2373</v>
-      </c>
-      <c r="B18" s="99" t="s">
-        <v>2374</v>
       </c>
       <c r="C18" s="97"/>
       <c r="D18" s="97"/>
@@ -14617,10 +14617,10 @@
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A19" s="100" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B19" s="95" t="s">
         <v>2375</v>
-      </c>
-      <c r="B19" s="95" t="s">
-        <v>2376</v>
       </c>
       <c r="C19" s="97"/>
       <c r="D19" s="97"/>
@@ -14630,10 +14630,10 @@
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A20" s="100" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B20" s="95" t="s">
         <v>2377</v>
-      </c>
-      <c r="B20" s="95" t="s">
-        <v>2378</v>
       </c>
       <c r="C20" s="97"/>
       <c r="D20" s="97"/>
@@ -14643,10 +14643,10 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A21" s="100" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B21" s="95" t="s">
         <v>2379</v>
-      </c>
-      <c r="B21" s="95" t="s">
-        <v>2380</v>
       </c>
       <c r="C21" s="97"/>
       <c r="D21" s="97"/>
@@ -14659,7 +14659,7 @@
         <v>44564</v>
       </c>
       <c r="B22" s="95" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="C22" s="97"/>
       <c r="D22" s="97"/>
@@ -14672,7 +14672,7 @@
         <v>44565</v>
       </c>
       <c r="B23" s="95" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="C23" s="97"/>
       <c r="D23" s="97"/>
@@ -14685,7 +14685,7 @@
         <v>44566</v>
       </c>
       <c r="B24" s="95" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
       <c r="C24" s="97"/>
       <c r="D24" s="97"/>
@@ -14698,7 +14698,7 @@
         <v>44567</v>
       </c>
       <c r="B25" s="95" t="s">
-        <v>2384</v>
+        <v>2383</v>
       </c>
       <c r="C25" s="97"/>
       <c r="D25" s="97"/>
@@ -14711,7 +14711,7 @@
         <v>44584</v>
       </c>
       <c r="B26" s="95" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="C26" s="97"/>
       <c r="D26" s="97"/>
@@ -14724,7 +14724,7 @@
         <v>44614</v>
       </c>
       <c r="B27" s="95" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="C27" s="97"/>
       <c r="D27" s="97"/>
@@ -14734,10 +14734,10 @@
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A28" s="102" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="B28" s="99" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
       <c r="C28" s="97"/>
       <c r="D28" s="97"/>
@@ -14747,10 +14747,10 @@
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A29" s="102" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="B29" s="99" t="s">
-        <v>2388</v>
+        <v>2387</v>
       </c>
       <c r="C29" s="97"/>
       <c r="D29" s="97"/>
@@ -14760,10 +14760,10 @@
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A30" s="95" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B30" s="95" t="s">
         <v>2389</v>
-      </c>
-      <c r="B30" s="95" t="s">
-        <v>2390</v>
       </c>
       <c r="C30" s="97"/>
       <c r="D30" s="97"/>
@@ -14773,10 +14773,10 @@
     </row>
     <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A31" s="95" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B31" s="95" t="s">
         <v>2391</v>
-      </c>
-      <c r="B31" s="95" t="s">
-        <v>2392</v>
       </c>
       <c r="C31" s="97"/>
       <c r="D31" s="97"/>
@@ -14786,10 +14786,10 @@
     </row>
     <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A32" s="95" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B32" s="95" t="s">
         <v>2393</v>
-      </c>
-      <c r="B32" s="95" t="s">
-        <v>2394</v>
       </c>
       <c r="C32" s="97"/>
       <c r="D32" s="97"/>
@@ -14799,10 +14799,10 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A33" s="95" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="B33" s="95" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="C33" s="97"/>
       <c r="D33" s="97"/>
@@ -14812,10 +14812,10 @@
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A34" s="95" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="B34" s="95" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="C34" s="97"/>
       <c r="D34" s="97"/>
@@ -14825,10 +14825,10 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A35" s="95" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B35" s="95" t="s">
         <v>2399</v>
-      </c>
-      <c r="B35" s="95" t="s">
-        <v>2400</v>
       </c>
       <c r="C35" s="97"/>
       <c r="D35" s="97"/>
@@ -14838,10 +14838,10 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A36" s="95" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B36" s="95" t="s">
         <v>2401</v>
-      </c>
-      <c r="B36" s="95" t="s">
-        <v>2402</v>
       </c>
       <c r="C36" s="97"/>
       <c r="D36" s="97"/>
@@ -14851,10 +14851,10 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A37" s="95" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B37" s="95" t="s">
         <v>2403</v>
-      </c>
-      <c r="B37" s="95" t="s">
-        <v>2404</v>
       </c>
       <c r="C37" s="97"/>
       <c r="D37" s="97"/>
@@ -14864,10 +14864,10 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A38" s="95" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B38" s="95" t="s">
         <v>2405</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>2406</v>
       </c>
       <c r="C38" s="97"/>
       <c r="D38" s="97"/>
@@ -14877,10 +14877,10 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A39" s="95" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B39" s="95" t="s">
         <v>2407</v>
-      </c>
-      <c r="B39" s="95" t="s">
-        <v>2408</v>
       </c>
       <c r="C39" s="97"/>
       <c r="D39" s="97"/>
@@ -14890,10 +14890,10 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B40" s="95" t="s">
         <v>2409</v>
-      </c>
-      <c r="B40" s="95" t="s">
-        <v>2410</v>
       </c>
       <c r="C40" s="97"/>
       <c r="D40" s="97"/>
@@ -14903,10 +14903,10 @@
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A41" s="95" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B41" s="95" t="s">
         <v>2411</v>
-      </c>
-      <c r="B41" s="95" t="s">
-        <v>2412</v>
       </c>
       <c r="C41" s="97"/>
       <c r="D41" s="97"/>
@@ -14916,10 +14916,10 @@
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A42" s="95" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B42" s="95" t="s">
         <v>2413</v>
-      </c>
-      <c r="B42" s="95" t="s">
-        <v>2414</v>
       </c>
       <c r="C42" s="97"/>
       <c r="D42" s="97"/>
@@ -14929,10 +14929,10 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A43" s="95" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B43" s="95" t="s">
         <v>2415</v>
-      </c>
-      <c r="B43" s="95" t="s">
-        <v>2416</v>
       </c>
       <c r="C43" s="97"/>
       <c r="D43" s="97"/>
@@ -14942,10 +14942,10 @@
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="B44" s="95" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="C44" s="97"/>
       <c r="D44" s="97"/>
@@ -14955,10 +14955,10 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A45" s="95" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B45" s="95" t="s">
         <v>2419</v>
-      </c>
-      <c r="B45" s="95" t="s">
-        <v>2420</v>
       </c>
       <c r="C45" s="97"/>
       <c r="D45" s="97"/>
@@ -14968,10 +14968,10 @@
     </row>
     <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A46" s="95" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B46" s="95" t="s">
         <v>2340</v>
-      </c>
-      <c r="B46" s="95" t="s">
-        <v>2341</v>
       </c>
       <c r="C46" s="97"/>
       <c r="D46" s="97"/>
@@ -14981,10 +14981,10 @@
     </row>
     <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A47" s="95" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B47" s="95" t="s">
         <v>2342</v>
-      </c>
-      <c r="B47" s="95" t="s">
-        <v>2343</v>
       </c>
       <c r="C47" s="97"/>
       <c r="D47" s="97"/>
@@ -14994,10 +14994,10 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A48" s="95" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B48" s="95" t="s">
         <v>2421</v>
-      </c>
-      <c r="B48" s="95" t="s">
-        <v>2422</v>
       </c>
       <c r="C48" s="97"/>
       <c r="D48" s="97"/>
@@ -15007,10 +15007,10 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A49" s="95" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B49" s="95" t="s">
         <v>2423</v>
-      </c>
-      <c r="B49" s="95" t="s">
-        <v>2424</v>
       </c>
       <c r="C49" s="97"/>
       <c r="D49" s="97"/>
@@ -15020,10 +15020,10 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A50" s="95" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B50" s="95" t="s">
         <v>2425</v>
-      </c>
-      <c r="B50" s="95" t="s">
-        <v>2426</v>
       </c>
       <c r="C50" s="97"/>
       <c r="D50" s="97"/>
@@ -15033,10 +15033,10 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A51" s="95" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B51" s="95" t="s">
         <v>2427</v>
-      </c>
-      <c r="B51" s="95" t="s">
-        <v>2428</v>
       </c>
       <c r="C51" s="97"/>
       <c r="D51" s="97"/>
@@ -15046,10 +15046,10 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="95" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B52" s="95" t="s">
         <v>2429</v>
-      </c>
-      <c r="B52" s="95" t="s">
-        <v>2430</v>
       </c>
       <c r="C52" s="97"/>
       <c r="D52" s="97"/>
@@ -15059,10 +15059,10 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="95" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B53" s="95" t="s">
         <v>2431</v>
-      </c>
-      <c r="B53" s="95" t="s">
-        <v>2432</v>
       </c>
       <c r="C53" s="97"/>
       <c r="D53" s="97"/>
@@ -15072,10 +15072,10 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A54" s="95" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B54" s="95" t="s">
         <v>2433</v>
-      </c>
-      <c r="B54" s="95" t="s">
-        <v>2434</v>
       </c>
       <c r="C54" s="97"/>
       <c r="D54" s="97"/>
@@ -15085,10 +15085,10 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A55" s="95" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B55" s="95" t="s">
         <v>2435</v>
-      </c>
-      <c r="B55" s="95" t="s">
-        <v>2436</v>
       </c>
       <c r="C55" s="97"/>
       <c r="D55" s="97"/>
@@ -15098,10 +15098,10 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A56" s="95" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B56" s="95" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C56" s="97"/>
       <c r="D56" s="97"/>
@@ -15111,10 +15111,10 @@
     </row>
     <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A57" s="95" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B57" s="95" t="s">
         <v>2338</v>
-      </c>
-      <c r="B57" s="95" t="s">
-        <v>2339</v>
       </c>
       <c r="C57" s="97"/>
       <c r="D57" s="97"/>
@@ -15124,10 +15124,10 @@
     </row>
     <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A58" s="95" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B58" s="95" t="s">
         <v>2336</v>
-      </c>
-      <c r="B58" s="95" t="s">
-        <v>2337</v>
       </c>
       <c r="C58" s="97"/>
       <c r="D58" s="97"/>
@@ -15137,10 +15137,10 @@
     </row>
     <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A59" s="95" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B59" s="95" t="s">
         <v>2334</v>
-      </c>
-      <c r="B59" s="95" t="s">
-        <v>2335</v>
       </c>
       <c r="C59" s="97"/>
       <c r="D59" s="97"/>
@@ -15150,10 +15150,10 @@
     </row>
     <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A60" s="95" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B60" s="95" t="s">
         <v>2332</v>
-      </c>
-      <c r="B60" s="95" t="s">
-        <v>2333</v>
       </c>
       <c r="C60" s="97"/>
       <c r="D60" s="97"/>
@@ -15163,10 +15163,10 @@
     </row>
     <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A61" s="95" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B61" s="95" t="s">
         <v>2330</v>
-      </c>
-      <c r="B61" s="95" t="s">
-        <v>2331</v>
       </c>
       <c r="C61" s="97"/>
       <c r="D61" s="97"/>
@@ -15176,42 +15176,42 @@
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="95" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B62" s="95" t="s">
         <v>2438</v>
-      </c>
-      <c r="B62" s="95" t="s">
-        <v>2439</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="95" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="B63" s="95" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="95" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B64" s="95" t="s">
         <v>2706</v>
-      </c>
-      <c r="B64" s="95" t="s">
-        <v>2707</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="95" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B65" s="95" t="s">
         <v>2720</v>
-      </c>
-      <c r="B65" s="95" t="s">
-        <v>2721</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="95" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B66" s="95" t="s">
         <v>2881</v>
-      </c>
-      <c r="B66" s="95" t="s">
-        <v>2882</v>
       </c>
     </row>
   </sheetData>
@@ -15782,286 +15782,286 @@
   <sheetData>
     <row r="1" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A1" s="108" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="B1" s="108"/>
       <c r="C1" s="84"/>
       <c r="D1" s="108"/>
       <c r="E1" s="108" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F1" s="108" t="s">
+        <v>2126</v>
+      </c>
+      <c r="G1" s="27" t="s">
+        <v>2882</v>
+      </c>
+      <c r="H1" s="28" t="s">
         <v>2125</v>
-      </c>
-      <c r="F1" s="108" t="s">
-        <v>2127</v>
-      </c>
-      <c r="G1" s="27" t="s">
-        <v>2883</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>2126</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="108" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="B2" s="108"/>
       <c r="C2" s="109" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D2" s="109" t="s">
         <v>2140</v>
       </c>
-      <c r="D2" s="109" t="s">
-        <v>2141</v>
-      </c>
       <c r="E2" s="108" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F2" s="108" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="108" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B3" s="108"/>
       <c r="C3" s="109" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D3" s="109" t="s">
         <v>2140</v>
       </c>
-      <c r="D3" s="109" t="s">
+      <c r="E3" s="108" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F3" s="108" t="s">
+        <v>2138</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>2884</v>
+      </c>
+      <c r="H3" s="28" t="s">
         <v>2141</v>
-      </c>
-      <c r="E3" s="108" t="s">
-        <v>2224</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>2139</v>
-      </c>
-      <c r="G3" s="27" t="s">
-        <v>2885</v>
-      </c>
-      <c r="H3" s="28" t="s">
-        <v>2142</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="108" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="B4" s="108"/>
       <c r="C4" s="109"/>
       <c r="D4" s="109"/>
       <c r="E4" s="108" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="F4" s="108" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="B5" s="108" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="C5" s="109"/>
       <c r="D5" s="109"/>
       <c r="E5" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="108" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="B6" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C6" s="109"/>
       <c r="D6" s="109"/>
       <c r="E6" s="108" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="F6" s="108" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="108" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="B7" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C7" s="109"/>
       <c r="D7" s="109"/>
       <c r="E7" s="108" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="F7" s="108" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="108" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="B8" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="108" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="F8" s="108" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="108" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C9" s="109"/>
       <c r="D9" s="109"/>
       <c r="E9" s="108" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="108" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="B10" s="108"/>
       <c r="C10" s="109"/>
       <c r="D10" s="109"/>
       <c r="E10" s="108" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="F10" s="108" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="108" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B11" s="108" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="C11" s="109"/>
       <c r="D11" s="109"/>
       <c r="E11" s="108" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="F11" s="108" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="108" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="B12" s="108" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="C12" s="109"/>
       <c r="D12" s="109"/>
       <c r="E12" s="108" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="F12" s="108" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="108" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="C13" s="109"/>
       <c r="D13" s="109"/>
       <c r="E13" s="108" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="F13" s="108" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
     </row>
   </sheetData>
@@ -16111,8 +16111,8 @@
         <v>879</v>
       </c>
       <c r="B1" s="56"/>
-      <c r="C1" s="56" t="s">
-        <v>232</v>
+      <c r="C1" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D1" s="56"/>
       <c r="E1" s="57"/>
@@ -16135,10 +16135,10 @@
       <c r="P1" s="56"/>
       <c r="Q1" s="56"/>
       <c r="R1" s="24" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S1" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="T1" s="51" t="s">
         <v>871</v>
@@ -16147,7 +16147,7 @@
         <v>881</v>
       </c>
       <c r="V1" s="52" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="W1" s="60" t="s">
         <v>878</v>
@@ -16158,11 +16158,11 @@
     </row>
     <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="B2" s="56"/>
-      <c r="C2" s="56" t="s">
-        <v>232</v>
+      <c r="C2" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D2" s="56"/>
       <c r="E2" s="57"/>
@@ -16172,10 +16172,10 @@
       <c r="G2" s="53"/>
       <c r="H2" s="53"/>
       <c r="I2" s="56" t="s">
+        <v>2721</v>
+      </c>
+      <c r="J2" s="56" t="s">
         <v>2722</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>2723</v>
       </c>
       <c r="K2" s="63"/>
       <c r="L2" s="64"/>
@@ -16185,10 +16185,10 @@
       <c r="P2" s="56"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="24" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S2" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="T2" s="51" t="s">
         <v>869</v>
@@ -16197,7 +16197,7 @@
         <v>881</v>
       </c>
       <c r="V2" s="52" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="W2" s="60" t="s">
         <v>878</v>
@@ -16211,8 +16211,8 @@
         <v>882</v>
       </c>
       <c r="B3" s="56"/>
-      <c r="C3" s="56" t="s">
-        <v>232</v>
+      <c r="C3" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D3" s="56"/>
       <c r="E3" s="57"/>
@@ -16235,10 +16235,10 @@
       <c r="P3" s="56"/>
       <c r="Q3" s="56"/>
       <c r="R3" s="24" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S3" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="S3" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="T3" s="51" t="s">
         <v>871</v>
@@ -16247,7 +16247,7 @@
         <v>884</v>
       </c>
       <c r="V3" s="52" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="W3" s="60" t="s">
         <v>878</v>
@@ -16258,11 +16258,11 @@
     </row>
     <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="B4" s="56"/>
-      <c r="C4" s="56" t="s">
-        <v>232</v>
+      <c r="C4" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D4" s="56"/>
       <c r="E4" s="57"/>
@@ -16272,10 +16272,10 @@
       <c r="G4" s="53"/>
       <c r="H4" s="53"/>
       <c r="I4" s="56" t="s">
+        <v>2723</v>
+      </c>
+      <c r="J4" s="56" t="s">
         <v>2724</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>2725</v>
       </c>
       <c r="K4" s="63"/>
       <c r="L4" s="64"/>
@@ -16285,10 +16285,10 @@
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
       <c r="R4" s="24" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S4" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="S4" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="T4" s="51" t="s">
         <v>869</v>
@@ -16297,7 +16297,7 @@
         <v>884</v>
       </c>
       <c r="V4" s="52" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="W4" s="60" t="s">
         <v>878</v>
@@ -16308,11 +16308,11 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
-        <v>2738</v>
+        <v>2737</v>
       </c>
       <c r="B5" s="56"/>
-      <c r="C5" s="56" t="s">
-        <v>232</v>
+      <c r="C5" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D5" s="56"/>
       <c r="E5" s="57"/>
@@ -16322,10 +16322,10 @@
       <c r="G5" s="53"/>
       <c r="H5" s="53"/>
       <c r="I5" s="56" t="s">
+        <v>2737</v>
+      </c>
+      <c r="J5" s="56" t="s">
         <v>2738</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>2739</v>
       </c>
       <c r="K5" s="63"/>
       <c r="L5" s="64"/>
@@ -16335,22 +16335,22 @@
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
       <c r="R5" s="24" t="s">
+        <v>2716</v>
+      </c>
+      <c r="S5" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="S5" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="T5" s="51" t="s">
         <v>869</v>
       </c>
       <c r="U5" s="56" t="s">
+        <v>2739</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>2734</v>
+      </c>
+      <c r="W5" s="60" t="s">
         <v>2740</v>
-      </c>
-      <c r="V5" s="52" t="s">
-        <v>2735</v>
-      </c>
-      <c r="W5" s="60" t="s">
-        <v>2741</v>
       </c>
       <c r="X5" s="50" t="s">
         <v>815</v>
@@ -16361,11 +16361,11 @@
         <v>1075</v>
       </c>
       <c r="B6" s="56"/>
-      <c r="C6" s="56" t="s">
-        <v>232</v>
+      <c r="C6" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>516</v>
@@ -16374,7 +16374,7 @@
         <v>74</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H6" s="53"/>
       <c r="I6" s="56" t="s">
@@ -16396,7 +16396,7 @@
         <v>257</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="T6" s="68" t="s">
         <v>826</v>
@@ -16421,11 +16421,11 @@
       <c r="B7" s="56" t="s">
         <v>1075</v>
       </c>
-      <c r="C7" s="56" t="s">
-        <v>232</v>
+      <c r="C7" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>516</v>
@@ -16434,7 +16434,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H7" s="53"/>
       <c r="I7" s="56" t="s">
@@ -16453,26 +16453,26 @@
         <v>108</v>
       </c>
       <c r="N7" s="26" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="P7" s="56"/>
       <c r="Q7" s="35" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T7" s="56" t="s">
         <v>827</v>
       </c>
       <c r="U7" s="56" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="V7" s="69" t="s">
         <v>213</v>
@@ -16491,11 +16491,11 @@
       <c r="B8" s="56" t="s">
         <v>1075</v>
       </c>
-      <c r="C8" s="56" t="s">
-        <v>232</v>
+      <c r="C8" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>516</v>
@@ -16504,7 +16504,7 @@
         <v>74</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H8" s="53"/>
       <c r="I8" s="56" t="s">
@@ -16523,26 +16523,26 @@
         <v>108</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="O8" s="28" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="P8" s="56"/>
       <c r="Q8" s="35" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="S8" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T8" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U8" s="56" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="V8" s="56" t="s">
         <v>577</v>
@@ -16559,8 +16559,8 @@
         <v>908</v>
       </c>
       <c r="B9" s="59"/>
-      <c r="C9" s="56" t="s">
-        <v>232</v>
+      <c r="C9" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D9" s="56"/>
       <c r="E9" s="57" t="s">
@@ -16570,7 +16570,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H9" s="53" t="s">
         <v>886</v>
@@ -16594,7 +16594,7 @@
         <v>257</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="T9" s="68" t="s">
         <v>826</v>
@@ -16619,8 +16619,8 @@
       <c r="B10" s="56" t="s">
         <v>908</v>
       </c>
-      <c r="C10" s="56" t="s">
-        <v>232</v>
+      <c r="C10" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D10" s="56"/>
       <c r="E10" s="57" t="s">
@@ -16630,7 +16630,7 @@
         <v>74</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H10" s="53"/>
       <c r="I10" s="56" t="s">
@@ -16649,7 +16649,7 @@
         <v>143</v>
       </c>
       <c r="N10" s="56" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
@@ -16657,16 +16657,16 @@
         <v>304</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="S10" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="T10" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U10" s="56" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="V10" s="56" t="s">
         <v>577</v>
@@ -16685,8 +16685,8 @@
       <c r="B11" s="56" t="s">
         <v>908</v>
       </c>
-      <c r="C11" s="56" t="s">
-        <v>232</v>
+      <c r="C11" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D11" s="56"/>
       <c r="E11" s="57" t="s">
@@ -16696,7 +16696,7 @@
         <v>74</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H11" s="53"/>
       <c r="I11" s="56" t="s">
@@ -16721,16 +16721,16 @@
       </c>
       <c r="Q11" s="56"/>
       <c r="R11" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="S11" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T11" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U11" s="56" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="V11" s="56" t="s">
         <v>577</v>
@@ -16749,8 +16749,8 @@
       <c r="B12" s="56" t="s">
         <v>908</v>
       </c>
-      <c r="C12" s="56" t="s">
-        <v>232</v>
+      <c r="C12" s="41" t="s">
+        <v>2766</v>
       </c>
       <c r="D12" s="56"/>
       <c r="E12" s="57" t="s">
@@ -16760,7 +16760,7 @@
         <v>74</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="H12" s="53"/>
       <c r="I12" s="56" t="s">
@@ -16779,7 +16779,7 @@
         <v>143</v>
       </c>
       <c r="N12" s="56" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="O12" s="56"/>
       <c r="P12" s="56"/>
@@ -16787,16 +16787,16 @@
         <v>304</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="S12" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="T12" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U12" s="56" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="V12" s="56" t="s">
         <v>577</v>
@@ -18797,7 +18797,7 @@
       </c>
       <c r="Q46" s="56"/>
       <c r="R46" s="66" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="S46" s="67" t="s">
         <v>682</v>
@@ -30386,7 +30386,7 @@
         <v>1410</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="27"/>
@@ -30405,7 +30405,7 @@
         <v>1412</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="27"/>
@@ -30424,7 +30424,7 @@
         <v>1414</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="27"/>
@@ -30443,7 +30443,7 @@
         <v>1416</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="27"/>
@@ -30459,7 +30459,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>1407</v>
@@ -30467,10 +30467,10 @@
       <c r="C21" s="22"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F21" s="27" t="s">
         <v>2747</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>2748</v>
       </c>
       <c r="G21" s="45" t="s">
         <v>626</v>
@@ -30519,7 +30519,7 @@
         <v>1421</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="27"/>
@@ -30538,7 +30538,7 @@
         <v>1423</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="27"/>
@@ -30595,7 +30595,7 @@
         <v>1428</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="27"/>
@@ -30614,7 +30614,7 @@
         <v>1430</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="27"/>
@@ -30725,7 +30725,7 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="27" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B35" s="27" t="s">
         <v>1407</v>
@@ -30733,10 +30733,10 @@
       <c r="C35" s="22"/>
       <c r="D35" s="27"/>
       <c r="E35" s="27" t="s">
+        <v>2301</v>
+      </c>
+      <c r="F35" s="27" t="s">
         <v>2302</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>2303</v>
       </c>
       <c r="G35" s="45" t="s">
         <v>626</v>
@@ -30744,7 +30744,7 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>1407</v>
@@ -30752,10 +30752,10 @@
       <c r="C36" s="22"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="F36" s="27" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="G36" s="45" t="s">
         <v>626</v>
@@ -30763,7 +30763,7 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>1407</v>
@@ -30771,10 +30771,10 @@
       <c r="C37" s="22"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="F37" s="27" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="G37" s="45" t="s">
         <v>626</v>
@@ -30782,7 +30782,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>1407</v>
@@ -30790,7 +30790,7 @@
       <c r="C38" s="22"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>681</v>
@@ -30801,7 +30801,7 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>1407</v>
@@ -30809,7 +30809,7 @@
       <c r="C39" s="22"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="F39" s="33" t="s">
         <v>601</v>
@@ -30820,7 +30820,7 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="B40" s="27" t="s">
         <v>1407</v>
@@ -30828,10 +30828,10 @@
       <c r="C40" s="22"/>
       <c r="D40" s="27"/>
       <c r="E40" s="27" t="s">
+        <v>2725</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>2726</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>2727</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>626</v>
@@ -30913,7 +30913,7 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="B45" s="27" t="s">
         <v>1442</v>
@@ -30921,7 +30921,7 @@
       <c r="C45" s="22"/>
       <c r="D45" s="27"/>
       <c r="E45" s="34" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="F45" s="27" t="s">
         <v>1446</v>
@@ -30989,7 +30989,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
       <c r="B49" s="27" t="s">
         <v>1442</v>
@@ -30997,10 +30997,10 @@
       <c r="C49" s="32"/>
       <c r="D49" s="27"/>
       <c r="E49" s="27" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F49" s="27" t="s">
         <v>2579</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>2580</v>
       </c>
       <c r="G49" s="45" t="s">
         <v>626</v>
@@ -31550,7 +31550,7 @@
         <v>1498</v>
       </c>
       <c r="G78" s="45" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -31726,7 +31726,7 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B88" s="27" t="s">
         <v>1330</v>
@@ -31734,7 +31734,7 @@
       <c r="C88" s="53"/>
       <c r="D88" s="27"/>
       <c r="E88" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="F88" s="27" t="s">
         <v>666</v>
@@ -31745,7 +31745,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="27" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B89" s="27" t="s">
         <v>1330</v>
@@ -31753,10 +31753,10 @@
       <c r="C89" s="53"/>
       <c r="D89" s="27"/>
       <c r="E89" s="27" t="s">
+        <v>2153</v>
+      </c>
+      <c r="F89" s="27" t="s">
         <v>2154</v>
-      </c>
-      <c r="F89" s="27" t="s">
-        <v>2155</v>
       </c>
       <c r="G89" s="45" t="s">
         <v>626</v>
@@ -31764,7 +31764,7 @@
     </row>
     <row r="90" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="27" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B90" s="27" t="s">
         <v>1330</v>
@@ -31772,10 +31772,10 @@
       <c r="C90" s="53"/>
       <c r="D90" s="27"/>
       <c r="E90" s="27" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="F90" s="27" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="G90" s="45" t="s">
         <v>626</v>
@@ -31783,7 +31783,7 @@
     </row>
     <row r="91" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="27" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="B91" s="27" t="s">
         <v>1330</v>
@@ -31791,10 +31791,10 @@
       <c r="C91" s="53"/>
       <c r="D91" s="27"/>
       <c r="E91" s="27" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F91" s="27" t="s">
         <v>2164</v>
-      </c>
-      <c r="F91" s="27" t="s">
-        <v>2165</v>
       </c>
       <c r="G91" s="45" t="s">
         <v>626</v>
@@ -31802,7 +31802,7 @@
     </row>
     <row r="92" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B92" s="27" t="s">
         <v>1330</v>
@@ -31810,10 +31810,10 @@
       <c r="C92" s="53"/>
       <c r="D92" s="27"/>
       <c r="E92" s="27" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F92" s="27" t="s">
         <v>2171</v>
-      </c>
-      <c r="F92" s="27" t="s">
-        <v>2172</v>
       </c>
       <c r="G92" s="45" t="s">
         <v>626</v>
@@ -31821,7 +31821,7 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="B93" s="27" t="s">
         <v>1330</v>
@@ -31829,10 +31829,10 @@
       <c r="C93" s="53"/>
       <c r="D93" s="27"/>
       <c r="E93" s="27" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F93" s="27" t="s">
         <v>2196</v>
-      </c>
-      <c r="F93" s="27" t="s">
-        <v>2197</v>
       </c>
       <c r="G93" s="45" t="s">
         <v>626</v>
@@ -31840,7 +31840,7 @@
     </row>
     <row r="94" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="27" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="B94" s="27" t="s">
         <v>1330</v>
@@ -31848,10 +31848,10 @@
       <c r="C94" s="53"/>
       <c r="D94" s="27"/>
       <c r="E94" s="27" t="s">
+        <v>2199</v>
+      </c>
+      <c r="F94" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="F94" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="G94" s="45" t="s">
         <v>626</v>
@@ -31859,7 +31859,7 @@
     </row>
     <row r="95" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="27" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="B95" s="27" t="s">
         <v>1330</v>
@@ -31867,10 +31867,10 @@
       <c r="C95" s="53"/>
       <c r="D95" s="27"/>
       <c r="E95" s="27" t="s">
+        <v>2235</v>
+      </c>
+      <c r="F95" s="27" t="s">
         <v>2236</v>
-      </c>
-      <c r="F95" s="27" t="s">
-        <v>2237</v>
       </c>
       <c r="G95" s="45" t="s">
         <v>626</v>
@@ -31878,7 +31878,7 @@
     </row>
     <row r="96" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="27" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="B96" s="27" t="s">
         <v>1330</v>
@@ -31886,10 +31886,10 @@
       <c r="C96" s="53"/>
       <c r="D96" s="27"/>
       <c r="E96" s="27" t="s">
+        <v>2205</v>
+      </c>
+      <c r="F96" s="27" t="s">
         <v>2206</v>
-      </c>
-      <c r="F96" s="27" t="s">
-        <v>2207</v>
       </c>
       <c r="G96" s="45" t="s">
         <v>626</v>
@@ -31897,7 +31897,7 @@
     </row>
     <row r="97" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="27" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B97" s="27" t="s">
         <v>1330</v>
@@ -31905,10 +31905,10 @@
       <c r="C97" s="53"/>
       <c r="D97" s="27"/>
       <c r="E97" s="27" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F97" s="27" t="s">
         <v>2210</v>
-      </c>
-      <c r="F97" s="27" t="s">
-        <v>2211</v>
       </c>
       <c r="G97" s="45" t="s">
         <v>626</v>
@@ -31916,7 +31916,7 @@
     </row>
     <row r="98" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="27" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B98" s="27" t="s">
         <v>1330</v>
@@ -31924,10 +31924,10 @@
       <c r="C98" s="53"/>
       <c r="D98" s="27"/>
       <c r="E98" s="27" t="s">
+        <v>2247</v>
+      </c>
+      <c r="F98" s="27" t="s">
         <v>2248</v>
-      </c>
-      <c r="F98" s="27" t="s">
-        <v>2249</v>
       </c>
       <c r="G98" s="45" t="s">
         <v>626</v>
@@ -31935,7 +31935,7 @@
     </row>
     <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="B99" s="27" t="s">
         <v>1330</v>
@@ -31943,10 +31943,10 @@
       <c r="C99" s="53"/>
       <c r="D99" s="27"/>
       <c r="E99" s="27" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F99" s="27" t="s">
         <v>2480</v>
-      </c>
-      <c r="F99" s="27" t="s">
-        <v>2481</v>
       </c>
       <c r="G99" s="45" t="s">
         <v>626</v>
@@ -32292,13 +32292,13 @@
     </row>
     <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="27" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="B118" s="27"/>
       <c r="C118" s="22"/>
       <c r="D118" s="27"/>
       <c r="E118" s="27" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="F118" s="27" t="s">
         <v>60</v>
@@ -32309,18 +32309,18 @@
     </row>
     <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="C119" s="22"/>
       <c r="D119" s="27"/>
       <c r="E119" s="27" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F119" s="27" t="s">
         <v>2757</v>
-      </c>
-      <c r="F119" s="27" t="s">
-        <v>2758</v>
       </c>
       <c r="G119" s="45" t="s">
         <v>626</v>
@@ -32328,15 +32328,15 @@
     </row>
     <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A120" s="24" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="C120" s="22"/>
       <c r="D120" s="27"/>
       <c r="E120" s="24" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="F120" s="27" t="s">
         <v>1513</v>
@@ -32347,16 +32347,16 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="B121" s="27"/>
       <c r="C121" s="22"/>
       <c r="D121" s="27"/>
       <c r="E121" s="24" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F121" s="27" t="s">
         <v>2875</v>
-      </c>
-      <c r="F121" s="27" t="s">
-        <v>2876</v>
       </c>
       <c r="G121" s="45" t="s">
         <v>626</v>
@@ -32364,18 +32364,18 @@
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A122" s="27" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C122" s="22"/>
       <c r="D122" s="27"/>
       <c r="E122" s="27" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="G122" s="45" t="s">
         <v>626</v>
@@ -32383,18 +32383,18 @@
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A123" s="27" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C123" s="22"/>
       <c r="D123" s="27"/>
       <c r="E123" s="27" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="G123" s="45" t="s">
         <v>626</v>
@@ -32402,18 +32402,18 @@
     </row>
     <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A124" s="27" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B124" s="24" t="s">
         <v>2874</v>
-      </c>
-      <c r="B124" s="24" t="s">
-        <v>2875</v>
       </c>
       <c r="C124" s="22"/>
       <c r="D124" s="27"/>
       <c r="E124" s="27" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="G124" s="45" t="s">
         <v>626</v>
@@ -32421,18 +32421,18 @@
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A125" s="27" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C125" s="22"/>
       <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="G125" s="45" t="s">
         <v>626</v>
@@ -32440,18 +32440,18 @@
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A126" s="27" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C126" s="22"/>
       <c r="D126" s="27"/>
       <c r="E126" s="27" t="s">
+        <v>2882</v>
+      </c>
+      <c r="F126" s="27" t="s">
         <v>2883</v>
-      </c>
-      <c r="F126" s="27" t="s">
-        <v>2884</v>
       </c>
       <c r="G126" s="45" t="s">
         <v>626</v>
@@ -32459,18 +32459,18 @@
     </row>
     <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A127" s="27" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="B127" s="24" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C127" s="22"/>
       <c r="D127" s="27"/>
       <c r="E127" s="27" t="s">
+        <v>2884</v>
+      </c>
+      <c r="F127" s="27" t="s">
         <v>2885</v>
-      </c>
-      <c r="F127" s="27" t="s">
-        <v>2886</v>
       </c>
       <c r="G127" s="45" t="s">
         <v>626</v>
@@ -32666,7 +32666,7 @@
     </row>
     <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="27" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="B138" s="27" t="s">
         <v>1533</v>
@@ -32674,10 +32674,10 @@
       <c r="C138" s="22"/>
       <c r="D138" s="27"/>
       <c r="E138" s="27" t="s">
+        <v>2189</v>
+      </c>
+      <c r="F138" s="27" t="s">
         <v>2190</v>
-      </c>
-      <c r="F138" s="27" t="s">
-        <v>2191</v>
       </c>
       <c r="G138" s="45" t="s">
         <v>626</v>
@@ -33192,7 +33192,7 @@
     </row>
     <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="27" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="B166" s="27" t="s">
         <v>1581</v>
@@ -33200,10 +33200,10 @@
       <c r="C166" s="22"/>
       <c r="D166" s="27"/>
       <c r="E166" s="27" t="s">
+        <v>2708</v>
+      </c>
+      <c r="F166" s="27" t="s">
         <v>2709</v>
-      </c>
-      <c r="F166" s="27" t="s">
-        <v>2710</v>
       </c>
       <c r="G166" s="45" t="s">
         <v>626</v>
@@ -34552,13 +34552,13 @@
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A6" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B6" s="52"/>
       <c r="C6" s="36"/>
       <c r="D6" s="52"/>
       <c r="E6" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="F6" s="52" t="s">
         <v>1717</v>
@@ -34685,7 +34685,7 @@
         <v>569</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C12" s="36"/>
       <c r="D12" s="52"/>
@@ -34984,7 +34984,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A26" s="52" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>866</v>
@@ -34992,16 +34992,16 @@
       <c r="C26" s="36"/>
       <c r="D26" s="52"/>
       <c r="E26" s="52" t="s">
+        <v>2710</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>2711</v>
-      </c>
-      <c r="F26" s="52" t="s">
-        <v>2712</v>
       </c>
       <c r="G26" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35029,7 +35029,7 @@
         <v>577</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C28" s="36"/>
       <c r="D28" s="52"/>
@@ -35085,7 +35085,7 @@
         <v>290</v>
       </c>
       <c r="H30" s="52" t="s">
-        <v>2115</v>
+        <v>2886</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35147,7 +35147,7 @@
         <v>290</v>
       </c>
       <c r="H33" s="52" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35415,7 +35415,7 @@
         <v>580</v>
       </c>
       <c r="B46" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C46" s="36"/>
       <c r="D46" s="52"/>
@@ -35518,7 +35518,7 @@
     </row>
     <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A51" s="52" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="B51" s="52" t="s">
         <v>213</v>
@@ -35526,21 +35526,21 @@
       <c r="C51" s="36"/>
       <c r="D51" s="52"/>
       <c r="E51" s="52" t="s">
+        <v>2731</v>
+      </c>
+      <c r="F51" s="52" t="s">
         <v>2732</v>
-      </c>
-      <c r="F51" s="52" t="s">
-        <v>2733</v>
       </c>
       <c r="G51" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H51" s="52" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="52" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
       <c r="B52" s="52" t="s">
         <v>213</v>
@@ -35548,21 +35548,21 @@
       <c r="C52" s="36"/>
       <c r="D52" s="52"/>
       <c r="E52" s="52" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F52" s="52" t="s">
         <v>2735</v>
-      </c>
-      <c r="F52" s="52" t="s">
-        <v>2736</v>
       </c>
       <c r="G52" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H52" s="52" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="52" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="B53" s="52" t="s">
         <v>213</v>
@@ -35570,16 +35570,16 @@
       <c r="C53" s="36"/>
       <c r="D53" s="52"/>
       <c r="E53" s="52" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F53" s="52" t="s">
         <v>2742</v>
-      </c>
-      <c r="F53" s="52" t="s">
-        <v>2743</v>
       </c>
       <c r="G53" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35587,7 +35587,7 @@
         <v>583</v>
       </c>
       <c r="B54" s="52" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="C54" s="36"/>
       <c r="D54" s="52"/>
@@ -35670,22 +35670,22 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A58" s="52" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="B58" s="52"/>
       <c r="C58" s="36"/>
       <c r="D58" s="52"/>
       <c r="E58" s="52" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F58" s="52" t="s">
         <v>2654</v>
-      </c>
-      <c r="F58" s="52" t="s">
-        <v>2655</v>
       </c>
       <c r="G58" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H58" s="52" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35859,7 +35859,7 @@
         <v>290</v>
       </c>
       <c r="H66" s="52" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35972,7 +35972,7 @@
     </row>
     <row r="72" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A72" s="52" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="B72" s="52" t="s">
         <v>832</v>
@@ -35980,36 +35980,36 @@
       <c r="C72" s="53"/>
       <c r="D72" s="52"/>
       <c r="E72" s="52" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="F72" s="52" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="G72" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H72" s="52" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A73" s="33" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B73" s="52"/>
       <c r="C73" s="53"/>
       <c r="D73" s="33"/>
       <c r="E73" s="33" t="s">
+        <v>2315</v>
+      </c>
+      <c r="F73" s="33" t="s">
         <v>2316</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>2317</v>
       </c>
       <c r="G73" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H73" s="45" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
     </row>
   </sheetData>
@@ -36058,7 +36058,7 @@
         <v>78</v>
       </c>
       <c r="I1" s="110" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36083,7 +36083,7 @@
         <v>78</v>
       </c>
       <c r="I2" s="110" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36108,7 +36108,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="110" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36133,7 +36133,7 @@
         <v>78</v>
       </c>
       <c r="I4" s="110" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36158,7 +36158,7 @@
         <v>78</v>
       </c>
       <c r="I5" s="110" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36183,7 +36183,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="110" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36208,7 +36208,7 @@
         <v>78</v>
       </c>
       <c r="I7" s="110" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36231,7 +36231,7 @@
         <v>78</v>
       </c>
       <c r="I8" s="110" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36256,7 +36256,7 @@
         <v>84</v>
       </c>
       <c r="I9" s="110" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36279,7 +36279,7 @@
         <v>84</v>
       </c>
       <c r="I10" s="110" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36302,7 +36302,7 @@
         <v>78</v>
       </c>
       <c r="I11" s="110" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36327,7 +36327,7 @@
         <v>78</v>
       </c>
       <c r="I12" s="110" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36352,7 +36352,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="110" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36377,7 +36377,7 @@
         <v>78</v>
       </c>
       <c r="I14" s="110" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36402,7 +36402,7 @@
         <v>78</v>
       </c>
       <c r="I15" s="110" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36427,7 +36427,7 @@
         <v>78</v>
       </c>
       <c r="I16" s="110" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36450,7 +36450,7 @@
         <v>78</v>
       </c>
       <c r="I17" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36475,7 +36475,7 @@
         <v>78</v>
       </c>
       <c r="I18" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36500,7 +36500,7 @@
         <v>78</v>
       </c>
       <c r="I19" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36525,7 +36525,7 @@
         <v>84</v>
       </c>
       <c r="I20" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36550,7 +36550,7 @@
         <v>78</v>
       </c>
       <c r="I21" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36575,7 +36575,7 @@
         <v>78</v>
       </c>
       <c r="I22" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36600,7 +36600,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36625,7 +36625,7 @@
         <v>78</v>
       </c>
       <c r="I24" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36650,7 +36650,7 @@
         <v>78</v>
       </c>
       <c r="I25" s="110" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36673,7 +36673,7 @@
         <v>78</v>
       </c>
       <c r="I26" s="110" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36696,7 +36696,7 @@
         <v>78</v>
       </c>
       <c r="I27" s="110" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36719,7 +36719,7 @@
         <v>84</v>
       </c>
       <c r="I28" s="110" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36744,7 +36744,7 @@
         <v>84</v>
       </c>
       <c r="I29" s="110" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36769,7 +36769,7 @@
         <v>84</v>
       </c>
       <c r="I30" s="110" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36794,7 +36794,7 @@
         <v>84</v>
       </c>
       <c r="I31" s="110" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36819,7 +36819,7 @@
         <v>84</v>
       </c>
       <c r="I32" s="110" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36842,7 +36842,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="110" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36867,7 +36867,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="110" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36892,7 +36892,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="110" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36917,7 +36917,7 @@
         <v>78</v>
       </c>
       <c r="I36" s="110" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36940,7 +36940,7 @@
         <v>84</v>
       </c>
       <c r="I37" s="110" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36965,7 +36965,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="110" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36988,7 +36988,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="110" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37013,7 +37013,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="110" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37036,7 +37036,7 @@
         <v>84</v>
       </c>
       <c r="I41" s="110" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37061,7 +37061,7 @@
         <v>84</v>
       </c>
       <c r="I42" s="110" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37086,7 +37086,7 @@
         <v>84</v>
       </c>
       <c r="I43" s="110" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37111,7 +37111,7 @@
         <v>84</v>
       </c>
       <c r="I44" s="110" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37136,7 +37136,7 @@
         <v>84</v>
       </c>
       <c r="I45" s="110" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37161,7 +37161,7 @@
         <v>84</v>
       </c>
       <c r="I46" s="110" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37186,7 +37186,7 @@
         <v>84</v>
       </c>
       <c r="I47" s="110" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37211,7 +37211,7 @@
         <v>84</v>
       </c>
       <c r="I48" s="110" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37236,7 +37236,7 @@
         <v>84</v>
       </c>
       <c r="I49" s="110" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37261,7 +37261,7 @@
         <v>84</v>
       </c>
       <c r="I50" s="110" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37286,7 +37286,7 @@
         <v>84</v>
       </c>
       <c r="I51" s="110" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37311,7 +37311,7 @@
         <v>84</v>
       </c>
       <c r="I52" s="110" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37336,7 +37336,7 @@
         <v>84</v>
       </c>
       <c r="I53" s="110" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37361,7 +37361,7 @@
         <v>84</v>
       </c>
       <c r="I54" s="110" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37386,7 +37386,7 @@
         <v>78</v>
       </c>
       <c r="I55" s="110" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37411,7 +37411,7 @@
         <v>84</v>
       </c>
       <c r="I56" s="110" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37425,7 +37425,7 @@
         <v>1251</v>
       </c>
       <c r="F57" s="110" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="G57" s="110" t="s">
         <v>86</v>
@@ -37434,7 +37434,7 @@
         <v>78</v>
       </c>
       <c r="I57" s="110" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
     </row>
   </sheetData>
@@ -37475,7 +37475,7 @@
   <sheetData>
     <row r="1" spans="1:23" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>232</v>
@@ -37487,13 +37487,13 @@
         <v>76</v>
       </c>
       <c r="G1" s="106" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="I1" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="J1" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="K1" s="56" t="s">
         <v>215</v>
@@ -37505,7 +37505,7 @@
         <v>257</v>
       </c>
       <c r="R1" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="S1" s="68" t="s">
         <v>826</v>
@@ -37517,18 +37517,18 @@
         <v>829</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W1" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>232</v>
@@ -37540,13 +37540,13 @@
         <v>76</v>
       </c>
       <c r="G2" s="106" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="I2" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="J2" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="K2" s="56" t="s">
         <v>215</v>
@@ -37561,10 +37561,10 @@
         <v>1077</v>
       </c>
       <c r="O2" s="105" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R2" s="33" t="s">
         <v>682</v>
@@ -37579,18 +37579,18 @@
         <v>213</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W2" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="B3" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>232</v>
@@ -37602,13 +37602,13 @@
         <v>76</v>
       </c>
       <c r="G3" s="106" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="I3" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="J3" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="K3" s="56" t="s">
         <v>215</v>
@@ -37623,10 +37623,10 @@
         <v>1080</v>
       </c>
       <c r="O3" s="105" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R3" s="33" t="s">
         <v>674</v>
@@ -37641,18 +37641,18 @@
         <v>577</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W3" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="4" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="B4" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C4" s="41" t="s">
         <v>232</v>
@@ -37664,13 +37664,13 @@
         <v>76</v>
       </c>
       <c r="G4" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I4" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="J4" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>215</v>
@@ -37685,10 +37685,10 @@
         <v>1077</v>
       </c>
       <c r="O4" s="105" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R4" s="33" t="s">
         <v>682</v>
@@ -37703,18 +37703,18 @@
         <v>213</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W4" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="105" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>232</v>
@@ -37726,13 +37726,13 @@
         <v>76</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I5" s="105" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="J5" s="105" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="K5" s="56" t="s">
         <v>215</v>
@@ -37747,10 +37747,10 @@
         <v>1080</v>
       </c>
       <c r="O5" s="105" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R5" s="33" t="s">
         <v>674</v>
@@ -37765,15 +37765,15 @@
         <v>577</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W5" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="6" spans="1:23" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>232</v>
@@ -37785,13 +37785,13 @@
         <v>76</v>
       </c>
       <c r="G6" s="106" t="s">
+        <v>2780</v>
+      </c>
+      <c r="I6" s="105" t="s">
         <v>2781</v>
       </c>
-      <c r="I6" s="105" t="s">
-        <v>2782</v>
-      </c>
       <c r="J6" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="K6" s="56" t="s">
         <v>215</v>
@@ -37803,7 +37803,7 @@
         <v>257</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="S6" s="68" t="s">
         <v>826</v>
@@ -37815,18 +37815,18 @@
         <v>829</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W6" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>232</v>
@@ -37841,13 +37841,13 @@
         <v>76</v>
       </c>
       <c r="G7" s="106" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="I7" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="J7" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="K7" s="56" t="s">
         <v>215</v>
@@ -37863,7 +37863,7 @@
       </c>
       <c r="O7" s="105"/>
       <c r="Q7" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>674</v>
@@ -37878,18 +37878,18 @@
         <v>577</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W7" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="105" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>232</v>
@@ -37904,13 +37904,13 @@
         <v>76</v>
       </c>
       <c r="G8" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I8" s="105" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="J8" s="105" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="K8" s="56" t="s">
         <v>215</v>
@@ -37926,7 +37926,7 @@
       </c>
       <c r="O8" s="105"/>
       <c r="Q8" s="27" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="R8" s="33" t="s">
         <v>674</v>
@@ -37941,10 +37941,10 @@
         <v>577</v>
       </c>
       <c r="V8" s="37" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="W8" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
   </sheetData>
@@ -38706,7 +38706,7 @@
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="77" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="F29" s="77" t="s">
         <v>76</v>
@@ -38716,7 +38716,7 @@
       </c>
       <c r="H29" s="77"/>
       <c r="I29" s="77" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="J29" s="77" t="s">
         <v>1840</v>
@@ -38728,7 +38728,7 @@
         <v>851</v>
       </c>
       <c r="T29" s="77" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="U29" s="77" t="s">
         <v>1734</v>
@@ -39269,7 +39269,7 @@
         <v>835</v>
       </c>
       <c r="T50" s="77" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="U50" s="77" t="s">
         <v>1728</v>
@@ -39321,7 +39321,7 @@
     </row>
     <row r="52" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="77" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="F52" s="77" t="s">
         <v>76</v>
@@ -39333,10 +39333,10 @@
         <v>1917</v>
       </c>
       <c r="I52" s="77" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="J52" s="77" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="K52" s="77" t="s">
         <v>215</v>
@@ -39345,7 +39345,7 @@
         <v>835</v>
       </c>
       <c r="T52" s="77" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="U52" s="77" t="s">
         <v>1728</v>
@@ -39359,7 +39359,7 @@
     </row>
     <row r="53" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="77" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="F53" s="77" t="s">
         <v>76</v>
@@ -39371,10 +39371,10 @@
         <v>1921</v>
       </c>
       <c r="I53" s="77" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="J53" s="77" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="K53" s="77" t="s">
         <v>215</v>
@@ -39383,7 +39383,7 @@
         <v>835</v>
       </c>
       <c r="T53" s="77" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="U53" s="77" t="s">
         <v>1728</v>
@@ -39397,7 +39397,7 @@
     </row>
     <row r="54" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="77" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="F54" s="77" t="s">
         <v>76</v>
@@ -39406,13 +39406,13 @@
         <v>1924</v>
       </c>
       <c r="H54" s="77" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="I54" s="77" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="J54" s="77" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="K54" s="77" t="s">
         <v>215</v>
@@ -39421,7 +39421,7 @@
         <v>835</v>
       </c>
       <c r="T54" s="77" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="U54" s="77" t="s">
         <v>1728</v>
@@ -39435,22 +39435,22 @@
     </row>
     <row r="55" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="77" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="F55" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G55" s="77" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="H55" s="77" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="I55" s="77" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="J55" s="77" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="K55" s="77" t="s">
         <v>215</v>
@@ -39459,7 +39459,7 @@
         <v>835</v>
       </c>
       <c r="T55" s="77" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="U55" s="77" t="s">
         <v>1728</v>
@@ -39473,22 +39473,22 @@
     </row>
     <row r="56" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="77" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="F56" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G56" s="77" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="H56" s="77" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="I56" s="77" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="J56" s="77" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="K56" s="77" t="s">
         <v>215</v>
@@ -39497,7 +39497,7 @@
         <v>835</v>
       </c>
       <c r="T56" s="77" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="U56" s="77" t="s">
         <v>1728</v>
@@ -39511,22 +39511,22 @@
     </row>
     <row r="57" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="77" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="F57" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G57" s="77" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="H57" s="77" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="I57" s="77" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="J57" s="77" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="K57" s="77" t="s">
         <v>215</v>
@@ -39535,7 +39535,7 @@
         <v>835</v>
       </c>
       <c r="T57" s="77" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="U57" s="77" t="s">
         <v>1728</v>
@@ -39549,22 +39549,22 @@
     </row>
     <row r="58" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="77" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="F58" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G58" s="77" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="H58" s="77" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="I58" s="77" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="J58" s="77" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="K58" s="77" t="s">
         <v>215</v>
@@ -39573,7 +39573,7 @@
         <v>835</v>
       </c>
       <c r="T58" s="77" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="U58" s="77" t="s">
         <v>1728</v>
@@ -39587,22 +39587,22 @@
     </row>
     <row r="59" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="77" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="F59" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G59" s="77" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="H59" s="77" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="I59" s="77" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="J59" s="77" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="K59" s="77" t="s">
         <v>215</v>
@@ -39611,7 +39611,7 @@
         <v>835</v>
       </c>
       <c r="T59" s="77" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="U59" s="77" t="s">
         <v>1728</v>
@@ -39625,22 +39625,22 @@
     </row>
     <row r="60" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="77" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="F60" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G60" s="77" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="H60" s="77" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="I60" s="77" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="J60" s="77" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="K60" s="77" t="s">
         <v>215</v>
@@ -39649,7 +39649,7 @@
         <v>835</v>
       </c>
       <c r="T60" s="77" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="U60" s="77" t="s">
         <v>1728</v>
@@ -39663,22 +39663,22 @@
     </row>
     <row r="61" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="77" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="F61" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="77" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="H61" s="77" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="I61" s="77" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="J61" s="77" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="K61" s="77" t="s">
         <v>215</v>
@@ -39687,7 +39687,7 @@
         <v>835</v>
       </c>
       <c r="T61" s="77" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="U61" s="77" t="s">
         <v>1728</v>
@@ -39701,22 +39701,22 @@
     </row>
     <row r="62" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="77" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="F62" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G62" s="77" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="H62" s="77" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="I62" s="77" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="J62" s="77" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="K62" s="77" t="s">
         <v>215</v>
@@ -39725,7 +39725,7 @@
         <v>835</v>
       </c>
       <c r="T62" s="77" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="U62" s="77" t="s">
         <v>1728</v>
@@ -39739,22 +39739,22 @@
     </row>
     <row r="63" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="77" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="F63" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G63" s="77" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="H63" s="77" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="I63" s="77" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="J63" s="77" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="K63" s="77" t="s">
         <v>215</v>
@@ -39763,7 +39763,7 @@
         <v>835</v>
       </c>
       <c r="T63" s="77" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="U63" s="77" t="s">
         <v>1728</v>
@@ -39777,22 +39777,22 @@
     </row>
     <row r="64" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="77" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="F64" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G64" s="77" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="H64" s="77" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="I64" s="77" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="J64" s="77" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="K64" s="77" t="s">
         <v>215</v>
@@ -39801,7 +39801,7 @@
         <v>835</v>
       </c>
       <c r="T64" s="77" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="U64" s="77" t="s">
         <v>1728</v>
@@ -39815,22 +39815,22 @@
     </row>
     <row r="65" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="77" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="F65" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G65" s="77" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="H65" s="77" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="I65" s="77" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="J65" s="77" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="K65" s="77" t="s">
         <v>215</v>
@@ -39839,7 +39839,7 @@
         <v>835</v>
       </c>
       <c r="T65" s="77" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="U65" s="77" t="s">
         <v>1728</v>
@@ -40147,7 +40147,7 @@
     </row>
     <row r="75" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="77" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="F75" s="77" t="s">
         <v>76</v>
@@ -40159,10 +40159,10 @@
         <v>1917</v>
       </c>
       <c r="I75" s="77" t="s">
+        <v>2618</v>
+      </c>
+      <c r="J75" s="77" t="s">
         <v>2619</v>
-      </c>
-      <c r="J75" s="77" t="s">
-        <v>2620</v>
       </c>
       <c r="K75" s="77" t="s">
         <v>215</v>
@@ -40171,7 +40171,7 @@
         <v>819</v>
       </c>
       <c r="T75" s="77" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="U75" s="77" t="s">
         <v>577</v>
@@ -40737,7 +40737,7 @@
     </row>
     <row r="97" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="77" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="F97" s="77" t="s">
         <v>76</v>
@@ -40746,10 +40746,10 @@
         <v>1916</v>
       </c>
       <c r="I97" s="77" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="J97" s="77" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="K97" s="77" t="s">
         <v>215</v>
@@ -40761,7 +40761,7 @@
         <v>854</v>
       </c>
       <c r="T97" s="75" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="U97" s="82" t="s">
         <v>1752</v>
@@ -40801,7 +40801,7 @@
     </row>
     <row r="100" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="77" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="F100" s="77" t="s">
         <v>76</v>
@@ -40810,10 +40810,10 @@
         <v>1916</v>
       </c>
       <c r="I100" s="77" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="J100" s="77" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="K100" s="77" t="s">
         <v>215</v>
@@ -40825,7 +40825,7 @@
         <v>854</v>
       </c>
       <c r="T100" s="75" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="U100" s="77" t="s">
         <v>856</v>
@@ -40973,7 +40973,7 @@
     </row>
     <row r="107" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="79" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="F107" s="77" t="s">
         <v>76</v>
@@ -40983,7 +40983,7 @@
       </c>
       <c r="H107" s="77"/>
       <c r="I107" s="79" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="J107" s="79" t="s">
         <v>366</v>
@@ -41001,7 +41001,7 @@
         <v>827</v>
       </c>
       <c r="T107" s="75" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="U107" s="82" t="s">
         <v>1752</v>
@@ -41578,7 +41578,7 @@
     </row>
     <row r="131" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="77" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="F131" s="77" t="s">
         <v>76</v>
@@ -41587,7 +41587,7 @@
         <v>1916</v>
       </c>
       <c r="I131" s="77" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="J131" s="77" t="s">
         <v>2074</v>
@@ -41602,7 +41602,7 @@
         <v>827</v>
       </c>
       <c r="T131" s="75" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="U131" s="77" t="s">
         <v>1754</v>
@@ -41811,7 +41811,7 @@
     </row>
     <row r="141" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="77" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="F141" s="77" t="s">
         <v>76</v>
@@ -41820,7 +41820,7 @@
         <v>1916</v>
       </c>
       <c r="I141" s="77" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="J141" s="77" t="s">
         <v>2079</v>
@@ -41835,7 +41835,7 @@
         <v>827</v>
       </c>
       <c r="T141" s="75" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="U141" s="77" t="s">
         <v>1754</v>
@@ -42021,7 +42021,7 @@
     </row>
     <row r="149" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="77" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="F149" s="77" t="s">
         <v>76</v>
@@ -42030,7 +42030,7 @@
         <v>1916</v>
       </c>
       <c r="I149" s="77" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="J149" s="77" t="s">
         <v>1906</v>
@@ -42045,7 +42045,7 @@
         <v>854</v>
       </c>
       <c r="T149" s="75" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="U149" s="77" t="s">
         <v>856</v>
@@ -42085,7 +42085,7 @@
     </row>
     <row r="152" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="77" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="F152" s="77" t="s">
         <v>76</v>
@@ -42094,10 +42094,10 @@
         <v>1846</v>
       </c>
       <c r="I152" s="77" t="s">
+        <v>2628</v>
+      </c>
+      <c r="J152" s="77" t="s">
         <v>2629</v>
-      </c>
-      <c r="J152" s="77" t="s">
-        <v>2630</v>
       </c>
       <c r="K152" s="77" t="s">
         <v>215</v>
@@ -42109,7 +42109,7 @@
         <v>827</v>
       </c>
       <c r="T152" s="75" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="U152" s="82" t="s">
         <v>1752</v>
@@ -42371,7 +42371,7 @@
     </row>
     <row r="162" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="77" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="F162" s="77" t="s">
         <v>76</v>
@@ -42380,7 +42380,7 @@
         <v>1916</v>
       </c>
       <c r="I162" s="77" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="J162" s="77" t="s">
         <v>464</v>
@@ -42398,7 +42398,7 @@
         <v>854</v>
       </c>
       <c r="T162" s="75" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="U162" s="77" t="s">
         <v>856</v>
@@ -42484,7 +42484,7 @@
     </row>
     <row r="166" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="77" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F166" s="77" t="s">
         <v>76</v>
@@ -42493,7 +42493,7 @@
         <v>1916</v>
       </c>
       <c r="I166" s="77" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="J166" s="77" t="s">
         <v>468</v>
@@ -42511,7 +42511,7 @@
         <v>854</v>
       </c>
       <c r="T166" s="75" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="U166" s="77" t="s">
         <v>856</v>
@@ -42553,19 +42553,19 @@
     </row>
     <row r="169" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="77" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="F169" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G169" s="77" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="H169" s="77" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="I169" s="77" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="J169" s="77" t="s">
         <v>1907</v>
@@ -42625,7 +42625,7 @@
     </row>
     <row r="172" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="77" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="F172" s="77" t="s">
         <v>76</v>
@@ -42635,10 +42635,10 @@
       </c>
       <c r="H172" s="77"/>
       <c r="I172" s="77" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="J172" s="77" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K172" s="77" t="s">
         <v>215</v>
@@ -42667,7 +42667,7 @@
     </row>
     <row r="173" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="77" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="F173" s="77" t="s">
         <v>76</v>
@@ -42677,10 +42677,10 @@
       </c>
       <c r="H173" s="77"/>
       <c r="I173" s="77" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="J173" s="77" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="K173" s="77" t="s">
         <v>215</v>
@@ -42695,7 +42695,7 @@
         <v>854</v>
       </c>
       <c r="T173" s="75" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="U173" s="77" t="s">
         <v>856</v>
@@ -42781,7 +42781,7 @@
     </row>
     <row r="177" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="77" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F177" s="77" t="s">
         <v>76</v>
@@ -42790,7 +42790,7 @@
         <v>1916</v>
       </c>
       <c r="I177" s="77" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="J177" s="77" t="s">
         <v>487</v>
@@ -42808,7 +42808,7 @@
         <v>854</v>
       </c>
       <c r="T177" s="75" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="U177" s="77" t="s">
         <v>856</v>
@@ -42850,19 +42850,19 @@
     </row>
     <row r="180" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="77" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="F180" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G180" s="77" t="s">
+        <v>2631</v>
+      </c>
+      <c r="H180" s="77" t="s">
+        <v>2633</v>
+      </c>
+      <c r="I180" s="77" t="s">
         <v>2632</v>
-      </c>
-      <c r="H180" s="77" t="s">
-        <v>2634</v>
-      </c>
-      <c r="I180" s="77" t="s">
-        <v>2633</v>
       </c>
       <c r="J180" s="77" t="s">
         <v>1908</v>
@@ -42924,7 +42924,7 @@
     </row>
     <row r="183" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="77" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="F183" s="77" t="s">
         <v>76</v>
@@ -42934,10 +42934,10 @@
       </c>
       <c r="H183" s="77"/>
       <c r="I183" s="77" t="s">
+        <v>2634</v>
+      </c>
+      <c r="J183" s="77" t="s">
         <v>2635</v>
-      </c>
-      <c r="J183" s="77" t="s">
-        <v>2636</v>
       </c>
       <c r="K183" s="77" t="s">
         <v>215</v>
@@ -42966,7 +42966,7 @@
     </row>
     <row r="184" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="77" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="F184" s="77" t="s">
         <v>76</v>
@@ -42976,10 +42976,10 @@
       </c>
       <c r="H184" s="77"/>
       <c r="I184" s="77" t="s">
+        <v>2636</v>
+      </c>
+      <c r="J184" s="77" t="s">
         <v>2637</v>
-      </c>
-      <c r="J184" s="77" t="s">
-        <v>2638</v>
       </c>
       <c r="K184" s="77" t="s">
         <v>215</v>
@@ -42994,7 +42994,7 @@
         <v>854</v>
       </c>
       <c r="T184" s="75" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="U184" s="77" t="s">
         <v>856</v>
@@ -43035,7 +43035,7 @@
     </row>
     <row r="187" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="77" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="F187" s="77" t="s">
         <v>76</v>
@@ -43044,10 +43044,10 @@
         <v>876</v>
       </c>
       <c r="I187" s="77" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="J187" s="77" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="K187" s="77" t="s">
         <v>215</v>
@@ -43062,13 +43062,13 @@
         <v>846</v>
       </c>
       <c r="T187" s="75" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="U187" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V187" s="78" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="W187" s="77" t="s">
         <v>815</v>
@@ -43076,7 +43076,7 @@
     </row>
     <row r="188" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="77" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="F188" s="77" t="s">
         <v>76</v>
@@ -43085,10 +43085,10 @@
         <v>876</v>
       </c>
       <c r="I188" s="77" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="J188" s="77" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="K188" s="77" t="s">
         <v>215</v>
@@ -43103,13 +43103,13 @@
         <v>846</v>
       </c>
       <c r="T188" s="75" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="U188" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V188" s="78" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="W188" s="77" t="s">
         <v>815</v>
@@ -43117,7 +43117,7 @@
     </row>
     <row r="189" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="77" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="F189" s="77" t="s">
         <v>76</v>
@@ -43126,10 +43126,10 @@
         <v>876</v>
       </c>
       <c r="I189" s="77" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="J189" s="77" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="K189" s="77" t="s">
         <v>215</v>
@@ -43144,13 +43144,13 @@
         <v>846</v>
       </c>
       <c r="T189" s="75" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="U189" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V189" s="78" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="W189" s="77" t="s">
         <v>815</v>
@@ -43158,7 +43158,7 @@
     </row>
     <row r="190" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="77" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="F190" s="77" t="s">
         <v>76</v>
@@ -43167,10 +43167,10 @@
         <v>876</v>
       </c>
       <c r="I190" s="77" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="J190" s="77" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="K190" s="77" t="s">
         <v>215</v>
@@ -43185,13 +43185,13 @@
         <v>846</v>
       </c>
       <c r="T190" s="75" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="U190" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V190" s="78" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="W190" s="77" t="s">
         <v>815</v>
@@ -43297,7 +43297,7 @@
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="75" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="F196" s="75" t="s">
         <v>76</v>
@@ -43309,10 +43309,10 @@
         <v>1862</v>
       </c>
       <c r="I196" s="75" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="J196" s="75" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="K196" s="75" t="s">
         <v>215</v>
@@ -43324,13 +43324,13 @@
         <v>860</v>
       </c>
       <c r="T196" s="75" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="U196" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V196" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W196" s="77" t="s">
         <v>815</v>
@@ -43338,7 +43338,7 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="75" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="F197" s="75" t="s">
         <v>76</v>
@@ -43350,10 +43350,10 @@
         <v>1867</v>
       </c>
       <c r="I197" s="75" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="J197" s="75" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="K197" s="75" t="s">
         <v>215</v>
@@ -43365,13 +43365,13 @@
         <v>860</v>
       </c>
       <c r="T197" s="75" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="U197" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V197" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W197" s="77" t="s">
         <v>815</v>
@@ -43379,7 +43379,7 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="75" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="F198" s="75" t="s">
         <v>76</v>
@@ -43391,10 +43391,10 @@
         <v>1871</v>
       </c>
       <c r="I198" s="75" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="J198" s="75" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="K198" s="75" t="s">
         <v>215</v>
@@ -43406,13 +43406,13 @@
         <v>860</v>
       </c>
       <c r="T198" s="75" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="U198" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V198" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W198" s="77" t="s">
         <v>815</v>
@@ -43420,7 +43420,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="75" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="F199" s="75" t="s">
         <v>76</v>
@@ -43432,10 +43432,10 @@
         <v>1913</v>
       </c>
       <c r="I199" s="75" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="J199" s="75" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="K199" s="75" t="s">
         <v>215</v>
@@ -43447,13 +43447,13 @@
         <v>860</v>
       </c>
       <c r="T199" s="75" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="U199" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V199" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W199" s="77" t="s">
         <v>815</v>
@@ -43461,7 +43461,7 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="75" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="F200" s="75" t="s">
         <v>76</v>
@@ -43473,10 +43473,10 @@
         <v>1917</v>
       </c>
       <c r="I200" s="75" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="J200" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="K200" s="75" t="s">
         <v>215</v>
@@ -43488,13 +43488,13 @@
         <v>860</v>
       </c>
       <c r="T200" s="75" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="U200" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V200" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W200" s="77" t="s">
         <v>815</v>
@@ -43502,7 +43502,7 @@
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="75" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="F201" s="75" t="s">
         <v>76</v>
@@ -43514,10 +43514,10 @@
         <v>1921</v>
       </c>
       <c r="I201" s="75" t="s">
+        <v>2671</v>
+      </c>
+      <c r="J201" s="75" t="s">
         <v>2672</v>
-      </c>
-      <c r="J201" s="75" t="s">
-        <v>2673</v>
       </c>
       <c r="K201" s="75" t="s">
         <v>215</v>
@@ -43529,10 +43529,10 @@
         <v>860</v>
       </c>
       <c r="U201" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V201" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W201" s="75" t="s">
         <v>815</v>
@@ -43540,7 +43540,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="75" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="F202" s="75" t="s">
         <v>76</v>
@@ -43549,13 +43549,13 @@
         <v>1924</v>
       </c>
       <c r="H202" s="75" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="I202" s="75" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J202" s="75" t="s">
         <v>2674</v>
-      </c>
-      <c r="J202" s="75" t="s">
-        <v>2675</v>
       </c>
       <c r="K202" s="75" t="s">
         <v>215</v>
@@ -43567,10 +43567,10 @@
         <v>860</v>
       </c>
       <c r="U202" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V202" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W202" s="75" t="s">
         <v>815</v>
@@ -43578,22 +43578,22 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="75" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="F203" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G203" s="75" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="H203" s="75" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="I203" s="75" t="s">
+        <v>2675</v>
+      </c>
+      <c r="J203" s="75" t="s">
         <v>2676</v>
-      </c>
-      <c r="J203" s="75" t="s">
-        <v>2677</v>
       </c>
       <c r="K203" s="75" t="s">
         <v>215</v>
@@ -43605,10 +43605,10 @@
         <v>860</v>
       </c>
       <c r="U203" s="75" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="V203" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="W203" s="75" t="s">
         <v>815</v>
@@ -43665,7 +43665,7 @@
         <v>591</v>
       </c>
       <c r="J1" s="26" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K1" s="26" t="s">
         <v>217</v>
@@ -43676,13 +43676,13 @@
     </row>
     <row r="2" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="84"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>90</v>
@@ -43691,16 +43691,16 @@
         <v>215</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>591</v>
       </c>
       <c r="J2" s="26" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="L2" s="87" t="s">
         <v>815</v>
@@ -43708,70 +43708,70 @@
     </row>
     <row r="3" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C3" s="84"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="I3" s="26" t="s">
         <v>591</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="L3" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C4" s="84"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="I4" s="26" t="s">
         <v>591</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="L4" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -43800,7 +43800,7 @@
         <v>213</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="L5" s="87" t="s">
         <v>815</v>
@@ -43808,7 +43808,7 @@
     </row>
     <row r="6" spans="1:12" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>218</v>
@@ -43816,16 +43816,16 @@
       <c r="C6" s="84"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26" t="s">
+        <v>2464</v>
+      </c>
+      <c r="F6" s="86" t="s">
         <v>2465</v>
       </c>
-      <c r="F6" s="86" t="s">
-        <v>2466</v>
-      </c>
       <c r="G6" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>591</v>
@@ -43834,7 +43834,7 @@
         <v>213</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="L6" s="87" t="s">
         <v>815</v>
@@ -43842,16 +43842,16 @@
     </row>
     <row r="7" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B7" s="26"/>
       <c r="C7" s="84"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26" t="s">
+        <v>2261</v>
+      </c>
+      <c r="F7" s="86" t="s">
         <v>2262</v>
-      </c>
-      <c r="F7" s="86" t="s">
-        <v>2263</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>215</v>
@@ -43866,7 +43866,7 @@
         <v>213</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="L7" s="87" t="s">
         <v>815</v>
@@ -43874,24 +43874,24 @@
     </row>
     <row r="8" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="C8" s="84"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26" t="s">
+        <v>2467</v>
+      </c>
+      <c r="F8" s="86" t="s">
         <v>2468</v>
       </c>
-      <c r="F8" s="86" t="s">
-        <v>2469</v>
-      </c>
       <c r="G8" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="I8" s="26" t="s">
         <v>591</v>
@@ -43900,7 +43900,7 @@
         <v>213</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="L8" s="87" t="s">
         <v>815</v>
@@ -43932,129 +43932,129 @@
         <v>213</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="L9" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>2048</v>
       </c>
       <c r="C10" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D10" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D10" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E10" s="26" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="I10" s="31" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="J10" s="26" t="s">
         <v>577</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="L10" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>2048</v>
       </c>
       <c r="C11" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D11" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E11" s="26" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="I11" s="31" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="J11" s="26" t="s">
         <v>583</v>
       </c>
       <c r="K11" s="26" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="L11" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>2048</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D12" s="88" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>2134</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>2474</v>
+      </c>
+      <c r="I12" s="31" t="s">
         <v>2130</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>2135</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>2135</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>2475</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>2131</v>
       </c>
       <c r="J12" s="26" t="s">
         <v>213</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="L12" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>2048</v>
@@ -44063,19 +44063,19 @@
         <v>1912</v>
       </c>
       <c r="D13" s="88" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="G13" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="I13" s="33" t="s">
         <v>252</v>
@@ -44084,36 +44084,36 @@
         <v>213</v>
       </c>
       <c r="K13" s="26" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="L13" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>2048</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="D14" s="88" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="I14" s="33" t="s">
         <v>252</v>
@@ -44122,24 +44122,24 @@
         <v>213</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="L14" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="B15" s="26"/>
       <c r="C15" s="84"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26" t="s">
+        <v>2292</v>
+      </c>
+      <c r="F15" s="86" t="s">
         <v>2293</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>2294</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>215</v>
@@ -44154,7 +44154,7 @@
         <v>213</v>
       </c>
       <c r="K15" s="26" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="L15" s="87" t="s">
         <v>815</v>
@@ -44162,18 +44162,18 @@
     </row>
     <row r="16" spans="1:12" ht="87" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C16" s="84"/>
       <c r="D16" s="26"/>
       <c r="E16" s="26" t="s">
+        <v>2294</v>
+      </c>
+      <c r="F16" s="86" t="s">
         <v>2295</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>2296</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>215</v>
@@ -44188,7 +44188,7 @@
         <v>213</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="L16" s="87" t="s">
         <v>815</v>
@@ -44196,18 +44196,18 @@
     </row>
     <row r="17" spans="1:12" ht="84" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C17" s="84"/>
       <c r="D17" s="26"/>
       <c r="E17" s="26" t="s">
+        <v>2296</v>
+      </c>
+      <c r="F17" s="86" t="s">
         <v>2297</v>
-      </c>
-      <c r="F17" s="86" t="s">
-        <v>2298</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>215</v>
@@ -44222,7 +44222,7 @@
         <v>213</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="L17" s="87" t="s">
         <v>815</v>
@@ -44230,22 +44230,22 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="88"/>
       <c r="D18" s="26"/>
       <c r="E18" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>591</v>
@@ -44254,30 +44254,30 @@
         <v>829</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="L18" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A19" s="26" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="88"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>591</v>
@@ -44286,24 +44286,24 @@
         <v>829</v>
       </c>
       <c r="K19" s="26" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="L19" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="84"/>
       <c r="D20" s="26"/>
       <c r="E20" s="26" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F20" s="86" t="s">
         <v>2774</v>
-      </c>
-      <c r="F20" s="86" t="s">
-        <v>2775</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>215</v>
@@ -44318,7 +44318,7 @@
         <v>213</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="L20" s="87" t="s">
         <v>815</v>
@@ -44451,7 +44451,7 @@
         <v>234</v>
       </c>
       <c r="M3" s="28" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="N3" s="83" t="s">
         <v>815</v>
@@ -44655,7 +44655,7 @@
         <v>251</v>
       </c>
       <c r="M9" s="28" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="N9" s="83" t="s">
         <v>815</v>
@@ -44663,7 +44663,7 @@
     </row>
     <row r="10" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28" t="s">
@@ -44674,22 +44674,22 @@
       <c r="F10" s="32"/>
       <c r="G10" s="29"/>
       <c r="H10" s="28" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I10" s="28" t="s">
         <v>2291</v>
       </c>
-      <c r="I10" s="28" t="s">
-        <v>2292</v>
-      </c>
       <c r="J10" s="28" t="s">
         <v>215</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="L10" s="33" t="s">
         <v>254</v>
       </c>
       <c r="M10" s="28" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="N10" s="83" t="s">
         <v>815</v>
@@ -44697,7 +44697,7 @@
     </row>
     <row r="11" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28" t="s">
@@ -44708,10 +44708,10 @@
       <c r="F11" s="32"/>
       <c r="G11" s="29"/>
       <c r="H11" s="28" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I11" s="28" t="s">
         <v>2306</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>2307</v>
       </c>
       <c r="J11" s="28" t="s">
         <v>215</v>
@@ -44720,21 +44720,21 @@
         <v>250</v>
       </c>
       <c r="L11" s="31" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="M11" s="28" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="N11" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>232</v>
@@ -44742,39 +44742,39 @@
       <c r="D12" s="28"/>
       <c r="E12" s="28"/>
       <c r="F12" s="88" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="G12" s="88" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="H12" s="28" t="s">
+        <v>2303</v>
+      </c>
+      <c r="I12" s="28" t="s">
         <v>2304</v>
       </c>
-      <c r="I12" s="28" t="s">
-        <v>2305</v>
-      </c>
       <c r="J12" s="28" t="s">
         <v>215</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="L12" s="33" t="s">
         <v>254</v>
       </c>
       <c r="M12" s="28" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="N12" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>232</v>
@@ -44782,39 +44782,39 @@
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
       <c r="F13" s="88" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="G13" s="88" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="H13" s="28" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I13" s="28" t="s">
         <v>2314</v>
       </c>
-      <c r="I13" s="28" t="s">
-        <v>2315</v>
-      </c>
       <c r="J13" s="28" t="s">
         <v>215</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="L13" s="33" t="s">
         <v>254</v>
       </c>
       <c r="M13" s="28" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="N13" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>232</v>
@@ -44825,13 +44825,13 @@
         <v>1912</v>
       </c>
       <c r="G14" s="88" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="J14" s="28" t="s">
         <v>215</v>
@@ -44843,18 +44843,18 @@
         <v>254</v>
       </c>
       <c r="M14" s="28" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="N14" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="C15" s="28" t="s">
         <v>232</v>
@@ -44862,16 +44862,16 @@
       <c r="D15" s="28"/>
       <c r="E15" s="28"/>
       <c r="F15" s="88" t="s">
-        <v>2353</v>
+        <v>2352</v>
       </c>
       <c r="G15" s="88" t="s">
-        <v>2349</v>
+        <v>2348</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>2351</v>
+        <v>2350</v>
       </c>
       <c r="J15" s="28" t="s">
         <v>215</v>
@@ -44883,29 +44883,29 @@
         <v>254</v>
       </c>
       <c r="M15" s="28" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="N15" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
       <c r="E16" s="28" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="F16" s="22"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
+        <v>2775</v>
+      </c>
+      <c r="I16" s="28" t="s">
         <v>2776</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>2777</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>215</v>
@@ -47645,16 +47645,16 @@
     </row>
     <row r="98" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="B98" s="35"/>
       <c r="C98" s="36"/>
       <c r="D98" s="35"/>
       <c r="E98" s="35" t="s">
+        <v>2771</v>
+      </c>
+      <c r="F98" s="35" t="s">
         <v>2772</v>
-      </c>
-      <c r="F98" s="35" t="s">
-        <v>2773</v>
       </c>
       <c r="G98" s="35" t="s">
         <v>215</v>
@@ -47920,7 +47920,7 @@
         <v>254</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="K2" s="87" t="s">
         <v>815</v>
@@ -47928,72 +47928,72 @@
     </row>
     <row r="3" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>232</v>
       </c>
       <c r="C3" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D3" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D3" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E3" s="41" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F3" s="41" t="s">
         <v>2156</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>2157</v>
       </c>
       <c r="G3" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I3" s="33" t="s">
         <v>618</v>
       </c>
       <c r="J3" s="26" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="K3" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B4" s="41" t="s">
         <v>232</v>
       </c>
       <c r="C4" s="88" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D4" s="88" t="s">
         <v>2147</v>
       </c>
-      <c r="D4" s="88" t="s">
-        <v>2148</v>
-      </c>
       <c r="E4" s="41" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F4" s="41" t="s">
         <v>2161</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>2162</v>
       </c>
       <c r="G4" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I4" s="33" t="s">
         <v>621</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="K4" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
@@ -48004,7 +48004,7 @@
         <v>232</v>
       </c>
       <c r="C5" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D5" s="88"/>
       <c r="E5" s="41" t="s">
@@ -48023,7 +48023,7 @@
         <v>254</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="K5" s="87" t="s">
         <v>815</v>
@@ -48031,26 +48031,26 @@
     </row>
     <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>504</v>
       </c>
       <c r="C6" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="41" t="s">
+        <v>2477</v>
+      </c>
+      <c r="F6" s="41" t="s">
         <v>2478</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>2479</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="I6" s="41" t="s">
         <v>254</v>
@@ -48064,203 +48064,203 @@
     </row>
     <row r="7" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="B7" s="41" t="s">
         <v>504</v>
       </c>
       <c r="C7" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D7" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D7" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E7" s="41" t="s">
+        <v>2285</v>
+      </c>
+      <c r="F7" s="41" t="s">
         <v>2286</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>2287</v>
       </c>
       <c r="G7" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="I7" s="33" t="s">
         <v>670</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="K7" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="B8" s="41" t="s">
         <v>504</v>
       </c>
       <c r="C8" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D8" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D8" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E8" s="41" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F8" s="41" t="s">
         <v>2192</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>2193</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H8" s="41" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="I8" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="K8" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="41" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="B9" s="41" t="s">
         <v>504</v>
       </c>
       <c r="C9" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D9" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D9" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E9" s="41" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F9" s="41" t="s">
         <v>2213</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>2214</v>
       </c>
       <c r="G9" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="I9" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="K9" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="41" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="C10" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D10" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D10" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E10" s="41" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="G10" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J10" s="28" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="K10" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="41" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="B11" s="41" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="C11" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D11" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E11" s="41" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="G11" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="I11" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="K11" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D12" s="88" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E12" s="93" t="s">
+        <v>2230</v>
+      </c>
+      <c r="F12" s="41" t="s">
         <v>2202</v>
-      </c>
-      <c r="E12" s="93" t="s">
-        <v>2231</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>2203</v>
       </c>
       <c r="G12" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="I12" s="33" t="s">
         <v>670</v>
@@ -48269,73 +48269,73 @@
         <v>499</v>
       </c>
       <c r="K12" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B13" s="41" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C13" s="88" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="D13" s="88"/>
       <c r="E13" s="41" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="G13" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="I13" s="33" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="K13" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="D14" s="88"/>
       <c r="E14" s="41" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="G14" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="K14" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
@@ -48363,7 +48363,7 @@
         <v>254</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K15" s="87" t="s">
         <v>815</v>
@@ -48394,7 +48394,7 @@
         <v>254</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="K16" s="87" t="s">
         <v>815</v>
@@ -48402,22 +48402,22 @@
     </row>
     <row r="17" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="41" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B17" s="41" t="s">
         <v>232</v>
       </c>
       <c r="C17" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D17" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D17" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E17" s="41" t="s">
+        <v>2148</v>
+      </c>
+      <c r="F17" s="41" t="s">
         <v>2149</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>2150</v>
       </c>
       <c r="G17" s="41" t="s">
         <v>501</v>
@@ -48429,30 +48429,30 @@
         <v>515</v>
       </c>
       <c r="J17" s="28" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="K17" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B18" s="41" t="s">
         <v>232</v>
       </c>
       <c r="C18" s="88" t="s">
+        <v>2146</v>
+      </c>
+      <c r="D18" s="88" t="s">
         <v>2147</v>
       </c>
-      <c r="D18" s="88" t="s">
-        <v>2148</v>
-      </c>
       <c r="E18" s="41" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>501</v>
@@ -48464,10 +48464,10 @@
         <v>517</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="K18" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -48478,7 +48478,7 @@
         <v>232</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D19" s="41"/>
       <c r="E19" s="41" t="s">
@@ -48497,7 +48497,7 @@
         <v>254</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="K19" s="87" t="s">
         <v>815</v>
@@ -48514,7 +48514,7 @@
         <v>1912</v>
       </c>
       <c r="D20" s="88" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="E20" s="41" t="s">
         <v>521</v>
@@ -48526,13 +48526,13 @@
         <v>501</v>
       </c>
       <c r="H20" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="I20" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="K20" s="87" t="s">
         <v>815</v>
@@ -48540,7 +48540,7 @@
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="B21" s="41" t="s">
         <v>232</v>
@@ -48550,30 +48550,30 @@
       </c>
       <c r="D21" s="88"/>
       <c r="E21" s="41" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>2482</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>2483</v>
       </c>
       <c r="G21" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H21" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="I21" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="K21" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="B22" s="41" t="s">
         <v>232</v>
@@ -48583,30 +48583,30 @@
       </c>
       <c r="D22" s="88"/>
       <c r="E22" s="41" t="s">
+        <v>2483</v>
+      </c>
+      <c r="F22" s="41" t="s">
         <v>2484</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>2485</v>
       </c>
       <c r="G22" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H22" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="I22" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="K22" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>232</v>
@@ -48616,30 +48616,30 @@
       </c>
       <c r="D23" s="88"/>
       <c r="E23" s="41" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F23" s="41" t="s">
         <v>2486</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>2487</v>
       </c>
       <c r="G23" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H23" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="I23" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="K23" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A24" s="41" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B24" s="41" t="s">
         <v>232</v>
@@ -48647,22 +48647,22 @@
       <c r="C24" s="88"/>
       <c r="D24" s="88"/>
       <c r="E24" s="41" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F24" s="41" t="s">
         <v>2173</v>
-      </c>
-      <c r="F24" s="41" t="s">
-        <v>2174</v>
       </c>
       <c r="G24" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H24" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I24" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J24" s="28" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="K24" s="87" t="s">
         <v>815</v>
@@ -48670,34 +48670,34 @@
     </row>
     <row r="25" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="41" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B25" s="41" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="C25" s="88" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D25" s="88" t="s">
         <v>2129</v>
       </c>
-      <c r="D25" s="88" t="s">
-        <v>2130</v>
-      </c>
       <c r="E25" s="41" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="G25" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H25" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I25" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="K25" s="87" t="s">
         <v>815</v>
@@ -48705,32 +48705,32 @@
     </row>
     <row r="26" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B26" s="41" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D26" s="88"/>
       <c r="E26" s="41" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="G26" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H26" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I26" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J26" s="28" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="K26" s="87" t="s">
         <v>815</v>
@@ -48738,7 +48738,7 @@
     </row>
     <row r="27" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B27" s="41" t="s">
         <v>232</v>
@@ -48746,22 +48746,22 @@
       <c r="C27" s="88"/>
       <c r="D27" s="88"/>
       <c r="E27" s="41" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="G27" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H27" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I27" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="K27" s="87" t="s">
         <v>815</v>
@@ -48769,32 +48769,32 @@
     </row>
     <row r="28" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="B28" s="41" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C28" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D28" s="88"/>
       <c r="E28" s="41" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="G28" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H28" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I28" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="K28" s="87" t="s">
         <v>815</v>
@@ -48802,32 +48802,32 @@
     </row>
     <row r="29" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B29" s="41" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="C29" s="88" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="D29" s="88"/>
       <c r="E29" s="41" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="G29" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H29" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I29" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="K29" s="87" t="s">
         <v>815</v>
@@ -48856,7 +48856,7 @@
         <v>498</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="K30" s="87" t="s">
         <v>815</v>
@@ -48887,7 +48887,7 @@
         <v>254</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K31" s="87" t="s">
         <v>815</v>
@@ -48918,7 +48918,7 @@
         <v>254</v>
       </c>
       <c r="J32" s="41" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="K32" s="87" t="s">
         <v>815</v>
@@ -48926,7 +48926,7 @@
     </row>
     <row r="33" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="41" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="B33" s="41" t="s">
         <v>236</v>
@@ -48934,7 +48934,7 @@
       <c r="C33" s="84"/>
       <c r="D33" s="41"/>
       <c r="E33" s="41" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="F33" s="41" t="s">
         <v>529</v>
@@ -48949,7 +48949,7 @@
         <v>254</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="K33" s="87" t="s">
         <v>815</v>
@@ -48980,7 +48980,7 @@
         <v>254</v>
       </c>
       <c r="J34" s="41" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="K34" s="87" t="s">
         <v>815</v>
@@ -49009,7 +49009,7 @@
         <v>498</v>
       </c>
       <c r="J35" s="42" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="K35" s="87" t="s">
         <v>815</v>
@@ -49040,7 +49040,7 @@
         <v>254</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="K36" s="87" t="s">
         <v>815</v>
@@ -49071,7 +49071,7 @@
         <v>254</v>
       </c>
       <c r="J37" s="39" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="K37" s="87" t="s">
         <v>815</v>
@@ -49104,7 +49104,7 @@
         <v>255</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="K38" s="87" t="s">
         <v>815</v>
@@ -49137,7 +49137,7 @@
         <v>255</v>
       </c>
       <c r="J39" s="28" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="K39" s="87" t="s">
         <v>815</v>
@@ -49160,13 +49160,13 @@
         <v>215</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="I40" s="33" t="s">
         <v>234</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="K40" s="87" t="s">
         <v>815</v>
@@ -49174,112 +49174,112 @@
     </row>
     <row r="41" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A41" s="39" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B41" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C41" s="88" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D41" s="88" t="s">
         <v>2251</v>
       </c>
-      <c r="D41" s="88" t="s">
+      <c r="E41" s="39" t="s">
         <v>2252</v>
       </c>
-      <c r="E41" s="39" t="s">
-        <v>2253</v>
-      </c>
       <c r="F41" s="43" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="G41" s="94" t="s">
         <v>1994</v>
       </c>
       <c r="H41" s="27" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="J41" s="39" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="K41" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A42" s="39" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B42" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C42" s="88" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D42" s="88" t="s">
         <v>2251</v>
       </c>
-      <c r="D42" s="88" t="s">
-        <v>2252</v>
-      </c>
       <c r="E42" s="39" t="s">
+        <v>2253</v>
+      </c>
+      <c r="F42" s="43" t="s">
         <v>2254</v>
-      </c>
-      <c r="F42" s="43" t="s">
-        <v>2255</v>
       </c>
       <c r="G42" s="94" t="s">
         <v>1994</v>
       </c>
       <c r="H42" s="27" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="I42" s="33" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="J42" s="39" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="K42" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A43" s="39" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B43" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="D43" s="88" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="E43" s="39" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F43" s="43" t="s">
         <v>2208</v>
       </c>
-      <c r="F43" s="43" t="s">
-        <v>2209</v>
-      </c>
       <c r="G43" s="39" t="s">
         <v>215</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="I43" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J43" s="39" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="K43" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>543</v>
@@ -49288,83 +49288,83 @@
         <v>1912</v>
       </c>
       <c r="D44" s="88" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="G44" s="39" t="s">
         <v>215</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="I44" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J44" s="39" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="K44" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B45" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="D45" s="88" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="G45" s="39" t="s">
         <v>215</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="I45" s="41" t="s">
         <v>254</v>
       </c>
       <c r="J45" s="39" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="K45" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A46" s="39" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B46" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C46" s="88" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="G46" s="39" t="s">
         <v>215</v>
@@ -49376,28 +49376,28 @@
         <v>254</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="K46" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A47" s="39" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="B47" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="41" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="F47" s="43" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="G47" s="39" t="s">
         <v>215</v>
@@ -49409,10 +49409,10 @@
         <v>255</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="K47" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
@@ -49440,7 +49440,7 @@
         <v>254</v>
       </c>
       <c r="J48" s="28" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="K48" s="87" t="s">
         <v>815</v>
@@ -49471,7 +49471,7 @@
         <v>254</v>
       </c>
       <c r="J49" s="28" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="K49" s="87" t="s">
         <v>815</v>
@@ -49479,18 +49479,18 @@
     </row>
     <row r="50" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="41" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="B50" s="42"/>
       <c r="C50" s="39" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="D50" s="41"/>
       <c r="E50" s="41" t="s">
+        <v>2226</v>
+      </c>
+      <c r="F50" s="41" t="s">
         <v>2227</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>2228</v>
       </c>
       <c r="G50" s="41" t="s">
         <v>501</v>
@@ -49502,7 +49502,7 @@
         <v>254</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="K50" s="87" t="s">
         <v>815</v>
@@ -49510,16 +49510,16 @@
     </row>
     <row r="51" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="B51" s="26"/>
       <c r="C51" s="84"/>
       <c r="D51" s="26"/>
       <c r="E51" s="26" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>215</v>
@@ -49528,29 +49528,29 @@
         <v>514</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="K51" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="C52" s="84"/>
       <c r="D52" s="26"/>
       <c r="E52" s="26" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>215</v>
@@ -49559,29 +49559,29 @@
         <v>514</v>
       </c>
       <c r="I52" s="33" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="K52" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="C53" s="84"/>
       <c r="D53" s="26"/>
       <c r="E53" s="26" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="F53" s="86" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>215</v>
@@ -49590,62 +49590,62 @@
         <v>514</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="K53" s="83" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="41" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="B54" s="41" t="s">
         <v>232</v>
       </c>
       <c r="C54" s="88" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="D54" s="88" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="E54" s="41" t="s">
+        <v>2445</v>
+      </c>
+      <c r="F54" s="41" t="s">
         <v>2446</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>2447</v>
       </c>
       <c r="G54" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H54" s="27" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="I54" s="41" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="J54" s="28" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K54" s="87" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="55" spans="1:11" s="103" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="104" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B55" s="104"/>
       <c r="C55" s="104"/>
       <c r="D55" s="104"/>
       <c r="E55" s="104" t="s">
+        <v>2508</v>
+      </c>
+      <c r="F55" s="104" t="s">
         <v>2509</v>
-      </c>
-      <c r="F55" s="104" t="s">
-        <v>2510</v>
       </c>
       <c r="G55" s="104" t="s">
         <v>215</v>
@@ -49654,10 +49654,10 @@
         <v>82</v>
       </c>
       <c r="I55" s="104" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J55" s="104" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="K55" s="104" t="s">
         <v>815</v>
@@ -49665,16 +49665,16 @@
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="84"/>
       <c r="D56" s="41"/>
       <c r="E56" s="41" t="s">
+        <v>2766</v>
+      </c>
+      <c r="F56" s="41" t="s">
         <v>2767</v>
-      </c>
-      <c r="F56" s="41" t="s">
-        <v>2768</v>
       </c>
       <c r="G56" s="41" t="s">
         <v>215</v>
@@ -49686,7 +49686,7 @@
         <v>644</v>
       </c>
       <c r="J56" s="41" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="K56" s="87" t="s">
         <v>815</v>
@@ -49717,16 +49717,16 @@
   <sheetData>
     <row r="1" spans="1:11" s="85" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="84"/>
       <c r="D1" s="41"/>
       <c r="E1" s="41" t="s">
+        <v>2503</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>2504</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>2505</v>
       </c>
       <c r="G1" s="56" t="s">
         <v>215</v>
@@ -49735,10 +49735,10 @@
         <v>82</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="K1" s="87" t="s">
         <v>815</v>
@@ -49746,16 +49746,16 @@
     </row>
     <row r="2" spans="1:11" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="84"/>
       <c r="D2" s="41"/>
       <c r="E2" s="41" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F2" s="41" t="s">
         <v>2507</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>2508</v>
       </c>
       <c r="G2" s="56" t="s">
         <v>215</v>
@@ -49764,10 +49764,10 @@
         <v>82</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="J2" s="60" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="K2" s="87" t="s">
         <v>815</v>
@@ -49938,7 +49938,7 @@
         <v>565</v>
       </c>
       <c r="H7" s="94" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -49998,7 +49998,7 @@
         <v>558</v>
       </c>
       <c r="H10" s="94" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -50018,7 +50018,7 @@
         <v>558</v>
       </c>
       <c r="H11" s="94" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -50038,7 +50038,7 @@
         <v>558</v>
       </c>
       <c r="H12" s="94" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">

--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{407ED8E5-CBB5-4F7C-8F95-F9C1D99FA09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB91120-32DF-4BD3-8B40-798CFFF35D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="7" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10631" uniqueCount="2887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10649" uniqueCount="2900">
   <si>
     <t>WB_Specification</t>
   </si>
@@ -7240,9 +7240,6 @@
     <t>По официальному сообщения бухгалтеров и руководства Мост-Ломбарда, успешно завершен проект "Начисление вознаграждения в бухбазе".</t>
   </si>
   <si>
-    <t>Проект реализован на основе Универсал-бухгалтерии 77, активно использованы идеи процессов --- https://docs.google.com/spreadsheets/d/1dCdmRIvF6KH5ybWXCFcZBJ2P0vTzcBl4hrMp8JhRggA/edit#gid=1084768438</t>
-  </si>
-  <si>
     <t>Проект начат в феврале 2021.</t>
   </si>
   <si>
@@ -8416,21 +8413,9 @@
     <t>Описание прайс листа. Товарная группа1</t>
   </si>
   <si>
-    <t>Fullname=Металлопрокат;</t>
-  </si>
-  <si>
     <t>Описание прайс листа. Товарная группа2</t>
   </si>
   <si>
-    <t>PriceListDescription.Root1</t>
-  </si>
-  <si>
-    <t>Fullname=Арматура ГОСТ 5781-82, 52544-2006;UnitLimit=тн,5;</t>
-  </si>
-  <si>
-    <t>Fullname=Катанка ГОСТ 30136-95;UnitLimit=тн;</t>
-  </si>
-  <si>
     <t>AbcBasic=Account.Basic;NormCode=1300;</t>
   </si>
   <si>
@@ -8602,72 +8587,12 @@
     <t>-03-15</t>
   </si>
   <si>
-    <t>Описание прайс листа. Корень 1</t>
-  </si>
-  <si>
     <t>19;20;18;22;17;22;22;21;22;21;21;22;</t>
   </si>
   <si>
     <t>PublicHoliday.ConstitutionDay.2027</t>
   </si>
   <si>
-    <t>PriceListDescription.Root2</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root1.Partition1</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root2.Partition1</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root2.Partition1.ProductGroup1</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root2.Partition1.ProductGroup2</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root1.Partition1.ProductGroup1</t>
-  </si>
-  <si>
-    <t>PriceListDescription.Root1.Partition1.ProductGroup2</t>
-  </si>
-  <si>
-    <t>Описание прайс листа. Корень 2</t>
-  </si>
-  <si>
-    <t>Fullname=ТНП;</t>
-  </si>
-  <si>
-    <t>Fullname=Валенки рабочие;UnitLimit=шт,5;</t>
-  </si>
-  <si>
-    <t>Fullname=Спецовка;UnitLimit=шт;</t>
-  </si>
-  <si>
-    <t>Fullname=price.xlsx;PriceListMap=(35, 5 , 1,2 ,   3 , 4   )(5,6)|(35, 5 , 7,8 ,   9 , 10   )(11,12);</t>
-  </si>
-  <si>
-    <t>ProductVar1</t>
-  </si>
-  <si>
-    <t>ProductVar2</t>
-  </si>
-  <si>
-    <t>Переменная товара 1</t>
-  </si>
-  <si>
-    <t>Переменная товара 2</t>
-  </si>
-  <si>
-    <t>Fullname=Цена1;</t>
-  </si>
-  <si>
-    <t>Fullname=Цена2;</t>
-  </si>
-  <si>
-    <t>Fullname=price.xlsx;PriceListMap=(35, 5 , 1,2 ,   3 , 4   )(5,6);Context=PriceList;</t>
-  </si>
-  <si>
     <t>Role.ProductList.Root</t>
   </si>
   <si>
@@ -8717,6 +8642,120 @@
   </si>
   <si>
     <t>FullName=метр;MKEI=6;Lenght=100.00(Unit.Cm);Width=100.00(Unit.Cm);Height=100.00(Unit.Cm);Squared=Unit.SquareMeter;Cubed=Unit.Cbm;AbcBasic=Unit.Basic;AbcExpectedValue=Unit.ExpectedDouble;</t>
+  </si>
+  <si>
+    <t>Проект реализован на основе Универсал-бухгалтерии 77, активно использованы идеи процессов</t>
+  </si>
+  <si>
+    <t>Fullname=Цена1;Unit=Unit.KZT;</t>
+  </si>
+  <si>
+    <t>Fullname=Цена2;Unit=Unit.KZT;</t>
+  </si>
+  <si>
+    <t>Fullname=Длина штуки (плети);Unit=Unit.Mm;</t>
+  </si>
+  <si>
+    <t>Fullname=Вес 1 пог.м.;Unit=Unit.Kg;</t>
+  </si>
+  <si>
+    <t>Fullname=Диаметр;Unit=Unit.Mm;</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Раздел 1</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Товарная группа1</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Товарная группа2</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Переменная товара 1</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Переменная товара 2</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Переменная товара 3</t>
+  </si>
+  <si>
+    <t>Описание прайс листа. Переменная товара 1</t>
+  </si>
+  <si>
+    <t>Описание прайс листа. Переменная товара 2</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root</t>
+  </si>
+  <si>
+    <t>Описание прайс листа. Корень</t>
+  </si>
+  <si>
+    <t>Описание сортамент листа. Корень</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root.Part1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root.Part1.ProductVar1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root.Part1.ProductVar2</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root.Part1.ProductGroup1</t>
+  </si>
+  <si>
+    <t>PriceListDescription.Root.Part1.ProductGroup2</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1.ProductGroup1</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1.ProductGroup2</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1.ProductVar1</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1.ProductVar2</t>
+  </si>
+  <si>
+    <t>SortamentListDescription.Root.Part1.ProductVar3</t>
+  </si>
+  <si>
+    <t>Role.ProductList.Part</t>
+  </si>
+  <si>
+    <t>Fullname=ТНП;Map=(35,5,1,2,3,4 )(5,6);</t>
+  </si>
+  <si>
+    <t>Fullname=Металлопрокат;Map=(35,5,1,2,3,4)(5,6,7);</t>
+  </si>
+  <si>
+    <t>Fullname=SortamentListTest.csv;Context=SortamentList;</t>
+  </si>
+  <si>
+    <t>Fullname=PriceListTest.csv;Context=PriceList;</t>
+  </si>
+  <si>
+    <t>Fullname=Спецовка;UnitLimit=Unit.Piece;</t>
+  </si>
+  <si>
+    <t>Fullname=Арматура ГОСТ 5781-82, 52544-2006;UnitLimit=Unit.T,5;</t>
+  </si>
+  <si>
+    <t>Fullname=Катанка ГОСТ 30136-95;UnitLimit=Unit.T;</t>
+  </si>
+  <si>
+    <t>Fullname=Валенки;UnitLimit=Unit.Piece,5;</t>
   </si>
 </sst>
 </file>
@@ -11116,7 +11155,7 @@
         <v>42</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -11504,7 +11543,7 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>589</v>
@@ -11512,18 +11551,18 @@
       <c r="C10" s="22"/>
       <c r="D10" s="33"/>
       <c r="E10" s="33" t="s">
+        <v>2535</v>
+      </c>
+      <c r="F10" s="33" t="s">
         <v>2536</v>
       </c>
-      <c r="F10" s="33" t="s">
+      <c r="G10" s="33" t="s">
         <v>2537</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>2538</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>589</v>
@@ -11531,18 +11570,18 @@
       <c r="C11" s="22"/>
       <c r="D11" s="33"/>
       <c r="E11" s="33" t="s">
+        <v>2538</v>
+      </c>
+      <c r="F11" s="33" t="s">
         <v>2539</v>
       </c>
-      <c r="F11" s="33" t="s">
+      <c r="G11" s="33" t="s">
         <v>2540</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>589</v>
@@ -11550,18 +11589,18 @@
       <c r="C12" s="22"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33" t="s">
+        <v>2541</v>
+      </c>
+      <c r="F12" s="33" t="s">
         <v>2542</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="G12" s="33" t="s">
         <v>2543</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>2544</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>589</v>
@@ -11569,18 +11608,18 @@
       <c r="C13" s="22"/>
       <c r="D13" s="33"/>
       <c r="E13" s="33" t="s">
+        <v>2544</v>
+      </c>
+      <c r="F13" s="33" t="s">
         <v>2545</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="G13" s="33" t="s">
         <v>2546</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>2547</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="B14" s="33" t="s">
         <v>589</v>
@@ -11588,18 +11627,18 @@
       <c r="C14" s="22"/>
       <c r="D14" s="33"/>
       <c r="E14" s="33" t="s">
+        <v>2547</v>
+      </c>
+      <c r="F14" s="33" t="s">
         <v>2548</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="G14" s="33" t="s">
         <v>2549</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>2550</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>589</v>
@@ -11607,18 +11646,18 @@
       <c r="C15" s="22"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33" t="s">
+        <v>2550</v>
+      </c>
+      <c r="F15" s="33" t="s">
         <v>2551</v>
       </c>
-      <c r="F15" s="33" t="s">
+      <c r="G15" s="33" t="s">
         <v>2552</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>2553</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>589</v>
@@ -11626,18 +11665,18 @@
       <c r="C16" s="22"/>
       <c r="D16" s="33"/>
       <c r="E16" s="33" t="s">
+        <v>2553</v>
+      </c>
+      <c r="F16" s="33" t="s">
         <v>2554</v>
       </c>
-      <c r="F16" s="33" t="s">
+      <c r="G16" s="33" t="s">
         <v>2555</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>2556</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="B17" s="33" t="s">
         <v>589</v>
@@ -11645,18 +11684,18 @@
       <c r="C17" s="22"/>
       <c r="D17" s="33"/>
       <c r="E17" s="33" t="s">
+        <v>2556</v>
+      </c>
+      <c r="F17" s="33" t="s">
         <v>2557</v>
       </c>
-      <c r="F17" s="33" t="s">
+      <c r="G17" s="33" t="s">
         <v>2558</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>2559</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>589</v>
@@ -11664,18 +11703,18 @@
       <c r="C18" s="22"/>
       <c r="D18" s="33"/>
       <c r="E18" s="33" t="s">
+        <v>2559</v>
+      </c>
+      <c r="F18" s="33" t="s">
         <v>2560</v>
       </c>
-      <c r="F18" s="33" t="s">
+      <c r="G18" s="33" t="s">
         <v>2561</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>2562</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="B19" s="33" t="s">
         <v>589</v>
@@ -11683,18 +11722,18 @@
       <c r="C19" s="22"/>
       <c r="D19" s="33"/>
       <c r="E19" s="33" t="s">
+        <v>2562</v>
+      </c>
+      <c r="F19" s="33" t="s">
         <v>2563</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="G19" s="33" t="s">
         <v>2564</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>589</v>
@@ -11702,18 +11741,18 @@
       <c r="C20" s="22"/>
       <c r="D20" s="33"/>
       <c r="E20" s="33" t="s">
+        <v>2565</v>
+      </c>
+      <c r="F20" s="33" t="s">
         <v>2566</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="G20" s="33" t="s">
         <v>2567</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>2568</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>589</v>
@@ -11721,18 +11760,18 @@
       <c r="C21" s="22"/>
       <c r="D21" s="33"/>
       <c r="E21" s="33" t="s">
+        <v>2568</v>
+      </c>
+      <c r="F21" s="33" t="s">
         <v>2569</v>
       </c>
-      <c r="F21" s="33" t="s">
+      <c r="G21" s="33" t="s">
         <v>2570</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>2571</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>589</v>
@@ -11740,18 +11779,18 @@
       <c r="C22" s="22"/>
       <c r="D22" s="33"/>
       <c r="E22" s="33" t="s">
+        <v>2571</v>
+      </c>
+      <c r="F22" s="33" t="s">
         <v>2572</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="G22" s="33" t="s">
         <v>2573</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>2574</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>589</v>
@@ -11759,13 +11798,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="33"/>
       <c r="E23" s="33" t="s">
+        <v>2574</v>
+      </c>
+      <c r="F23" s="33" t="s">
         <v>2575</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="G23" s="33" t="s">
         <v>2576</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11800,10 +11839,10 @@
         <v>606</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="G25" s="33" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11838,15 +11877,15 @@
         <v>610</v>
       </c>
       <c r="F27" s="33" t="s">
+        <v>2489</v>
+      </c>
+      <c r="G27" s="33" t="s">
         <v>2490</v>
-      </c>
-      <c r="G27" s="33" t="s">
-        <v>2491</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>602</v>
@@ -11854,18 +11893,18 @@
       <c r="C28" s="22"/>
       <c r="D28" s="33"/>
       <c r="E28" s="33" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F28" s="33" t="s">
         <v>2495</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="G28" s="31" t="s">
         <v>2496</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>2497</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>602</v>
@@ -11873,13 +11912,13 @@
       <c r="C29" s="22"/>
       <c r="D29" s="33"/>
       <c r="E29" s="33" t="s">
+        <v>2497</v>
+      </c>
+      <c r="F29" s="33" t="s">
         <v>2498</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="G29" s="33" t="s">
         <v>2499</v>
-      </c>
-      <c r="G29" s="33" t="s">
-        <v>2500</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -11941,7 +11980,7 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>602</v>
@@ -11949,13 +11988,13 @@
       <c r="C33" s="22"/>
       <c r="D33" s="33"/>
       <c r="E33" s="33" t="s">
+        <v>2712</v>
+      </c>
+      <c r="F33" s="33" t="s">
         <v>2713</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="G33" s="33" t="s">
         <v>2714</v>
-      </c>
-      <c r="G33" s="33" t="s">
-        <v>2715</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -12028,10 +12067,10 @@
         <v>625</v>
       </c>
       <c r="F37" s="33" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="G37" s="33" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -12066,15 +12105,15 @@
         <v>1928</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>602</v>
@@ -12082,18 +12121,18 @@
       <c r="C40" s="32"/>
       <c r="D40" s="33"/>
       <c r="E40" s="33" t="s">
+        <v>2527</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>2528</v>
       </c>
-      <c r="F40" s="33" t="s">
-        <v>2529</v>
-      </c>
       <c r="G40" s="45" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="33" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="B41" s="33" t="s">
         <v>602</v>
@@ -12101,18 +12140,18 @@
       <c r="C41" s="32"/>
       <c r="D41" s="33"/>
       <c r="E41" s="33" t="s">
+        <v>2529</v>
+      </c>
+      <c r="F41" s="33" t="s">
         <v>2530</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="G41" s="45" t="s">
         <v>2531</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>2532</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="B42" s="33" t="s">
         <v>602</v>
@@ -12120,18 +12159,18 @@
       <c r="C42" s="32"/>
       <c r="D42" s="33"/>
       <c r="E42" s="33" t="s">
+        <v>2532</v>
+      </c>
+      <c r="F42" s="33" t="s">
         <v>2533</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="G42" s="45" t="s">
         <v>2534</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>2535</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="B43" s="33" t="s">
         <v>602</v>
@@ -12139,10 +12178,10 @@
       <c r="C43" s="32"/>
       <c r="D43" s="33"/>
       <c r="E43" s="33" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F43" s="33" t="s">
         <v>2501</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>2502</v>
       </c>
       <c r="G43" s="45" t="s">
         <v>590</v>
@@ -12735,7 +12774,7 @@
     </row>
     <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="27" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="B75" s="33" t="s">
         <v>644</v>
@@ -12743,10 +12782,10 @@
       <c r="C75" s="32"/>
       <c r="D75" s="27"/>
       <c r="E75" s="27" t="s">
+        <v>2442</v>
+      </c>
+      <c r="F75" s="33" t="s">
         <v>2443</v>
-      </c>
-      <c r="F75" s="33" t="s">
-        <v>2444</v>
       </c>
       <c r="G75" s="45" t="s">
         <v>626</v>
@@ -12754,7 +12793,7 @@
     </row>
     <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="27" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="B76" s="33" t="s">
         <v>644</v>
@@ -12762,10 +12801,10 @@
       <c r="C76" s="32"/>
       <c r="D76" s="27"/>
       <c r="E76" s="27" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F76" s="33" t="s">
         <v>2487</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>2488</v>
       </c>
       <c r="G76" s="45" t="s">
         <v>626</v>
@@ -12959,7 +12998,7 @@
     </row>
     <row r="87" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="B87" s="33" t="s">
         <v>673</v>
@@ -12967,10 +13006,10 @@
       <c r="C87" s="22"/>
       <c r="D87" s="33"/>
       <c r="E87" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="F87" s="33" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="G87" s="45" t="s">
         <v>590</v>
@@ -12978,7 +13017,7 @@
     </row>
     <row r="88" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="B88" s="33" t="s">
         <v>673</v>
@@ -12986,10 +13025,10 @@
       <c r="C88" s="22"/>
       <c r="D88" s="33"/>
       <c r="E88" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="F88" s="33" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="G88" s="45" t="s">
         <v>590</v>
@@ -12997,7 +13036,7 @@
     </row>
     <row r="89" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="B89" s="33" t="s">
         <v>673</v>
@@ -13005,10 +13044,10 @@
       <c r="C89" s="22"/>
       <c r="D89" s="33"/>
       <c r="E89" s="33" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="G89" s="45" t="s">
         <v>590</v>
@@ -13073,7 +13112,7 @@
     </row>
     <row r="93" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="B93" s="33" t="s">
         <v>673</v>
@@ -13081,10 +13120,10 @@
       <c r="C93" s="22"/>
       <c r="D93" s="33"/>
       <c r="E93" s="33" t="s">
+        <v>2716</v>
+      </c>
+      <c r="F93" s="33" t="s">
         <v>2717</v>
-      </c>
-      <c r="F93" s="33" t="s">
-        <v>2718</v>
       </c>
       <c r="G93" s="45" t="s">
         <v>590</v>
@@ -13601,7 +13640,7 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="B121" s="33" t="s">
         <v>697</v>
@@ -13609,10 +13648,10 @@
       <c r="C121" s="22"/>
       <c r="D121" s="33"/>
       <c r="E121" s="33" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F121" s="33" t="s">
         <v>2644</v>
-      </c>
-      <c r="F121" s="33" t="s">
-        <v>2645</v>
       </c>
       <c r="G121" s="45" t="s">
         <v>590</v>
@@ -14734,7 +14773,7 @@
     </row>
     <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A28" s="102" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="B28" s="99" t="s">
         <v>2386</v>
@@ -14747,7 +14786,7 @@
     </row>
     <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A29" s="102" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="B29" s="99" t="s">
         <v>2387</v>
@@ -14799,10 +14838,10 @@
     </row>
     <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A33" s="95" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
       <c r="B33" s="95" t="s">
-        <v>2394</v>
+        <v>2862</v>
       </c>
       <c r="C33" s="97"/>
       <c r="D33" s="97"/>
@@ -14812,10 +14851,10 @@
     </row>
     <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A34" s="95" t="s">
-        <v>2397</v>
+        <v>2396</v>
       </c>
       <c r="B34" s="95" t="s">
-        <v>2395</v>
+        <v>2394</v>
       </c>
       <c r="C34" s="97"/>
       <c r="D34" s="97"/>
@@ -14825,10 +14864,10 @@
     </row>
     <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A35" s="95" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B35" s="95" t="s">
         <v>2398</v>
-      </c>
-      <c r="B35" s="95" t="s">
-        <v>2399</v>
       </c>
       <c r="C35" s="97"/>
       <c r="D35" s="97"/>
@@ -14838,10 +14877,10 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A36" s="95" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B36" s="95" t="s">
         <v>2400</v>
-      </c>
-      <c r="B36" s="95" t="s">
-        <v>2401</v>
       </c>
       <c r="C36" s="97"/>
       <c r="D36" s="97"/>
@@ -14851,10 +14890,10 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A37" s="95" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B37" s="95" t="s">
         <v>2402</v>
-      </c>
-      <c r="B37" s="95" t="s">
-        <v>2403</v>
       </c>
       <c r="C37" s="97"/>
       <c r="D37" s="97"/>
@@ -14864,10 +14903,10 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A38" s="95" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B38" s="95" t="s">
         <v>2404</v>
-      </c>
-      <c r="B38" s="95" t="s">
-        <v>2405</v>
       </c>
       <c r="C38" s="97"/>
       <c r="D38" s="97"/>
@@ -14877,10 +14916,10 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A39" s="95" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B39" s="95" t="s">
         <v>2406</v>
-      </c>
-      <c r="B39" s="95" t="s">
-        <v>2407</v>
       </c>
       <c r="C39" s="97"/>
       <c r="D39" s="97"/>
@@ -14890,10 +14929,10 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A40" s="95" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B40" s="95" t="s">
         <v>2408</v>
-      </c>
-      <c r="B40" s="95" t="s">
-        <v>2409</v>
       </c>
       <c r="C40" s="97"/>
       <c r="D40" s="97"/>
@@ -14903,10 +14942,10 @@
     </row>
     <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A41" s="95" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B41" s="95" t="s">
         <v>2410</v>
-      </c>
-      <c r="B41" s="95" t="s">
-        <v>2411</v>
       </c>
       <c r="C41" s="97"/>
       <c r="D41" s="97"/>
@@ -14916,10 +14955,10 @@
     </row>
     <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A42" s="95" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B42" s="95" t="s">
         <v>2412</v>
-      </c>
-      <c r="B42" s="95" t="s">
-        <v>2413</v>
       </c>
       <c r="C42" s="97"/>
       <c r="D42" s="97"/>
@@ -14929,10 +14968,10 @@
     </row>
     <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A43" s="95" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B43" s="95" t="s">
         <v>2414</v>
-      </c>
-      <c r="B43" s="95" t="s">
-        <v>2415</v>
       </c>
       <c r="C43" s="97"/>
       <c r="D43" s="97"/>
@@ -14942,10 +14981,10 @@
     </row>
     <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A44" s="95" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="B44" s="95" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C44" s="97"/>
       <c r="D44" s="97"/>
@@ -14955,10 +14994,10 @@
     </row>
     <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A45" s="95" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B45" s="95" t="s">
         <v>2418</v>
-      </c>
-      <c r="B45" s="95" t="s">
-        <v>2419</v>
       </c>
       <c r="C45" s="97"/>
       <c r="D45" s="97"/>
@@ -14994,10 +15033,10 @@
     </row>
     <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A48" s="95" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B48" s="95" t="s">
         <v>2420</v>
-      </c>
-      <c r="B48" s="95" t="s">
-        <v>2421</v>
       </c>
       <c r="C48" s="97"/>
       <c r="D48" s="97"/>
@@ -15007,10 +15046,10 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A49" s="95" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B49" s="95" t="s">
         <v>2422</v>
-      </c>
-      <c r="B49" s="95" t="s">
-        <v>2423</v>
       </c>
       <c r="C49" s="97"/>
       <c r="D49" s="97"/>
@@ -15020,10 +15059,10 @@
     </row>
     <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A50" s="95" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B50" s="95" t="s">
         <v>2424</v>
-      </c>
-      <c r="B50" s="95" t="s">
-        <v>2425</v>
       </c>
       <c r="C50" s="97"/>
       <c r="D50" s="97"/>
@@ -15033,10 +15072,10 @@
     </row>
     <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A51" s="95" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B51" s="95" t="s">
         <v>2426</v>
-      </c>
-      <c r="B51" s="95" t="s">
-        <v>2427</v>
       </c>
       <c r="C51" s="97"/>
       <c r="D51" s="97"/>
@@ -15046,10 +15085,10 @@
     </row>
     <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="95" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B52" s="95" t="s">
         <v>2428</v>
-      </c>
-      <c r="B52" s="95" t="s">
-        <v>2429</v>
       </c>
       <c r="C52" s="97"/>
       <c r="D52" s="97"/>
@@ -15059,10 +15098,10 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="95" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B53" s="95" t="s">
         <v>2430</v>
-      </c>
-      <c r="B53" s="95" t="s">
-        <v>2431</v>
       </c>
       <c r="C53" s="97"/>
       <c r="D53" s="97"/>
@@ -15072,10 +15111,10 @@
     </row>
     <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A54" s="95" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B54" s="95" t="s">
         <v>2432</v>
-      </c>
-      <c r="B54" s="95" t="s">
-        <v>2433</v>
       </c>
       <c r="C54" s="97"/>
       <c r="D54" s="97"/>
@@ -15085,10 +15124,10 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A55" s="95" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B55" s="95" t="s">
         <v>2434</v>
-      </c>
-      <c r="B55" s="95" t="s">
-        <v>2435</v>
       </c>
       <c r="C55" s="97"/>
       <c r="D55" s="97"/>
@@ -15098,10 +15137,10 @@
     </row>
     <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A56" s="95" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="B56" s="95" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C56" s="97"/>
       <c r="D56" s="97"/>
@@ -15176,42 +15215,42 @@
     </row>
     <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="95" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B62" s="95" t="s">
         <v>2437</v>
-      </c>
-      <c r="B62" s="95" t="s">
-        <v>2438</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="95" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="B63" s="95" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="95" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B64" s="95" t="s">
         <v>2705</v>
-      </c>
-      <c r="B64" s="95" t="s">
-        <v>2706</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="95" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B65" s="95" t="s">
         <v>2719</v>
-      </c>
-      <c r="B65" s="95" t="s">
-        <v>2720</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="95" t="s">
-        <v>2880</v>
+        <v>2855</v>
       </c>
       <c r="B66" s="95" t="s">
-        <v>2881</v>
+        <v>2856</v>
       </c>
     </row>
   </sheetData>
@@ -15766,15 +15805,15 @@
   <sheetPr codeName="Лист13">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="65.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52" style="85" customWidth="1"/>
-    <col min="2" max="2" width="35.42578125" style="85" customWidth="1"/>
+    <col min="1" max="1" width="52.7109375" style="85" customWidth="1"/>
+    <col min="2" max="2" width="38" style="85" customWidth="1"/>
     <col min="3" max="3" width="27.28515625" style="85" customWidth="1"/>
     <col min="4" max="4" width="27.140625" style="85" customWidth="1"/>
-    <col min="5" max="5" width="51.28515625" style="85" customWidth="1"/>
-    <col min="6" max="6" width="42.28515625" style="85" customWidth="1"/>
+    <col min="5" max="5" width="51" style="85" customWidth="1"/>
+    <col min="6" max="6" width="52.28515625" style="85" customWidth="1"/>
     <col min="7" max="7" width="34.85546875" style="85" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="58" style="85" customWidth="1"/>
     <col min="9" max="16384" width="65.5703125" style="85"/>
@@ -15794,7 +15833,7 @@
         <v>2126</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>2882</v>
+        <v>2857</v>
       </c>
       <c r="H1" s="28" t="s">
         <v>2125</v>
@@ -15818,7 +15857,7 @@
         <v>2137</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>2884</v>
+        <v>2859</v>
       </c>
       <c r="H2" s="28" t="s">
         <v>2142</v>
@@ -15842,226 +15881,292 @@
         <v>2138</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>2884</v>
+        <v>2859</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>2141</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="108" t="s">
-        <v>2788</v>
+        <v>2876</v>
       </c>
       <c r="B4" s="108"/>
       <c r="C4" s="109"/>
       <c r="D4" s="109"/>
       <c r="E4" s="108" t="s">
-        <v>2788</v>
+        <v>2876</v>
       </c>
       <c r="F4" s="108" t="s">
-        <v>2848</v>
+        <v>2878</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>2870</v>
+        <v>2845</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>2869</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="B5" s="108" t="s">
-        <v>2788</v>
+        <v>2876</v>
       </c>
       <c r="C5" s="109"/>
       <c r="D5" s="109"/>
       <c r="E5" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>2871</v>
+        <v>2846</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>2859</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>2892</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="108" t="s">
-        <v>2863</v>
+        <v>2881</v>
       </c>
       <c r="B6" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="C6" s="109"/>
       <c r="D6" s="109"/>
       <c r="E6" s="108" t="s">
+        <v>2881</v>
+      </c>
+      <c r="F6" s="108" t="s">
+        <v>2874</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H6" s="28" t="s">
         <v>2863</v>
       </c>
-      <c r="F6" s="108" t="s">
-        <v>2865</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>2872</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>2867</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="108" t="s">
-        <v>2864</v>
+        <v>2882</v>
       </c>
       <c r="B7" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="C7" s="109"/>
       <c r="D7" s="109"/>
       <c r="E7" s="108" t="s">
+        <v>2882</v>
+      </c>
+      <c r="F7" s="108" t="s">
+        <v>2875</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H7" s="28" t="s">
         <v>2864</v>
       </c>
-      <c r="F7" s="108" t="s">
-        <v>2866</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>2872</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>2868</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="108" t="s">
-        <v>2856</v>
+        <v>2883</v>
       </c>
       <c r="B8" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
       <c r="E8" s="108" t="s">
-        <v>2856</v>
+        <v>2883</v>
       </c>
       <c r="F8" s="108" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>2860</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="108" t="s">
-        <v>2857</v>
+        <v>2884</v>
       </c>
       <c r="B9" s="108" t="s">
-        <v>2852</v>
+        <v>2880</v>
       </c>
       <c r="C9" s="109"/>
       <c r="D9" s="109"/>
       <c r="E9" s="108" t="s">
-        <v>2857</v>
+        <v>2884</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>2861</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="108" t="s">
-        <v>2851</v>
+        <v>2877</v>
       </c>
       <c r="B10" s="108"/>
       <c r="C10" s="109"/>
       <c r="D10" s="109"/>
       <c r="E10" s="108" t="s">
-        <v>2851</v>
+        <v>2877</v>
       </c>
       <c r="F10" s="108" t="s">
-        <v>2858</v>
+        <v>2879</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>2870</v>
+        <v>2845</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>2862</v>
+        <v>2894</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="108" t="s">
-        <v>2853</v>
+        <v>2885</v>
       </c>
       <c r="B11" s="108" t="s">
-        <v>2851</v>
+        <v>2877</v>
       </c>
       <c r="C11" s="109"/>
       <c r="D11" s="109"/>
       <c r="E11" s="108" t="s">
-        <v>2853</v>
+        <v>2885</v>
       </c>
       <c r="F11" s="108" t="s">
-        <v>2784</v>
+        <v>2868</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>2871</v>
+        <v>2846</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>2786</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="108" t="s">
-        <v>2854</v>
+        <v>2886</v>
       </c>
       <c r="B12" s="108" t="s">
-        <v>2853</v>
+        <v>2885</v>
       </c>
       <c r="C12" s="109"/>
       <c r="D12" s="109"/>
       <c r="E12" s="108" t="s">
-        <v>2854</v>
+        <v>2886</v>
       </c>
       <c r="F12" s="108" t="s">
-        <v>2785</v>
+        <v>2869</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>2789</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="108" t="s">
-        <v>2855</v>
+        <v>2887</v>
       </c>
       <c r="B13" s="108" t="s">
-        <v>2853</v>
+        <v>2885</v>
       </c>
       <c r="C13" s="109"/>
       <c r="D13" s="109"/>
       <c r="E13" s="108" t="s">
-        <v>2855</v>
+        <v>2887</v>
       </c>
       <c r="F13" s="108" t="s">
-        <v>2787</v>
+        <v>2870</v>
       </c>
       <c r="G13" s="27" t="s">
+        <v>2848</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>2898</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="108" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B14" s="108" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C14" s="109"/>
+      <c r="D14" s="109"/>
+      <c r="E14" s="108" t="s">
+        <v>2888</v>
+      </c>
+      <c r="F14" s="108" t="s">
+        <v>2871</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="108" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="108" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F15" s="108" t="s">
+        <v>2872</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="108" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B16" s="108" t="s">
+        <v>2885</v>
+      </c>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="108" t="s">
+        <v>2890</v>
+      </c>
+      <c r="F16" s="108" t="s">
         <v>2873</v>
       </c>
-      <c r="H13" s="28" t="s">
-        <v>2790</v>
+      <c r="G16" s="27" t="s">
+        <v>2847</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>2867</v>
       </c>
     </row>
   </sheetData>
@@ -16112,7 +16217,7 @@
       </c>
       <c r="B1" s="56"/>
       <c r="C1" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D1" s="56"/>
       <c r="E1" s="57"/>
@@ -16135,10 +16240,10 @@
       <c r="P1" s="56"/>
       <c r="Q1" s="56"/>
       <c r="R1" s="24" t="s">
+        <v>2715</v>
+      </c>
+      <c r="S1" s="33" t="s">
         <v>2716</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>2717</v>
       </c>
       <c r="T1" s="51" t="s">
         <v>871</v>
@@ -16147,7 +16252,7 @@
         <v>881</v>
       </c>
       <c r="V1" s="52" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="W1" s="60" t="s">
         <v>878</v>
@@ -16158,11 +16263,11 @@
     </row>
     <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="B2" s="56"/>
       <c r="C2" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D2" s="56"/>
       <c r="E2" s="57"/>
@@ -16172,10 +16277,10 @@
       <c r="G2" s="53"/>
       <c r="H2" s="53"/>
       <c r="I2" s="56" t="s">
+        <v>2720</v>
+      </c>
+      <c r="J2" s="56" t="s">
         <v>2721</v>
-      </c>
-      <c r="J2" s="56" t="s">
-        <v>2722</v>
       </c>
       <c r="K2" s="63"/>
       <c r="L2" s="64"/>
@@ -16185,10 +16290,10 @@
       <c r="P2" s="56"/>
       <c r="Q2" s="56"/>
       <c r="R2" s="24" t="s">
+        <v>2715</v>
+      </c>
+      <c r="S2" s="33" t="s">
         <v>2716</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>2717</v>
       </c>
       <c r="T2" s="51" t="s">
         <v>869</v>
@@ -16197,7 +16302,7 @@
         <v>881</v>
       </c>
       <c r="V2" s="52" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="W2" s="60" t="s">
         <v>878</v>
@@ -16212,7 +16317,7 @@
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D3" s="56"/>
       <c r="E3" s="57"/>
@@ -16235,10 +16340,10 @@
       <c r="P3" s="56"/>
       <c r="Q3" s="56"/>
       <c r="R3" s="24" t="s">
+        <v>2715</v>
+      </c>
+      <c r="S3" s="33" t="s">
         <v>2716</v>
-      </c>
-      <c r="S3" s="33" t="s">
-        <v>2717</v>
       </c>
       <c r="T3" s="51" t="s">
         <v>871</v>
@@ -16247,7 +16352,7 @@
         <v>884</v>
       </c>
       <c r="V3" s="52" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="W3" s="60" t="s">
         <v>878</v>
@@ -16258,11 +16363,11 @@
     </row>
     <row r="4" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="B4" s="56"/>
       <c r="C4" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D4" s="56"/>
       <c r="E4" s="57"/>
@@ -16272,10 +16377,10 @@
       <c r="G4" s="53"/>
       <c r="H4" s="53"/>
       <c r="I4" s="56" t="s">
+        <v>2722</v>
+      </c>
+      <c r="J4" s="56" t="s">
         <v>2723</v>
-      </c>
-      <c r="J4" s="56" t="s">
-        <v>2724</v>
       </c>
       <c r="K4" s="63"/>
       <c r="L4" s="64"/>
@@ -16285,10 +16390,10 @@
       <c r="P4" s="56"/>
       <c r="Q4" s="56"/>
       <c r="R4" s="24" t="s">
+        <v>2715</v>
+      </c>
+      <c r="S4" s="33" t="s">
         <v>2716</v>
-      </c>
-      <c r="S4" s="33" t="s">
-        <v>2717</v>
       </c>
       <c r="T4" s="51" t="s">
         <v>869</v>
@@ -16297,7 +16402,7 @@
         <v>884</v>
       </c>
       <c r="V4" s="52" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="W4" s="60" t="s">
         <v>878</v>
@@ -16308,11 +16413,11 @@
     </row>
     <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D5" s="56"/>
       <c r="E5" s="57"/>
@@ -16322,10 +16427,10 @@
       <c r="G5" s="53"/>
       <c r="H5" s="53"/>
       <c r="I5" s="56" t="s">
+        <v>2736</v>
+      </c>
+      <c r="J5" s="56" t="s">
         <v>2737</v>
-      </c>
-      <c r="J5" s="56" t="s">
-        <v>2738</v>
       </c>
       <c r="K5" s="63"/>
       <c r="L5" s="64"/>
@@ -16335,22 +16440,22 @@
       <c r="P5" s="56"/>
       <c r="Q5" s="56"/>
       <c r="R5" s="24" t="s">
+        <v>2715</v>
+      </c>
+      <c r="S5" s="33" t="s">
         <v>2716</v>
-      </c>
-      <c r="S5" s="33" t="s">
-        <v>2717</v>
       </c>
       <c r="T5" s="51" t="s">
         <v>869</v>
       </c>
       <c r="U5" s="56" t="s">
+        <v>2738</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>2733</v>
+      </c>
+      <c r="W5" s="60" t="s">
         <v>2739</v>
-      </c>
-      <c r="V5" s="52" t="s">
-        <v>2734</v>
-      </c>
-      <c r="W5" s="60" t="s">
-        <v>2740</v>
       </c>
       <c r="X5" s="50" t="s">
         <v>815</v>
@@ -16362,10 +16467,10 @@
       </c>
       <c r="B6" s="56"/>
       <c r="C6" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E6" s="57" t="s">
         <v>516</v>
@@ -16374,7 +16479,7 @@
         <v>74</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H6" s="53"/>
       <c r="I6" s="56" t="s">
@@ -16396,7 +16501,7 @@
         <v>257</v>
       </c>
       <c r="S6" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T6" s="68" t="s">
         <v>826</v>
@@ -16422,10 +16527,10 @@
         <v>1075</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E7" s="57" t="s">
         <v>516</v>
@@ -16434,7 +16539,7 @@
         <v>74</v>
       </c>
       <c r="G7" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H7" s="53"/>
       <c r="I7" s="56" t="s">
@@ -16453,26 +16558,26 @@
         <v>108</v>
       </c>
       <c r="N7" s="26" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="O7" s="28" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="P7" s="56"/>
       <c r="Q7" s="35" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="T7" s="56" t="s">
         <v>827</v>
       </c>
       <c r="U7" s="56" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="V7" s="69" t="s">
         <v>213</v>
@@ -16492,10 +16597,10 @@
         <v>1075</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="E8" s="57" t="s">
         <v>516</v>
@@ -16504,7 +16609,7 @@
         <v>74</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H8" s="53"/>
       <c r="I8" s="56" t="s">
@@ -16523,26 +16628,26 @@
         <v>108</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="O8" s="28" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="P8" s="56"/>
       <c r="Q8" s="35" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="S8" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="T8" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U8" s="56" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="V8" s="56" t="s">
         <v>577</v>
@@ -16560,7 +16665,7 @@
       </c>
       <c r="B9" s="59"/>
       <c r="C9" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D9" s="56"/>
       <c r="E9" s="57" t="s">
@@ -16570,7 +16675,7 @@
         <v>74</v>
       </c>
       <c r="G9" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H9" s="53" t="s">
         <v>886</v>
@@ -16594,7 +16699,7 @@
         <v>257</v>
       </c>
       <c r="S9" s="33" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="T9" s="68" t="s">
         <v>826</v>
@@ -16620,7 +16725,7 @@
         <v>908</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D10" s="56"/>
       <c r="E10" s="57" t="s">
@@ -16630,7 +16735,7 @@
         <v>74</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H10" s="53"/>
       <c r="I10" s="56" t="s">
@@ -16649,7 +16754,7 @@
         <v>143</v>
       </c>
       <c r="N10" s="56" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
@@ -16657,16 +16762,16 @@
         <v>304</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="S10" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T10" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U10" s="56" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="V10" s="56" t="s">
         <v>577</v>
@@ -16686,7 +16791,7 @@
         <v>908</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D11" s="56"/>
       <c r="E11" s="57" t="s">
@@ -16696,7 +16801,7 @@
         <v>74</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H11" s="53"/>
       <c r="I11" s="56" t="s">
@@ -16721,16 +16826,16 @@
       </c>
       <c r="Q11" s="56"/>
       <c r="R11" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="S11" s="33" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="T11" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U11" s="56" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="V11" s="56" t="s">
         <v>577</v>
@@ -16750,7 +16855,7 @@
         <v>908</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="D12" s="56"/>
       <c r="E12" s="57" t="s">
@@ -16760,7 +16865,7 @@
         <v>74</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="H12" s="53"/>
       <c r="I12" s="56" t="s">
@@ -16779,7 +16884,7 @@
         <v>143</v>
       </c>
       <c r="N12" s="56" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="O12" s="56"/>
       <c r="P12" s="56"/>
@@ -16787,16 +16892,16 @@
         <v>304</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="S12" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="T12" s="56" t="s">
         <v>819</v>
       </c>
       <c r="U12" s="56" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="V12" s="56" t="s">
         <v>577</v>
@@ -30386,7 +30491,7 @@
         <v>1410</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="27"/>
@@ -30405,7 +30510,7 @@
         <v>1412</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C18" s="22"/>
       <c r="D18" s="27"/>
@@ -30424,7 +30529,7 @@
         <v>1414</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C19" s="22"/>
       <c r="D19" s="27"/>
@@ -30443,7 +30548,7 @@
         <v>1416</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C20" s="22"/>
       <c r="D20" s="27"/>
@@ -30459,7 +30564,7 @@
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>1407</v>
@@ -30467,10 +30572,10 @@
       <c r="C21" s="22"/>
       <c r="D21" s="27"/>
       <c r="E21" s="27" t="s">
+        <v>2745</v>
+      </c>
+      <c r="F21" s="27" t="s">
         <v>2746</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>2747</v>
       </c>
       <c r="G21" s="45" t="s">
         <v>626</v>
@@ -30519,7 +30624,7 @@
         <v>1421</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C24" s="22"/>
       <c r="D24" s="27"/>
@@ -30538,7 +30643,7 @@
         <v>1423</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="27"/>
@@ -30595,7 +30700,7 @@
         <v>1428</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="27"/>
@@ -30614,7 +30719,7 @@
         <v>1430</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C29" s="22"/>
       <c r="D29" s="27"/>
@@ -30744,7 +30849,7 @@
     </row>
     <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="27" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="B36" s="27" t="s">
         <v>1407</v>
@@ -30752,7 +30857,7 @@
       <c r="C36" s="22"/>
       <c r="D36" s="27"/>
       <c r="E36" s="27" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="F36" s="27" t="s">
         <v>2248</v>
@@ -30763,7 +30868,7 @@
     </row>
     <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="27" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="B37" s="27" t="s">
         <v>1407</v>
@@ -30771,7 +30876,7 @@
       <c r="C37" s="22"/>
       <c r="D37" s="27"/>
       <c r="E37" s="27" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="F37" s="27" t="s">
         <v>2131</v>
@@ -30782,7 +30887,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="B38" s="27" t="s">
         <v>1407</v>
@@ -30790,7 +30895,7 @@
       <c r="C38" s="22"/>
       <c r="D38" s="27"/>
       <c r="E38" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="F38" s="27" t="s">
         <v>681</v>
@@ -30801,7 +30906,7 @@
     </row>
     <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="B39" s="27" t="s">
         <v>1407</v>
@@ -30809,7 +30914,7 @@
       <c r="C39" s="22"/>
       <c r="D39" s="27"/>
       <c r="E39" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="F39" s="33" t="s">
         <v>601</v>
@@ -30820,7 +30925,7 @@
     </row>
     <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="27" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="B40" s="27" t="s">
         <v>1407</v>
@@ -30828,10 +30933,10 @@
       <c r="C40" s="22"/>
       <c r="D40" s="27"/>
       <c r="E40" s="27" t="s">
+        <v>2724</v>
+      </c>
+      <c r="F40" s="33" t="s">
         <v>2725</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>2726</v>
       </c>
       <c r="G40" s="45" t="s">
         <v>626</v>
@@ -30989,7 +31094,7 @@
     </row>
     <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>2578</v>
+        <v>2577</v>
       </c>
       <c r="B49" s="27" t="s">
         <v>1442</v>
@@ -30997,10 +31102,10 @@
       <c r="C49" s="32"/>
       <c r="D49" s="27"/>
       <c r="E49" s="27" t="s">
+        <v>2577</v>
+      </c>
+      <c r="F49" s="27" t="s">
         <v>2578</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>2579</v>
       </c>
       <c r="G49" s="45" t="s">
         <v>626</v>
@@ -31935,7 +32040,7 @@
     </row>
     <row r="99" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="27" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="B99" s="27" t="s">
         <v>1330</v>
@@ -31943,10 +32048,10 @@
       <c r="C99" s="53"/>
       <c r="D99" s="27"/>
       <c r="E99" s="27" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F99" s="27" t="s">
         <v>2479</v>
-      </c>
-      <c r="F99" s="27" t="s">
-        <v>2480</v>
       </c>
       <c r="G99" s="45" t="s">
         <v>626</v>
@@ -32292,13 +32397,13 @@
     </row>
     <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="27" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="B118" s="27"/>
       <c r="C118" s="22"/>
       <c r="D118" s="27"/>
       <c r="E118" s="27" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="F118" s="27" t="s">
         <v>60</v>
@@ -32309,18 +32414,18 @@
     </row>
     <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="B119" s="27" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C119" s="22"/>
       <c r="D119" s="27"/>
       <c r="E119" s="27" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F119" s="27" t="s">
         <v>2756</v>
-      </c>
-      <c r="F119" s="27" t="s">
-        <v>2757</v>
       </c>
       <c r="G119" s="45" t="s">
         <v>626</v>
@@ -32328,15 +32433,15 @@
     </row>
     <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A120" s="24" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="B120" s="27" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C120" s="22"/>
       <c r="D120" s="27"/>
       <c r="E120" s="24" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="F120" s="27" t="s">
         <v>1513</v>
@@ -32347,16 +32452,16 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="B121" s="27"/>
       <c r="C121" s="22"/>
       <c r="D121" s="27"/>
       <c r="E121" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="F121" s="27" t="s">
-        <v>2875</v>
+        <v>2850</v>
       </c>
       <c r="G121" s="45" t="s">
         <v>626</v>
@@ -32364,18 +32469,18 @@
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A122" s="27" t="s">
-        <v>2870</v>
+        <v>2845</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C122" s="22"/>
       <c r="D122" s="27"/>
       <c r="E122" s="27" t="s">
-        <v>2870</v>
+        <v>2845</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>2876</v>
+        <v>2851</v>
       </c>
       <c r="G122" s="45" t="s">
         <v>626</v>
@@ -32383,18 +32488,18 @@
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A123" s="27" t="s">
-        <v>2871</v>
+        <v>2891</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C123" s="22"/>
       <c r="D123" s="27"/>
       <c r="E123" s="27" t="s">
-        <v>2871</v>
+        <v>2891</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>2877</v>
+        <v>2852</v>
       </c>
       <c r="G123" s="45" t="s">
         <v>626</v>
@@ -32402,18 +32507,18 @@
     </row>
     <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A124" s="27" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="B124" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C124" s="22"/>
       <c r="D124" s="27"/>
       <c r="E124" s="27" t="s">
-        <v>2873</v>
+        <v>2848</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>2878</v>
+        <v>2853</v>
       </c>
       <c r="G124" s="45" t="s">
         <v>626</v>
@@ -32421,18 +32526,18 @@
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A125" s="27" t="s">
-        <v>2872</v>
+        <v>2847</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C125" s="22"/>
       <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
-        <v>2872</v>
+        <v>2847</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>2879</v>
+        <v>2854</v>
       </c>
       <c r="G125" s="45" t="s">
         <v>626</v>
@@ -32440,18 +32545,18 @@
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A126" s="27" t="s">
-        <v>2882</v>
+        <v>2857</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C126" s="22"/>
       <c r="D126" s="27"/>
       <c r="E126" s="27" t="s">
-        <v>2882</v>
+        <v>2857</v>
       </c>
       <c r="F126" s="27" t="s">
-        <v>2883</v>
+        <v>2858</v>
       </c>
       <c r="G126" s="45" t="s">
         <v>626</v>
@@ -32459,18 +32564,18 @@
     </row>
     <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A127" s="27" t="s">
-        <v>2884</v>
+        <v>2859</v>
       </c>
       <c r="B127" s="24" t="s">
-        <v>2874</v>
+        <v>2849</v>
       </c>
       <c r="C127" s="22"/>
       <c r="D127" s="27"/>
       <c r="E127" s="27" t="s">
-        <v>2884</v>
+        <v>2859</v>
       </c>
       <c r="F127" s="27" t="s">
-        <v>2885</v>
+        <v>2860</v>
       </c>
       <c r="G127" s="45" t="s">
         <v>626</v>
@@ -33192,7 +33297,7 @@
     </row>
     <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="27" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="B166" s="27" t="s">
         <v>1581</v>
@@ -33200,10 +33305,10 @@
       <c r="C166" s="22"/>
       <c r="D166" s="27"/>
       <c r="E166" s="27" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F166" s="27" t="s">
         <v>2708</v>
-      </c>
-      <c r="F166" s="27" t="s">
-        <v>2709</v>
       </c>
       <c r="G166" s="45" t="s">
         <v>626</v>
@@ -34984,7 +35089,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A26" s="52" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>866</v>
@@ -34992,16 +35097,16 @@
       <c r="C26" s="36"/>
       <c r="D26" s="52"/>
       <c r="E26" s="52" t="s">
+        <v>2709</v>
+      </c>
+      <c r="F26" s="52" t="s">
         <v>2710</v>
-      </c>
-      <c r="F26" s="52" t="s">
-        <v>2711</v>
       </c>
       <c r="G26" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35085,7 +35190,7 @@
         <v>290</v>
       </c>
       <c r="H30" s="52" t="s">
-        <v>2886</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35518,7 +35623,7 @@
     </row>
     <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A51" s="52" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="B51" s="52" t="s">
         <v>213</v>
@@ -35526,21 +35631,21 @@
       <c r="C51" s="36"/>
       <c r="D51" s="52"/>
       <c r="E51" s="52" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F51" s="52" t="s">
         <v>2731</v>
-      </c>
-      <c r="F51" s="52" t="s">
-        <v>2732</v>
       </c>
       <c r="G51" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H51" s="52" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A52" s="52" t="s">
-        <v>2734</v>
+        <v>2733</v>
       </c>
       <c r="B52" s="52" t="s">
         <v>213</v>
@@ -35548,21 +35653,21 @@
       <c r="C52" s="36"/>
       <c r="D52" s="52"/>
       <c r="E52" s="52" t="s">
+        <v>2733</v>
+      </c>
+      <c r="F52" s="52" t="s">
         <v>2734</v>
-      </c>
-      <c r="F52" s="52" t="s">
-        <v>2735</v>
       </c>
       <c r="G52" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H52" s="52" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="52" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="B53" s="52" t="s">
         <v>213</v>
@@ -35570,16 +35675,16 @@
       <c r="C53" s="36"/>
       <c r="D53" s="52"/>
       <c r="E53" s="52" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F53" s="52" t="s">
         <v>2741</v>
-      </c>
-      <c r="F53" s="52" t="s">
-        <v>2742</v>
       </c>
       <c r="G53" s="24" t="s">
         <v>294</v>
       </c>
       <c r="H53" s="52" t="s">
-        <v>2743</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -35670,22 +35775,22 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A58" s="52" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="B58" s="52"/>
       <c r="C58" s="36"/>
       <c r="D58" s="52"/>
       <c r="E58" s="52" t="s">
+        <v>2652</v>
+      </c>
+      <c r="F58" s="52" t="s">
         <v>2653</v>
-      </c>
-      <c r="F58" s="52" t="s">
-        <v>2654</v>
       </c>
       <c r="G58" s="24" t="s">
         <v>290</v>
       </c>
       <c r="H58" s="52" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.3">
@@ -36058,7 +36163,7 @@
         <v>78</v>
       </c>
       <c r="I1" s="110" t="s">
-        <v>2791</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36083,7 +36188,7 @@
         <v>78</v>
       </c>
       <c r="I2" s="110" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36108,7 +36213,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="110" t="s">
-        <v>2794</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36133,7 +36238,7 @@
         <v>78</v>
       </c>
       <c r="I4" s="110" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36158,7 +36263,7 @@
         <v>78</v>
       </c>
       <c r="I5" s="110" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36183,7 +36288,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="110" t="s">
-        <v>2793</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36208,7 +36313,7 @@
         <v>78</v>
       </c>
       <c r="I7" s="110" t="s">
-        <v>2795</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36231,7 +36336,7 @@
         <v>78</v>
       </c>
       <c r="I8" s="110" t="s">
-        <v>2796</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36256,7 +36361,7 @@
         <v>84</v>
       </c>
       <c r="I9" s="110" t="s">
-        <v>2797</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36279,7 +36384,7 @@
         <v>84</v>
       </c>
       <c r="I10" s="110" t="s">
-        <v>2798</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36302,7 +36407,7 @@
         <v>78</v>
       </c>
       <c r="I11" s="110" t="s">
-        <v>2799</v>
+        <v>2794</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36327,7 +36432,7 @@
         <v>78</v>
       </c>
       <c r="I12" s="110" t="s">
-        <v>2800</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36352,7 +36457,7 @@
         <v>78</v>
       </c>
       <c r="I13" s="110" t="s">
-        <v>2801</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36377,7 +36482,7 @@
         <v>78</v>
       </c>
       <c r="I14" s="110" t="s">
-        <v>2802</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36402,7 +36507,7 @@
         <v>78</v>
       </c>
       <c r="I15" s="110" t="s">
-        <v>2803</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36427,7 +36532,7 @@
         <v>78</v>
       </c>
       <c r="I16" s="110" t="s">
-        <v>2804</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36450,7 +36555,7 @@
         <v>78</v>
       </c>
       <c r="I17" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36475,7 +36580,7 @@
         <v>78</v>
       </c>
       <c r="I18" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36500,7 +36605,7 @@
         <v>78</v>
       </c>
       <c r="I19" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36525,7 +36630,7 @@
         <v>84</v>
       </c>
       <c r="I20" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36550,7 +36655,7 @@
         <v>78</v>
       </c>
       <c r="I21" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36575,7 +36680,7 @@
         <v>78</v>
       </c>
       <c r="I22" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36600,7 +36705,7 @@
         <v>78</v>
       </c>
       <c r="I23" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36625,7 +36730,7 @@
         <v>78</v>
       </c>
       <c r="I24" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36650,7 +36755,7 @@
         <v>78</v>
       </c>
       <c r="I25" s="110" t="s">
-        <v>2792</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36673,7 +36778,7 @@
         <v>78</v>
       </c>
       <c r="I26" s="110" t="s">
-        <v>2805</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36696,7 +36801,7 @@
         <v>78</v>
       </c>
       <c r="I27" s="110" t="s">
-        <v>2806</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36719,7 +36824,7 @@
         <v>84</v>
       </c>
       <c r="I28" s="110" t="s">
-        <v>2807</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36744,7 +36849,7 @@
         <v>84</v>
       </c>
       <c r="I29" s="110" t="s">
-        <v>2808</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36769,7 +36874,7 @@
         <v>84</v>
       </c>
       <c r="I30" s="110" t="s">
-        <v>2809</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36794,7 +36899,7 @@
         <v>84</v>
       </c>
       <c r="I31" s="110" t="s">
-        <v>2810</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36819,7 +36924,7 @@
         <v>84</v>
       </c>
       <c r="I32" s="110" t="s">
-        <v>2811</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36842,7 +36947,7 @@
         <v>78</v>
       </c>
       <c r="I33" s="110" t="s">
-        <v>2812</v>
+        <v>2807</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36867,7 +36972,7 @@
         <v>78</v>
       </c>
       <c r="I34" s="110" t="s">
-        <v>2813</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36892,7 +36997,7 @@
         <v>78</v>
       </c>
       <c r="I35" s="110" t="s">
-        <v>2814</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36917,7 +37022,7 @@
         <v>78</v>
       </c>
       <c r="I36" s="110" t="s">
-        <v>2815</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36940,7 +37045,7 @@
         <v>84</v>
       </c>
       <c r="I37" s="110" t="s">
-        <v>2816</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36965,7 +37070,7 @@
         <v>84</v>
       </c>
       <c r="I38" s="110" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -36988,7 +37093,7 @@
         <v>84</v>
       </c>
       <c r="I39" s="110" t="s">
-        <v>2818</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37013,7 +37118,7 @@
         <v>84</v>
       </c>
       <c r="I40" s="110" t="s">
-        <v>2819</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37036,7 +37141,7 @@
         <v>84</v>
       </c>
       <c r="I41" s="110" t="s">
-        <v>2820</v>
+        <v>2815</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37061,7 +37166,7 @@
         <v>84</v>
       </c>
       <c r="I42" s="110" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37086,7 +37191,7 @@
         <v>84</v>
       </c>
       <c r="I43" s="110" t="s">
-        <v>2821</v>
+        <v>2816</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37111,7 +37216,7 @@
         <v>84</v>
       </c>
       <c r="I44" s="110" t="s">
-        <v>2822</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37136,7 +37241,7 @@
         <v>84</v>
       </c>
       <c r="I45" s="110" t="s">
-        <v>2823</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37161,7 +37266,7 @@
         <v>84</v>
       </c>
       <c r="I46" s="110" t="s">
-        <v>2824</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37186,7 +37291,7 @@
         <v>84</v>
       </c>
       <c r="I47" s="110" t="s">
-        <v>2825</v>
+        <v>2820</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37211,7 +37316,7 @@
         <v>84</v>
       </c>
       <c r="I48" s="110" t="s">
-        <v>2826</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37236,7 +37341,7 @@
         <v>84</v>
       </c>
       <c r="I49" s="110" t="s">
-        <v>2823</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37261,7 +37366,7 @@
         <v>84</v>
       </c>
       <c r="I50" s="110" t="s">
-        <v>2823</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37286,7 +37391,7 @@
         <v>84</v>
       </c>
       <c r="I51" s="110" t="s">
-        <v>2827</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37311,7 +37416,7 @@
         <v>84</v>
       </c>
       <c r="I52" s="110" t="s">
-        <v>2828</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37336,7 +37441,7 @@
         <v>84</v>
       </c>
       <c r="I53" s="110" t="s">
-        <v>2829</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37361,7 +37466,7 @@
         <v>84</v>
       </c>
       <c r="I54" s="110" t="s">
-        <v>2830</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37386,7 +37491,7 @@
         <v>78</v>
       </c>
       <c r="I55" s="110" t="s">
-        <v>2831</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37411,7 +37516,7 @@
         <v>84</v>
       </c>
       <c r="I56" s="110" t="s">
-        <v>2832</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -37425,7 +37530,7 @@
         <v>1251</v>
       </c>
       <c r="F57" s="110" t="s">
-        <v>2845</v>
+        <v>2840</v>
       </c>
       <c r="G57" s="110" t="s">
         <v>86</v>
@@ -37434,7 +37539,7 @@
         <v>78</v>
       </c>
       <c r="I57" s="110" t="s">
-        <v>2846</v>
+        <v>2841</v>
       </c>
     </row>
   </sheetData>
@@ -37475,7 +37580,7 @@
   <sheetData>
     <row r="1" spans="1:23" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C1" s="41" t="s">
         <v>232</v>
@@ -37487,13 +37592,13 @@
         <v>76</v>
       </c>
       <c r="G1" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I1" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="J1" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="K1" s="56" t="s">
         <v>215</v>
@@ -37505,7 +37610,7 @@
         <v>257</v>
       </c>
       <c r="R1" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="S1" s="68" t="s">
         <v>826</v>
@@ -37517,7 +37622,7 @@
         <v>829</v>
       </c>
       <c r="V1" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W1" s="83" t="s">
         <v>2132</v>
@@ -37525,10 +37630,10 @@
     </row>
     <row r="2" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A2" s="105" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="B2" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C2" s="41" t="s">
         <v>232</v>
@@ -37540,13 +37645,13 @@
         <v>76</v>
       </c>
       <c r="G2" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I2" s="105" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="J2" s="105" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="K2" s="56" t="s">
         <v>215</v>
@@ -37561,10 +37666,10 @@
         <v>1077</v>
       </c>
       <c r="O2" s="105" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R2" s="33" t="s">
         <v>682</v>
@@ -37579,7 +37684,7 @@
         <v>213</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W2" s="83" t="s">
         <v>2132</v>
@@ -37587,10 +37692,10 @@
     </row>
     <row r="3" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A3" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="B3" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>232</v>
@@ -37602,13 +37707,13 @@
         <v>76</v>
       </c>
       <c r="G3" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I3" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="J3" s="105" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="K3" s="56" t="s">
         <v>215</v>
@@ -37623,10 +37728,10 @@
         <v>1080</v>
       </c>
       <c r="O3" s="105" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R3" s="33" t="s">
         <v>674</v>
@@ -37641,7 +37746,7 @@
         <v>577</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W3" s="83" t="s">
         <v>2132</v>
@@ -37649,10 +37754,10 @@
     </row>
     <row r="4" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="B4" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C4" s="41" t="s">
         <v>232</v>
@@ -37664,13 +37769,13 @@
         <v>76</v>
       </c>
       <c r="G4" s="106" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I4" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="J4" s="105" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>215</v>
@@ -37685,10 +37790,10 @@
         <v>1077</v>
       </c>
       <c r="O4" s="105" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R4" s="33" t="s">
         <v>682</v>
@@ -37703,7 +37808,7 @@
         <v>213</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W4" s="83" t="s">
         <v>2132</v>
@@ -37711,10 +37816,10 @@
     </row>
     <row r="5" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A5" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C5" s="41" t="s">
         <v>232</v>
@@ -37726,13 +37831,13 @@
         <v>76</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I5" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="J5" s="105" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="K5" s="56" t="s">
         <v>215</v>
@@ -37747,10 +37852,10 @@
         <v>1080</v>
       </c>
       <c r="O5" s="105" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R5" s="33" t="s">
         <v>674</v>
@@ -37765,7 +37870,7 @@
         <v>577</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W5" s="83" t="s">
         <v>2132</v>
@@ -37773,7 +37878,7 @@
     </row>
     <row r="6" spans="1:23" s="107" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="105" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="C6" s="41" t="s">
         <v>232</v>
@@ -37785,13 +37890,13 @@
         <v>76</v>
       </c>
       <c r="G6" s="106" t="s">
+        <v>2779</v>
+      </c>
+      <c r="I6" s="105" t="s">
         <v>2780</v>
       </c>
-      <c r="I6" s="105" t="s">
-        <v>2781</v>
-      </c>
       <c r="J6" s="105" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="K6" s="56" t="s">
         <v>215</v>
@@ -37803,7 +37908,7 @@
         <v>257</v>
       </c>
       <c r="R6" s="33" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="S6" s="68" t="s">
         <v>826</v>
@@ -37815,7 +37920,7 @@
         <v>829</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W6" s="83" t="s">
         <v>2132</v>
@@ -37823,10 +37928,10 @@
     </row>
     <row r="7" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="C7" s="41" t="s">
         <v>232</v>
@@ -37841,13 +37946,13 @@
         <v>76</v>
       </c>
       <c r="G7" s="106" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="I7" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="J7" s="105" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="K7" s="56" t="s">
         <v>215</v>
@@ -37863,7 +37968,7 @@
       </c>
       <c r="O7" s="105"/>
       <c r="Q7" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>674</v>
@@ -37878,7 +37983,7 @@
         <v>577</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W7" s="83" t="s">
         <v>2132</v>
@@ -37886,10 +37991,10 @@
     </row>
     <row r="8" spans="1:23" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A8" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>232</v>
@@ -37904,13 +38009,13 @@
         <v>76</v>
       </c>
       <c r="G8" s="106" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="I8" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="J8" s="105" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="K8" s="56" t="s">
         <v>215</v>
@@ -37926,7 +38031,7 @@
       </c>
       <c r="O8" s="105"/>
       <c r="Q8" s="27" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="R8" s="33" t="s">
         <v>674</v>
@@ -37941,7 +38046,7 @@
         <v>577</v>
       </c>
       <c r="V8" s="37" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="W8" s="83" t="s">
         <v>2132</v>
@@ -38706,7 +38811,7 @@
     </row>
     <row r="29" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="77" t="s">
-        <v>2850</v>
+        <v>2844</v>
       </c>
       <c r="F29" s="77" t="s">
         <v>76</v>
@@ -38716,7 +38821,7 @@
       </c>
       <c r="H29" s="77"/>
       <c r="I29" s="77" t="s">
-        <v>2850</v>
+        <v>2844</v>
       </c>
       <c r="J29" s="77" t="s">
         <v>1840</v>
@@ -38728,7 +38833,7 @@
         <v>851</v>
       </c>
       <c r="T29" s="77" t="s">
-        <v>2847</v>
+        <v>2842</v>
       </c>
       <c r="U29" s="77" t="s">
         <v>1734</v>
@@ -39269,7 +39374,7 @@
         <v>835</v>
       </c>
       <c r="T50" s="77" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="U50" s="77" t="s">
         <v>1728</v>
@@ -39321,7 +39426,7 @@
     </row>
     <row r="52" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="77" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="F52" s="77" t="s">
         <v>76</v>
@@ -39333,10 +39438,10 @@
         <v>1917</v>
       </c>
       <c r="I52" s="77" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="J52" s="77" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="K52" s="77" t="s">
         <v>215</v>
@@ -39345,7 +39450,7 @@
         <v>835</v>
       </c>
       <c r="T52" s="77" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="U52" s="77" t="s">
         <v>1728</v>
@@ -39359,7 +39464,7 @@
     </row>
     <row r="53" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="77" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="F53" s="77" t="s">
         <v>76</v>
@@ -39371,10 +39476,10 @@
         <v>1921</v>
       </c>
       <c r="I53" s="77" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="J53" s="77" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="K53" s="77" t="s">
         <v>215</v>
@@ -39383,7 +39488,7 @@
         <v>835</v>
       </c>
       <c r="T53" s="77" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="U53" s="77" t="s">
         <v>1728</v>
@@ -39397,7 +39502,7 @@
     </row>
     <row r="54" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="77" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="F54" s="77" t="s">
         <v>76</v>
@@ -39406,13 +39511,13 @@
         <v>1924</v>
       </c>
       <c r="H54" s="77" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="I54" s="77" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="J54" s="77" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="K54" s="77" t="s">
         <v>215</v>
@@ -39421,7 +39526,7 @@
         <v>835</v>
       </c>
       <c r="T54" s="77" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="U54" s="77" t="s">
         <v>1728</v>
@@ -39435,22 +39540,22 @@
     </row>
     <row r="55" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="77" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="F55" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G55" s="77" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="H55" s="77" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="I55" s="77" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="J55" s="77" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="K55" s="77" t="s">
         <v>215</v>
@@ -39459,7 +39564,7 @@
         <v>835</v>
       </c>
       <c r="T55" s="77" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="U55" s="77" t="s">
         <v>1728</v>
@@ -39473,22 +39578,22 @@
     </row>
     <row r="56" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="77" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="F56" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G56" s="77" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="H56" s="77" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="I56" s="77" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="J56" s="77" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="K56" s="77" t="s">
         <v>215</v>
@@ -39497,7 +39602,7 @@
         <v>835</v>
       </c>
       <c r="T56" s="77" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="U56" s="77" t="s">
         <v>1728</v>
@@ -39511,22 +39616,22 @@
     </row>
     <row r="57" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="77" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="F57" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G57" s="77" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="H57" s="77" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="I57" s="77" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="J57" s="77" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="K57" s="77" t="s">
         <v>215</v>
@@ -39535,7 +39640,7 @@
         <v>835</v>
       </c>
       <c r="T57" s="77" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="U57" s="77" t="s">
         <v>1728</v>
@@ -39549,22 +39654,22 @@
     </row>
     <row r="58" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="77" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="F58" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G58" s="77" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="H58" s="77" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="I58" s="77" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="J58" s="77" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="K58" s="77" t="s">
         <v>215</v>
@@ -39573,7 +39678,7 @@
         <v>835</v>
       </c>
       <c r="T58" s="77" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="U58" s="77" t="s">
         <v>1728</v>
@@ -39587,22 +39692,22 @@
     </row>
     <row r="59" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="77" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="F59" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G59" s="77" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="H59" s="77" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="I59" s="77" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="J59" s="77" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="K59" s="77" t="s">
         <v>215</v>
@@ -39611,7 +39716,7 @@
         <v>835</v>
       </c>
       <c r="T59" s="77" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="U59" s="77" t="s">
         <v>1728</v>
@@ -39625,22 +39730,22 @@
     </row>
     <row r="60" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="77" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="F60" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G60" s="77" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="H60" s="77" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="I60" s="77" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="J60" s="77" t="s">
-        <v>2694</v>
+        <v>2693</v>
       </c>
       <c r="K60" s="77" t="s">
         <v>215</v>
@@ -39649,7 +39754,7 @@
         <v>835</v>
       </c>
       <c r="T60" s="77" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="U60" s="77" t="s">
         <v>1728</v>
@@ -39663,22 +39768,22 @@
     </row>
     <row r="61" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="77" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="F61" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G61" s="77" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="H61" s="77" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="I61" s="77" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="J61" s="77" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="K61" s="77" t="s">
         <v>215</v>
@@ -39687,7 +39792,7 @@
         <v>835</v>
       </c>
       <c r="T61" s="77" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="U61" s="77" t="s">
         <v>1728</v>
@@ -39701,22 +39806,22 @@
     </row>
     <row r="62" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="77" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="F62" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G62" s="77" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="H62" s="77" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="I62" s="77" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="J62" s="77" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="K62" s="77" t="s">
         <v>215</v>
@@ -39725,7 +39830,7 @@
         <v>835</v>
       </c>
       <c r="T62" s="77" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="U62" s="77" t="s">
         <v>1728</v>
@@ -39739,22 +39844,22 @@
     </row>
     <row r="63" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="77" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="F63" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G63" s="77" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="H63" s="77" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="I63" s="77" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="J63" s="77" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="K63" s="77" t="s">
         <v>215</v>
@@ -39763,7 +39868,7 @@
         <v>835</v>
       </c>
       <c r="T63" s="77" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="U63" s="77" t="s">
         <v>1728</v>
@@ -39777,22 +39882,22 @@
     </row>
     <row r="64" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="77" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="F64" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G64" s="77" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="H64" s="77" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="I64" s="77" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="J64" s="77" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="K64" s="77" t="s">
         <v>215</v>
@@ -39801,7 +39906,7 @@
         <v>835</v>
       </c>
       <c r="T64" s="77" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="U64" s="77" t="s">
         <v>1728</v>
@@ -39815,22 +39920,22 @@
     </row>
     <row r="65" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="77" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="F65" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G65" s="77" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
       <c r="H65" s="77" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="I65" s="77" t="s">
-        <v>2593</v>
+        <v>2592</v>
       </c>
       <c r="J65" s="77" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="K65" s="77" t="s">
         <v>215</v>
@@ -39839,7 +39944,7 @@
         <v>835</v>
       </c>
       <c r="T65" s="77" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="U65" s="77" t="s">
         <v>1728</v>
@@ -40147,7 +40252,7 @@
     </row>
     <row r="75" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="77" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="F75" s="77" t="s">
         <v>76</v>
@@ -40159,10 +40264,10 @@
         <v>1917</v>
       </c>
       <c r="I75" s="77" t="s">
+        <v>2617</v>
+      </c>
+      <c r="J75" s="77" t="s">
         <v>2618</v>
-      </c>
-      <c r="J75" s="77" t="s">
-        <v>2619</v>
       </c>
       <c r="K75" s="77" t="s">
         <v>215</v>
@@ -40171,7 +40276,7 @@
         <v>819</v>
       </c>
       <c r="T75" s="77" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="U75" s="77" t="s">
         <v>577</v>
@@ -40737,7 +40842,7 @@
     </row>
     <row r="97" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="77" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="F97" s="77" t="s">
         <v>76</v>
@@ -40746,10 +40851,10 @@
         <v>1916</v>
       </c>
       <c r="I97" s="77" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="J97" s="77" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="K97" s="77" t="s">
         <v>215</v>
@@ -40761,7 +40866,7 @@
         <v>854</v>
       </c>
       <c r="T97" s="75" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="U97" s="82" t="s">
         <v>1752</v>
@@ -40801,7 +40906,7 @@
     </row>
     <row r="100" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="77" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="F100" s="77" t="s">
         <v>76</v>
@@ -40810,10 +40915,10 @@
         <v>1916</v>
       </c>
       <c r="I100" s="77" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="J100" s="77" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="K100" s="77" t="s">
         <v>215</v>
@@ -40825,7 +40930,7 @@
         <v>854</v>
       </c>
       <c r="T100" s="75" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="U100" s="77" t="s">
         <v>856</v>
@@ -40973,7 +41078,7 @@
     </row>
     <row r="107" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="79" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="F107" s="77" t="s">
         <v>76</v>
@@ -40983,7 +41088,7 @@
       </c>
       <c r="H107" s="77"/>
       <c r="I107" s="79" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="J107" s="79" t="s">
         <v>366</v>
@@ -41001,7 +41106,7 @@
         <v>827</v>
       </c>
       <c r="T107" s="75" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="U107" s="82" t="s">
         <v>1752</v>
@@ -41578,7 +41683,7 @@
     </row>
     <row r="131" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="77" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="F131" s="77" t="s">
         <v>76</v>
@@ -41587,7 +41692,7 @@
         <v>1916</v>
       </c>
       <c r="I131" s="77" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="J131" s="77" t="s">
         <v>2074</v>
@@ -41602,7 +41707,7 @@
         <v>827</v>
       </c>
       <c r="T131" s="75" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="U131" s="77" t="s">
         <v>1754</v>
@@ -41811,7 +41916,7 @@
     </row>
     <row r="141" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="77" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="F141" s="77" t="s">
         <v>76</v>
@@ -41820,7 +41925,7 @@
         <v>1916</v>
       </c>
       <c r="I141" s="77" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="J141" s="77" t="s">
         <v>2079</v>
@@ -41835,7 +41940,7 @@
         <v>827</v>
       </c>
       <c r="T141" s="75" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="U141" s="77" t="s">
         <v>1754</v>
@@ -42021,7 +42126,7 @@
     </row>
     <row r="149" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="77" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="F149" s="77" t="s">
         <v>76</v>
@@ -42030,7 +42135,7 @@
         <v>1916</v>
       </c>
       <c r="I149" s="77" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="J149" s="77" t="s">
         <v>1906</v>
@@ -42045,7 +42150,7 @@
         <v>854</v>
       </c>
       <c r="T149" s="75" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="U149" s="77" t="s">
         <v>856</v>
@@ -42085,7 +42190,7 @@
     </row>
     <row r="152" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="77" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="F152" s="77" t="s">
         <v>76</v>
@@ -42094,10 +42199,10 @@
         <v>1846</v>
       </c>
       <c r="I152" s="77" t="s">
+        <v>2627</v>
+      </c>
+      <c r="J152" s="77" t="s">
         <v>2628</v>
-      </c>
-      <c r="J152" s="77" t="s">
-        <v>2629</v>
       </c>
       <c r="K152" s="77" t="s">
         <v>215</v>
@@ -42109,7 +42214,7 @@
         <v>827</v>
       </c>
       <c r="T152" s="75" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="U152" s="82" t="s">
         <v>1752</v>
@@ -42371,7 +42476,7 @@
     </row>
     <row r="162" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="77" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="F162" s="77" t="s">
         <v>76</v>
@@ -42380,7 +42485,7 @@
         <v>1916</v>
       </c>
       <c r="I162" s="77" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="J162" s="77" t="s">
         <v>464</v>
@@ -42398,7 +42503,7 @@
         <v>854</v>
       </c>
       <c r="T162" s="75" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="U162" s="77" t="s">
         <v>856</v>
@@ -42484,7 +42589,7 @@
     </row>
     <row r="166" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="77" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="F166" s="77" t="s">
         <v>76</v>
@@ -42493,7 +42598,7 @@
         <v>1916</v>
       </c>
       <c r="I166" s="77" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="J166" s="77" t="s">
         <v>468</v>
@@ -42511,7 +42616,7 @@
         <v>854</v>
       </c>
       <c r="T166" s="75" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="U166" s="77" t="s">
         <v>856</v>
@@ -42553,19 +42658,19 @@
     </row>
     <row r="169" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" s="77" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="F169" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G169" s="77" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="H169" s="77" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="I169" s="77" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="J169" s="77" t="s">
         <v>1907</v>
@@ -42625,7 +42730,7 @@
     </row>
     <row r="172" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" s="77" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="F172" s="77" t="s">
         <v>76</v>
@@ -42635,10 +42740,10 @@
       </c>
       <c r="H172" s="77"/>
       <c r="I172" s="77" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="J172" s="77" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="K172" s="77" t="s">
         <v>215</v>
@@ -42667,7 +42772,7 @@
     </row>
     <row r="173" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" s="77" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="F173" s="77" t="s">
         <v>76</v>
@@ -42677,10 +42782,10 @@
       </c>
       <c r="H173" s="77"/>
       <c r="I173" s="77" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="J173" s="77" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K173" s="77" t="s">
         <v>215</v>
@@ -42695,7 +42800,7 @@
         <v>854</v>
       </c>
       <c r="T173" s="75" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="U173" s="77" t="s">
         <v>856</v>
@@ -42781,7 +42886,7 @@
     </row>
     <row r="177" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" s="77" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="F177" s="77" t="s">
         <v>76</v>
@@ -42790,7 +42895,7 @@
         <v>1916</v>
       </c>
       <c r="I177" s="77" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="J177" s="77" t="s">
         <v>487</v>
@@ -42808,7 +42913,7 @@
         <v>854</v>
       </c>
       <c r="T177" s="75" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="U177" s="77" t="s">
         <v>856</v>
@@ -42850,19 +42955,19 @@
     </row>
     <row r="180" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="77" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="F180" s="77" t="s">
         <v>76</v>
       </c>
       <c r="G180" s="77" t="s">
+        <v>2630</v>
+      </c>
+      <c r="H180" s="77" t="s">
+        <v>2632</v>
+      </c>
+      <c r="I180" s="77" t="s">
         <v>2631</v>
-      </c>
-      <c r="H180" s="77" t="s">
-        <v>2633</v>
-      </c>
-      <c r="I180" s="77" t="s">
-        <v>2632</v>
       </c>
       <c r="J180" s="77" t="s">
         <v>1908</v>
@@ -42924,7 +43029,7 @@
     </row>
     <row r="183" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="77" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="F183" s="77" t="s">
         <v>76</v>
@@ -42934,10 +43039,10 @@
       </c>
       <c r="H183" s="77"/>
       <c r="I183" s="77" t="s">
+        <v>2633</v>
+      </c>
+      <c r="J183" s="77" t="s">
         <v>2634</v>
-      </c>
-      <c r="J183" s="77" t="s">
-        <v>2635</v>
       </c>
       <c r="K183" s="77" t="s">
         <v>215</v>
@@ -42966,7 +43071,7 @@
     </row>
     <row r="184" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="77" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="F184" s="77" t="s">
         <v>76</v>
@@ -42976,10 +43081,10 @@
       </c>
       <c r="H184" s="77"/>
       <c r="I184" s="77" t="s">
+        <v>2635</v>
+      </c>
+      <c r="J184" s="77" t="s">
         <v>2636</v>
-      </c>
-      <c r="J184" s="77" t="s">
-        <v>2637</v>
       </c>
       <c r="K184" s="77" t="s">
         <v>215</v>
@@ -42994,7 +43099,7 @@
         <v>854</v>
       </c>
       <c r="T184" s="75" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="U184" s="77" t="s">
         <v>856</v>
@@ -43035,7 +43140,7 @@
     </row>
     <row r="187" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="77" t="s">
-        <v>2837</v>
+        <v>2832</v>
       </c>
       <c r="F187" s="77" t="s">
         <v>76</v>
@@ -43044,10 +43149,10 @@
         <v>876</v>
       </c>
       <c r="I187" s="77" t="s">
-        <v>2837</v>
+        <v>2832</v>
       </c>
       <c r="J187" s="77" t="s">
-        <v>2839</v>
+        <v>2834</v>
       </c>
       <c r="K187" s="77" t="s">
         <v>215</v>
@@ -43062,13 +43167,13 @@
         <v>846</v>
       </c>
       <c r="T187" s="75" t="s">
-        <v>2835</v>
+        <v>2830</v>
       </c>
       <c r="U187" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V187" s="78" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="W187" s="77" t="s">
         <v>815</v>
@@ -43076,7 +43181,7 @@
     </row>
     <row r="188" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="77" t="s">
-        <v>2838</v>
+        <v>2833</v>
       </c>
       <c r="F188" s="77" t="s">
         <v>76</v>
@@ -43085,10 +43190,10 @@
         <v>876</v>
       </c>
       <c r="I188" s="77" t="s">
-        <v>2838</v>
+        <v>2833</v>
       </c>
       <c r="J188" s="77" t="s">
-        <v>2840</v>
+        <v>2835</v>
       </c>
       <c r="K188" s="77" t="s">
         <v>215</v>
@@ -43103,13 +43208,13 @@
         <v>846</v>
       </c>
       <c r="T188" s="75" t="s">
-        <v>2833</v>
+        <v>2828</v>
       </c>
       <c r="U188" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V188" s="78" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="W188" s="77" t="s">
         <v>815</v>
@@ -43117,7 +43222,7 @@
     </row>
     <row r="189" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" s="77" t="s">
-        <v>2843</v>
+        <v>2838</v>
       </c>
       <c r="F189" s="77" t="s">
         <v>76</v>
@@ -43126,10 +43231,10 @@
         <v>876</v>
       </c>
       <c r="I189" s="77" t="s">
-        <v>2843</v>
+        <v>2838</v>
       </c>
       <c r="J189" s="77" t="s">
-        <v>2842</v>
+        <v>2837</v>
       </c>
       <c r="K189" s="77" t="s">
         <v>215</v>
@@ -43144,13 +43249,13 @@
         <v>846</v>
       </c>
       <c r="T189" s="75" t="s">
-        <v>2834</v>
+        <v>2829</v>
       </c>
       <c r="U189" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V189" s="78" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="W189" s="77" t="s">
         <v>815</v>
@@ -43158,7 +43263,7 @@
     </row>
     <row r="190" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" s="77" t="s">
-        <v>2844</v>
+        <v>2839</v>
       </c>
       <c r="F190" s="77" t="s">
         <v>76</v>
@@ -43167,10 +43272,10 @@
         <v>876</v>
       </c>
       <c r="I190" s="77" t="s">
-        <v>2844</v>
+        <v>2839</v>
       </c>
       <c r="J190" s="77" t="s">
-        <v>2841</v>
+        <v>2836</v>
       </c>
       <c r="K190" s="77" t="s">
         <v>215</v>
@@ -43185,13 +43290,13 @@
         <v>846</v>
       </c>
       <c r="T190" s="75" t="s">
-        <v>2836</v>
+        <v>2831</v>
       </c>
       <c r="U190" s="77" t="s">
         <v>1707</v>
       </c>
       <c r="V190" s="78" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="W190" s="77" t="s">
         <v>815</v>
@@ -43297,7 +43402,7 @@
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A196" s="75" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="F196" s="75" t="s">
         <v>76</v>
@@ -43309,10 +43414,10 @@
         <v>1862</v>
       </c>
       <c r="I196" s="75" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="J196" s="75" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="K196" s="75" t="s">
         <v>215</v>
@@ -43324,13 +43429,13 @@
         <v>860</v>
       </c>
       <c r="T196" s="75" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="U196" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V196" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W196" s="77" t="s">
         <v>815</v>
@@ -43338,7 +43443,7 @@
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A197" s="75" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="F197" s="75" t="s">
         <v>76</v>
@@ -43350,10 +43455,10 @@
         <v>1867</v>
       </c>
       <c r="I197" s="75" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="J197" s="75" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="K197" s="75" t="s">
         <v>215</v>
@@ -43365,13 +43470,13 @@
         <v>860</v>
       </c>
       <c r="T197" s="75" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="U197" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V197" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W197" s="77" t="s">
         <v>815</v>
@@ -43379,7 +43484,7 @@
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A198" s="75" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="F198" s="75" t="s">
         <v>76</v>
@@ -43391,10 +43496,10 @@
         <v>1871</v>
       </c>
       <c r="I198" s="75" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="J198" s="75" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="K198" s="75" t="s">
         <v>215</v>
@@ -43406,13 +43511,13 @@
         <v>860</v>
       </c>
       <c r="T198" s="75" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="U198" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V198" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W198" s="77" t="s">
         <v>815</v>
@@ -43420,7 +43525,7 @@
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A199" s="75" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="F199" s="75" t="s">
         <v>76</v>
@@ -43432,10 +43537,10 @@
         <v>1913</v>
       </c>
       <c r="I199" s="75" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="J199" s="75" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="K199" s="75" t="s">
         <v>215</v>
@@ -43447,13 +43552,13 @@
         <v>860</v>
       </c>
       <c r="T199" s="75" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="U199" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V199" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W199" s="77" t="s">
         <v>815</v>
@@ -43461,7 +43566,7 @@
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A200" s="75" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="F200" s="75" t="s">
         <v>76</v>
@@ -43473,10 +43578,10 @@
         <v>1917</v>
       </c>
       <c r="I200" s="75" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="J200" s="75" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="K200" s="75" t="s">
         <v>215</v>
@@ -43488,13 +43593,13 @@
         <v>860</v>
       </c>
       <c r="T200" s="75" t="s">
-        <v>2849</v>
+        <v>2843</v>
       </c>
       <c r="U200" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V200" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W200" s="77" t="s">
         <v>815</v>
@@ -43502,7 +43607,7 @@
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A201" s="75" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="F201" s="75" t="s">
         <v>76</v>
@@ -43514,10 +43619,10 @@
         <v>1921</v>
       </c>
       <c r="I201" s="75" t="s">
+        <v>2670</v>
+      </c>
+      <c r="J201" s="75" t="s">
         <v>2671</v>
-      </c>
-      <c r="J201" s="75" t="s">
-        <v>2672</v>
       </c>
       <c r="K201" s="75" t="s">
         <v>215</v>
@@ -43529,10 +43634,10 @@
         <v>860</v>
       </c>
       <c r="U201" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V201" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W201" s="75" t="s">
         <v>815</v>
@@ -43540,7 +43645,7 @@
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A202" s="75" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="F202" s="75" t="s">
         <v>76</v>
@@ -43549,13 +43654,13 @@
         <v>1924</v>
       </c>
       <c r="H202" s="75" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="I202" s="75" t="s">
+        <v>2672</v>
+      </c>
+      <c r="J202" s="75" t="s">
         <v>2673</v>
-      </c>
-      <c r="J202" s="75" t="s">
-        <v>2674</v>
       </c>
       <c r="K202" s="75" t="s">
         <v>215</v>
@@ -43567,10 +43672,10 @@
         <v>860</v>
       </c>
       <c r="U202" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V202" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W202" s="75" t="s">
         <v>815</v>
@@ -43578,22 +43683,22 @@
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A203" s="75" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="F203" s="75" t="s">
         <v>76</v>
       </c>
       <c r="G203" s="75" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="H203" s="75" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="I203" s="75" t="s">
+        <v>2674</v>
+      </c>
+      <c r="J203" s="75" t="s">
         <v>2675</v>
-      </c>
-      <c r="J203" s="75" t="s">
-        <v>2676</v>
       </c>
       <c r="K203" s="75" t="s">
         <v>215</v>
@@ -43605,10 +43710,10 @@
         <v>860</v>
       </c>
       <c r="U203" s="75" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="V203" s="75" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="W203" s="75" t="s">
         <v>815</v>
@@ -43676,13 +43781,13 @@
     </row>
     <row r="2" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="B2" s="26"/>
       <c r="C2" s="84"/>
       <c r="D2" s="26"/>
       <c r="E2" s="26" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="F2" s="86" t="s">
         <v>90</v>
@@ -43691,7 +43796,7 @@
         <v>215</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="I2" s="26" t="s">
         <v>591</v>
@@ -43700,7 +43805,7 @@
         <v>2145</v>
       </c>
       <c r="K2" s="26" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="L2" s="87" t="s">
         <v>815</v>
@@ -43708,24 +43813,24 @@
     </row>
     <row r="3" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="C3" s="84"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="G3" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H3" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="I3" s="26" t="s">
         <v>591</v>
@@ -43734,7 +43839,7 @@
         <v>2145</v>
       </c>
       <c r="K3" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="L3" s="83" t="s">
         <v>2132</v>
@@ -43742,24 +43847,24 @@
     </row>
     <row r="4" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
       <c r="C4" s="84"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="F4" s="26" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="G4" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="I4" s="26" t="s">
         <v>591</v>
@@ -43768,7 +43873,7 @@
         <v>2145</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="L4" s="83" t="s">
         <v>2132</v>
@@ -43800,7 +43905,7 @@
         <v>213</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="L5" s="87" t="s">
         <v>815</v>
@@ -43808,7 +43913,7 @@
     </row>
     <row r="6" spans="1:12" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>218</v>
@@ -43816,16 +43921,16 @@
       <c r="C6" s="84"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26" t="s">
+        <v>2463</v>
+      </c>
+      <c r="F6" s="86" t="s">
         <v>2464</v>
       </c>
-      <c r="F6" s="86" t="s">
-        <v>2465</v>
-      </c>
       <c r="G6" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H6" s="30" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>591</v>
@@ -43834,7 +43939,7 @@
         <v>213</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="L6" s="87" t="s">
         <v>815</v>
@@ -43866,7 +43971,7 @@
         <v>213</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="L7" s="87" t="s">
         <v>815</v>
@@ -43874,7 +43979,7 @@
     </row>
     <row r="8" spans="1:12" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>2261</v>
@@ -43882,16 +43987,16 @@
       <c r="C8" s="84"/>
       <c r="D8" s="26"/>
       <c r="E8" s="26" t="s">
+        <v>2466</v>
+      </c>
+      <c r="F8" s="86" t="s">
         <v>2467</v>
       </c>
-      <c r="F8" s="86" t="s">
-        <v>2468</v>
-      </c>
       <c r="G8" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="I8" s="26" t="s">
         <v>591</v>
@@ -43900,7 +44005,7 @@
         <v>213</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="L8" s="87" t="s">
         <v>815</v>
@@ -43961,7 +44066,7 @@
         <v>215</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="I10" s="31" t="s">
         <v>2127</v>
@@ -43999,7 +44104,7 @@
         <v>215</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="I11" s="31" t="s">
         <v>2127</v>
@@ -44037,7 +44142,7 @@
         <v>215</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="I12" s="31" t="s">
         <v>2130</v>
@@ -44075,7 +44180,7 @@
         <v>215</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="I13" s="33" t="s">
         <v>252</v>
@@ -44113,7 +44218,7 @@
         <v>215</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="I14" s="33" t="s">
         <v>252</v>
@@ -44230,22 +44335,22 @@
     </row>
     <row r="18" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="88"/>
       <c r="D18" s="26"/>
       <c r="E18" s="26" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H18" s="27" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="I18" s="26" t="s">
         <v>591</v>
@@ -44254,7 +44359,7 @@
         <v>829</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="L18" s="83" t="s">
         <v>2132</v>
@@ -44262,22 +44367,22 @@
     </row>
     <row r="19" spans="1:12" ht="31.5" x14ac:dyDescent="0.3">
       <c r="A19" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="88"/>
       <c r="D19" s="26"/>
       <c r="E19" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>215</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="I19" s="26" t="s">
         <v>591</v>
@@ -44286,7 +44391,7 @@
         <v>829</v>
       </c>
       <c r="K19" s="26" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="L19" s="83" t="s">
         <v>2132</v>
@@ -44294,16 +44399,16 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="B20" s="26"/>
       <c r="C20" s="84"/>
       <c r="D20" s="26"/>
       <c r="E20" s="26" t="s">
+        <v>2772</v>
+      </c>
+      <c r="F20" s="86" t="s">
         <v>2773</v>
-      </c>
-      <c r="F20" s="86" t="s">
-        <v>2774</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>215</v>
@@ -44318,7 +44423,7 @@
         <v>213</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="L20" s="87" t="s">
         <v>815</v>
@@ -44891,21 +44996,21 @@
     </row>
     <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
       <c r="E16" s="28" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="F16" s="22"/>
       <c r="G16" s="28"/>
       <c r="H16" s="28" t="s">
+        <v>2774</v>
+      </c>
+      <c r="I16" s="28" t="s">
         <v>2775</v>
-      </c>
-      <c r="I16" s="28" t="s">
-        <v>2776</v>
       </c>
       <c r="J16" s="28" t="s">
         <v>215</v>
@@ -47645,16 +47750,16 @@
     </row>
     <row r="98" spans="1:10" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A98" s="35" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="B98" s="35"/>
       <c r="C98" s="36"/>
       <c r="D98" s="35"/>
       <c r="E98" s="35" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F98" s="35" t="s">
         <v>2771</v>
-      </c>
-      <c r="F98" s="35" t="s">
-        <v>2772</v>
       </c>
       <c r="G98" s="35" t="s">
         <v>215</v>
@@ -47920,7 +48025,7 @@
         <v>254</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="K2" s="87" t="s">
         <v>815</v>
@@ -48023,7 +48128,7 @@
         <v>254</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="K5" s="87" t="s">
         <v>815</v>
@@ -48031,7 +48136,7 @@
     </row>
     <row r="6" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="B6" s="41" t="s">
         <v>504</v>
@@ -48041,16 +48146,16 @@
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="41" t="s">
+        <v>2476</v>
+      </c>
+      <c r="F6" s="41" t="s">
         <v>2477</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>2478</v>
       </c>
       <c r="G6" s="41" t="s">
         <v>501</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="I6" s="41" t="s">
         <v>254</v>
@@ -48363,7 +48468,7 @@
         <v>254</v>
       </c>
       <c r="J15" s="28" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="K15" s="87" t="s">
         <v>815</v>
@@ -48532,7 +48637,7 @@
         <v>254</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="K20" s="87" t="s">
         <v>815</v>
@@ -48540,7 +48645,7 @@
     </row>
     <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="B21" s="41" t="s">
         <v>232</v>
@@ -48550,10 +48655,10 @@
       </c>
       <c r="D21" s="88"/>
       <c r="E21" s="41" t="s">
+        <v>2480</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>2481</v>
-      </c>
-      <c r="F21" s="41" t="s">
-        <v>2482</v>
       </c>
       <c r="G21" s="41" t="s">
         <v>501</v>
@@ -48565,7 +48670,7 @@
         <v>254</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="K21" s="87" t="s">
         <v>2132</v>
@@ -48573,7 +48678,7 @@
     </row>
     <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B22" s="41" t="s">
         <v>232</v>
@@ -48583,10 +48688,10 @@
       </c>
       <c r="D22" s="88"/>
       <c r="E22" s="41" t="s">
+        <v>2482</v>
+      </c>
+      <c r="F22" s="41" t="s">
         <v>2483</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>2484</v>
       </c>
       <c r="G22" s="41" t="s">
         <v>501</v>
@@ -48598,7 +48703,7 @@
         <v>254</v>
       </c>
       <c r="J22" s="28" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="K22" s="87" t="s">
         <v>2132</v>
@@ -48606,7 +48711,7 @@
     </row>
     <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="41" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="B23" s="41" t="s">
         <v>232</v>
@@ -48616,10 +48721,10 @@
       </c>
       <c r="D23" s="88"/>
       <c r="E23" s="41" t="s">
+        <v>2484</v>
+      </c>
+      <c r="F23" s="41" t="s">
         <v>2485</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>2486</v>
       </c>
       <c r="G23" s="41" t="s">
         <v>501</v>
@@ -48631,7 +48736,7 @@
         <v>254</v>
       </c>
       <c r="J23" s="28" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="K23" s="87" t="s">
         <v>2132</v>
@@ -48856,7 +48961,7 @@
         <v>498</v>
       </c>
       <c r="J30" s="41" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="K30" s="87" t="s">
         <v>815</v>
@@ -48887,7 +48992,7 @@
         <v>254</v>
       </c>
       <c r="J31" s="41" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="K31" s="87" t="s">
         <v>815</v>
@@ -48918,7 +49023,7 @@
         <v>254</v>
       </c>
       <c r="J32" s="41" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K32" s="87" t="s">
         <v>815</v>
@@ -48949,7 +49054,7 @@
         <v>254</v>
       </c>
       <c r="J33" s="41" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K33" s="87" t="s">
         <v>815</v>
@@ -48980,7 +49085,7 @@
         <v>254</v>
       </c>
       <c r="J34" s="41" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="K34" s="87" t="s">
         <v>815</v>
@@ -49040,7 +49145,7 @@
         <v>254</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="K36" s="87" t="s">
         <v>815</v>
@@ -49071,7 +49176,7 @@
         <v>254</v>
       </c>
       <c r="J37" s="39" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="K37" s="87" t="s">
         <v>815</v>
@@ -49104,7 +49209,7 @@
         <v>255</v>
       </c>
       <c r="J38" s="39" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="K38" s="87" t="s">
         <v>815</v>
@@ -49166,7 +49271,7 @@
         <v>234</v>
       </c>
       <c r="J40" s="39" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="K40" s="87" t="s">
         <v>815</v>
@@ -49279,7 +49384,7 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="39" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="B44" s="39" t="s">
         <v>543</v>
@@ -49291,10 +49396,10 @@
         <v>2220</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="F44" s="43" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="G44" s="39" t="s">
         <v>215</v>
@@ -49314,22 +49419,22 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="B45" s="39" t="s">
         <v>543</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="D45" s="88" t="s">
         <v>2221</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="F45" s="43" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="G45" s="39" t="s">
         <v>215</v>
@@ -49361,7 +49466,7 @@
         <v>2169</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="F46" s="43" t="s">
         <v>2165</v>
@@ -49394,7 +49499,7 @@
       </c>
       <c r="D47" s="88"/>
       <c r="E47" s="41" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="F47" s="43" t="s">
         <v>2166</v>
@@ -49502,7 +49607,7 @@
         <v>254</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="K50" s="87" t="s">
         <v>815</v>
@@ -49601,7 +49706,7 @@
     </row>
     <row r="54" spans="1:11" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="41" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="B54" s="41" t="s">
         <v>232</v>
@@ -49610,13 +49715,13 @@
         <v>2128</v>
       </c>
       <c r="D54" s="88" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="E54" s="41" t="s">
+        <v>2444</v>
+      </c>
+      <c r="F54" s="41" t="s">
         <v>2445</v>
-      </c>
-      <c r="F54" s="41" t="s">
-        <v>2446</v>
       </c>
       <c r="G54" s="41" t="s">
         <v>501</v>
@@ -49625,10 +49730,10 @@
         <v>2247</v>
       </c>
       <c r="I54" s="41" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="J54" s="28" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="K54" s="87" t="s">
         <v>2132</v>
@@ -49636,16 +49741,16 @@
     </row>
     <row r="55" spans="1:11" s="103" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A55" s="104" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="B55" s="104"/>
       <c r="C55" s="104"/>
       <c r="D55" s="104"/>
       <c r="E55" s="104" t="s">
+        <v>2507</v>
+      </c>
+      <c r="F55" s="104" t="s">
         <v>2508</v>
-      </c>
-      <c r="F55" s="104" t="s">
-        <v>2509</v>
       </c>
       <c r="G55" s="104" t="s">
         <v>215</v>
@@ -49654,10 +49759,10 @@
         <v>82</v>
       </c>
       <c r="I55" s="104" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J55" s="104" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="K55" s="104" t="s">
         <v>815</v>
@@ -49665,16 +49770,16 @@
     </row>
     <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="84"/>
       <c r="D56" s="41"/>
       <c r="E56" s="41" t="s">
+        <v>2765</v>
+      </c>
+      <c r="F56" s="41" t="s">
         <v>2766</v>
-      </c>
-      <c r="F56" s="41" t="s">
-        <v>2767</v>
       </c>
       <c r="G56" s="41" t="s">
         <v>215</v>
@@ -49686,7 +49791,7 @@
         <v>644</v>
       </c>
       <c r="J56" s="41" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="K56" s="87" t="s">
         <v>815</v>
@@ -49717,16 +49822,16 @@
   <sheetData>
     <row r="1" spans="1:11" s="85" customFormat="1" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A1" s="41" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="84"/>
       <c r="D1" s="41"/>
       <c r="E1" s="41" t="s">
+        <v>2502</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>2503</v>
-      </c>
-      <c r="F1" s="41" t="s">
-        <v>2504</v>
       </c>
       <c r="G1" s="56" t="s">
         <v>215</v>
@@ -49735,10 +49840,10 @@
         <v>82</v>
       </c>
       <c r="I1" s="33" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="K1" s="87" t="s">
         <v>815</v>
@@ -49746,16 +49851,16 @@
     </row>
     <row r="2" spans="1:11" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B2" s="41"/>
       <c r="C2" s="84"/>
       <c r="D2" s="41"/>
       <c r="E2" s="41" t="s">
+        <v>2505</v>
+      </c>
+      <c r="F2" s="41" t="s">
         <v>2506</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>2507</v>
       </c>
       <c r="G2" s="56" t="s">
         <v>215</v>
@@ -49764,10 +49869,10 @@
         <v>82</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="J2" s="60" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="K2" s="87" t="s">
         <v>815</v>

--- a/WB_DatabaseTemplateGlobal_tables.xlsx
+++ b/WB_DatabaseTemplateGlobal_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkbookBasic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB91120-32DF-4BD3-8B40-798CFFF35D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F3F669-966F-43FD-AF08-B510444D84C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="10" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="500" firstSheet="8" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spec" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10649" uniqueCount="2900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10659" uniqueCount="2905">
   <si>
     <t>WB_Specification</t>
   </si>
@@ -8756,6 +8756,21 @@
   </si>
   <si>
     <t>Fullname=Валенки;UnitLimit=Unit.Piece,5;</t>
+  </si>
+  <si>
+    <t>CodeList.KPVED</t>
+  </si>
+  <si>
+    <t>Описание листа кодов. КПВЭД</t>
+  </si>
+  <si>
+    <t>Role.Generic.CodeList</t>
+  </si>
+  <si>
+    <t>лист кодов</t>
+  </si>
+  <si>
+    <t>Fullname=KPVED_TNVED_GTIN.csv;Map=1,4;</t>
   </si>
 </sst>
 </file>
@@ -15805,7 +15820,7 @@
   <sheetPr codeName="Лист13">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="65.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.7109375" style="85" customWidth="1"/>
@@ -16167,6 +16182,26 @@
       </c>
       <c r="H16" s="28" t="s">
         <v>2867</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="108" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B17" s="108"/>
+      <c r="C17" s="109"/>
+      <c r="D17" s="109"/>
+      <c r="E17" s="108" t="s">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="108" t="s">
+        <v>2901</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>2902</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>2904</v>
       </c>
     </row>
   </sheetData>
@@ -30174,7 +30209,7 @@
   <sheetPr codeName="Лист15">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" style="16" customWidth="1"/>
@@ -32171,16 +32206,18 @@
     </row>
     <row r="106" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="27" t="s">
-        <v>1514</v>
-      </c>
-      <c r="B106" s="27"/>
-      <c r="C106" s="22"/>
+        <v>2902</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C106" s="53"/>
       <c r="D106" s="27"/>
       <c r="E106" s="27" t="s">
-        <v>1514</v>
+        <v>2902</v>
       </c>
       <c r="F106" s="27" t="s">
-        <v>26</v>
+        <v>2903</v>
       </c>
       <c r="G106" s="45" t="s">
         <v>626</v>
@@ -32188,18 +32225,16 @@
     </row>
     <row r="107" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="27" t="s">
-        <v>552</v>
-      </c>
-      <c r="B107" s="27" t="s">
         <v>1514</v>
       </c>
+      <c r="B107" s="27"/>
       <c r="C107" s="22"/>
       <c r="D107" s="27"/>
       <c r="E107" s="27" t="s">
-        <v>552</v>
+        <v>1514</v>
       </c>
       <c r="F107" s="27" t="s">
-        <v>1515</v>
+        <v>26</v>
       </c>
       <c r="G107" s="45" t="s">
         <v>626</v>
@@ -32207,7 +32242,7 @@
     </row>
     <row r="108" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="27" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B108" s="27" t="s">
         <v>1514</v>
@@ -32215,10 +32250,10 @@
       <c r="C108" s="22"/>
       <c r="D108" s="27"/>
       <c r="E108" s="27" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F108" s="27" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="G108" s="45" t="s">
         <v>626</v>
@@ -32226,7 +32261,7 @@
     </row>
     <row r="109" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="27" t="s">
-        <v>1517</v>
+        <v>558</v>
       </c>
       <c r="B109" s="27" t="s">
         <v>1514</v>
@@ -32234,10 +32269,10 @@
       <c r="C109" s="22"/>
       <c r="D109" s="27"/>
       <c r="E109" s="27" t="s">
-        <v>1517</v>
+        <v>558</v>
       </c>
       <c r="F109" s="27" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="G109" s="45" t="s">
         <v>626</v>
@@ -32245,7 +32280,7 @@
     </row>
     <row r="110" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="27" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B110" s="27" t="s">
         <v>1514</v>
@@ -32253,10 +32288,10 @@
       <c r="C110" s="22"/>
       <c r="D110" s="27"/>
       <c r="E110" s="27" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="F110" s="27" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="G110" s="45" t="s">
         <v>626</v>
@@ -32264,7 +32299,7 @@
     </row>
     <row r="111" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="27" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B111" s="27" t="s">
         <v>1514</v>
@@ -32272,10 +32307,10 @@
       <c r="C111" s="22"/>
       <c r="D111" s="27"/>
       <c r="E111" s="27" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="F111" s="27" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="G111" s="45" t="s">
         <v>626</v>
@@ -32283,7 +32318,7 @@
     </row>
     <row r="112" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="27" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="B112" s="27" t="s">
         <v>1514</v>
@@ -32291,10 +32326,10 @@
       <c r="C112" s="22"/>
       <c r="D112" s="27"/>
       <c r="E112" s="27" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="F112" s="27" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="G112" s="45" t="s">
         <v>626</v>
@@ -32302,7 +32337,7 @@
     </row>
     <row r="113" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="27" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="B113" s="27" t="s">
         <v>1514</v>
@@ -32310,10 +32345,10 @@
       <c r="C113" s="22"/>
       <c r="D113" s="27"/>
       <c r="E113" s="27" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="F113" s="27" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="G113" s="45" t="s">
         <v>626</v>
@@ -32321,7 +32356,7 @@
     </row>
     <row r="114" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="27" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="B114" s="27" t="s">
         <v>1514</v>
@@ -32329,10 +32364,10 @@
       <c r="C114" s="22"/>
       <c r="D114" s="27"/>
       <c r="E114" s="27" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="F114" s="27" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="G114" s="45" t="s">
         <v>626</v>
@@ -32340,7 +32375,7 @@
     </row>
     <row r="115" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="27" t="s">
-        <v>565</v>
+        <v>1527</v>
       </c>
       <c r="B115" s="27" t="s">
         <v>1514</v>
@@ -32348,10 +32383,10 @@
       <c r="C115" s="22"/>
       <c r="D115" s="27"/>
       <c r="E115" s="27" t="s">
-        <v>565</v>
+        <v>1527</v>
       </c>
       <c r="F115" s="27" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="G115" s="45" t="s">
         <v>626</v>
@@ -32359,7 +32394,7 @@
     </row>
     <row r="116" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="27" t="s">
-        <v>1530</v>
+        <v>565</v>
       </c>
       <c r="B116" s="27" t="s">
         <v>1514</v>
@@ -32367,10 +32402,10 @@
       <c r="C116" s="22"/>
       <c r="D116" s="27"/>
       <c r="E116" s="27" t="s">
-        <v>1530</v>
+        <v>565</v>
       </c>
       <c r="F116" s="27" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="G116" s="45" t="s">
         <v>626</v>
@@ -32378,7 +32413,7 @@
     </row>
     <row r="117" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="27" t="s">
-        <v>574</v>
+        <v>1530</v>
       </c>
       <c r="B117" s="27" t="s">
         <v>1514</v>
@@ -32386,10 +32421,10 @@
       <c r="C117" s="22"/>
       <c r="D117" s="27"/>
       <c r="E117" s="27" t="s">
-        <v>574</v>
+        <v>1530</v>
       </c>
       <c r="F117" s="27" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="G117" s="45" t="s">
         <v>626</v>
@@ -32397,16 +32432,18 @@
     </row>
     <row r="118" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="27" t="s">
-        <v>2454</v>
-      </c>
-      <c r="B118" s="27"/>
+        <v>574</v>
+      </c>
+      <c r="B118" s="27" t="s">
+        <v>1514</v>
+      </c>
       <c r="C118" s="22"/>
       <c r="D118" s="27"/>
       <c r="E118" s="27" t="s">
-        <v>2454</v>
+        <v>574</v>
       </c>
       <c r="F118" s="27" t="s">
-        <v>60</v>
+        <v>1532</v>
       </c>
       <c r="G118" s="45" t="s">
         <v>626</v>
@@ -32414,37 +32451,35 @@
     </row>
     <row r="119" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="27" t="s">
-        <v>2755</v>
-      </c>
-      <c r="B119" s="27" t="s">
         <v>2454</v>
       </c>
+      <c r="B119" s="27"/>
       <c r="C119" s="22"/>
       <c r="D119" s="27"/>
       <c r="E119" s="27" t="s">
-        <v>2755</v>
+        <v>2454</v>
       </c>
       <c r="F119" s="27" t="s">
-        <v>2756</v>
+        <v>60</v>
       </c>
       <c r="G119" s="45" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A120" s="24" t="s">
-        <v>2715</v>
+    <row r="120" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="27" t="s">
+        <v>2755</v>
       </c>
       <c r="B120" s="27" t="s">
         <v>2454</v>
       </c>
       <c r="C120" s="22"/>
       <c r="D120" s="27"/>
-      <c r="E120" s="24" t="s">
-        <v>2715</v>
+      <c r="E120" s="27" t="s">
+        <v>2755</v>
       </c>
       <c r="F120" s="27" t="s">
-        <v>1513</v>
+        <v>2756</v>
       </c>
       <c r="G120" s="45" t="s">
         <v>626</v>
@@ -32452,35 +32487,35 @@
     </row>
     <row r="121" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
-        <v>2849</v>
-      </c>
-      <c r="B121" s="27"/>
+        <v>2715</v>
+      </c>
+      <c r="B121" s="27" t="s">
+        <v>2454</v>
+      </c>
       <c r="C121" s="22"/>
       <c r="D121" s="27"/>
       <c r="E121" s="24" t="s">
-        <v>2849</v>
+        <v>2715</v>
       </c>
       <c r="F121" s="27" t="s">
-        <v>2850</v>
+        <v>1513</v>
       </c>
       <c r="G121" s="45" t="s">
         <v>626</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A122" s="27" t="s">
-        <v>2845</v>
-      </c>
-      <c r="B122" s="24" t="s">
+      <c r="A122" s="24" t="s">
         <v>2849</v>
       </c>
+      <c r="B122" s="27"/>
       <c r="C122" s="22"/>
       <c r="D122" s="27"/>
-      <c r="E122" s="27" t="s">
-        <v>2845</v>
+      <c r="E122" s="24" t="s">
+        <v>2849</v>
       </c>
       <c r="F122" s="27" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="G122" s="45" t="s">
         <v>626</v>
@@ -32488,7 +32523,7 @@
     </row>
     <row r="123" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A123" s="27" t="s">
-        <v>2891</v>
+        <v>2845</v>
       </c>
       <c r="B123" s="24" t="s">
         <v>2849</v>
@@ -32496,10 +32531,10 @@
       <c r="C123" s="22"/>
       <c r="D123" s="27"/>
       <c r="E123" s="27" t="s">
-        <v>2891</v>
+        <v>2845</v>
       </c>
       <c r="F123" s="27" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="G123" s="45" t="s">
         <v>626</v>
@@ -32507,7 +32542,7 @@
     </row>
     <row r="124" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A124" s="27" t="s">
-        <v>2848</v>
+        <v>2891</v>
       </c>
       <c r="B124" s="24" t="s">
         <v>2849</v>
@@ -32515,10 +32550,10 @@
       <c r="C124" s="22"/>
       <c r="D124" s="27"/>
       <c r="E124" s="27" t="s">
-        <v>2848</v>
+        <v>2891</v>
       </c>
       <c r="F124" s="27" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="G124" s="45" t="s">
         <v>626</v>
@@ -32526,7 +32561,7 @@
     </row>
     <row r="125" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A125" s="27" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>2849</v>
@@ -32534,10 +32569,10 @@
       <c r="C125" s="22"/>
       <c r="D125" s="27"/>
       <c r="E125" s="27" t="s">
-        <v>2847</v>
+        <v>2848</v>
       </c>
       <c r="F125" s="27" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="G125" s="45" t="s">
         <v>626</v>
@@ -32545,7 +32580,7 @@
     </row>
     <row r="126" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A126" s="27" t="s">
-        <v>2857</v>
+        <v>2847</v>
       </c>
       <c r="B126" s="24" t="s">
         <v>2849</v>
@@ -32553,10 +32588,10 @@
       <c r="C126" s="22"/>
       <c r="D126" s="27"/>
       <c r="E126" s="27" t="s">
-        <v>2857</v>
+        <v>2847</v>
       </c>
       <c r="F126" s="27" t="s">
-        <v>2858</v>
+        <v>2854</v>
       </c>
       <c r="G126" s="45" t="s">
         <v>626</v>
@@ -32564,7 +32599,7 @@
     </row>
     <row r="127" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A127" s="27" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="B127" s="24" t="s">
         <v>2849</v>
@@ -32572,27 +32607,29 @@
       <c r="C127" s="22"/>
       <c r="D127" s="27"/>
       <c r="E127" s="27" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="F127" s="27" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="G127" s="45" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A128" s="27" t="s">
-        <v>1533</v>
-      </c>
-      <c r="B128" s="27"/>
+        <v>2859</v>
+      </c>
+      <c r="B128" s="24" t="s">
+        <v>2849</v>
+      </c>
       <c r="C128" s="22"/>
       <c r="D128" s="27"/>
       <c r="E128" s="27" t="s">
-        <v>1533</v>
+        <v>2859</v>
       </c>
       <c r="F128" s="27" t="s">
-        <v>1534</v>
+        <v>2860</v>
       </c>
       <c r="G128" s="45" t="s">
         <v>626</v>
@@ -32600,18 +32637,16 @@
     </row>
     <row r="129" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="B129" s="27" t="s">
         <v>1533</v>
       </c>
+      <c r="B129" s="27"/>
       <c r="C129" s="22"/>
       <c r="D129" s="27"/>
       <c r="E129" s="27" t="s">
-        <v>82</v>
+        <v>1533</v>
       </c>
       <c r="F129" s="27" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="G129" s="45" t="s">
         <v>626</v>
@@ -32619,7 +32654,7 @@
     </row>
     <row r="130" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B130" s="27" t="s">
         <v>1533</v>
@@ -32627,10 +32662,10 @@
       <c r="C130" s="22"/>
       <c r="D130" s="27"/>
       <c r="E130" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F130" s="27" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="G130" s="45" t="s">
         <v>626</v>
@@ -32638,7 +32673,7 @@
     </row>
     <row r="131" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="27" t="s">
-        <v>1537</v>
+        <v>81</v>
       </c>
       <c r="B131" s="27" t="s">
         <v>1533</v>
@@ -32646,10 +32681,10 @@
       <c r="C131" s="22"/>
       <c r="D131" s="27"/>
       <c r="E131" s="27" t="s">
-        <v>1537</v>
+        <v>81</v>
       </c>
       <c r="F131" s="27" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="G131" s="45" t="s">
         <v>626</v>
@@ -32657,7 +32692,7 @@
     </row>
     <row r="132" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="27" t="s">
-        <v>506</v>
+        <v>1537</v>
       </c>
       <c r="B132" s="27" t="s">
         <v>1533</v>
@@ -32665,10 +32700,10 @@
       <c r="C132" s="22"/>
       <c r="D132" s="27"/>
       <c r="E132" s="27" t="s">
-        <v>506</v>
+        <v>1537</v>
       </c>
       <c r="F132" s="27" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="G132" s="45" t="s">
         <v>626</v>
@@ -32676,7 +32711,7 @@
     </row>
     <row r="133" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="27" t="s">
-        <v>1540</v>
+        <v>506</v>
       </c>
       <c r="B133" s="27" t="s">
         <v>1533</v>
@@ -32684,10 +32719,10 @@
       <c r="C133" s="22"/>
       <c r="D133" s="27"/>
       <c r="E133" s="27" t="s">
-        <v>1540</v>
+        <v>506</v>
       </c>
       <c r="F133" s="27" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="G133" s="45" t="s">
         <v>626</v>
@@ -32695,7 +32730,7 @@
     </row>
     <row r="134" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="27" t="s">
-        <v>520</v>
+        <v>1540</v>
       </c>
       <c r="B134" s="27" t="s">
         <v>1533</v>
@@ -32703,10 +32738,10 @@
       <c r="C134" s="22"/>
       <c r="D134" s="27"/>
       <c r="E134" s="27" t="s">
-        <v>520</v>
+        <v>1540</v>
       </c>
       <c r="F134" s="27" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="G134" s="45" t="s">
         <v>626</v>
@@ -32714,7 +32749,7 @@
     </row>
     <row r="135" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="27" t="s">
-        <v>1543</v>
+        <v>520</v>
       </c>
       <c r="B135" s="27" t="s">
         <v>1533</v>
@@ -32722,10 +32757,10 @@
       <c r="C135" s="22"/>
       <c r="D135" s="27"/>
       <c r="E135" s="27" t="s">
-        <v>1543</v>
+        <v>520</v>
       </c>
       <c r="F135" s="27" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="G135" s="45" t="s">
         <v>626</v>
@@ -32733,7 +32768,7 @@
     </row>
     <row r="136" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="27" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="B136" s="27" t="s">
         <v>1533</v>
@@ -32741,10 +32776,10 @@
       <c r="C136" s="22"/>
       <c r="D136" s="27"/>
       <c r="E136" s="27" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F136" s="27" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="G136" s="45" t="s">
         <v>626</v>
@@ -32752,7 +32787,7 @@
     </row>
     <row r="137" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="27" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="B137" s="27" t="s">
         <v>1533</v>
@@ -32760,10 +32795,10 @@
       <c r="C137" s="22"/>
       <c r="D137" s="27"/>
       <c r="E137" s="27" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="F137" s="27" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="G137" s="45" t="s">
         <v>626</v>
@@ -32771,7 +32806,7 @@
     </row>
     <row r="138" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="27" t="s">
-        <v>2189</v>
+        <v>1547</v>
       </c>
       <c r="B138" s="27" t="s">
         <v>1533</v>
@@ -32779,10 +32814,10 @@
       <c r="C138" s="22"/>
       <c r="D138" s="27"/>
       <c r="E138" s="27" t="s">
-        <v>2189</v>
+        <v>1547</v>
       </c>
       <c r="F138" s="27" t="s">
-        <v>2190</v>
+        <v>1548</v>
       </c>
       <c r="G138" s="45" t="s">
         <v>626</v>
@@ -32790,16 +32825,18 @@
     </row>
     <row r="139" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="27" t="s">
-        <v>1549</v>
-      </c>
-      <c r="B139" s="27"/>
+        <v>2189</v>
+      </c>
+      <c r="B139" s="27" t="s">
+        <v>1533</v>
+      </c>
       <c r="C139" s="22"/>
       <c r="D139" s="27"/>
       <c r="E139" s="27" t="s">
-        <v>1549</v>
+        <v>2189</v>
       </c>
       <c r="F139" s="27" t="s">
-        <v>1550</v>
+        <v>2190</v>
       </c>
       <c r="G139" s="45" t="s">
         <v>626</v>
@@ -32807,18 +32844,16 @@
     </row>
     <row r="140" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="27" t="s">
-        <v>1551</v>
-      </c>
-      <c r="B140" s="27" t="s">
         <v>1549</v>
       </c>
+      <c r="B140" s="27"/>
       <c r="C140" s="22"/>
       <c r="D140" s="27"/>
       <c r="E140" s="27" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F140" s="27" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="G140" s="45" t="s">
         <v>626</v>
@@ -32826,7 +32861,7 @@
     </row>
     <row r="141" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="27" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="B141" s="27" t="s">
         <v>1549</v>
@@ -32834,10 +32869,10 @@
       <c r="C141" s="22"/>
       <c r="D141" s="27"/>
       <c r="E141" s="27" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="F141" s="27" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="G141" s="45" t="s">
         <v>626</v>
@@ -32845,7 +32880,7 @@
     </row>
     <row r="142" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="27" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="B142" s="27" t="s">
         <v>1549</v>
@@ -32853,10 +32888,10 @@
       <c r="C142" s="22"/>
       <c r="D142" s="27"/>
       <c r="E142" s="27" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="F142" s="27" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="G142" s="45" t="s">
         <v>626</v>
@@ -32864,7 +32899,7 @@
     </row>
     <row r="143" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="27" t="s">
-        <v>329</v>
+        <v>1555</v>
       </c>
       <c r="B143" s="27" t="s">
         <v>1549</v>
@@ -32872,10 +32907,10 @@
       <c r="C143" s="22"/>
       <c r="D143" s="27"/>
       <c r="E143" s="27" t="s">
-        <v>329</v>
+        <v>1555</v>
       </c>
       <c r="F143" s="27" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="G143" s="45" t="s">
         <v>626</v>
@@ -32883,7 +32918,7 @@
     </row>
     <row r="144" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="27" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="B144" s="27" t="s">
         <v>1549</v>
@@ -32891,10 +32926,10 @@
       <c r="C144" s="22"/>
       <c r="D144" s="27"/>
       <c r="E144" s="27" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="F144" s="27" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="G144" s="45" t="s">
         <v>626</v>
@@ -32902,7 +32937,7 @@
     </row>
     <row r="145" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="27" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="B145" s="27" t="s">
         <v>1549</v>
@@ -32910,10 +32945,10 @@
       <c r="C145" s="22"/>
       <c r="D145" s="27"/>
       <c r="E145" s="27" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="F145" s="27" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="G145" s="45" t="s">
         <v>626</v>
@@ -32921,7 +32956,7 @@
     </row>
     <row r="146" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="27" t="s">
-        <v>1560</v>
+        <v>274</v>
       </c>
       <c r="B146" s="27" t="s">
         <v>1549</v>
@@ -32929,10 +32964,10 @@
       <c r="C146" s="22"/>
       <c r="D146" s="27"/>
       <c r="E146" s="27" t="s">
-        <v>1560</v>
+        <v>274</v>
       </c>
       <c r="F146" s="27" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="G146" s="45" t="s">
         <v>626</v>
@@ -32940,7 +32975,7 @@
     </row>
     <row r="147" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="27" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B147" s="27" t="s">
         <v>1549</v>
@@ -32948,10 +32983,10 @@
       <c r="C147" s="22"/>
       <c r="D147" s="27"/>
       <c r="E147" s="27" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="F147" s="27" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="G147" s="45" t="s">
         <v>626</v>
@@ -32959,7 +32994,7 @@
     </row>
     <row r="148" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="27" t="s">
-        <v>282</v>
+        <v>1562</v>
       </c>
       <c r="B148" s="27" t="s">
         <v>1549</v>
@@ -32967,10 +33002,10 @@
       <c r="C148" s="22"/>
       <c r="D148" s="27"/>
       <c r="E148" s="27" t="s">
-        <v>282</v>
+        <v>1562</v>
       </c>
       <c r="F148" s="27" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="G148" s="45" t="s">
         <v>626</v>
@@ -32978,7 +33013,7 @@
     </row>
     <row r="149" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="27" t="s">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="B149" s="27" t="s">
         <v>1549</v>
@@ -32986,10 +33021,10 @@
       <c r="C149" s="22"/>
       <c r="D149" s="27"/>
       <c r="E149" s="27" t="s">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="F149" s="27" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="G149" s="45" t="s">
         <v>626</v>
@@ -32997,7 +33032,7 @@
     </row>
     <row r="150" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="27" t="s">
-        <v>1566</v>
+        <v>361</v>
       </c>
       <c r="B150" s="27" t="s">
         <v>1549</v>
@@ -33005,10 +33040,10 @@
       <c r="C150" s="22"/>
       <c r="D150" s="27"/>
       <c r="E150" s="27" t="s">
-        <v>1566</v>
+        <v>361</v>
       </c>
       <c r="F150" s="27" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="G150" s="45" t="s">
         <v>626</v>
@@ -33016,7 +33051,7 @@
     </row>
     <row r="151" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="27" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="B151" s="27" t="s">
         <v>1549</v>
@@ -33024,10 +33059,10 @@
       <c r="C151" s="22"/>
       <c r="D151" s="27"/>
       <c r="E151" s="27" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F151" s="27" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="G151" s="45" t="s">
         <v>626</v>
@@ -33035,7 +33070,7 @@
     </row>
     <row r="152" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" s="27" t="s">
-        <v>354</v>
+        <v>1568</v>
       </c>
       <c r="B152" s="27" t="s">
         <v>1549</v>
@@ -33043,10 +33078,10 @@
       <c r="C152" s="22"/>
       <c r="D152" s="27"/>
       <c r="E152" s="27" t="s">
-        <v>354</v>
+        <v>1568</v>
       </c>
       <c r="F152" s="27" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="G152" s="45" t="s">
         <v>626</v>
@@ -33054,16 +33089,18 @@
     </row>
     <row r="153" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" s="27" t="s">
-        <v>1571</v>
-      </c>
-      <c r="B153" s="27"/>
+        <v>354</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>1549</v>
+      </c>
       <c r="C153" s="22"/>
       <c r="D153" s="27"/>
       <c r="E153" s="27" t="s">
-        <v>1571</v>
+        <v>354</v>
       </c>
       <c r="F153" s="27" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="G153" s="45" t="s">
         <v>626</v>
@@ -33071,18 +33108,16 @@
     </row>
     <row r="154" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="B154" s="27" t="s">
         <v>1571</v>
       </c>
+      <c r="B154" s="27"/>
       <c r="C154" s="22"/>
       <c r="D154" s="27"/>
       <c r="E154" s="27" t="s">
-        <v>306</v>
+        <v>1571</v>
       </c>
       <c r="F154" s="27" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="G154" s="45" t="s">
         <v>626</v>
@@ -33090,7 +33125,7 @@
     </row>
     <row r="155" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" s="27" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B155" s="27" t="s">
         <v>1571</v>
@@ -33098,10 +33133,10 @@
       <c r="C155" s="22"/>
       <c r="D155" s="27"/>
       <c r="E155" s="27" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="F155" s="27" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="G155" s="45" t="s">
         <v>626</v>
@@ -33109,7 +33144,7 @@
     </row>
     <row r="156" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" s="27" t="s">
-        <v>1575</v>
+        <v>312</v>
       </c>
       <c r="B156" s="27" t="s">
         <v>1571</v>
@@ -33117,10 +33152,10 @@
       <c r="C156" s="22"/>
       <c r="D156" s="27"/>
       <c r="E156" s="27" t="s">
-        <v>1575</v>
+        <v>312</v>
       </c>
       <c r="F156" s="27" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="G156" s="45" t="s">
         <v>626</v>
@@ -33128,7 +33163,7 @@
     </row>
     <row r="157" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="27" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="B157" s="27" t="s">
         <v>1571</v>
@@ -33136,10 +33171,10 @@
       <c r="C157" s="22"/>
       <c r="D157" s="27"/>
       <c r="E157" s="27" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="F157" s="27" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="G157" s="45" t="s">
         <v>626</v>
@@ -33147,7 +33182,7 @@
     </row>
     <row r="158" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" s="27" t="s">
-        <v>270</v>
+        <v>1577</v>
       </c>
       <c r="B158" s="27" t="s">
         <v>1571</v>
@@ -33155,10 +33190,10 @@
       <c r="C158" s="22"/>
       <c r="D158" s="27"/>
       <c r="E158" s="27" t="s">
-        <v>270</v>
+        <v>1577</v>
       </c>
       <c r="F158" s="27" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="G158" s="45" t="s">
         <v>626</v>
@@ -33166,7 +33201,7 @@
     </row>
     <row r="159" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" s="27" t="s">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="B159" s="27" t="s">
         <v>1571</v>
@@ -33174,10 +33209,10 @@
       <c r="C159" s="22"/>
       <c r="D159" s="27"/>
       <c r="E159" s="27" t="s">
-        <v>482</v>
+        <v>270</v>
       </c>
       <c r="F159" s="27" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="G159" s="45" t="s">
         <v>626</v>
@@ -33185,16 +33220,18 @@
     </row>
     <row r="160" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="27" t="s">
-        <v>1581</v>
-      </c>
-      <c r="B160" s="27"/>
+        <v>482</v>
+      </c>
+      <c r="B160" s="27" t="s">
+        <v>1571</v>
+      </c>
       <c r="C160" s="22"/>
       <c r="D160" s="27"/>
       <c r="E160" s="27" t="s">
-        <v>1581</v>
+        <v>482</v>
       </c>
       <c r="F160" s="27" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="G160" s="45" t="s">
         <v>626</v>
@@ -33202,18 +33239,16 @@
     </row>
     <row r="161" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" s="27" t="s">
-        <v>1583</v>
-      </c>
-      <c r="B161" s="27" t="s">
         <v>1581</v>
       </c>
+      <c r="B161" s="27"/>
       <c r="C161" s="22"/>
       <c r="D161" s="27"/>
       <c r="E161" s="27" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="F161" s="27" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="G161" s="45" t="s">
         <v>626</v>
@@ -33221,7 +33256,7 @@
     </row>
     <row r="162" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" s="27" t="s">
-        <v>378</v>
+        <v>1583</v>
       </c>
       <c r="B162" s="27" t="s">
         <v>1581</v>
@@ -33229,10 +33264,10 @@
       <c r="C162" s="22"/>
       <c r="D162" s="27"/>
       <c r="E162" s="27" t="s">
-        <v>378</v>
+        <v>1583</v>
       </c>
       <c r="F162" s="27" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="G162" s="45" t="s">
         <v>626</v>
@@ -33240,7 +33275,7 @@
     </row>
     <row r="163" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" s="27" t="s">
-        <v>1586</v>
+        <v>378</v>
       </c>
       <c r="B163" s="27" t="s">
         <v>1581</v>
@@ -33248,10 +33283,10 @@
       <c r="C163" s="22"/>
       <c r="D163" s="27"/>
       <c r="E163" s="27" t="s">
-        <v>1586</v>
+        <v>378</v>
       </c>
       <c r="F163" s="27" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="G163" s="45" t="s">
         <v>626</v>
@@ -33259,7 +33294,7 @@
     </row>
     <row r="164" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="27" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="B164" s="27" t="s">
         <v>1581</v>
@@ -33267,10 +33302,10 @@
       <c r="C164" s="22"/>
       <c r="D164" s="27"/>
       <c r="E164" s="27" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="F164" s="27" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="G164" s="45" t="s">
         <v>626</v>
@@ -33278,7 +33313,7 @@
     </row>
     <row r="165" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" s="27" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B165" s="27" t="s">
         <v>1581</v>
@@ -33286,10 +33321,10 @@
       <c r="C165" s="22"/>
       <c r="D165" s="27"/>
       <c r="E165" s="27" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="F165" s="27" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="G165" s="45" t="s">
         <v>626</v>
@@ -33297,7 +33332,7 @@
     </row>
     <row r="166" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" s="27" t="s">
-        <v>2707</v>
+        <v>1590</v>
       </c>
       <c r="B166" s="27" t="s">
         <v>1581</v>
@@ -33305,12 +33340,31 @@
       <c r="C166" s="22"/>
       <c r="D166" s="27"/>
       <c r="E166" s="27" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F166" s="27" t="s">
+        <v>1591</v>
+      </c>
+      <c r="G166" s="45" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A167" s="27" t="s">
         <v>2707</v>
       </c>
-      <c r="F166" s="27" t="s">
+      <c r="B167" s="27" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C167" s="22"/>
+      <c r="D167" s="27"/>
+      <c r="E167" s="27" t="s">
+        <v>2707</v>
+      </c>
+      <c r="F167" s="27" t="s">
         <v>2708</v>
       </c>
-      <c r="G166" s="45" t="s">
+      <c r="G167" s="45" t="s">
         <v>626</v>
       </c>
     </row>
